--- a/templates/vacation_map_template.xlsx
+++ b/templates/vacation_map_template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\F. Martins\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geral\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7CABC304-81B1-428A-A931-3211D2F198AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B973D284-DFA9-427C-8AE4-A1AD7844636B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B7894565-86C4-4C3D-8BBD-69A912659748}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B7894565-86C4-4C3D-8BBD-69A912659748}"/>
   </bookViews>
   <sheets>
     <sheet name="Folha1" sheetId="1" r:id="rId1"/>
@@ -110,7 +110,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -175,6 +175,14 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF002060"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -385,7 +393,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -402,43 +410,13 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -451,20 +429,44 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -539,9 +541,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema Office 2013 - 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -579,7 +581,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -685,7 +687,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -827,7 +829,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -838,19 +840,19 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:P323"/>
+  <dimension ref="A2:P323"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.85546875" customWidth="1"/>
     <col min="2" max="2" width="28.5703125" customWidth="1"/>
     <col min="3" max="14" width="16.42578125" style="1" customWidth="1"/>
-    <col min="15" max="15" width="10" style="15" customWidth="1"/>
+    <col min="15" max="15" width="10" style="7" customWidth="1"/>
     <col min="16" max="16" width="2.85546875" customWidth="1"/>
     <col min="17" max="16384" width="9.140625" hidden="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="6" t="s">
         <v>13</v>
       </c>
     </row>
@@ -860,41 +862,41 @@
       </c>
     </row>
     <row r="4" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="C4" s="27" t="s">
+      <c r="C4" s="14" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="6" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="9"/>
-      <c r="J6" s="9"/>
-      <c r="K6" s="9"/>
-      <c r="L6" s="9"/>
-      <c r="M6" s="9"/>
-      <c r="N6" s="9"/>
-      <c r="O6" s="9"/>
+      <c r="B6" s="15"/>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="15"/>
+      <c r="H6" s="15"/>
+      <c r="I6" s="15"/>
+      <c r="J6" s="15"/>
+      <c r="K6" s="15"/>
+      <c r="L6" s="15"/>
+      <c r="M6" s="15"/>
+      <c r="N6" s="15"/>
+      <c r="O6" s="15"/>
     </row>
     <row r="7" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="9"/>
-      <c r="K7" s="9"/>
-      <c r="L7" s="9"/>
-      <c r="M7" s="9"/>
-      <c r="N7" s="9"/>
-      <c r="O7" s="9"/>
+      <c r="B7" s="15"/>
+      <c r="C7" s="15"/>
+      <c r="D7" s="15"/>
+      <c r="E7" s="15"/>
+      <c r="F7" s="15"/>
+      <c r="G7" s="15"/>
+      <c r="H7" s="15"/>
+      <c r="I7" s="15"/>
+      <c r="J7" s="15"/>
+      <c r="K7" s="15"/>
+      <c r="L7" s="15"/>
+      <c r="M7" s="15"/>
+      <c r="N7" s="15"/>
+      <c r="O7" s="15"/>
     </row>
     <row r="8" spans="2:15" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="9" spans="2:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -937,684 +939,684 @@
       <c r="N9" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="O9" s="16" t="s">
+      <c r="O9" s="8" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B10" s="11"/>
-      <c r="C10" s="6"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
-      <c r="I10" s="7"/>
-      <c r="J10" s="7"/>
-      <c r="K10" s="7"/>
-      <c r="L10" s="7"/>
-      <c r="M10" s="7"/>
-      <c r="N10" s="13"/>
-      <c r="O10" s="17"/>
-    </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B11" s="26"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
-      <c r="I11" s="7"/>
-      <c r="J11" s="7"/>
-      <c r="K11" s="7"/>
-      <c r="L11" s="7"/>
-      <c r="M11" s="7"/>
-      <c r="N11" s="13"/>
-      <c r="O11" s="17"/>
-    </row>
-    <row r="12" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B12" s="26"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
-      <c r="I12" s="7"/>
-      <c r="J12" s="7"/>
-      <c r="K12" s="7"/>
-      <c r="L12" s="7"/>
-      <c r="M12" s="7"/>
-      <c r="N12" s="13"/>
-      <c r="O12" s="17"/>
-    </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B13" s="26"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
-      <c r="I13" s="7"/>
-      <c r="J13" s="7"/>
-      <c r="K13" s="7"/>
-      <c r="L13" s="7"/>
-      <c r="M13" s="7"/>
-      <c r="N13" s="13"/>
-      <c r="O13" s="17"/>
-    </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B14" s="26"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="7"/>
-      <c r="I14" s="7"/>
-      <c r="J14" s="7"/>
-      <c r="K14" s="7"/>
-      <c r="L14" s="7"/>
-      <c r="M14" s="7"/>
-      <c r="N14" s="13"/>
-      <c r="O14" s="17"/>
-    </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B15" s="26"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="7"/>
-      <c r="I15" s="7"/>
-      <c r="J15" s="7"/>
-      <c r="K15" s="7"/>
-      <c r="L15" s="7"/>
-      <c r="M15" s="7"/>
-      <c r="N15" s="13"/>
-      <c r="O15" s="17"/>
-    </row>
-    <row r="16" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B16" s="26"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
-      <c r="I16" s="7"/>
-      <c r="J16" s="7"/>
-      <c r="K16" s="7"/>
-      <c r="L16" s="7"/>
-      <c r="M16" s="7"/>
-      <c r="N16" s="13"/>
-      <c r="O16" s="17"/>
-    </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B17" s="26"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="7"/>
-      <c r="I17" s="7"/>
-      <c r="J17" s="7"/>
-      <c r="K17" s="7"/>
-      <c r="L17" s="7"/>
-      <c r="M17" s="7"/>
-      <c r="N17" s="13"/>
-      <c r="O17" s="17"/>
-    </row>
-    <row r="18" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B18" s="26"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
-      <c r="H18" s="7"/>
-      <c r="I18" s="7"/>
-      <c r="J18" s="7"/>
-      <c r="K18" s="7"/>
-      <c r="L18" s="7"/>
-      <c r="M18" s="7"/>
-      <c r="N18" s="13"/>
-      <c r="O18" s="17"/>
-    </row>
-    <row r="19" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B19" s="26"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
-      <c r="G19" s="7"/>
-      <c r="H19" s="7"/>
-      <c r="I19" s="7"/>
-      <c r="J19" s="7"/>
-      <c r="K19" s="7"/>
-      <c r="L19" s="7"/>
-      <c r="M19" s="7"/>
-      <c r="N19" s="13"/>
-      <c r="O19" s="17"/>
-    </row>
-    <row r="20" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B20" s="26"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
-      <c r="G20" s="7"/>
-      <c r="H20" s="7"/>
-      <c r="I20" s="7"/>
-      <c r="J20" s="7"/>
-      <c r="K20" s="7"/>
-      <c r="L20" s="7"/>
-      <c r="M20" s="7"/>
-      <c r="N20" s="13"/>
-      <c r="O20" s="17"/>
-    </row>
-    <row r="21" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B21" s="26"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
-      <c r="G21" s="7"/>
-      <c r="H21" s="7"/>
-      <c r="I21" s="7"/>
-      <c r="J21" s="7"/>
-      <c r="K21" s="7"/>
-      <c r="L21" s="7"/>
-      <c r="M21" s="7"/>
-      <c r="N21" s="13"/>
-      <c r="O21" s="17"/>
-    </row>
-    <row r="22" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B22" s="26"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
-      <c r="G22" s="7"/>
-      <c r="H22" s="7"/>
-      <c r="I22" s="7"/>
-      <c r="J22" s="7"/>
-      <c r="K22" s="7"/>
-      <c r="L22" s="7"/>
-      <c r="M22" s="7"/>
-      <c r="N22" s="13"/>
-      <c r="O22" s="17"/>
-    </row>
-    <row r="23" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B23" s="26"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="7"/>
-      <c r="G23" s="7"/>
-      <c r="H23" s="7"/>
-      <c r="I23" s="7"/>
-      <c r="J23" s="7"/>
-      <c r="K23" s="7"/>
-      <c r="L23" s="7"/>
-      <c r="M23" s="7"/>
-      <c r="N23" s="13"/>
-      <c r="O23" s="17"/>
-    </row>
-    <row r="24" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B24" s="26"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
-      <c r="G24" s="7"/>
-      <c r="H24" s="7"/>
-      <c r="I24" s="7"/>
-      <c r="J24" s="7"/>
-      <c r="K24" s="7"/>
-      <c r="L24" s="7"/>
-      <c r="M24" s="7"/>
-      <c r="N24" s="13"/>
-      <c r="O24" s="17"/>
-    </row>
-    <row r="25" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B25" s="26"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
-      <c r="G25" s="7"/>
-      <c r="H25" s="7"/>
-      <c r="I25" s="7"/>
-      <c r="J25" s="7"/>
-      <c r="K25" s="7"/>
-      <c r="L25" s="7"/>
-      <c r="M25" s="7"/>
-      <c r="N25" s="13"/>
-      <c r="O25" s="17"/>
-    </row>
-    <row r="26" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B26" s="26"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="7"/>
-      <c r="G26" s="7"/>
-      <c r="H26" s="7"/>
-      <c r="I26" s="7"/>
-      <c r="J26" s="7"/>
-      <c r="K26" s="7"/>
-      <c r="L26" s="7"/>
-      <c r="M26" s="7"/>
-      <c r="N26" s="13"/>
-      <c r="O26" s="17"/>
-    </row>
-    <row r="27" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B27" s="26"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
-      <c r="F27" s="7"/>
-      <c r="G27" s="7"/>
-      <c r="H27" s="7"/>
-      <c r="I27" s="7"/>
-      <c r="J27" s="7"/>
-      <c r="K27" s="7"/>
-      <c r="L27" s="7"/>
-      <c r="M27" s="7"/>
-      <c r="N27" s="13"/>
-      <c r="O27" s="17"/>
-    </row>
-    <row r="28" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B28" s="26"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="7"/>
-      <c r="F28" s="7"/>
-      <c r="G28" s="7"/>
-      <c r="H28" s="7"/>
-      <c r="I28" s="7"/>
-      <c r="J28" s="7"/>
-      <c r="K28" s="7"/>
-      <c r="L28" s="7"/>
-      <c r="M28" s="7"/>
-      <c r="N28" s="13"/>
-      <c r="O28" s="17"/>
-    </row>
-    <row r="29" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B29" s="26"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="7"/>
-      <c r="E29" s="7"/>
-      <c r="F29" s="7"/>
-      <c r="G29" s="7"/>
-      <c r="H29" s="7"/>
-      <c r="I29" s="7"/>
-      <c r="J29" s="7"/>
-      <c r="K29" s="7"/>
-      <c r="L29" s="7"/>
-      <c r="M29" s="7"/>
-      <c r="N29" s="13"/>
-      <c r="O29" s="17"/>
-    </row>
-    <row r="30" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B30" s="26"/>
-      <c r="C30" s="7"/>
-      <c r="D30" s="7"/>
-      <c r="E30" s="7"/>
-      <c r="F30" s="7"/>
-      <c r="G30" s="7"/>
-      <c r="H30" s="7"/>
-      <c r="I30" s="7"/>
-      <c r="J30" s="7"/>
-      <c r="K30" s="7"/>
-      <c r="L30" s="7"/>
-      <c r="M30" s="7"/>
-      <c r="N30" s="13"/>
-      <c r="O30" s="17"/>
-    </row>
-    <row r="31" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B31" s="26"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="7"/>
-      <c r="E31" s="7"/>
-      <c r="F31" s="7"/>
-      <c r="G31" s="7"/>
-      <c r="H31" s="7"/>
-      <c r="I31" s="7"/>
-      <c r="J31" s="7"/>
-      <c r="K31" s="7"/>
-      <c r="L31" s="7"/>
-      <c r="M31" s="7"/>
-      <c r="N31" s="13"/>
-      <c r="O31" s="17"/>
-    </row>
-    <row r="32" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B32" s="26"/>
-      <c r="C32" s="7"/>
-      <c r="D32" s="7"/>
-      <c r="E32" s="7"/>
-      <c r="F32" s="7"/>
-      <c r="G32" s="7"/>
-      <c r="H32" s="7"/>
-      <c r="I32" s="7"/>
-      <c r="J32" s="7"/>
-      <c r="K32" s="7"/>
-      <c r="L32" s="7"/>
-      <c r="M32" s="7"/>
-      <c r="N32" s="13"/>
-      <c r="O32" s="17"/>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B33" s="26"/>
-      <c r="C33" s="7"/>
-      <c r="D33" s="7"/>
-      <c r="E33" s="7"/>
-      <c r="F33" s="7"/>
-      <c r="G33" s="7"/>
-      <c r="H33" s="7"/>
-      <c r="I33" s="7"/>
-      <c r="J33" s="7"/>
-      <c r="K33" s="7"/>
-      <c r="L33" s="7"/>
-      <c r="M33" s="7"/>
-      <c r="N33" s="13"/>
-      <c r="O33" s="17"/>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B34" s="26"/>
-      <c r="C34" s="7"/>
-      <c r="D34" s="7"/>
-      <c r="E34" s="7"/>
-      <c r="F34" s="7"/>
-      <c r="G34" s="7"/>
-      <c r="H34" s="7"/>
-      <c r="I34" s="7"/>
-      <c r="J34" s="7"/>
-      <c r="K34" s="7"/>
-      <c r="L34" s="7"/>
-      <c r="M34" s="7"/>
-      <c r="N34" s="13"/>
-      <c r="O34" s="17"/>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B35" s="26"/>
-      <c r="C35" s="7"/>
-      <c r="D35" s="7"/>
-      <c r="E35" s="7"/>
-      <c r="F35" s="7"/>
-      <c r="G35" s="7"/>
-      <c r="H35" s="7"/>
-      <c r="I35" s="7"/>
-      <c r="J35" s="7"/>
-      <c r="K35" s="7"/>
-      <c r="L35" s="7"/>
-      <c r="M35" s="7"/>
-      <c r="N35" s="13"/>
-      <c r="O35" s="17"/>
-    </row>
-    <row r="36" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B36" s="26"/>
-      <c r="C36" s="7"/>
-      <c r="D36" s="7"/>
-      <c r="E36" s="7"/>
-      <c r="F36" s="7"/>
-      <c r="G36" s="7"/>
-      <c r="H36" s="7"/>
-      <c r="I36" s="7"/>
-      <c r="J36" s="7"/>
-      <c r="K36" s="7"/>
-      <c r="L36" s="7"/>
-      <c r="M36" s="7"/>
-      <c r="N36" s="13"/>
-      <c r="O36" s="17"/>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B37" s="26"/>
-      <c r="C37" s="7"/>
-      <c r="D37" s="7"/>
-      <c r="E37" s="7"/>
-      <c r="F37" s="7"/>
-      <c r="G37" s="7"/>
-      <c r="H37" s="7"/>
-      <c r="I37" s="7"/>
-      <c r="J37" s="7"/>
-      <c r="K37" s="7"/>
-      <c r="L37" s="7"/>
-      <c r="M37" s="7"/>
-      <c r="N37" s="13"/>
-      <c r="O37" s="17"/>
-    </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B38" s="26"/>
-      <c r="C38" s="7"/>
-      <c r="D38" s="7"/>
-      <c r="E38" s="7"/>
-      <c r="F38" s="7"/>
-      <c r="G38" s="7"/>
-      <c r="H38" s="7"/>
-      <c r="I38" s="7"/>
-      <c r="J38" s="7"/>
-      <c r="K38" s="7"/>
-      <c r="L38" s="7"/>
-      <c r="M38" s="7"/>
-      <c r="N38" s="13"/>
-      <c r="O38" s="17"/>
-    </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B39" s="26"/>
-      <c r="C39" s="7"/>
-      <c r="D39" s="7"/>
-      <c r="E39" s="7"/>
-      <c r="F39" s="7"/>
-      <c r="G39" s="7"/>
-      <c r="H39" s="7"/>
-      <c r="I39" s="7"/>
-      <c r="J39" s="7"/>
-      <c r="K39" s="7"/>
-      <c r="L39" s="7"/>
-      <c r="M39" s="7"/>
-      <c r="N39" s="13"/>
-      <c r="O39" s="17"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B40" s="26"/>
-      <c r="C40" s="7"/>
-      <c r="D40" s="7"/>
-      <c r="E40" s="7"/>
-      <c r="F40" s="7"/>
-      <c r="G40" s="7"/>
-      <c r="H40" s="7"/>
-      <c r="I40" s="7"/>
-      <c r="J40" s="7"/>
-      <c r="K40" s="7"/>
-      <c r="L40" s="7"/>
-      <c r="M40" s="7"/>
-      <c r="N40" s="13"/>
-      <c r="O40" s="17"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B41" s="26"/>
-      <c r="C41" s="7"/>
-      <c r="D41" s="7"/>
-      <c r="E41" s="7"/>
-      <c r="F41" s="7"/>
-      <c r="G41" s="7"/>
-      <c r="H41" s="7"/>
-      <c r="I41" s="7"/>
-      <c r="J41" s="7"/>
-      <c r="K41" s="7"/>
-      <c r="L41" s="7"/>
-      <c r="M41" s="7"/>
-      <c r="N41" s="13"/>
-      <c r="O41" s="17"/>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B42" s="26"/>
-      <c r="C42" s="7"/>
-      <c r="D42" s="7"/>
-      <c r="E42" s="7"/>
-      <c r="F42" s="7"/>
-      <c r="G42" s="7"/>
-      <c r="H42" s="7"/>
-      <c r="I42" s="7"/>
-      <c r="J42" s="7"/>
-      <c r="K42" s="7"/>
-      <c r="L42" s="7"/>
-      <c r="M42" s="7"/>
-      <c r="N42" s="13"/>
-      <c r="O42" s="17"/>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B43" s="26"/>
-      <c r="C43" s="7"/>
-      <c r="D43" s="7"/>
-      <c r="E43" s="7"/>
-      <c r="F43" s="7"/>
-      <c r="G43" s="7"/>
-      <c r="H43" s="7"/>
-      <c r="I43" s="7"/>
-      <c r="J43" s="7"/>
-      <c r="K43" s="7"/>
-      <c r="L43" s="7"/>
-      <c r="M43" s="7"/>
-      <c r="N43" s="13"/>
-      <c r="O43" s="17"/>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B44" s="26"/>
-      <c r="C44" s="7"/>
-      <c r="D44" s="7"/>
-      <c r="E44" s="7"/>
-      <c r="F44" s="7"/>
-      <c r="G44" s="7"/>
-      <c r="H44" s="7"/>
-      <c r="I44" s="7"/>
-      <c r="J44" s="7"/>
-      <c r="K44" s="7"/>
-      <c r="L44" s="7"/>
-      <c r="M44" s="7"/>
-      <c r="N44" s="13"/>
-      <c r="O44" s="17"/>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B45" s="26"/>
-      <c r="C45" s="7"/>
-      <c r="D45" s="7"/>
-      <c r="E45" s="7"/>
-      <c r="F45" s="7"/>
-      <c r="G45" s="7"/>
-      <c r="H45" s="7"/>
-      <c r="I45" s="7"/>
-      <c r="J45" s="7"/>
-      <c r="K45" s="7"/>
-      <c r="L45" s="7"/>
-      <c r="M45" s="7"/>
-      <c r="N45" s="13"/>
-      <c r="O45" s="17"/>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B46" s="26"/>
-      <c r="C46" s="7"/>
-      <c r="D46" s="7"/>
-      <c r="E46" s="7"/>
-      <c r="F46" s="7"/>
-      <c r="G46" s="7"/>
-      <c r="H46" s="7"/>
-      <c r="I46" s="7"/>
-      <c r="J46" s="7"/>
-      <c r="K46" s="7"/>
-      <c r="L46" s="7"/>
-      <c r="M46" s="7"/>
-      <c r="N46" s="13"/>
-      <c r="O46" s="17"/>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B47" s="26"/>
-      <c r="C47" s="7"/>
-      <c r="D47" s="7"/>
-      <c r="E47" s="7"/>
-      <c r="F47" s="7"/>
-      <c r="G47" s="7"/>
-      <c r="H47" s="7"/>
-      <c r="I47" s="7"/>
-      <c r="J47" s="7"/>
-      <c r="K47" s="7"/>
-      <c r="L47" s="7"/>
-      <c r="M47" s="7"/>
-      <c r="N47" s="13"/>
-      <c r="O47" s="17"/>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B48" s="26"/>
-      <c r="C48" s="7"/>
-      <c r="D48" s="7"/>
-      <c r="E48" s="7"/>
-      <c r="F48" s="7"/>
-      <c r="G48" s="7"/>
-      <c r="H48" s="7"/>
-      <c r="I48" s="7"/>
-      <c r="J48" s="7"/>
-      <c r="K48" s="7"/>
-      <c r="L48" s="7"/>
-      <c r="M48" s="7"/>
-      <c r="N48" s="13"/>
-      <c r="O48" s="17"/>
-    </row>
-    <row r="49" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B49" s="12"/>
-      <c r="C49" s="8"/>
-      <c r="D49" s="8"/>
-      <c r="E49" s="8"/>
-      <c r="F49" s="8"/>
-      <c r="G49" s="8"/>
-      <c r="H49" s="8"/>
-      <c r="I49" s="8"/>
-      <c r="J49" s="8"/>
-      <c r="K49" s="8"/>
-      <c r="L49" s="8"/>
-      <c r="M49" s="8"/>
-      <c r="N49" s="14"/>
-      <c r="O49" s="18"/>
+    <row r="10" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B10" s="18"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="19"/>
+      <c r="I10" s="19"/>
+      <c r="J10" s="19"/>
+      <c r="K10" s="19"/>
+      <c r="L10" s="19"/>
+      <c r="M10" s="19"/>
+      <c r="N10" s="20"/>
+      <c r="O10" s="21"/>
+    </row>
+    <row r="11" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B11" s="18"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="19"/>
+      <c r="I11" s="19"/>
+      <c r="J11" s="19"/>
+      <c r="K11" s="19"/>
+      <c r="L11" s="19"/>
+      <c r="M11" s="19"/>
+      <c r="N11" s="20"/>
+      <c r="O11" s="21"/>
+    </row>
+    <row r="12" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B12" s="18"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="19"/>
+      <c r="H12" s="19"/>
+      <c r="I12" s="19"/>
+      <c r="J12" s="19"/>
+      <c r="K12" s="19"/>
+      <c r="L12" s="19"/>
+      <c r="M12" s="19"/>
+      <c r="N12" s="20"/>
+      <c r="O12" s="21"/>
+    </row>
+    <row r="13" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B13" s="18"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="19"/>
+      <c r="H13" s="19"/>
+      <c r="I13" s="19"/>
+      <c r="J13" s="19"/>
+      <c r="K13" s="19"/>
+      <c r="L13" s="19"/>
+      <c r="M13" s="19"/>
+      <c r="N13" s="20"/>
+      <c r="O13" s="21"/>
+    </row>
+    <row r="14" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B14" s="18"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="19"/>
+      <c r="H14" s="19"/>
+      <c r="I14" s="19"/>
+      <c r="J14" s="19"/>
+      <c r="K14" s="19"/>
+      <c r="L14" s="19"/>
+      <c r="M14" s="19"/>
+      <c r="N14" s="20"/>
+      <c r="O14" s="21"/>
+    </row>
+    <row r="15" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B15" s="18"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="19"/>
+      <c r="H15" s="19"/>
+      <c r="I15" s="19"/>
+      <c r="J15" s="19"/>
+      <c r="K15" s="19"/>
+      <c r="L15" s="19"/>
+      <c r="M15" s="19"/>
+      <c r="N15" s="20"/>
+      <c r="O15" s="21"/>
+    </row>
+    <row r="16" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B16" s="18"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="19"/>
+      <c r="G16" s="19"/>
+      <c r="H16" s="19"/>
+      <c r="I16" s="19"/>
+      <c r="J16" s="19"/>
+      <c r="K16" s="19"/>
+      <c r="L16" s="19"/>
+      <c r="M16" s="19"/>
+      <c r="N16" s="20"/>
+      <c r="O16" s="21"/>
+    </row>
+    <row r="17" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B17" s="18"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="19"/>
+      <c r="F17" s="19"/>
+      <c r="G17" s="19"/>
+      <c r="H17" s="19"/>
+      <c r="I17" s="19"/>
+      <c r="J17" s="19"/>
+      <c r="K17" s="19"/>
+      <c r="L17" s="19"/>
+      <c r="M17" s="19"/>
+      <c r="N17" s="20"/>
+      <c r="O17" s="21"/>
+    </row>
+    <row r="18" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B18" s="18"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="19"/>
+      <c r="F18" s="19"/>
+      <c r="G18" s="19"/>
+      <c r="H18" s="19"/>
+      <c r="I18" s="19"/>
+      <c r="J18" s="19"/>
+      <c r="K18" s="19"/>
+      <c r="L18" s="19"/>
+      <c r="M18" s="19"/>
+      <c r="N18" s="20"/>
+      <c r="O18" s="21"/>
+    </row>
+    <row r="19" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B19" s="18"/>
+      <c r="C19" s="19"/>
+      <c r="D19" s="19"/>
+      <c r="E19" s="19"/>
+      <c r="F19" s="19"/>
+      <c r="G19" s="19"/>
+      <c r="H19" s="19"/>
+      <c r="I19" s="19"/>
+      <c r="J19" s="19"/>
+      <c r="K19" s="19"/>
+      <c r="L19" s="19"/>
+      <c r="M19" s="19"/>
+      <c r="N19" s="20"/>
+      <c r="O19" s="21"/>
+    </row>
+    <row r="20" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B20" s="18"/>
+      <c r="C20" s="19"/>
+      <c r="D20" s="19"/>
+      <c r="E20" s="19"/>
+      <c r="F20" s="19"/>
+      <c r="G20" s="19"/>
+      <c r="H20" s="19"/>
+      <c r="I20" s="19"/>
+      <c r="J20" s="19"/>
+      <c r="K20" s="19"/>
+      <c r="L20" s="19"/>
+      <c r="M20" s="19"/>
+      <c r="N20" s="20"/>
+      <c r="O20" s="21"/>
+    </row>
+    <row r="21" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B21" s="18"/>
+      <c r="C21" s="19"/>
+      <c r="D21" s="19"/>
+      <c r="E21" s="19"/>
+      <c r="F21" s="19"/>
+      <c r="G21" s="19"/>
+      <c r="H21" s="19"/>
+      <c r="I21" s="19"/>
+      <c r="J21" s="19"/>
+      <c r="K21" s="19"/>
+      <c r="L21" s="19"/>
+      <c r="M21" s="19"/>
+      <c r="N21" s="20"/>
+      <c r="O21" s="21"/>
+    </row>
+    <row r="22" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B22" s="18"/>
+      <c r="C22" s="19"/>
+      <c r="D22" s="19"/>
+      <c r="E22" s="19"/>
+      <c r="F22" s="19"/>
+      <c r="G22" s="19"/>
+      <c r="H22" s="19"/>
+      <c r="I22" s="19"/>
+      <c r="J22" s="19"/>
+      <c r="K22" s="19"/>
+      <c r="L22" s="19"/>
+      <c r="M22" s="19"/>
+      <c r="N22" s="20"/>
+      <c r="O22" s="21"/>
+    </row>
+    <row r="23" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B23" s="18"/>
+      <c r="C23" s="19"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="19"/>
+      <c r="F23" s="19"/>
+      <c r="G23" s="19"/>
+      <c r="H23" s="19"/>
+      <c r="I23" s="19"/>
+      <c r="J23" s="19"/>
+      <c r="K23" s="19"/>
+      <c r="L23" s="19"/>
+      <c r="M23" s="19"/>
+      <c r="N23" s="20"/>
+      <c r="O23" s="21"/>
+    </row>
+    <row r="24" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B24" s="18"/>
+      <c r="C24" s="19"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="19"/>
+      <c r="F24" s="19"/>
+      <c r="G24" s="19"/>
+      <c r="H24" s="19"/>
+      <c r="I24" s="19"/>
+      <c r="J24" s="19"/>
+      <c r="K24" s="19"/>
+      <c r="L24" s="19"/>
+      <c r="M24" s="19"/>
+      <c r="N24" s="20"/>
+      <c r="O24" s="21"/>
+    </row>
+    <row r="25" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B25" s="18"/>
+      <c r="C25" s="19"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="19"/>
+      <c r="G25" s="19"/>
+      <c r="H25" s="19"/>
+      <c r="I25" s="19"/>
+      <c r="J25" s="19"/>
+      <c r="K25" s="19"/>
+      <c r="L25" s="19"/>
+      <c r="M25" s="19"/>
+      <c r="N25" s="20"/>
+      <c r="O25" s="21"/>
+    </row>
+    <row r="26" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B26" s="18"/>
+      <c r="C26" s="19"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
+      <c r="G26" s="19"/>
+      <c r="H26" s="19"/>
+      <c r="I26" s="19"/>
+      <c r="J26" s="19"/>
+      <c r="K26" s="19"/>
+      <c r="L26" s="19"/>
+      <c r="M26" s="19"/>
+      <c r="N26" s="20"/>
+      <c r="O26" s="21"/>
+    </row>
+    <row r="27" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B27" s="18"/>
+      <c r="C27" s="19"/>
+      <c r="D27" s="19"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="19"/>
+      <c r="G27" s="19"/>
+      <c r="H27" s="19"/>
+      <c r="I27" s="19"/>
+      <c r="J27" s="19"/>
+      <c r="K27" s="19"/>
+      <c r="L27" s="19"/>
+      <c r="M27" s="19"/>
+      <c r="N27" s="20"/>
+      <c r="O27" s="21"/>
+    </row>
+    <row r="28" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B28" s="18"/>
+      <c r="C28" s="19"/>
+      <c r="D28" s="19"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="19"/>
+      <c r="G28" s="19"/>
+      <c r="H28" s="19"/>
+      <c r="I28" s="19"/>
+      <c r="J28" s="19"/>
+      <c r="K28" s="19"/>
+      <c r="L28" s="19"/>
+      <c r="M28" s="19"/>
+      <c r="N28" s="20"/>
+      <c r="O28" s="21"/>
+    </row>
+    <row r="29" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B29" s="18"/>
+      <c r="C29" s="19"/>
+      <c r="D29" s="19"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="19"/>
+      <c r="G29" s="19"/>
+      <c r="H29" s="19"/>
+      <c r="I29" s="19"/>
+      <c r="J29" s="19"/>
+      <c r="K29" s="19"/>
+      <c r="L29" s="19"/>
+      <c r="M29" s="19"/>
+      <c r="N29" s="20"/>
+      <c r="O29" s="21"/>
+    </row>
+    <row r="30" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B30" s="18"/>
+      <c r="C30" s="19"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="19"/>
+      <c r="H30" s="19"/>
+      <c r="I30" s="19"/>
+      <c r="J30" s="19"/>
+      <c r="K30" s="19"/>
+      <c r="L30" s="19"/>
+      <c r="M30" s="19"/>
+      <c r="N30" s="20"/>
+      <c r="O30" s="21"/>
+    </row>
+    <row r="31" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B31" s="18"/>
+      <c r="C31" s="19"/>
+      <c r="D31" s="19"/>
+      <c r="E31" s="19"/>
+      <c r="F31" s="19"/>
+      <c r="G31" s="19"/>
+      <c r="H31" s="19"/>
+      <c r="I31" s="19"/>
+      <c r="J31" s="19"/>
+      <c r="K31" s="19"/>
+      <c r="L31" s="19"/>
+      <c r="M31" s="19"/>
+      <c r="N31" s="20"/>
+      <c r="O31" s="21"/>
+    </row>
+    <row r="32" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B32" s="18"/>
+      <c r="C32" s="19"/>
+      <c r="D32" s="19"/>
+      <c r="E32" s="19"/>
+      <c r="F32" s="19"/>
+      <c r="G32" s="19"/>
+      <c r="H32" s="19"/>
+      <c r="I32" s="19"/>
+      <c r="J32" s="19"/>
+      <c r="K32" s="19"/>
+      <c r="L32" s="19"/>
+      <c r="M32" s="19"/>
+      <c r="N32" s="20"/>
+      <c r="O32" s="21"/>
+    </row>
+    <row r="33" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B33" s="18"/>
+      <c r="C33" s="19"/>
+      <c r="D33" s="19"/>
+      <c r="E33" s="19"/>
+      <c r="F33" s="19"/>
+      <c r="G33" s="19"/>
+      <c r="H33" s="19"/>
+      <c r="I33" s="19"/>
+      <c r="J33" s="19"/>
+      <c r="K33" s="19"/>
+      <c r="L33" s="19"/>
+      <c r="M33" s="19"/>
+      <c r="N33" s="20"/>
+      <c r="O33" s="21"/>
+    </row>
+    <row r="34" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B34" s="18"/>
+      <c r="C34" s="19"/>
+      <c r="D34" s="19"/>
+      <c r="E34" s="19"/>
+      <c r="F34" s="19"/>
+      <c r="G34" s="19"/>
+      <c r="H34" s="19"/>
+      <c r="I34" s="19"/>
+      <c r="J34" s="19"/>
+      <c r="K34" s="19"/>
+      <c r="L34" s="19"/>
+      <c r="M34" s="19"/>
+      <c r="N34" s="20"/>
+      <c r="O34" s="21"/>
+    </row>
+    <row r="35" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B35" s="18"/>
+      <c r="C35" s="19"/>
+      <c r="D35" s="19"/>
+      <c r="E35" s="19"/>
+      <c r="F35" s="19"/>
+      <c r="G35" s="19"/>
+      <c r="H35" s="19"/>
+      <c r="I35" s="19"/>
+      <c r="J35" s="19"/>
+      <c r="K35" s="19"/>
+      <c r="L35" s="19"/>
+      <c r="M35" s="19"/>
+      <c r="N35" s="20"/>
+      <c r="O35" s="21"/>
+    </row>
+    <row r="36" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B36" s="18"/>
+      <c r="C36" s="19"/>
+      <c r="D36" s="19"/>
+      <c r="E36" s="19"/>
+      <c r="F36" s="19"/>
+      <c r="G36" s="19"/>
+      <c r="H36" s="19"/>
+      <c r="I36" s="19"/>
+      <c r="J36" s="19"/>
+      <c r="K36" s="19"/>
+      <c r="L36" s="19"/>
+      <c r="M36" s="19"/>
+      <c r="N36" s="20"/>
+      <c r="O36" s="21"/>
+    </row>
+    <row r="37" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B37" s="18"/>
+      <c r="C37" s="19"/>
+      <c r="D37" s="19"/>
+      <c r="E37" s="19"/>
+      <c r="F37" s="19"/>
+      <c r="G37" s="19"/>
+      <c r="H37" s="19"/>
+      <c r="I37" s="19"/>
+      <c r="J37" s="19"/>
+      <c r="K37" s="19"/>
+      <c r="L37" s="19"/>
+      <c r="M37" s="19"/>
+      <c r="N37" s="20"/>
+      <c r="O37" s="21"/>
+    </row>
+    <row r="38" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B38" s="18"/>
+      <c r="C38" s="19"/>
+      <c r="D38" s="19"/>
+      <c r="E38" s="19"/>
+      <c r="F38" s="19"/>
+      <c r="G38" s="19"/>
+      <c r="H38" s="19"/>
+      <c r="I38" s="19"/>
+      <c r="J38" s="19"/>
+      <c r="K38" s="19"/>
+      <c r="L38" s="19"/>
+      <c r="M38" s="19"/>
+      <c r="N38" s="20"/>
+      <c r="O38" s="21"/>
+    </row>
+    <row r="39" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B39" s="18"/>
+      <c r="C39" s="19"/>
+      <c r="D39" s="19"/>
+      <c r="E39" s="19"/>
+      <c r="F39" s="19"/>
+      <c r="G39" s="19"/>
+      <c r="H39" s="19"/>
+      <c r="I39" s="19"/>
+      <c r="J39" s="19"/>
+      <c r="K39" s="19"/>
+      <c r="L39" s="19"/>
+      <c r="M39" s="19"/>
+      <c r="N39" s="20"/>
+      <c r="O39" s="21"/>
+    </row>
+    <row r="40" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B40" s="18"/>
+      <c r="C40" s="19"/>
+      <c r="D40" s="19"/>
+      <c r="E40" s="19"/>
+      <c r="F40" s="19"/>
+      <c r="G40" s="19"/>
+      <c r="H40" s="19"/>
+      <c r="I40" s="19"/>
+      <c r="J40" s="19"/>
+      <c r="K40" s="19"/>
+      <c r="L40" s="19"/>
+      <c r="M40" s="19"/>
+      <c r="N40" s="20"/>
+      <c r="O40" s="21"/>
+    </row>
+    <row r="41" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B41" s="18"/>
+      <c r="C41" s="19"/>
+      <c r="D41" s="19"/>
+      <c r="E41" s="19"/>
+      <c r="F41" s="19"/>
+      <c r="G41" s="19"/>
+      <c r="H41" s="19"/>
+      <c r="I41" s="19"/>
+      <c r="J41" s="19"/>
+      <c r="K41" s="19"/>
+      <c r="L41" s="19"/>
+      <c r="M41" s="19"/>
+      <c r="N41" s="20"/>
+      <c r="O41" s="21"/>
+    </row>
+    <row r="42" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B42" s="18"/>
+      <c r="C42" s="19"/>
+      <c r="D42" s="19"/>
+      <c r="E42" s="19"/>
+      <c r="F42" s="19"/>
+      <c r="G42" s="19"/>
+      <c r="H42" s="19"/>
+      <c r="I42" s="19"/>
+      <c r="J42" s="19"/>
+      <c r="K42" s="19"/>
+      <c r="L42" s="19"/>
+      <c r="M42" s="19"/>
+      <c r="N42" s="20"/>
+      <c r="O42" s="21"/>
+    </row>
+    <row r="43" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B43" s="18"/>
+      <c r="C43" s="19"/>
+      <c r="D43" s="19"/>
+      <c r="E43" s="19"/>
+      <c r="F43" s="19"/>
+      <c r="G43" s="19"/>
+      <c r="H43" s="19"/>
+      <c r="I43" s="19"/>
+      <c r="J43" s="19"/>
+      <c r="K43" s="19"/>
+      <c r="L43" s="19"/>
+      <c r="M43" s="19"/>
+      <c r="N43" s="20"/>
+      <c r="O43" s="21"/>
+    </row>
+    <row r="44" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B44" s="18"/>
+      <c r="C44" s="19"/>
+      <c r="D44" s="19"/>
+      <c r="E44" s="19"/>
+      <c r="F44" s="19"/>
+      <c r="G44" s="19"/>
+      <c r="H44" s="19"/>
+      <c r="I44" s="19"/>
+      <c r="J44" s="19"/>
+      <c r="K44" s="19"/>
+      <c r="L44" s="19"/>
+      <c r="M44" s="19"/>
+      <c r="N44" s="20"/>
+      <c r="O44" s="21"/>
+    </row>
+    <row r="45" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B45" s="18"/>
+      <c r="C45" s="19"/>
+      <c r="D45" s="19"/>
+      <c r="E45" s="19"/>
+      <c r="F45" s="19"/>
+      <c r="G45" s="19"/>
+      <c r="H45" s="19"/>
+      <c r="I45" s="19"/>
+      <c r="J45" s="19"/>
+      <c r="K45" s="19"/>
+      <c r="L45" s="19"/>
+      <c r="M45" s="19"/>
+      <c r="N45" s="20"/>
+      <c r="O45" s="21"/>
+    </row>
+    <row r="46" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B46" s="18"/>
+      <c r="C46" s="19"/>
+      <c r="D46" s="19"/>
+      <c r="E46" s="19"/>
+      <c r="F46" s="19"/>
+      <c r="G46" s="19"/>
+      <c r="H46" s="19"/>
+      <c r="I46" s="19"/>
+      <c r="J46" s="19"/>
+      <c r="K46" s="19"/>
+      <c r="L46" s="19"/>
+      <c r="M46" s="19"/>
+      <c r="N46" s="20"/>
+      <c r="O46" s="21"/>
+    </row>
+    <row r="47" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B47" s="18"/>
+      <c r="C47" s="19"/>
+      <c r="D47" s="19"/>
+      <c r="E47" s="19"/>
+      <c r="F47" s="19"/>
+      <c r="G47" s="19"/>
+      <c r="H47" s="19"/>
+      <c r="I47" s="19"/>
+      <c r="J47" s="19"/>
+      <c r="K47" s="19"/>
+      <c r="L47" s="19"/>
+      <c r="M47" s="19"/>
+      <c r="N47" s="20"/>
+      <c r="O47" s="21"/>
+    </row>
+    <row r="48" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B48" s="18"/>
+      <c r="C48" s="19"/>
+      <c r="D48" s="19"/>
+      <c r="E48" s="19"/>
+      <c r="F48" s="19"/>
+      <c r="G48" s="19"/>
+      <c r="H48" s="19"/>
+      <c r="I48" s="19"/>
+      <c r="J48" s="19"/>
+      <c r="K48" s="19"/>
+      <c r="L48" s="19"/>
+      <c r="M48" s="19"/>
+      <c r="N48" s="20"/>
+      <c r="O48" s="21"/>
+    </row>
+    <row r="49" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B49" s="22"/>
+      <c r="C49" s="23"/>
+      <c r="D49" s="23"/>
+      <c r="E49" s="23"/>
+      <c r="F49" s="23"/>
+      <c r="G49" s="23"/>
+      <c r="H49" s="23"/>
+      <c r="I49" s="23"/>
+      <c r="J49" s="23"/>
+      <c r="K49" s="23"/>
+      <c r="L49" s="23"/>
+      <c r="M49" s="23"/>
+      <c r="N49" s="24"/>
+      <c r="O49" s="25"/>
     </row>
     <row r="50" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B50" s="20"/>
-      <c r="C50" s="21"/>
-      <c r="D50" s="21"/>
-      <c r="E50" s="21"/>
-      <c r="F50" s="21"/>
-      <c r="G50" s="21"/>
-      <c r="H50" s="21"/>
-      <c r="I50" s="21"/>
-      <c r="J50" s="21"/>
-      <c r="K50" s="21"/>
-      <c r="L50" s="21"/>
-      <c r="M50" s="21"/>
-      <c r="N50" s="21"/>
-      <c r="O50" s="22"/>
+      <c r="B50" s="10"/>
+      <c r="C50" s="11"/>
+      <c r="D50" s="11"/>
+      <c r="E50" s="11"/>
+      <c r="F50" s="11"/>
+      <c r="G50" s="11"/>
+      <c r="H50" s="11"/>
+      <c r="I50" s="11"/>
+      <c r="J50" s="11"/>
+      <c r="K50" s="11"/>
+      <c r="L50" s="11"/>
+      <c r="M50" s="11"/>
+      <c r="N50" s="11"/>
+      <c r="O50" s="12"/>
     </row>
     <row r="51" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C51" s="2"/>
-      <c r="D51" s="24" t="s">
+      <c r="D51" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="E51" s="24"/>
+      <c r="E51" s="16"/>
       <c r="F51" s="2"/>
       <c r="G51" s="2"/>
       <c r="H51" s="2"/>
       <c r="I51" s="2"/>
       <c r="J51" s="2"/>
-      <c r="K51" s="23" t="s">
+      <c r="K51" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="L51" s="23"/>
+      <c r="L51" s="17"/>
       <c r="M51" s="2"/>
       <c r="N51" s="2"/>
-      <c r="O51" s="19"/>
+      <c r="O51" s="9"/>
     </row>
     <row r="52" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C52" s="2"/>
@@ -1629,7 +1631,7 @@
       <c r="L52" s="2"/>
       <c r="M52" s="2"/>
       <c r="N52" s="2"/>
-      <c r="O52" s="19"/>
+      <c r="O52" s="9"/>
     </row>
     <row r="53" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C53" s="2"/>
@@ -1644,7 +1646,7 @@
       <c r="L53" s="2"/>
       <c r="M53" s="2"/>
       <c r="N53" s="2"/>
-      <c r="O53" s="19"/>
+      <c r="O53" s="9"/>
     </row>
     <row r="54" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C54" s="2"/>
@@ -1659,22 +1661,22 @@
       <c r="L54" s="2"/>
       <c r="M54" s="2"/>
       <c r="N54" s="2"/>
-      <c r="O54" s="19"/>
+      <c r="O54" s="9"/>
     </row>
     <row r="55" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C55" s="2"/>
-      <c r="D55" s="25"/>
-      <c r="E55" s="25"/>
+      <c r="D55" s="13"/>
+      <c r="E55" s="13"/>
       <c r="F55" s="2"/>
       <c r="G55" s="2"/>
       <c r="H55" s="2"/>
       <c r="I55" s="2"/>
       <c r="J55" s="2"/>
-      <c r="K55" s="25"/>
-      <c r="L55" s="25"/>
+      <c r="K55" s="13"/>
+      <c r="L55" s="13"/>
       <c r="M55" s="2"/>
       <c r="N55" s="2"/>
-      <c r="O55" s="19"/>
+      <c r="O55" s="9"/>
     </row>
     <row r="56" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C56" s="2"/>
@@ -1689,7 +1691,7 @@
       <c r="L56" s="2"/>
       <c r="M56" s="2"/>
       <c r="N56" s="2"/>
-      <c r="O56" s="19"/>
+      <c r="O56" s="9"/>
     </row>
     <row r="57" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C57" s="2"/>
@@ -1704,7 +1706,7 @@
       <c r="L57" s="2"/>
       <c r="M57" s="2"/>
       <c r="N57" s="2"/>
-      <c r="O57" s="19"/>
+      <c r="O57" s="9"/>
     </row>
     <row r="58" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C58" s="2"/>
@@ -1719,7 +1721,7 @@
       <c r="L58" s="2"/>
       <c r="M58" s="2"/>
       <c r="N58" s="2"/>
-      <c r="O58" s="19"/>
+      <c r="O58" s="9"/>
     </row>
     <row r="59" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C59" s="2"/>
@@ -1734,7 +1736,7 @@
       <c r="L59" s="2"/>
       <c r="M59" s="2"/>
       <c r="N59" s="2"/>
-      <c r="O59" s="19"/>
+      <c r="O59" s="9"/>
     </row>
     <row r="60" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C60" s="2"/>
@@ -1749,7 +1751,7 @@
       <c r="L60" s="2"/>
       <c r="M60" s="2"/>
       <c r="N60" s="2"/>
-      <c r="O60" s="19"/>
+      <c r="O60" s="9"/>
     </row>
     <row r="61" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C61" s="2"/>
@@ -1764,7 +1766,7 @@
       <c r="L61" s="2"/>
       <c r="M61" s="2"/>
       <c r="N61" s="2"/>
-      <c r="O61" s="19"/>
+      <c r="O61" s="9"/>
     </row>
     <row r="62" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C62" s="2"/>
@@ -1779,7 +1781,7 @@
       <c r="L62" s="2"/>
       <c r="M62" s="2"/>
       <c r="N62" s="2"/>
-      <c r="O62" s="19"/>
+      <c r="O62" s="9"/>
     </row>
     <row r="63" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C63" s="2"/>
@@ -1794,7 +1796,7 @@
       <c r="L63" s="2"/>
       <c r="M63" s="2"/>
       <c r="N63" s="2"/>
-      <c r="O63" s="19"/>
+      <c r="O63" s="9"/>
     </row>
     <row r="64" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C64" s="2"/>
@@ -1809,7 +1811,7 @@
       <c r="L64" s="2"/>
       <c r="M64" s="2"/>
       <c r="N64" s="2"/>
-      <c r="O64" s="19"/>
+      <c r="O64" s="9"/>
     </row>
     <row r="65" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C65" s="2"/>
@@ -1824,7 +1826,7 @@
       <c r="L65" s="2"/>
       <c r="M65" s="2"/>
       <c r="N65" s="2"/>
-      <c r="O65" s="19"/>
+      <c r="O65" s="9"/>
     </row>
     <row r="66" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C66" s="2"/>
@@ -1839,7 +1841,7 @@
       <c r="L66" s="2"/>
       <c r="M66" s="2"/>
       <c r="N66" s="2"/>
-      <c r="O66" s="19"/>
+      <c r="O66" s="9"/>
     </row>
     <row r="67" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C67" s="2"/>
@@ -1854,7 +1856,7 @@
       <c r="L67" s="2"/>
       <c r="M67" s="2"/>
       <c r="N67" s="2"/>
-      <c r="O67" s="19"/>
+      <c r="O67" s="9"/>
     </row>
     <row r="68" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C68" s="2"/>
@@ -1869,7 +1871,7 @@
       <c r="L68" s="2"/>
       <c r="M68" s="2"/>
       <c r="N68" s="2"/>
-      <c r="O68" s="19"/>
+      <c r="O68" s="9"/>
     </row>
     <row r="69" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C69" s="2"/>
@@ -1884,7 +1886,7 @@
       <c r="L69" s="2"/>
       <c r="M69" s="2"/>
       <c r="N69" s="2"/>
-      <c r="O69" s="19"/>
+      <c r="O69" s="9"/>
     </row>
     <row r="70" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C70" s="2"/>
@@ -1899,7 +1901,7 @@
       <c r="L70" s="2"/>
       <c r="M70" s="2"/>
       <c r="N70" s="2"/>
-      <c r="O70" s="19"/>
+      <c r="O70" s="9"/>
     </row>
     <row r="71" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C71" s="2"/>
@@ -1914,7 +1916,7 @@
       <c r="L71" s="2"/>
       <c r="M71" s="2"/>
       <c r="N71" s="2"/>
-      <c r="O71" s="19"/>
+      <c r="O71" s="9"/>
     </row>
     <row r="72" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C72" s="2"/>
@@ -1929,7 +1931,7 @@
       <c r="L72" s="2"/>
       <c r="M72" s="2"/>
       <c r="N72" s="2"/>
-      <c r="O72" s="19"/>
+      <c r="O72" s="9"/>
     </row>
     <row r="73" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C73" s="2"/>
@@ -1944,7 +1946,7 @@
       <c r="L73" s="2"/>
       <c r="M73" s="2"/>
       <c r="N73" s="2"/>
-      <c r="O73" s="19"/>
+      <c r="O73" s="9"/>
     </row>
     <row r="74" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C74" s="2"/>
@@ -1959,7 +1961,7 @@
       <c r="L74" s="2"/>
       <c r="M74" s="2"/>
       <c r="N74" s="2"/>
-      <c r="O74" s="19"/>
+      <c r="O74" s="9"/>
     </row>
     <row r="75" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C75" s="2"/>
@@ -1974,7 +1976,7 @@
       <c r="L75" s="2"/>
       <c r="M75" s="2"/>
       <c r="N75" s="2"/>
-      <c r="O75" s="19"/>
+      <c r="O75" s="9"/>
     </row>
     <row r="76" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C76" s="2"/>
@@ -1989,7 +1991,7 @@
       <c r="L76" s="2"/>
       <c r="M76" s="2"/>
       <c r="N76" s="2"/>
-      <c r="O76" s="19"/>
+      <c r="O76" s="9"/>
     </row>
     <row r="77" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C77" s="2"/>
@@ -2004,7 +2006,7 @@
       <c r="L77" s="2"/>
       <c r="M77" s="2"/>
       <c r="N77" s="2"/>
-      <c r="O77" s="19"/>
+      <c r="O77" s="9"/>
     </row>
     <row r="78" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C78" s="2"/>
@@ -2019,7 +2021,7 @@
       <c r="L78" s="2"/>
       <c r="M78" s="2"/>
       <c r="N78" s="2"/>
-      <c r="O78" s="19"/>
+      <c r="O78" s="9"/>
     </row>
     <row r="79" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C79" s="2"/>
@@ -2034,7 +2036,7 @@
       <c r="L79" s="2"/>
       <c r="M79" s="2"/>
       <c r="N79" s="2"/>
-      <c r="O79" s="19"/>
+      <c r="O79" s="9"/>
     </row>
     <row r="80" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C80" s="2"/>
@@ -2049,7 +2051,7 @@
       <c r="L80" s="2"/>
       <c r="M80" s="2"/>
       <c r="N80" s="2"/>
-      <c r="O80" s="19"/>
+      <c r="O80" s="9"/>
     </row>
     <row r="81" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C81" s="2"/>
@@ -2064,7 +2066,7 @@
       <c r="L81" s="2"/>
       <c r="M81" s="2"/>
       <c r="N81" s="2"/>
-      <c r="O81" s="19"/>
+      <c r="O81" s="9"/>
     </row>
     <row r="82" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C82" s="2"/>
@@ -2079,7 +2081,7 @@
       <c r="L82" s="2"/>
       <c r="M82" s="2"/>
       <c r="N82" s="2"/>
-      <c r="O82" s="19"/>
+      <c r="O82" s="9"/>
     </row>
     <row r="83" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C83" s="2"/>
@@ -2094,7 +2096,7 @@
       <c r="L83" s="2"/>
       <c r="M83" s="2"/>
       <c r="N83" s="2"/>
-      <c r="O83" s="19"/>
+      <c r="O83" s="9"/>
     </row>
     <row r="84" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C84" s="2"/>
@@ -2109,7 +2111,7 @@
       <c r="L84" s="2"/>
       <c r="M84" s="2"/>
       <c r="N84" s="2"/>
-      <c r="O84" s="19"/>
+      <c r="O84" s="9"/>
     </row>
     <row r="85" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C85" s="2"/>
@@ -2124,7 +2126,7 @@
       <c r="L85" s="2"/>
       <c r="M85" s="2"/>
       <c r="N85" s="2"/>
-      <c r="O85" s="19"/>
+      <c r="O85" s="9"/>
     </row>
     <row r="86" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C86" s="2"/>
@@ -2139,7 +2141,7 @@
       <c r="L86" s="2"/>
       <c r="M86" s="2"/>
       <c r="N86" s="2"/>
-      <c r="O86" s="19"/>
+      <c r="O86" s="9"/>
     </row>
     <row r="87" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C87" s="2"/>
@@ -2154,7 +2156,7 @@
       <c r="L87" s="2"/>
       <c r="M87" s="2"/>
       <c r="N87" s="2"/>
-      <c r="O87" s="19"/>
+      <c r="O87" s="9"/>
     </row>
     <row r="88" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C88" s="2"/>
@@ -2169,7 +2171,7 @@
       <c r="L88" s="2"/>
       <c r="M88" s="2"/>
       <c r="N88" s="2"/>
-      <c r="O88" s="19"/>
+      <c r="O88" s="9"/>
     </row>
     <row r="89" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C89" s="2"/>
@@ -2184,7 +2186,7 @@
       <c r="L89" s="2"/>
       <c r="M89" s="2"/>
       <c r="N89" s="2"/>
-      <c r="O89" s="19"/>
+      <c r="O89" s="9"/>
     </row>
     <row r="90" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C90" s="2"/>
@@ -2199,7 +2201,7 @@
       <c r="L90" s="2"/>
       <c r="M90" s="2"/>
       <c r="N90" s="2"/>
-      <c r="O90" s="19"/>
+      <c r="O90" s="9"/>
     </row>
     <row r="91" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C91" s="2"/>
@@ -2214,7 +2216,7 @@
       <c r="L91" s="2"/>
       <c r="M91" s="2"/>
       <c r="N91" s="2"/>
-      <c r="O91" s="19"/>
+      <c r="O91" s="9"/>
     </row>
     <row r="92" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C92" s="2"/>
@@ -2229,7 +2231,7 @@
       <c r="L92" s="2"/>
       <c r="M92" s="2"/>
       <c r="N92" s="2"/>
-      <c r="O92" s="19"/>
+      <c r="O92" s="9"/>
     </row>
     <row r="93" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C93" s="2"/>
@@ -2244,7 +2246,7 @@
       <c r="L93" s="2"/>
       <c r="M93" s="2"/>
       <c r="N93" s="2"/>
-      <c r="O93" s="19"/>
+      <c r="O93" s="9"/>
     </row>
     <row r="94" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C94" s="2"/>
@@ -2259,7 +2261,7 @@
       <c r="L94" s="2"/>
       <c r="M94" s="2"/>
       <c r="N94" s="2"/>
-      <c r="O94" s="19"/>
+      <c r="O94" s="9"/>
     </row>
     <row r="95" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C95" s="2"/>
@@ -2274,7 +2276,7 @@
       <c r="L95" s="2"/>
       <c r="M95" s="2"/>
       <c r="N95" s="2"/>
-      <c r="O95" s="19"/>
+      <c r="O95" s="9"/>
     </row>
     <row r="96" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C96" s="2"/>
@@ -2289,7 +2291,7 @@
       <c r="L96" s="2"/>
       <c r="M96" s="2"/>
       <c r="N96" s="2"/>
-      <c r="O96" s="19"/>
+      <c r="O96" s="9"/>
     </row>
     <row r="97" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C97" s="2"/>
@@ -2304,7 +2306,7 @@
       <c r="L97" s="2"/>
       <c r="M97" s="2"/>
       <c r="N97" s="2"/>
-      <c r="O97" s="19"/>
+      <c r="O97" s="9"/>
     </row>
     <row r="98" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C98" s="2"/>
@@ -2319,7 +2321,7 @@
       <c r="L98" s="2"/>
       <c r="M98" s="2"/>
       <c r="N98" s="2"/>
-      <c r="O98" s="19"/>
+      <c r="O98" s="9"/>
     </row>
     <row r="99" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C99" s="2"/>
@@ -2334,7 +2336,7 @@
       <c r="L99" s="2"/>
       <c r="M99" s="2"/>
       <c r="N99" s="2"/>
-      <c r="O99" s="19"/>
+      <c r="O99" s="9"/>
     </row>
     <row r="100" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C100" s="2"/>
@@ -2349,7 +2351,7 @@
       <c r="L100" s="2"/>
       <c r="M100" s="2"/>
       <c r="N100" s="2"/>
-      <c r="O100" s="19"/>
+      <c r="O100" s="9"/>
     </row>
     <row r="101" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C101" s="2"/>
@@ -2364,7 +2366,7 @@
       <c r="L101" s="2"/>
       <c r="M101" s="2"/>
       <c r="N101" s="2"/>
-      <c r="O101" s="19"/>
+      <c r="O101" s="9"/>
     </row>
     <row r="102" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C102" s="2"/>
@@ -2379,7 +2381,7 @@
       <c r="L102" s="2"/>
       <c r="M102" s="2"/>
       <c r="N102" s="2"/>
-      <c r="O102" s="19"/>
+      <c r="O102" s="9"/>
     </row>
     <row r="103" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C103" s="2"/>
@@ -2394,7 +2396,7 @@
       <c r="L103" s="2"/>
       <c r="M103" s="2"/>
       <c r="N103" s="2"/>
-      <c r="O103" s="19"/>
+      <c r="O103" s="9"/>
     </row>
     <row r="104" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C104" s="2"/>
@@ -2409,7 +2411,7 @@
       <c r="L104" s="2"/>
       <c r="M104" s="2"/>
       <c r="N104" s="2"/>
-      <c r="O104" s="19"/>
+      <c r="O104" s="9"/>
     </row>
     <row r="105" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C105" s="2"/>
@@ -2424,7 +2426,7 @@
       <c r="L105" s="2"/>
       <c r="M105" s="2"/>
       <c r="N105" s="2"/>
-      <c r="O105" s="19"/>
+      <c r="O105" s="9"/>
     </row>
     <row r="106" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C106" s="2"/>
@@ -2439,7 +2441,7 @@
       <c r="L106" s="2"/>
       <c r="M106" s="2"/>
       <c r="N106" s="2"/>
-      <c r="O106" s="19"/>
+      <c r="O106" s="9"/>
     </row>
     <row r="107" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C107" s="2"/>
@@ -2454,7 +2456,7 @@
       <c r="L107" s="2"/>
       <c r="M107" s="2"/>
       <c r="N107" s="2"/>
-      <c r="O107" s="19"/>
+      <c r="O107" s="9"/>
     </row>
     <row r="108" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C108" s="2"/>
@@ -2469,7 +2471,7 @@
       <c r="L108" s="2"/>
       <c r="M108" s="2"/>
       <c r="N108" s="2"/>
-      <c r="O108" s="19"/>
+      <c r="O108" s="9"/>
     </row>
     <row r="109" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C109" s="2"/>
@@ -2484,7 +2486,7 @@
       <c r="L109" s="2"/>
       <c r="M109" s="2"/>
       <c r="N109" s="2"/>
-      <c r="O109" s="19"/>
+      <c r="O109" s="9"/>
     </row>
     <row r="110" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C110" s="2"/>
@@ -2499,7 +2501,7 @@
       <c r="L110" s="2"/>
       <c r="M110" s="2"/>
       <c r="N110" s="2"/>
-      <c r="O110" s="19"/>
+      <c r="O110" s="9"/>
     </row>
     <row r="111" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C111" s="2"/>
@@ -2514,7 +2516,7 @@
       <c r="L111" s="2"/>
       <c r="M111" s="2"/>
       <c r="N111" s="2"/>
-      <c r="O111" s="19"/>
+      <c r="O111" s="9"/>
     </row>
     <row r="112" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C112" s="2"/>
@@ -2529,7 +2531,7 @@
       <c r="L112" s="2"/>
       <c r="M112" s="2"/>
       <c r="N112" s="2"/>
-      <c r="O112" s="19"/>
+      <c r="O112" s="9"/>
     </row>
     <row r="113" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C113" s="2"/>
@@ -2544,7 +2546,7 @@
       <c r="L113" s="2"/>
       <c r="M113" s="2"/>
       <c r="N113" s="2"/>
-      <c r="O113" s="19"/>
+      <c r="O113" s="9"/>
     </row>
     <row r="114" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C114" s="2"/>
@@ -2559,7 +2561,7 @@
       <c r="L114" s="2"/>
       <c r="M114" s="2"/>
       <c r="N114" s="2"/>
-      <c r="O114" s="19"/>
+      <c r="O114" s="9"/>
     </row>
     <row r="115" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C115" s="2"/>
@@ -2574,7 +2576,7 @@
       <c r="L115" s="2"/>
       <c r="M115" s="2"/>
       <c r="N115" s="2"/>
-      <c r="O115" s="19"/>
+      <c r="O115" s="9"/>
     </row>
     <row r="116" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C116" s="2"/>
@@ -2589,7 +2591,7 @@
       <c r="L116" s="2"/>
       <c r="M116" s="2"/>
       <c r="N116" s="2"/>
-      <c r="O116" s="19"/>
+      <c r="O116" s="9"/>
     </row>
     <row r="117" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C117" s="2"/>
@@ -2604,7 +2606,7 @@
       <c r="L117" s="2"/>
       <c r="M117" s="2"/>
       <c r="N117" s="2"/>
-      <c r="O117" s="19"/>
+      <c r="O117" s="9"/>
     </row>
     <row r="118" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C118" s="2"/>
@@ -2619,7 +2621,7 @@
       <c r="L118" s="2"/>
       <c r="M118" s="2"/>
       <c r="N118" s="2"/>
-      <c r="O118" s="19"/>
+      <c r="O118" s="9"/>
     </row>
     <row r="119" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C119" s="2"/>
@@ -2634,7 +2636,7 @@
       <c r="L119" s="2"/>
       <c r="M119" s="2"/>
       <c r="N119" s="2"/>
-      <c r="O119" s="19"/>
+      <c r="O119" s="9"/>
     </row>
     <row r="120" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C120" s="2"/>
@@ -2649,7 +2651,7 @@
       <c r="L120" s="2"/>
       <c r="M120" s="2"/>
       <c r="N120" s="2"/>
-      <c r="O120" s="19"/>
+      <c r="O120" s="9"/>
     </row>
     <row r="121" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C121" s="2"/>
@@ -2664,7 +2666,7 @@
       <c r="L121" s="2"/>
       <c r="M121" s="2"/>
       <c r="N121" s="2"/>
-      <c r="O121" s="19"/>
+      <c r="O121" s="9"/>
     </row>
     <row r="122" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C122" s="2"/>
@@ -2679,7 +2681,7 @@
       <c r="L122" s="2"/>
       <c r="M122" s="2"/>
       <c r="N122" s="2"/>
-      <c r="O122" s="19"/>
+      <c r="O122" s="9"/>
     </row>
     <row r="123" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C123" s="2"/>
@@ -2694,7 +2696,7 @@
       <c r="L123" s="2"/>
       <c r="M123" s="2"/>
       <c r="N123" s="2"/>
-      <c r="O123" s="19"/>
+      <c r="O123" s="9"/>
     </row>
     <row r="124" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C124" s="2"/>
@@ -2709,7 +2711,7 @@
       <c r="L124" s="2"/>
       <c r="M124" s="2"/>
       <c r="N124" s="2"/>
-      <c r="O124" s="19"/>
+      <c r="O124" s="9"/>
     </row>
     <row r="125" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C125" s="2"/>
@@ -2724,7 +2726,7 @@
       <c r="L125" s="2"/>
       <c r="M125" s="2"/>
       <c r="N125" s="2"/>
-      <c r="O125" s="19"/>
+      <c r="O125" s="9"/>
     </row>
     <row r="126" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C126" s="2"/>
@@ -2739,7 +2741,7 @@
       <c r="L126" s="2"/>
       <c r="M126" s="2"/>
       <c r="N126" s="2"/>
-      <c r="O126" s="19"/>
+      <c r="O126" s="9"/>
     </row>
     <row r="127" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C127" s="2"/>
@@ -2754,7 +2756,7 @@
       <c r="L127" s="2"/>
       <c r="M127" s="2"/>
       <c r="N127" s="2"/>
-      <c r="O127" s="19"/>
+      <c r="O127" s="9"/>
     </row>
     <row r="128" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C128" s="2"/>
@@ -2769,7 +2771,7 @@
       <c r="L128" s="2"/>
       <c r="M128" s="2"/>
       <c r="N128" s="2"/>
-      <c r="O128" s="19"/>
+      <c r="O128" s="9"/>
     </row>
     <row r="129" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C129" s="2"/>
@@ -2784,7 +2786,7 @@
       <c r="L129" s="2"/>
       <c r="M129" s="2"/>
       <c r="N129" s="2"/>
-      <c r="O129" s="19"/>
+      <c r="O129" s="9"/>
     </row>
     <row r="130" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C130" s="2"/>
@@ -2799,7 +2801,7 @@
       <c r="L130" s="2"/>
       <c r="M130" s="2"/>
       <c r="N130" s="2"/>
-      <c r="O130" s="19"/>
+      <c r="O130" s="9"/>
     </row>
     <row r="131" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C131" s="2"/>
@@ -2814,7 +2816,7 @@
       <c r="L131" s="2"/>
       <c r="M131" s="2"/>
       <c r="N131" s="2"/>
-      <c r="O131" s="19"/>
+      <c r="O131" s="9"/>
     </row>
     <row r="132" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C132" s="2"/>
@@ -2829,7 +2831,7 @@
       <c r="L132" s="2"/>
       <c r="M132" s="2"/>
       <c r="N132" s="2"/>
-      <c r="O132" s="19"/>
+      <c r="O132" s="9"/>
     </row>
     <row r="133" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C133" s="2"/>
@@ -2844,7 +2846,7 @@
       <c r="L133" s="2"/>
       <c r="M133" s="2"/>
       <c r="N133" s="2"/>
-      <c r="O133" s="19"/>
+      <c r="O133" s="9"/>
     </row>
     <row r="134" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C134" s="2"/>
@@ -2859,7 +2861,7 @@
       <c r="L134" s="2"/>
       <c r="M134" s="2"/>
       <c r="N134" s="2"/>
-      <c r="O134" s="19"/>
+      <c r="O134" s="9"/>
     </row>
     <row r="135" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C135" s="2"/>
@@ -2874,7 +2876,7 @@
       <c r="L135" s="2"/>
       <c r="M135" s="2"/>
       <c r="N135" s="2"/>
-      <c r="O135" s="19"/>
+      <c r="O135" s="9"/>
     </row>
     <row r="136" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C136" s="2"/>
@@ -2889,7 +2891,7 @@
       <c r="L136" s="2"/>
       <c r="M136" s="2"/>
       <c r="N136" s="2"/>
-      <c r="O136" s="19"/>
+      <c r="O136" s="9"/>
     </row>
     <row r="137" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C137" s="2"/>
@@ -2904,7 +2906,7 @@
       <c r="L137" s="2"/>
       <c r="M137" s="2"/>
       <c r="N137" s="2"/>
-      <c r="O137" s="19"/>
+      <c r="O137" s="9"/>
     </row>
     <row r="138" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C138" s="2"/>
@@ -2919,7 +2921,7 @@
       <c r="L138" s="2"/>
       <c r="M138" s="2"/>
       <c r="N138" s="2"/>
-      <c r="O138" s="19"/>
+      <c r="O138" s="9"/>
     </row>
     <row r="139" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C139" s="2"/>
@@ -2934,7 +2936,7 @@
       <c r="L139" s="2"/>
       <c r="M139" s="2"/>
       <c r="N139" s="2"/>
-      <c r="O139" s="19"/>
+      <c r="O139" s="9"/>
     </row>
     <row r="140" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C140" s="2"/>
@@ -2949,7 +2951,7 @@
       <c r="L140" s="2"/>
       <c r="M140" s="2"/>
       <c r="N140" s="2"/>
-      <c r="O140" s="19"/>
+      <c r="O140" s="9"/>
     </row>
     <row r="141" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C141" s="2"/>
@@ -2964,7 +2966,7 @@
       <c r="L141" s="2"/>
       <c r="M141" s="2"/>
       <c r="N141" s="2"/>
-      <c r="O141" s="19"/>
+      <c r="O141" s="9"/>
     </row>
     <row r="142" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C142" s="2"/>
@@ -2979,7 +2981,7 @@
       <c r="L142" s="2"/>
       <c r="M142" s="2"/>
       <c r="N142" s="2"/>
-      <c r="O142" s="19"/>
+      <c r="O142" s="9"/>
     </row>
     <row r="143" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C143" s="2"/>
@@ -2994,7 +2996,7 @@
       <c r="L143" s="2"/>
       <c r="M143" s="2"/>
       <c r="N143" s="2"/>
-      <c r="O143" s="19"/>
+      <c r="O143" s="9"/>
     </row>
     <row r="144" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C144" s="2"/>
@@ -3009,7 +3011,7 @@
       <c r="L144" s="2"/>
       <c r="M144" s="2"/>
       <c r="N144" s="2"/>
-      <c r="O144" s="19"/>
+      <c r="O144" s="9"/>
     </row>
     <row r="145" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C145" s="2"/>
@@ -3024,7 +3026,7 @@
       <c r="L145" s="2"/>
       <c r="M145" s="2"/>
       <c r="N145" s="2"/>
-      <c r="O145" s="19"/>
+      <c r="O145" s="9"/>
     </row>
     <row r="146" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C146" s="2"/>
@@ -3039,7 +3041,7 @@
       <c r="L146" s="2"/>
       <c r="M146" s="2"/>
       <c r="N146" s="2"/>
-      <c r="O146" s="19"/>
+      <c r="O146" s="9"/>
     </row>
     <row r="147" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C147" s="2"/>
@@ -3054,7 +3056,7 @@
       <c r="L147" s="2"/>
       <c r="M147" s="2"/>
       <c r="N147" s="2"/>
-      <c r="O147" s="19"/>
+      <c r="O147" s="9"/>
     </row>
     <row r="148" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C148" s="2"/>
@@ -3069,7 +3071,7 @@
       <c r="L148" s="2"/>
       <c r="M148" s="2"/>
       <c r="N148" s="2"/>
-      <c r="O148" s="19"/>
+      <c r="O148" s="9"/>
     </row>
     <row r="149" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C149" s="2"/>
@@ -3084,7 +3086,7 @@
       <c r="L149" s="2"/>
       <c r="M149" s="2"/>
       <c r="N149" s="2"/>
-      <c r="O149" s="19"/>
+      <c r="O149" s="9"/>
     </row>
     <row r="150" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C150" s="2"/>
@@ -3099,7 +3101,7 @@
       <c r="L150" s="2"/>
       <c r="M150" s="2"/>
       <c r="N150" s="2"/>
-      <c r="O150" s="19"/>
+      <c r="O150" s="9"/>
     </row>
     <row r="151" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C151" s="2"/>
@@ -3114,7 +3116,7 @@
       <c r="L151" s="2"/>
       <c r="M151" s="2"/>
       <c r="N151" s="2"/>
-      <c r="O151" s="19"/>
+      <c r="O151" s="9"/>
     </row>
     <row r="152" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C152" s="2"/>
@@ -3129,7 +3131,7 @@
       <c r="L152" s="2"/>
       <c r="M152" s="2"/>
       <c r="N152" s="2"/>
-      <c r="O152" s="19"/>
+      <c r="O152" s="9"/>
     </row>
     <row r="153" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C153" s="2"/>
@@ -3144,7 +3146,7 @@
       <c r="L153" s="2"/>
       <c r="M153" s="2"/>
       <c r="N153" s="2"/>
-      <c r="O153" s="19"/>
+      <c r="O153" s="9"/>
     </row>
     <row r="154" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C154" s="2"/>
@@ -3159,7 +3161,7 @@
       <c r="L154" s="2"/>
       <c r="M154" s="2"/>
       <c r="N154" s="2"/>
-      <c r="O154" s="19"/>
+      <c r="O154" s="9"/>
     </row>
     <row r="155" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C155" s="2"/>
@@ -3174,7 +3176,7 @@
       <c r="L155" s="2"/>
       <c r="M155" s="2"/>
       <c r="N155" s="2"/>
-      <c r="O155" s="19"/>
+      <c r="O155" s="9"/>
     </row>
     <row r="156" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C156" s="2"/>
@@ -3189,7 +3191,7 @@
       <c r="L156" s="2"/>
       <c r="M156" s="2"/>
       <c r="N156" s="2"/>
-      <c r="O156" s="19"/>
+      <c r="O156" s="9"/>
     </row>
     <row r="157" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C157" s="2"/>
@@ -3204,7 +3206,7 @@
       <c r="L157" s="2"/>
       <c r="M157" s="2"/>
       <c r="N157" s="2"/>
-      <c r="O157" s="19"/>
+      <c r="O157" s="9"/>
     </row>
     <row r="158" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C158" s="2"/>
@@ -3219,7 +3221,7 @@
       <c r="L158" s="2"/>
       <c r="M158" s="2"/>
       <c r="N158" s="2"/>
-      <c r="O158" s="19"/>
+      <c r="O158" s="9"/>
     </row>
     <row r="159" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C159" s="2"/>
@@ -3234,7 +3236,7 @@
       <c r="L159" s="2"/>
       <c r="M159" s="2"/>
       <c r="N159" s="2"/>
-      <c r="O159" s="19"/>
+      <c r="O159" s="9"/>
     </row>
     <row r="160" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C160" s="2"/>
@@ -3249,7 +3251,7 @@
       <c r="L160" s="2"/>
       <c r="M160" s="2"/>
       <c r="N160" s="2"/>
-      <c r="O160" s="19"/>
+      <c r="O160" s="9"/>
     </row>
     <row r="161" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C161" s="2"/>
@@ -3264,7 +3266,7 @@
       <c r="L161" s="2"/>
       <c r="M161" s="2"/>
       <c r="N161" s="2"/>
-      <c r="O161" s="19"/>
+      <c r="O161" s="9"/>
     </row>
     <row r="162" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C162" s="2"/>
@@ -3279,7 +3281,7 @@
       <c r="L162" s="2"/>
       <c r="M162" s="2"/>
       <c r="N162" s="2"/>
-      <c r="O162" s="19"/>
+      <c r="O162" s="9"/>
     </row>
     <row r="163" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C163" s="2"/>
@@ -3294,7 +3296,7 @@
       <c r="L163" s="2"/>
       <c r="M163" s="2"/>
       <c r="N163" s="2"/>
-      <c r="O163" s="19"/>
+      <c r="O163" s="9"/>
     </row>
     <row r="164" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C164" s="2"/>
@@ -3309,7 +3311,7 @@
       <c r="L164" s="2"/>
       <c r="M164" s="2"/>
       <c r="N164" s="2"/>
-      <c r="O164" s="19"/>
+      <c r="O164" s="9"/>
     </row>
     <row r="165" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C165" s="2"/>
@@ -3324,7 +3326,7 @@
       <c r="L165" s="2"/>
       <c r="M165" s="2"/>
       <c r="N165" s="2"/>
-      <c r="O165" s="19"/>
+      <c r="O165" s="9"/>
     </row>
     <row r="166" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C166" s="2"/>
@@ -3339,7 +3341,7 @@
       <c r="L166" s="2"/>
       <c r="M166" s="2"/>
       <c r="N166" s="2"/>
-      <c r="O166" s="19"/>
+      <c r="O166" s="9"/>
     </row>
     <row r="167" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C167" s="2"/>
@@ -3354,7 +3356,7 @@
       <c r="L167" s="2"/>
       <c r="M167" s="2"/>
       <c r="N167" s="2"/>
-      <c r="O167" s="19"/>
+      <c r="O167" s="9"/>
     </row>
     <row r="168" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C168" s="2"/>
@@ -3369,7 +3371,7 @@
       <c r="L168" s="2"/>
       <c r="M168" s="2"/>
       <c r="N168" s="2"/>
-      <c r="O168" s="19"/>
+      <c r="O168" s="9"/>
     </row>
     <row r="169" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C169" s="2"/>
@@ -3384,7 +3386,7 @@
       <c r="L169" s="2"/>
       <c r="M169" s="2"/>
       <c r="N169" s="2"/>
-      <c r="O169" s="19"/>
+      <c r="O169" s="9"/>
     </row>
     <row r="170" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C170" s="2"/>
@@ -3399,7 +3401,7 @@
       <c r="L170" s="2"/>
       <c r="M170" s="2"/>
       <c r="N170" s="2"/>
-      <c r="O170" s="19"/>
+      <c r="O170" s="9"/>
     </row>
     <row r="171" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C171" s="2"/>
@@ -3414,7 +3416,7 @@
       <c r="L171" s="2"/>
       <c r="M171" s="2"/>
       <c r="N171" s="2"/>
-      <c r="O171" s="19"/>
+      <c r="O171" s="9"/>
     </row>
     <row r="172" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C172" s="2"/>
@@ -3429,7 +3431,7 @@
       <c r="L172" s="2"/>
       <c r="M172" s="2"/>
       <c r="N172" s="2"/>
-      <c r="O172" s="19"/>
+      <c r="O172" s="9"/>
     </row>
     <row r="173" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C173" s="2"/>
@@ -3444,7 +3446,7 @@
       <c r="L173" s="2"/>
       <c r="M173" s="2"/>
       <c r="N173" s="2"/>
-      <c r="O173" s="19"/>
+      <c r="O173" s="9"/>
     </row>
     <row r="174" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C174" s="2"/>
@@ -3459,7 +3461,7 @@
       <c r="L174" s="2"/>
       <c r="M174" s="2"/>
       <c r="N174" s="2"/>
-      <c r="O174" s="19"/>
+      <c r="O174" s="9"/>
     </row>
     <row r="175" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C175" s="2"/>
@@ -3474,7 +3476,7 @@
       <c r="L175" s="2"/>
       <c r="M175" s="2"/>
       <c r="N175" s="2"/>
-      <c r="O175" s="19"/>
+      <c r="O175" s="9"/>
     </row>
     <row r="176" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C176" s="2"/>
@@ -3489,7 +3491,7 @@
       <c r="L176" s="2"/>
       <c r="M176" s="2"/>
       <c r="N176" s="2"/>
-      <c r="O176" s="19"/>
+      <c r="O176" s="9"/>
     </row>
     <row r="177" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C177" s="2"/>
@@ -3504,7 +3506,7 @@
       <c r="L177" s="2"/>
       <c r="M177" s="2"/>
       <c r="N177" s="2"/>
-      <c r="O177" s="19"/>
+      <c r="O177" s="9"/>
     </row>
     <row r="178" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C178" s="2"/>
@@ -3519,7 +3521,7 @@
       <c r="L178" s="2"/>
       <c r="M178" s="2"/>
       <c r="N178" s="2"/>
-      <c r="O178" s="19"/>
+      <c r="O178" s="9"/>
     </row>
     <row r="179" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C179" s="2"/>
@@ -3534,7 +3536,7 @@
       <c r="L179" s="2"/>
       <c r="M179" s="2"/>
       <c r="N179" s="2"/>
-      <c r="O179" s="19"/>
+      <c r="O179" s="9"/>
     </row>
     <row r="180" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C180" s="2"/>
@@ -3549,7 +3551,7 @@
       <c r="L180" s="2"/>
       <c r="M180" s="2"/>
       <c r="N180" s="2"/>
-      <c r="O180" s="19"/>
+      <c r="O180" s="9"/>
     </row>
     <row r="181" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C181" s="2"/>
@@ -3564,7 +3566,7 @@
       <c r="L181" s="2"/>
       <c r="M181" s="2"/>
       <c r="N181" s="2"/>
-      <c r="O181" s="19"/>
+      <c r="O181" s="9"/>
     </row>
     <row r="182" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C182" s="2"/>
@@ -3579,7 +3581,7 @@
       <c r="L182" s="2"/>
       <c r="M182" s="2"/>
       <c r="N182" s="2"/>
-      <c r="O182" s="19"/>
+      <c r="O182" s="9"/>
     </row>
     <row r="183" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C183" s="2"/>
@@ -3594,7 +3596,7 @@
       <c r="L183" s="2"/>
       <c r="M183" s="2"/>
       <c r="N183" s="2"/>
-      <c r="O183" s="19"/>
+      <c r="O183" s="9"/>
     </row>
     <row r="184" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C184" s="2"/>
@@ -3609,7 +3611,7 @@
       <c r="L184" s="2"/>
       <c r="M184" s="2"/>
       <c r="N184" s="2"/>
-      <c r="O184" s="19"/>
+      <c r="O184" s="9"/>
     </row>
     <row r="185" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C185" s="2"/>
@@ -3624,7 +3626,7 @@
       <c r="L185" s="2"/>
       <c r="M185" s="2"/>
       <c r="N185" s="2"/>
-      <c r="O185" s="19"/>
+      <c r="O185" s="9"/>
     </row>
     <row r="186" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C186" s="2"/>
@@ -3639,7 +3641,7 @@
       <c r="L186" s="2"/>
       <c r="M186" s="2"/>
       <c r="N186" s="2"/>
-      <c r="O186" s="19"/>
+      <c r="O186" s="9"/>
     </row>
     <row r="187" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C187" s="2"/>
@@ -3654,7 +3656,7 @@
       <c r="L187" s="2"/>
       <c r="M187" s="2"/>
       <c r="N187" s="2"/>
-      <c r="O187" s="19"/>
+      <c r="O187" s="9"/>
     </row>
     <row r="188" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C188" s="2"/>
@@ -3669,7 +3671,7 @@
       <c r="L188" s="2"/>
       <c r="M188" s="2"/>
       <c r="N188" s="2"/>
-      <c r="O188" s="19"/>
+      <c r="O188" s="9"/>
     </row>
     <row r="189" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C189" s="2"/>
@@ -3684,7 +3686,7 @@
       <c r="L189" s="2"/>
       <c r="M189" s="2"/>
       <c r="N189" s="2"/>
-      <c r="O189" s="19"/>
+      <c r="O189" s="9"/>
     </row>
     <row r="190" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C190" s="2"/>
@@ -3699,7 +3701,7 @@
       <c r="L190" s="2"/>
       <c r="M190" s="2"/>
       <c r="N190" s="2"/>
-      <c r="O190" s="19"/>
+      <c r="O190" s="9"/>
     </row>
     <row r="191" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C191" s="2"/>
@@ -3714,7 +3716,7 @@
       <c r="L191" s="2"/>
       <c r="M191" s="2"/>
       <c r="N191" s="2"/>
-      <c r="O191" s="19"/>
+      <c r="O191" s="9"/>
     </row>
     <row r="192" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C192" s="2"/>
@@ -3729,7 +3731,7 @@
       <c r="L192" s="2"/>
       <c r="M192" s="2"/>
       <c r="N192" s="2"/>
-      <c r="O192" s="19"/>
+      <c r="O192" s="9"/>
     </row>
     <row r="193" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C193" s="2"/>
@@ -3744,7 +3746,7 @@
       <c r="L193" s="2"/>
       <c r="M193" s="2"/>
       <c r="N193" s="2"/>
-      <c r="O193" s="19"/>
+      <c r="O193" s="9"/>
     </row>
     <row r="194" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C194" s="2"/>
@@ -3759,7 +3761,7 @@
       <c r="L194" s="2"/>
       <c r="M194" s="2"/>
       <c r="N194" s="2"/>
-      <c r="O194" s="19"/>
+      <c r="O194" s="9"/>
     </row>
     <row r="195" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C195" s="2"/>
@@ -3774,7 +3776,7 @@
       <c r="L195" s="2"/>
       <c r="M195" s="2"/>
       <c r="N195" s="2"/>
-      <c r="O195" s="19"/>
+      <c r="O195" s="9"/>
     </row>
     <row r="196" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C196" s="2"/>
@@ -3789,7 +3791,7 @@
       <c r="L196" s="2"/>
       <c r="M196" s="2"/>
       <c r="N196" s="2"/>
-      <c r="O196" s="19"/>
+      <c r="O196" s="9"/>
     </row>
     <row r="197" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C197" s="2"/>
@@ -3804,7 +3806,7 @@
       <c r="L197" s="2"/>
       <c r="M197" s="2"/>
       <c r="N197" s="2"/>
-      <c r="O197" s="19"/>
+      <c r="O197" s="9"/>
     </row>
     <row r="198" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C198" s="2"/>
@@ -3819,7 +3821,7 @@
       <c r="L198" s="2"/>
       <c r="M198" s="2"/>
       <c r="N198" s="2"/>
-      <c r="O198" s="19"/>
+      <c r="O198" s="9"/>
     </row>
     <row r="199" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C199" s="2"/>
@@ -3834,7 +3836,7 @@
       <c r="L199" s="2"/>
       <c r="M199" s="2"/>
       <c r="N199" s="2"/>
-      <c r="O199" s="19"/>
+      <c r="O199" s="9"/>
     </row>
     <row r="200" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C200" s="2"/>
@@ -3849,7 +3851,7 @@
       <c r="L200" s="2"/>
       <c r="M200" s="2"/>
       <c r="N200" s="2"/>
-      <c r="O200" s="19"/>
+      <c r="O200" s="9"/>
     </row>
     <row r="201" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C201" s="2"/>
@@ -3864,7 +3866,7 @@
       <c r="L201" s="2"/>
       <c r="M201" s="2"/>
       <c r="N201" s="2"/>
-      <c r="O201" s="19"/>
+      <c r="O201" s="9"/>
     </row>
     <row r="202" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C202" s="2"/>
@@ -3879,7 +3881,7 @@
       <c r="L202" s="2"/>
       <c r="M202" s="2"/>
       <c r="N202" s="2"/>
-      <c r="O202" s="19"/>
+      <c r="O202" s="9"/>
     </row>
     <row r="203" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C203" s="2"/>
@@ -3894,7 +3896,7 @@
       <c r="L203" s="2"/>
       <c r="M203" s="2"/>
       <c r="N203" s="2"/>
-      <c r="O203" s="19"/>
+      <c r="O203" s="9"/>
     </row>
     <row r="204" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C204" s="2"/>
@@ -3909,7 +3911,7 @@
       <c r="L204" s="2"/>
       <c r="M204" s="2"/>
       <c r="N204" s="2"/>
-      <c r="O204" s="19"/>
+      <c r="O204" s="9"/>
     </row>
     <row r="205" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C205" s="2"/>
@@ -3924,7 +3926,7 @@
       <c r="L205" s="2"/>
       <c r="M205" s="2"/>
       <c r="N205" s="2"/>
-      <c r="O205" s="19"/>
+      <c r="O205" s="9"/>
     </row>
     <row r="206" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C206" s="2"/>
@@ -3939,7 +3941,7 @@
       <c r="L206" s="2"/>
       <c r="M206" s="2"/>
       <c r="N206" s="2"/>
-      <c r="O206" s="19"/>
+      <c r="O206" s="9"/>
     </row>
     <row r="207" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C207" s="2"/>
@@ -3954,7 +3956,7 @@
       <c r="L207" s="2"/>
       <c r="M207" s="2"/>
       <c r="N207" s="2"/>
-      <c r="O207" s="19"/>
+      <c r="O207" s="9"/>
     </row>
     <row r="208" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C208" s="2"/>
@@ -3969,7 +3971,7 @@
       <c r="L208" s="2"/>
       <c r="M208" s="2"/>
       <c r="N208" s="2"/>
-      <c r="O208" s="19"/>
+      <c r="O208" s="9"/>
     </row>
     <row r="209" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C209" s="2"/>
@@ -3984,7 +3986,7 @@
       <c r="L209" s="2"/>
       <c r="M209" s="2"/>
       <c r="N209" s="2"/>
-      <c r="O209" s="19"/>
+      <c r="O209" s="9"/>
     </row>
     <row r="210" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C210" s="2"/>
@@ -3999,7 +4001,7 @@
       <c r="L210" s="2"/>
       <c r="M210" s="2"/>
       <c r="N210" s="2"/>
-      <c r="O210" s="19"/>
+      <c r="O210" s="9"/>
     </row>
     <row r="211" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C211" s="2"/>
@@ -4014,7 +4016,7 @@
       <c r="L211" s="2"/>
       <c r="M211" s="2"/>
       <c r="N211" s="2"/>
-      <c r="O211" s="19"/>
+      <c r="O211" s="9"/>
     </row>
     <row r="212" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C212" s="2"/>
@@ -4029,7 +4031,7 @@
       <c r="L212" s="2"/>
       <c r="M212" s="2"/>
       <c r="N212" s="2"/>
-      <c r="O212" s="19"/>
+      <c r="O212" s="9"/>
     </row>
     <row r="213" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C213" s="2"/>
@@ -4044,7 +4046,7 @@
       <c r="L213" s="2"/>
       <c r="M213" s="2"/>
       <c r="N213" s="2"/>
-      <c r="O213" s="19"/>
+      <c r="O213" s="9"/>
     </row>
     <row r="214" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C214" s="2"/>
@@ -4059,7 +4061,7 @@
       <c r="L214" s="2"/>
       <c r="M214" s="2"/>
       <c r="N214" s="2"/>
-      <c r="O214" s="19"/>
+      <c r="O214" s="9"/>
     </row>
     <row r="215" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C215" s="2"/>
@@ -4074,7 +4076,7 @@
       <c r="L215" s="2"/>
       <c r="M215" s="2"/>
       <c r="N215" s="2"/>
-      <c r="O215" s="19"/>
+      <c r="O215" s="9"/>
     </row>
     <row r="216" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C216" s="2"/>
@@ -4089,7 +4091,7 @@
       <c r="L216" s="2"/>
       <c r="M216" s="2"/>
       <c r="N216" s="2"/>
-      <c r="O216" s="19"/>
+      <c r="O216" s="9"/>
     </row>
     <row r="217" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C217" s="2"/>
@@ -4104,7 +4106,7 @@
       <c r="L217" s="2"/>
       <c r="M217" s="2"/>
       <c r="N217" s="2"/>
-      <c r="O217" s="19"/>
+      <c r="O217" s="9"/>
     </row>
     <row r="218" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C218" s="2"/>
@@ -4119,7 +4121,7 @@
       <c r="L218" s="2"/>
       <c r="M218" s="2"/>
       <c r="N218" s="2"/>
-      <c r="O218" s="19"/>
+      <c r="O218" s="9"/>
     </row>
     <row r="219" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C219" s="2"/>
@@ -4134,7 +4136,7 @@
       <c r="L219" s="2"/>
       <c r="M219" s="2"/>
       <c r="N219" s="2"/>
-      <c r="O219" s="19"/>
+      <c r="O219" s="9"/>
     </row>
     <row r="220" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C220" s="2"/>
@@ -4149,7 +4151,7 @@
       <c r="L220" s="2"/>
       <c r="M220" s="2"/>
       <c r="N220" s="2"/>
-      <c r="O220" s="19"/>
+      <c r="O220" s="9"/>
     </row>
     <row r="221" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C221" s="2"/>
@@ -4164,7 +4166,7 @@
       <c r="L221" s="2"/>
       <c r="M221" s="2"/>
       <c r="N221" s="2"/>
-      <c r="O221" s="19"/>
+      <c r="O221" s="9"/>
     </row>
     <row r="222" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C222" s="2"/>
@@ -4179,7 +4181,7 @@
       <c r="L222" s="2"/>
       <c r="M222" s="2"/>
       <c r="N222" s="2"/>
-      <c r="O222" s="19"/>
+      <c r="O222" s="9"/>
     </row>
     <row r="223" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C223" s="2"/>
@@ -4194,7 +4196,7 @@
       <c r="L223" s="2"/>
       <c r="M223" s="2"/>
       <c r="N223" s="2"/>
-      <c r="O223" s="19"/>
+      <c r="O223" s="9"/>
     </row>
     <row r="224" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C224" s="2"/>
@@ -4209,7 +4211,7 @@
       <c r="L224" s="2"/>
       <c r="M224" s="2"/>
       <c r="N224" s="2"/>
-      <c r="O224" s="19"/>
+      <c r="O224" s="9"/>
     </row>
     <row r="225" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C225" s="2"/>
@@ -4224,7 +4226,7 @@
       <c r="L225" s="2"/>
       <c r="M225" s="2"/>
       <c r="N225" s="2"/>
-      <c r="O225" s="19"/>
+      <c r="O225" s="9"/>
     </row>
     <row r="226" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C226" s="2"/>
@@ -4239,7 +4241,7 @@
       <c r="L226" s="2"/>
       <c r="M226" s="2"/>
       <c r="N226" s="2"/>
-      <c r="O226" s="19"/>
+      <c r="O226" s="9"/>
     </row>
     <row r="227" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C227" s="2"/>
@@ -4254,7 +4256,7 @@
       <c r="L227" s="2"/>
       <c r="M227" s="2"/>
       <c r="N227" s="2"/>
-      <c r="O227" s="19"/>
+      <c r="O227" s="9"/>
     </row>
     <row r="228" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C228" s="2"/>
@@ -4269,7 +4271,7 @@
       <c r="L228" s="2"/>
       <c r="M228" s="2"/>
       <c r="N228" s="2"/>
-      <c r="O228" s="19"/>
+      <c r="O228" s="9"/>
     </row>
     <row r="229" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C229" s="2"/>
@@ -4284,7 +4286,7 @@
       <c r="L229" s="2"/>
       <c r="M229" s="2"/>
       <c r="N229" s="2"/>
-      <c r="O229" s="19"/>
+      <c r="O229" s="9"/>
     </row>
     <row r="230" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C230" s="2"/>
@@ -4299,7 +4301,7 @@
       <c r="L230" s="2"/>
       <c r="M230" s="2"/>
       <c r="N230" s="2"/>
-      <c r="O230" s="19"/>
+      <c r="O230" s="9"/>
     </row>
     <row r="231" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C231" s="2"/>
@@ -4314,7 +4316,7 @@
       <c r="L231" s="2"/>
       <c r="M231" s="2"/>
       <c r="N231" s="2"/>
-      <c r="O231" s="19"/>
+      <c r="O231" s="9"/>
     </row>
     <row r="232" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C232" s="2"/>
@@ -4329,7 +4331,7 @@
       <c r="L232" s="2"/>
       <c r="M232" s="2"/>
       <c r="N232" s="2"/>
-      <c r="O232" s="19"/>
+      <c r="O232" s="9"/>
     </row>
     <row r="233" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C233" s="2"/>
@@ -4344,7 +4346,7 @@
       <c r="L233" s="2"/>
       <c r="M233" s="2"/>
       <c r="N233" s="2"/>
-      <c r="O233" s="19"/>
+      <c r="O233" s="9"/>
     </row>
     <row r="234" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C234" s="2"/>
@@ -4359,7 +4361,7 @@
       <c r="L234" s="2"/>
       <c r="M234" s="2"/>
       <c r="N234" s="2"/>
-      <c r="O234" s="19"/>
+      <c r="O234" s="9"/>
     </row>
     <row r="235" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C235" s="2"/>
@@ -4374,7 +4376,7 @@
       <c r="L235" s="2"/>
       <c r="M235" s="2"/>
       <c r="N235" s="2"/>
-      <c r="O235" s="19"/>
+      <c r="O235" s="9"/>
     </row>
     <row r="236" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C236" s="2"/>
@@ -4389,7 +4391,7 @@
       <c r="L236" s="2"/>
       <c r="M236" s="2"/>
       <c r="N236" s="2"/>
-      <c r="O236" s="19"/>
+      <c r="O236" s="9"/>
     </row>
     <row r="237" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C237" s="2"/>
@@ -4404,7 +4406,7 @@
       <c r="L237" s="2"/>
       <c r="M237" s="2"/>
       <c r="N237" s="2"/>
-      <c r="O237" s="19"/>
+      <c r="O237" s="9"/>
     </row>
     <row r="238" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C238" s="2"/>
@@ -4419,7 +4421,7 @@
       <c r="L238" s="2"/>
       <c r="M238" s="2"/>
       <c r="N238" s="2"/>
-      <c r="O238" s="19"/>
+      <c r="O238" s="9"/>
     </row>
     <row r="239" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C239" s="2"/>
@@ -4434,7 +4436,7 @@
       <c r="L239" s="2"/>
       <c r="M239" s="2"/>
       <c r="N239" s="2"/>
-      <c r="O239" s="19"/>
+      <c r="O239" s="9"/>
     </row>
     <row r="240" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C240" s="2"/>
@@ -4449,7 +4451,7 @@
       <c r="L240" s="2"/>
       <c r="M240" s="2"/>
       <c r="N240" s="2"/>
-      <c r="O240" s="19"/>
+      <c r="O240" s="9"/>
     </row>
     <row r="241" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C241" s="2"/>
@@ -4464,7 +4466,7 @@
       <c r="L241" s="2"/>
       <c r="M241" s="2"/>
       <c r="N241" s="2"/>
-      <c r="O241" s="19"/>
+      <c r="O241" s="9"/>
     </row>
     <row r="242" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C242" s="2"/>
@@ -4479,7 +4481,7 @@
       <c r="L242" s="2"/>
       <c r="M242" s="2"/>
       <c r="N242" s="2"/>
-      <c r="O242" s="19"/>
+      <c r="O242" s="9"/>
     </row>
     <row r="243" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C243" s="2"/>
@@ -4494,7 +4496,7 @@
       <c r="L243" s="2"/>
       <c r="M243" s="2"/>
       <c r="N243" s="2"/>
-      <c r="O243" s="19"/>
+      <c r="O243" s="9"/>
     </row>
     <row r="244" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C244" s="2"/>
@@ -4509,7 +4511,7 @@
       <c r="L244" s="2"/>
       <c r="M244" s="2"/>
       <c r="N244" s="2"/>
-      <c r="O244" s="19"/>
+      <c r="O244" s="9"/>
     </row>
     <row r="245" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C245" s="2"/>
@@ -4524,7 +4526,7 @@
       <c r="L245" s="2"/>
       <c r="M245" s="2"/>
       <c r="N245" s="2"/>
-      <c r="O245" s="19"/>
+      <c r="O245" s="9"/>
     </row>
     <row r="246" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C246" s="2"/>
@@ -4539,7 +4541,7 @@
       <c r="L246" s="2"/>
       <c r="M246" s="2"/>
       <c r="N246" s="2"/>
-      <c r="O246" s="19"/>
+      <c r="O246" s="9"/>
     </row>
     <row r="247" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C247" s="2"/>
@@ -4554,7 +4556,7 @@
       <c r="L247" s="2"/>
       <c r="M247" s="2"/>
       <c r="N247" s="2"/>
-      <c r="O247" s="19"/>
+      <c r="O247" s="9"/>
     </row>
     <row r="248" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C248" s="2"/>
@@ -4569,7 +4571,7 @@
       <c r="L248" s="2"/>
       <c r="M248" s="2"/>
       <c r="N248" s="2"/>
-      <c r="O248" s="19"/>
+      <c r="O248" s="9"/>
     </row>
     <row r="249" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C249" s="2"/>
@@ -4584,7 +4586,7 @@
       <c r="L249" s="2"/>
       <c r="M249" s="2"/>
       <c r="N249" s="2"/>
-      <c r="O249" s="19"/>
+      <c r="O249" s="9"/>
     </row>
     <row r="250" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C250" s="2"/>
@@ -4599,7 +4601,7 @@
       <c r="L250" s="2"/>
       <c r="M250" s="2"/>
       <c r="N250" s="2"/>
-      <c r="O250" s="19"/>
+      <c r="O250" s="9"/>
     </row>
     <row r="251" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C251" s="2"/>
@@ -4614,7 +4616,7 @@
       <c r="L251" s="2"/>
       <c r="M251" s="2"/>
       <c r="N251" s="2"/>
-      <c r="O251" s="19"/>
+      <c r="O251" s="9"/>
     </row>
     <row r="252" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C252" s="2"/>
@@ -4629,7 +4631,7 @@
       <c r="L252" s="2"/>
       <c r="M252" s="2"/>
       <c r="N252" s="2"/>
-      <c r="O252" s="19"/>
+      <c r="O252" s="9"/>
     </row>
     <row r="253" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C253" s="2"/>
@@ -4644,7 +4646,7 @@
       <c r="L253" s="2"/>
       <c r="M253" s="2"/>
       <c r="N253" s="2"/>
-      <c r="O253" s="19"/>
+      <c r="O253" s="9"/>
     </row>
     <row r="254" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C254" s="2"/>
@@ -4659,7 +4661,7 @@
       <c r="L254" s="2"/>
       <c r="M254" s="2"/>
       <c r="N254" s="2"/>
-      <c r="O254" s="19"/>
+      <c r="O254" s="9"/>
     </row>
     <row r="255" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C255" s="2"/>
@@ -4674,7 +4676,7 @@
       <c r="L255" s="2"/>
       <c r="M255" s="2"/>
       <c r="N255" s="2"/>
-      <c r="O255" s="19"/>
+      <c r="O255" s="9"/>
     </row>
     <row r="256" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C256" s="2"/>
@@ -4689,7 +4691,7 @@
       <c r="L256" s="2"/>
       <c r="M256" s="2"/>
       <c r="N256" s="2"/>
-      <c r="O256" s="19"/>
+      <c r="O256" s="9"/>
     </row>
     <row r="257" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C257" s="2"/>
@@ -4704,7 +4706,7 @@
       <c r="L257" s="2"/>
       <c r="M257" s="2"/>
       <c r="N257" s="2"/>
-      <c r="O257" s="19"/>
+      <c r="O257" s="9"/>
     </row>
     <row r="258" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C258" s="2"/>
@@ -4719,7 +4721,7 @@
       <c r="L258" s="2"/>
       <c r="M258" s="2"/>
       <c r="N258" s="2"/>
-      <c r="O258" s="19"/>
+      <c r="O258" s="9"/>
     </row>
     <row r="259" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C259" s="2"/>
@@ -4734,7 +4736,7 @@
       <c r="L259" s="2"/>
       <c r="M259" s="2"/>
       <c r="N259" s="2"/>
-      <c r="O259" s="19"/>
+      <c r="O259" s="9"/>
     </row>
     <row r="260" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C260" s="2"/>
@@ -4749,7 +4751,7 @@
       <c r="L260" s="2"/>
       <c r="M260" s="2"/>
       <c r="N260" s="2"/>
-      <c r="O260" s="19"/>
+      <c r="O260" s="9"/>
     </row>
     <row r="261" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C261" s="2"/>
@@ -4764,7 +4766,7 @@
       <c r="L261" s="2"/>
       <c r="M261" s="2"/>
       <c r="N261" s="2"/>
-      <c r="O261" s="19"/>
+      <c r="O261" s="9"/>
     </row>
     <row r="262" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C262" s="2"/>
@@ -4779,7 +4781,7 @@
       <c r="L262" s="2"/>
       <c r="M262" s="2"/>
       <c r="N262" s="2"/>
-      <c r="O262" s="19"/>
+      <c r="O262" s="9"/>
     </row>
     <row r="263" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C263" s="2"/>
@@ -4794,7 +4796,7 @@
       <c r="L263" s="2"/>
       <c r="M263" s="2"/>
       <c r="N263" s="2"/>
-      <c r="O263" s="19"/>
+      <c r="O263" s="9"/>
     </row>
     <row r="264" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C264" s="2"/>
@@ -4809,7 +4811,7 @@
       <c r="L264" s="2"/>
       <c r="M264" s="2"/>
       <c r="N264" s="2"/>
-      <c r="O264" s="19"/>
+      <c r="O264" s="9"/>
     </row>
     <row r="265" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C265" s="2"/>
@@ -4824,7 +4826,7 @@
       <c r="L265" s="2"/>
       <c r="M265" s="2"/>
       <c r="N265" s="2"/>
-      <c r="O265" s="19"/>
+      <c r="O265" s="9"/>
     </row>
     <row r="266" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C266" s="2"/>
@@ -4839,7 +4841,7 @@
       <c r="L266" s="2"/>
       <c r="M266" s="2"/>
       <c r="N266" s="2"/>
-      <c r="O266" s="19"/>
+      <c r="O266" s="9"/>
     </row>
     <row r="267" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C267" s="2"/>
@@ -4854,7 +4856,7 @@
       <c r="L267" s="2"/>
       <c r="M267" s="2"/>
       <c r="N267" s="2"/>
-      <c r="O267" s="19"/>
+      <c r="O267" s="9"/>
     </row>
     <row r="268" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C268" s="2"/>
@@ -4869,7 +4871,7 @@
       <c r="L268" s="2"/>
       <c r="M268" s="2"/>
       <c r="N268" s="2"/>
-      <c r="O268" s="19"/>
+      <c r="O268" s="9"/>
     </row>
     <row r="269" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C269" s="2"/>
@@ -4884,7 +4886,7 @@
       <c r="L269" s="2"/>
       <c r="M269" s="2"/>
       <c r="N269" s="2"/>
-      <c r="O269" s="19"/>
+      <c r="O269" s="9"/>
     </row>
     <row r="270" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C270" s="2"/>
@@ -4899,7 +4901,7 @@
       <c r="L270" s="2"/>
       <c r="M270" s="2"/>
       <c r="N270" s="2"/>
-      <c r="O270" s="19"/>
+      <c r="O270" s="9"/>
     </row>
     <row r="271" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C271" s="2"/>
@@ -4914,7 +4916,7 @@
       <c r="L271" s="2"/>
       <c r="M271" s="2"/>
       <c r="N271" s="2"/>
-      <c r="O271" s="19"/>
+      <c r="O271" s="9"/>
     </row>
     <row r="272" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C272" s="2"/>
@@ -4929,7 +4931,7 @@
       <c r="L272" s="2"/>
       <c r="M272" s="2"/>
       <c r="N272" s="2"/>
-      <c r="O272" s="19"/>
+      <c r="O272" s="9"/>
     </row>
     <row r="273" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C273" s="2"/>
@@ -4944,7 +4946,7 @@
       <c r="L273" s="2"/>
       <c r="M273" s="2"/>
       <c r="N273" s="2"/>
-      <c r="O273" s="19"/>
+      <c r="O273" s="9"/>
     </row>
     <row r="274" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C274" s="2"/>
@@ -4959,7 +4961,7 @@
       <c r="L274" s="2"/>
       <c r="M274" s="2"/>
       <c r="N274" s="2"/>
-      <c r="O274" s="19"/>
+      <c r="O274" s="9"/>
     </row>
     <row r="275" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C275" s="2"/>
@@ -4974,7 +4976,7 @@
       <c r="L275" s="2"/>
       <c r="M275" s="2"/>
       <c r="N275" s="2"/>
-      <c r="O275" s="19"/>
+      <c r="O275" s="9"/>
     </row>
     <row r="276" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C276" s="2"/>
@@ -4989,7 +4991,7 @@
       <c r="L276" s="2"/>
       <c r="M276" s="2"/>
       <c r="N276" s="2"/>
-      <c r="O276" s="19"/>
+      <c r="O276" s="9"/>
     </row>
     <row r="277" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C277" s="2"/>
@@ -5004,7 +5006,7 @@
       <c r="L277" s="2"/>
       <c r="M277" s="2"/>
       <c r="N277" s="2"/>
-      <c r="O277" s="19"/>
+      <c r="O277" s="9"/>
     </row>
     <row r="278" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C278" s="2"/>
@@ -5019,7 +5021,7 @@
       <c r="L278" s="2"/>
       <c r="M278" s="2"/>
       <c r="N278" s="2"/>
-      <c r="O278" s="19"/>
+      <c r="O278" s="9"/>
     </row>
     <row r="279" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C279" s="2"/>
@@ -5034,7 +5036,7 @@
       <c r="L279" s="2"/>
       <c r="M279" s="2"/>
       <c r="N279" s="2"/>
-      <c r="O279" s="19"/>
+      <c r="O279" s="9"/>
     </row>
     <row r="280" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C280" s="2"/>
@@ -5049,7 +5051,7 @@
       <c r="L280" s="2"/>
       <c r="M280" s="2"/>
       <c r="N280" s="2"/>
-      <c r="O280" s="19"/>
+      <c r="O280" s="9"/>
     </row>
     <row r="281" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C281" s="2"/>
@@ -5064,7 +5066,7 @@
       <c r="L281" s="2"/>
       <c r="M281" s="2"/>
       <c r="N281" s="2"/>
-      <c r="O281" s="19"/>
+      <c r="O281" s="9"/>
     </row>
     <row r="282" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C282" s="2"/>
@@ -5079,7 +5081,7 @@
       <c r="L282" s="2"/>
       <c r="M282" s="2"/>
       <c r="N282" s="2"/>
-      <c r="O282" s="19"/>
+      <c r="O282" s="9"/>
     </row>
     <row r="283" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C283" s="2"/>
@@ -5094,7 +5096,7 @@
       <c r="L283" s="2"/>
       <c r="M283" s="2"/>
       <c r="N283" s="2"/>
-      <c r="O283" s="19"/>
+      <c r="O283" s="9"/>
     </row>
     <row r="284" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C284" s="2"/>
@@ -5109,7 +5111,7 @@
       <c r="L284" s="2"/>
       <c r="M284" s="2"/>
       <c r="N284" s="2"/>
-      <c r="O284" s="19"/>
+      <c r="O284" s="9"/>
     </row>
     <row r="285" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C285" s="2"/>
@@ -5124,7 +5126,7 @@
       <c r="L285" s="2"/>
       <c r="M285" s="2"/>
       <c r="N285" s="2"/>
-      <c r="O285" s="19"/>
+      <c r="O285" s="9"/>
     </row>
     <row r="286" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C286" s="2"/>
@@ -5139,7 +5141,7 @@
       <c r="L286" s="2"/>
       <c r="M286" s="2"/>
       <c r="N286" s="2"/>
-      <c r="O286" s="19"/>
+      <c r="O286" s="9"/>
     </row>
     <row r="287" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C287" s="2"/>
@@ -5154,7 +5156,7 @@
       <c r="L287" s="2"/>
       <c r="M287" s="2"/>
       <c r="N287" s="2"/>
-      <c r="O287" s="19"/>
+      <c r="O287" s="9"/>
     </row>
     <row r="288" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C288" s="2"/>
@@ -5169,7 +5171,7 @@
       <c r="L288" s="2"/>
       <c r="M288" s="2"/>
       <c r="N288" s="2"/>
-      <c r="O288" s="19"/>
+      <c r="O288" s="9"/>
     </row>
     <row r="289" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C289" s="2"/>
@@ -5184,7 +5186,7 @@
       <c r="L289" s="2"/>
       <c r="M289" s="2"/>
       <c r="N289" s="2"/>
-      <c r="O289" s="19"/>
+      <c r="O289" s="9"/>
     </row>
     <row r="290" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C290" s="2"/>
@@ -5199,7 +5201,7 @@
       <c r="L290" s="2"/>
       <c r="M290" s="2"/>
       <c r="N290" s="2"/>
-      <c r="O290" s="19"/>
+      <c r="O290" s="9"/>
     </row>
     <row r="291" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C291" s="2"/>
@@ -5214,7 +5216,7 @@
       <c r="L291" s="2"/>
       <c r="M291" s="2"/>
       <c r="N291" s="2"/>
-      <c r="O291" s="19"/>
+      <c r="O291" s="9"/>
     </row>
     <row r="292" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C292" s="2"/>
@@ -5229,7 +5231,7 @@
       <c r="L292" s="2"/>
       <c r="M292" s="2"/>
       <c r="N292" s="2"/>
-      <c r="O292" s="19"/>
+      <c r="O292" s="9"/>
     </row>
     <row r="293" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C293" s="2"/>
@@ -5244,7 +5246,7 @@
       <c r="L293" s="2"/>
       <c r="M293" s="2"/>
       <c r="N293" s="2"/>
-      <c r="O293" s="19"/>
+      <c r="O293" s="9"/>
     </row>
     <row r="294" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C294" s="2"/>
@@ -5259,7 +5261,7 @@
       <c r="L294" s="2"/>
       <c r="M294" s="2"/>
       <c r="N294" s="2"/>
-      <c r="O294" s="19"/>
+      <c r="O294" s="9"/>
     </row>
     <row r="295" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C295" s="2"/>
@@ -5274,7 +5276,7 @@
       <c r="L295" s="2"/>
       <c r="M295" s="2"/>
       <c r="N295" s="2"/>
-      <c r="O295" s="19"/>
+      <c r="O295" s="9"/>
     </row>
     <row r="296" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C296" s="2"/>
@@ -5289,7 +5291,7 @@
       <c r="L296" s="2"/>
       <c r="M296" s="2"/>
       <c r="N296" s="2"/>
-      <c r="O296" s="19"/>
+      <c r="O296" s="9"/>
     </row>
     <row r="297" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C297" s="2"/>
@@ -5304,7 +5306,7 @@
       <c r="L297" s="2"/>
       <c r="M297" s="2"/>
       <c r="N297" s="2"/>
-      <c r="O297" s="19"/>
+      <c r="O297" s="9"/>
     </row>
     <row r="298" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C298" s="2"/>
@@ -5319,7 +5321,7 @@
       <c r="L298" s="2"/>
       <c r="M298" s="2"/>
       <c r="N298" s="2"/>
-      <c r="O298" s="19"/>
+      <c r="O298" s="9"/>
     </row>
     <row r="299" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C299" s="2"/>
@@ -5334,7 +5336,7 @@
       <c r="L299" s="2"/>
       <c r="M299" s="2"/>
       <c r="N299" s="2"/>
-      <c r="O299" s="19"/>
+      <c r="O299" s="9"/>
     </row>
     <row r="300" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C300" s="2"/>
@@ -5349,7 +5351,7 @@
       <c r="L300" s="2"/>
       <c r="M300" s="2"/>
       <c r="N300" s="2"/>
-      <c r="O300" s="19"/>
+      <c r="O300" s="9"/>
     </row>
     <row r="301" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C301" s="2"/>
@@ -5364,7 +5366,7 @@
       <c r="L301" s="2"/>
       <c r="M301" s="2"/>
       <c r="N301" s="2"/>
-      <c r="O301" s="19"/>
+      <c r="O301" s="9"/>
     </row>
     <row r="302" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C302" s="2"/>
@@ -5379,7 +5381,7 @@
       <c r="L302" s="2"/>
       <c r="M302" s="2"/>
       <c r="N302" s="2"/>
-      <c r="O302" s="19"/>
+      <c r="O302" s="9"/>
     </row>
     <row r="303" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C303" s="2"/>
@@ -5394,7 +5396,7 @@
       <c r="L303" s="2"/>
       <c r="M303" s="2"/>
       <c r="N303" s="2"/>
-      <c r="O303" s="19"/>
+      <c r="O303" s="9"/>
     </row>
     <row r="304" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C304" s="2"/>
@@ -5409,7 +5411,7 @@
       <c r="L304" s="2"/>
       <c r="M304" s="2"/>
       <c r="N304" s="2"/>
-      <c r="O304" s="19"/>
+      <c r="O304" s="9"/>
     </row>
     <row r="305" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C305" s="2"/>
@@ -5424,7 +5426,7 @@
       <c r="L305" s="2"/>
       <c r="M305" s="2"/>
       <c r="N305" s="2"/>
-      <c r="O305" s="19"/>
+      <c r="O305" s="9"/>
     </row>
     <row r="306" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C306" s="2"/>
@@ -5439,7 +5441,7 @@
       <c r="L306" s="2"/>
       <c r="M306" s="2"/>
       <c r="N306" s="2"/>
-      <c r="O306" s="19"/>
+      <c r="O306" s="9"/>
     </row>
     <row r="307" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C307" s="2"/>
@@ -5454,7 +5456,7 @@
       <c r="L307" s="2"/>
       <c r="M307" s="2"/>
       <c r="N307" s="2"/>
-      <c r="O307" s="19"/>
+      <c r="O307" s="9"/>
     </row>
     <row r="308" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C308" s="2"/>
@@ -5469,7 +5471,7 @@
       <c r="L308" s="2"/>
       <c r="M308" s="2"/>
       <c r="N308" s="2"/>
-      <c r="O308" s="19"/>
+      <c r="O308" s="9"/>
     </row>
     <row r="309" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C309" s="2"/>
@@ -5484,7 +5486,7 @@
       <c r="L309" s="2"/>
       <c r="M309" s="2"/>
       <c r="N309" s="2"/>
-      <c r="O309" s="19"/>
+      <c r="O309" s="9"/>
     </row>
     <row r="310" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C310" s="2"/>
@@ -5499,7 +5501,7 @@
       <c r="L310" s="2"/>
       <c r="M310" s="2"/>
       <c r="N310" s="2"/>
-      <c r="O310" s="19"/>
+      <c r="O310" s="9"/>
     </row>
     <row r="311" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C311" s="2"/>
@@ -5514,7 +5516,7 @@
       <c r="L311" s="2"/>
       <c r="M311" s="2"/>
       <c r="N311" s="2"/>
-      <c r="O311" s="19"/>
+      <c r="O311" s="9"/>
     </row>
     <row r="312" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C312" s="2"/>
@@ -5529,7 +5531,7 @@
       <c r="L312" s="2"/>
       <c r="M312" s="2"/>
       <c r="N312" s="2"/>
-      <c r="O312" s="19"/>
+      <c r="O312" s="9"/>
     </row>
     <row r="313" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C313" s="2"/>
@@ -5544,7 +5546,7 @@
       <c r="L313" s="2"/>
       <c r="M313" s="2"/>
       <c r="N313" s="2"/>
-      <c r="O313" s="19"/>
+      <c r="O313" s="9"/>
     </row>
     <row r="314" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C314" s="2"/>
@@ -5559,7 +5561,7 @@
       <c r="L314" s="2"/>
       <c r="M314" s="2"/>
       <c r="N314" s="2"/>
-      <c r="O314" s="19"/>
+      <c r="O314" s="9"/>
     </row>
     <row r="315" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C315" s="2"/>
@@ -5574,7 +5576,7 @@
       <c r="L315" s="2"/>
       <c r="M315" s="2"/>
       <c r="N315" s="2"/>
-      <c r="O315" s="19"/>
+      <c r="O315" s="9"/>
     </row>
     <row r="316" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C316" s="2"/>
@@ -5589,7 +5591,7 @@
       <c r="L316" s="2"/>
       <c r="M316" s="2"/>
       <c r="N316" s="2"/>
-      <c r="O316" s="19"/>
+      <c r="O316" s="9"/>
     </row>
     <row r="317" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C317" s="2"/>
@@ -5604,7 +5606,7 @@
       <c r="L317" s="2"/>
       <c r="M317" s="2"/>
       <c r="N317" s="2"/>
-      <c r="O317" s="19"/>
+      <c r="O317" s="9"/>
     </row>
     <row r="318" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C318" s="2"/>
@@ -5619,7 +5621,7 @@
       <c r="L318" s="2"/>
       <c r="M318" s="2"/>
       <c r="N318" s="2"/>
-      <c r="O318" s="19"/>
+      <c r="O318" s="9"/>
     </row>
     <row r="319" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C319" s="2"/>
@@ -5634,7 +5636,7 @@
       <c r="L319" s="2"/>
       <c r="M319" s="2"/>
       <c r="N319" s="2"/>
-      <c r="O319" s="19"/>
+      <c r="O319" s="9"/>
     </row>
     <row r="320" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C320" s="2"/>
@@ -5649,7 +5651,7 @@
       <c r="L320" s="2"/>
       <c r="M320" s="2"/>
       <c r="N320" s="2"/>
-      <c r="O320" s="19"/>
+      <c r="O320" s="9"/>
     </row>
     <row r="321" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C321" s="2"/>
@@ -5664,7 +5666,7 @@
       <c r="L321" s="2"/>
       <c r="M321" s="2"/>
       <c r="N321" s="2"/>
-      <c r="O321" s="19"/>
+      <c r="O321" s="9"/>
     </row>
     <row r="322" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C322" s="2"/>
@@ -5679,7 +5681,7 @@
       <c r="L322" s="2"/>
       <c r="M322" s="2"/>
       <c r="N322" s="2"/>
-      <c r="O322" s="19"/>
+      <c r="O322" s="9"/>
     </row>
     <row r="323" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C323" s="2"/>
@@ -5694,7 +5696,7 @@
       <c r="L323" s="2"/>
       <c r="M323" s="2"/>
       <c r="N323" s="2"/>
-      <c r="O323" s="19"/>
+      <c r="O323" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/templates/vacation_map_template.xlsx
+++ b/templates/vacation_map_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geral\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B973D284-DFA9-427C-8AE4-A1AD7844636B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C58B953A-079F-4A0D-A29B-AA2FD4BEE4EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B7894565-86C4-4C3D-8BBD-69A912659748}"/>
   </bookViews>
@@ -97,13 +97,13 @@
     <t>Nif: 500 926 352</t>
   </si>
   <si>
-    <t>Qtd. Dias Úteis</t>
-  </si>
-  <si>
     <t>O PRESIDENTE</t>
   </si>
   <si>
     <t>O COMANDANTE</t>
+  </si>
+  <si>
+    <t>Dias Úteis</t>
   </si>
 </sst>
 </file>
@@ -401,22 +401,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -466,6 +454,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -844,15 +844,15 @@
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.85546875" customWidth="1"/>
-    <col min="2" max="2" width="28.5703125" customWidth="1"/>
-    <col min="3" max="14" width="16.42578125" style="1" customWidth="1"/>
-    <col min="15" max="15" width="10" style="7" customWidth="1"/>
+    <col min="2" max="2" width="24.28515625" customWidth="1"/>
+    <col min="3" max="14" width="17.140625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="10" style="4" customWidth="1"/>
     <col min="16" max="16" width="2.85546875" customWidth="1"/>
     <col min="17" max="16384" width="9.140625" hidden="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="3" t="s">
         <v>13</v>
       </c>
     </row>
@@ -862,761 +862,761 @@
       </c>
     </row>
     <row r="4" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="10" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="6" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B6" s="15"/>
-      <c r="C6" s="15"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="15"/>
-      <c r="G6" s="15"/>
-      <c r="H6" s="15"/>
-      <c r="I6" s="15"/>
-      <c r="J6" s="15"/>
-      <c r="K6" s="15"/>
-      <c r="L6" s="15"/>
-      <c r="M6" s="15"/>
-      <c r="N6" s="15"/>
-      <c r="O6" s="15"/>
+      <c r="B6" s="11"/>
+      <c r="C6" s="11"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="11"/>
+      <c r="M6" s="11"/>
+      <c r="N6" s="11"/>
+      <c r="O6" s="11"/>
     </row>
     <row r="7" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B7" s="15"/>
-      <c r="C7" s="15"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
-      <c r="F7" s="15"/>
-      <c r="G7" s="15"/>
-      <c r="H7" s="15"/>
-      <c r="I7" s="15"/>
-      <c r="J7" s="15"/>
-      <c r="K7" s="15"/>
-      <c r="L7" s="15"/>
-      <c r="M7" s="15"/>
-      <c r="N7" s="15"/>
-      <c r="O7" s="15"/>
+      <c r="B7" s="11"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="11"/>
+      <c r="J7" s="11"/>
+      <c r="K7" s="11"/>
+      <c r="L7" s="11"/>
+      <c r="M7" s="11"/>
+      <c r="N7" s="11"/>
+      <c r="O7" s="11"/>
     </row>
     <row r="8" spans="2:15" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9" spans="2:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="3" t="s">
+    <row r="9" spans="2:15" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="F9" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="G9" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="H9" s="4" t="s">
+      <c r="H9" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="I9" s="4" t="s">
+      <c r="I9" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="J9" s="4" t="s">
+      <c r="J9" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="K9" s="4" t="s">
+      <c r="K9" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="L9" s="4" t="s">
+      <c r="L9" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="M9" s="4" t="s">
+      <c r="M9" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="N9" s="5" t="s">
+      <c r="N9" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="O9" s="8" t="s">
+      <c r="O9" s="25" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B10" s="14"/>
+      <c r="C10" s="15"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="15"/>
+      <c r="H10" s="15"/>
+      <c r="I10" s="15"/>
+      <c r="J10" s="15"/>
+      <c r="K10" s="15"/>
+      <c r="L10" s="15"/>
+      <c r="M10" s="15"/>
+      <c r="N10" s="16"/>
+      <c r="O10" s="17"/>
+    </row>
+    <row r="11" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B11" s="14"/>
+      <c r="C11" s="15"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="15"/>
+      <c r="G11" s="15"/>
+      <c r="H11" s="15"/>
+      <c r="I11" s="15"/>
+      <c r="J11" s="15"/>
+      <c r="K11" s="15"/>
+      <c r="L11" s="15"/>
+      <c r="M11" s="15"/>
+      <c r="N11" s="16"/>
+      <c r="O11" s="17"/>
+    </row>
+    <row r="12" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B12" s="14"/>
+      <c r="C12" s="15"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="15"/>
+      <c r="G12" s="15"/>
+      <c r="H12" s="15"/>
+      <c r="I12" s="15"/>
+      <c r="J12" s="15"/>
+      <c r="K12" s="15"/>
+      <c r="L12" s="15"/>
+      <c r="M12" s="15"/>
+      <c r="N12" s="16"/>
+      <c r="O12" s="17"/>
+    </row>
+    <row r="13" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B13" s="14"/>
+      <c r="C13" s="15"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="15"/>
+      <c r="H13" s="15"/>
+      <c r="I13" s="15"/>
+      <c r="J13" s="15"/>
+      <c r="K13" s="15"/>
+      <c r="L13" s="15"/>
+      <c r="M13" s="15"/>
+      <c r="N13" s="16"/>
+      <c r="O13" s="17"/>
+    </row>
+    <row r="14" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B14" s="14"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="15"/>
+      <c r="H14" s="15"/>
+      <c r="I14" s="15"/>
+      <c r="J14" s="15"/>
+      <c r="K14" s="15"/>
+      <c r="L14" s="15"/>
+      <c r="M14" s="15"/>
+      <c r="N14" s="16"/>
+      <c r="O14" s="17"/>
+    </row>
+    <row r="15" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B15" s="14"/>
+      <c r="C15" s="15"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="15"/>
+      <c r="H15" s="15"/>
+      <c r="I15" s="15"/>
+      <c r="J15" s="15"/>
+      <c r="K15" s="15"/>
+      <c r="L15" s="15"/>
+      <c r="M15" s="15"/>
+      <c r="N15" s="16"/>
+      <c r="O15" s="17"/>
+    </row>
+    <row r="16" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B16" s="14"/>
+      <c r="C16" s="15"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="15"/>
+      <c r="G16" s="15"/>
+      <c r="H16" s="15"/>
+      <c r="I16" s="15"/>
+      <c r="J16" s="15"/>
+      <c r="K16" s="15"/>
+      <c r="L16" s="15"/>
+      <c r="M16" s="15"/>
+      <c r="N16" s="16"/>
+      <c r="O16" s="17"/>
+    </row>
+    <row r="17" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B17" s="14"/>
+      <c r="C17" s="15"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="15"/>
+      <c r="G17" s="15"/>
+      <c r="H17" s="15"/>
+      <c r="I17" s="15"/>
+      <c r="J17" s="15"/>
+      <c r="K17" s="15"/>
+      <c r="L17" s="15"/>
+      <c r="M17" s="15"/>
+      <c r="N17" s="16"/>
+      <c r="O17" s="17"/>
+    </row>
+    <row r="18" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B18" s="14"/>
+      <c r="C18" s="15"/>
+      <c r="D18" s="15"/>
+      <c r="E18" s="15"/>
+      <c r="F18" s="15"/>
+      <c r="G18" s="15"/>
+      <c r="H18" s="15"/>
+      <c r="I18" s="15"/>
+      <c r="J18" s="15"/>
+      <c r="K18" s="15"/>
+      <c r="L18" s="15"/>
+      <c r="M18" s="15"/>
+      <c r="N18" s="16"/>
+      <c r="O18" s="17"/>
+    </row>
+    <row r="19" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B19" s="14"/>
+      <c r="C19" s="15"/>
+      <c r="D19" s="15"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="15"/>
+      <c r="G19" s="15"/>
+      <c r="H19" s="15"/>
+      <c r="I19" s="15"/>
+      <c r="J19" s="15"/>
+      <c r="K19" s="15"/>
+      <c r="L19" s="15"/>
+      <c r="M19" s="15"/>
+      <c r="N19" s="16"/>
+      <c r="O19" s="17"/>
+    </row>
+    <row r="20" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B20" s="14"/>
+      <c r="C20" s="15"/>
+      <c r="D20" s="15"/>
+      <c r="E20" s="15"/>
+      <c r="F20" s="15"/>
+      <c r="G20" s="15"/>
+      <c r="H20" s="15"/>
+      <c r="I20" s="15"/>
+      <c r="J20" s="15"/>
+      <c r="K20" s="15"/>
+      <c r="L20" s="15"/>
+      <c r="M20" s="15"/>
+      <c r="N20" s="16"/>
+      <c r="O20" s="17"/>
+    </row>
+    <row r="21" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B21" s="14"/>
+      <c r="C21" s="15"/>
+      <c r="D21" s="15"/>
+      <c r="E21" s="15"/>
+      <c r="F21" s="15"/>
+      <c r="G21" s="15"/>
+      <c r="H21" s="15"/>
+      <c r="I21" s="15"/>
+      <c r="J21" s="15"/>
+      <c r="K21" s="15"/>
+      <c r="L21" s="15"/>
+      <c r="M21" s="15"/>
+      <c r="N21" s="16"/>
+      <c r="O21" s="17"/>
+    </row>
+    <row r="22" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B22" s="14"/>
+      <c r="C22" s="15"/>
+      <c r="D22" s="15"/>
+      <c r="E22" s="15"/>
+      <c r="F22" s="15"/>
+      <c r="G22" s="15"/>
+      <c r="H22" s="15"/>
+      <c r="I22" s="15"/>
+      <c r="J22" s="15"/>
+      <c r="K22" s="15"/>
+      <c r="L22" s="15"/>
+      <c r="M22" s="15"/>
+      <c r="N22" s="16"/>
+      <c r="O22" s="17"/>
+    </row>
+    <row r="23" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B23" s="14"/>
+      <c r="C23" s="15"/>
+      <c r="D23" s="15"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="15"/>
+      <c r="G23" s="15"/>
+      <c r="H23" s="15"/>
+      <c r="I23" s="15"/>
+      <c r="J23" s="15"/>
+      <c r="K23" s="15"/>
+      <c r="L23" s="15"/>
+      <c r="M23" s="15"/>
+      <c r="N23" s="16"/>
+      <c r="O23" s="17"/>
+    </row>
+    <row r="24" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B24" s="14"/>
+      <c r="C24" s="15"/>
+      <c r="D24" s="15"/>
+      <c r="E24" s="15"/>
+      <c r="F24" s="15"/>
+      <c r="G24" s="15"/>
+      <c r="H24" s="15"/>
+      <c r="I24" s="15"/>
+      <c r="J24" s="15"/>
+      <c r="K24" s="15"/>
+      <c r="L24" s="15"/>
+      <c r="M24" s="15"/>
+      <c r="N24" s="16"/>
+      <c r="O24" s="17"/>
+    </row>
+    <row r="25" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B25" s="14"/>
+      <c r="C25" s="15"/>
+      <c r="D25" s="15"/>
+      <c r="E25" s="15"/>
+      <c r="F25" s="15"/>
+      <c r="G25" s="15"/>
+      <c r="H25" s="15"/>
+      <c r="I25" s="15"/>
+      <c r="J25" s="15"/>
+      <c r="K25" s="15"/>
+      <c r="L25" s="15"/>
+      <c r="M25" s="15"/>
+      <c r="N25" s="16"/>
+      <c r="O25" s="17"/>
+    </row>
+    <row r="26" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B26" s="14"/>
+      <c r="C26" s="15"/>
+      <c r="D26" s="15"/>
+      <c r="E26" s="15"/>
+      <c r="F26" s="15"/>
+      <c r="G26" s="15"/>
+      <c r="H26" s="15"/>
+      <c r="I26" s="15"/>
+      <c r="J26" s="15"/>
+      <c r="K26" s="15"/>
+      <c r="L26" s="15"/>
+      <c r="M26" s="15"/>
+      <c r="N26" s="16"/>
+      <c r="O26" s="17"/>
+    </row>
+    <row r="27" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B27" s="14"/>
+      <c r="C27" s="15"/>
+      <c r="D27" s="15"/>
+      <c r="E27" s="15"/>
+      <c r="F27" s="15"/>
+      <c r="G27" s="15"/>
+      <c r="H27" s="15"/>
+      <c r="I27" s="15"/>
+      <c r="J27" s="15"/>
+      <c r="K27" s="15"/>
+      <c r="L27" s="15"/>
+      <c r="M27" s="15"/>
+      <c r="N27" s="16"/>
+      <c r="O27" s="17"/>
+    </row>
+    <row r="28" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B28" s="14"/>
+      <c r="C28" s="15"/>
+      <c r="D28" s="15"/>
+      <c r="E28" s="15"/>
+      <c r="F28" s="15"/>
+      <c r="G28" s="15"/>
+      <c r="H28" s="15"/>
+      <c r="I28" s="15"/>
+      <c r="J28" s="15"/>
+      <c r="K28" s="15"/>
+      <c r="L28" s="15"/>
+      <c r="M28" s="15"/>
+      <c r="N28" s="16"/>
+      <c r="O28" s="17"/>
+    </row>
+    <row r="29" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B29" s="14"/>
+      <c r="C29" s="15"/>
+      <c r="D29" s="15"/>
+      <c r="E29" s="15"/>
+      <c r="F29" s="15"/>
+      <c r="G29" s="15"/>
+      <c r="H29" s="15"/>
+      <c r="I29" s="15"/>
+      <c r="J29" s="15"/>
+      <c r="K29" s="15"/>
+      <c r="L29" s="15"/>
+      <c r="M29" s="15"/>
+      <c r="N29" s="16"/>
+      <c r="O29" s="17"/>
+    </row>
+    <row r="30" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B30" s="14"/>
+      <c r="C30" s="15"/>
+      <c r="D30" s="15"/>
+      <c r="E30" s="15"/>
+      <c r="F30" s="15"/>
+      <c r="G30" s="15"/>
+      <c r="H30" s="15"/>
+      <c r="I30" s="15"/>
+      <c r="J30" s="15"/>
+      <c r="K30" s="15"/>
+      <c r="L30" s="15"/>
+      <c r="M30" s="15"/>
+      <c r="N30" s="16"/>
+      <c r="O30" s="17"/>
+    </row>
+    <row r="31" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B31" s="14"/>
+      <c r="C31" s="15"/>
+      <c r="D31" s="15"/>
+      <c r="E31" s="15"/>
+      <c r="F31" s="15"/>
+      <c r="G31" s="15"/>
+      <c r="H31" s="15"/>
+      <c r="I31" s="15"/>
+      <c r="J31" s="15"/>
+      <c r="K31" s="15"/>
+      <c r="L31" s="15"/>
+      <c r="M31" s="15"/>
+      <c r="N31" s="16"/>
+      <c r="O31" s="17"/>
+    </row>
+    <row r="32" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B32" s="14"/>
+      <c r="C32" s="15"/>
+      <c r="D32" s="15"/>
+      <c r="E32" s="15"/>
+      <c r="F32" s="15"/>
+      <c r="G32" s="15"/>
+      <c r="H32" s="15"/>
+      <c r="I32" s="15"/>
+      <c r="J32" s="15"/>
+      <c r="K32" s="15"/>
+      <c r="L32" s="15"/>
+      <c r="M32" s="15"/>
+      <c r="N32" s="16"/>
+      <c r="O32" s="17"/>
+    </row>
+    <row r="33" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B33" s="14"/>
+      <c r="C33" s="15"/>
+      <c r="D33" s="15"/>
+      <c r="E33" s="15"/>
+      <c r="F33" s="15"/>
+      <c r="G33" s="15"/>
+      <c r="H33" s="15"/>
+      <c r="I33" s="15"/>
+      <c r="J33" s="15"/>
+      <c r="K33" s="15"/>
+      <c r="L33" s="15"/>
+      <c r="M33" s="15"/>
+      <c r="N33" s="16"/>
+      <c r="O33" s="17"/>
+    </row>
+    <row r="34" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B34" s="14"/>
+      <c r="C34" s="15"/>
+      <c r="D34" s="15"/>
+      <c r="E34" s="15"/>
+      <c r="F34" s="15"/>
+      <c r="G34" s="15"/>
+      <c r="H34" s="15"/>
+      <c r="I34" s="15"/>
+      <c r="J34" s="15"/>
+      <c r="K34" s="15"/>
+      <c r="L34" s="15"/>
+      <c r="M34" s="15"/>
+      <c r="N34" s="16"/>
+      <c r="O34" s="17"/>
+    </row>
+    <row r="35" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B35" s="14"/>
+      <c r="C35" s="15"/>
+      <c r="D35" s="15"/>
+      <c r="E35" s="15"/>
+      <c r="F35" s="15"/>
+      <c r="G35" s="15"/>
+      <c r="H35" s="15"/>
+      <c r="I35" s="15"/>
+      <c r="J35" s="15"/>
+      <c r="K35" s="15"/>
+      <c r="L35" s="15"/>
+      <c r="M35" s="15"/>
+      <c r="N35" s="16"/>
+      <c r="O35" s="17"/>
+    </row>
+    <row r="36" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B36" s="14"/>
+      <c r="C36" s="15"/>
+      <c r="D36" s="15"/>
+      <c r="E36" s="15"/>
+      <c r="F36" s="15"/>
+      <c r="G36" s="15"/>
+      <c r="H36" s="15"/>
+      <c r="I36" s="15"/>
+      <c r="J36" s="15"/>
+      <c r="K36" s="15"/>
+      <c r="L36" s="15"/>
+      <c r="M36" s="15"/>
+      <c r="N36" s="16"/>
+      <c r="O36" s="17"/>
+    </row>
+    <row r="37" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B37" s="14"/>
+      <c r="C37" s="15"/>
+      <c r="D37" s="15"/>
+      <c r="E37" s="15"/>
+      <c r="F37" s="15"/>
+      <c r="G37" s="15"/>
+      <c r="H37" s="15"/>
+      <c r="I37" s="15"/>
+      <c r="J37" s="15"/>
+      <c r="K37" s="15"/>
+      <c r="L37" s="15"/>
+      <c r="M37" s="15"/>
+      <c r="N37" s="16"/>
+      <c r="O37" s="17"/>
+    </row>
+    <row r="38" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B38" s="14"/>
+      <c r="C38" s="15"/>
+      <c r="D38" s="15"/>
+      <c r="E38" s="15"/>
+      <c r="F38" s="15"/>
+      <c r="G38" s="15"/>
+      <c r="H38" s="15"/>
+      <c r="I38" s="15"/>
+      <c r="J38" s="15"/>
+      <c r="K38" s="15"/>
+      <c r="L38" s="15"/>
+      <c r="M38" s="15"/>
+      <c r="N38" s="16"/>
+      <c r="O38" s="17"/>
+    </row>
+    <row r="39" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B39" s="14"/>
+      <c r="C39" s="15"/>
+      <c r="D39" s="15"/>
+      <c r="E39" s="15"/>
+      <c r="F39" s="15"/>
+      <c r="G39" s="15"/>
+      <c r="H39" s="15"/>
+      <c r="I39" s="15"/>
+      <c r="J39" s="15"/>
+      <c r="K39" s="15"/>
+      <c r="L39" s="15"/>
+      <c r="M39" s="15"/>
+      <c r="N39" s="16"/>
+      <c r="O39" s="17"/>
+    </row>
+    <row r="40" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B40" s="14"/>
+      <c r="C40" s="15"/>
+      <c r="D40" s="15"/>
+      <c r="E40" s="15"/>
+      <c r="F40" s="15"/>
+      <c r="G40" s="15"/>
+      <c r="H40" s="15"/>
+      <c r="I40" s="15"/>
+      <c r="J40" s="15"/>
+      <c r="K40" s="15"/>
+      <c r="L40" s="15"/>
+      <c r="M40" s="15"/>
+      <c r="N40" s="16"/>
+      <c r="O40" s="17"/>
+    </row>
+    <row r="41" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B41" s="14"/>
+      <c r="C41" s="15"/>
+      <c r="D41" s="15"/>
+      <c r="E41" s="15"/>
+      <c r="F41" s="15"/>
+      <c r="G41" s="15"/>
+      <c r="H41" s="15"/>
+      <c r="I41" s="15"/>
+      <c r="J41" s="15"/>
+      <c r="K41" s="15"/>
+      <c r="L41" s="15"/>
+      <c r="M41" s="15"/>
+      <c r="N41" s="16"/>
+      <c r="O41" s="17"/>
+    </row>
+    <row r="42" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B42" s="14"/>
+      <c r="C42" s="15"/>
+      <c r="D42" s="15"/>
+      <c r="E42" s="15"/>
+      <c r="F42" s="15"/>
+      <c r="G42" s="15"/>
+      <c r="H42" s="15"/>
+      <c r="I42" s="15"/>
+      <c r="J42" s="15"/>
+      <c r="K42" s="15"/>
+      <c r="L42" s="15"/>
+      <c r="M42" s="15"/>
+      <c r="N42" s="16"/>
+      <c r="O42" s="17"/>
+    </row>
+    <row r="43" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B43" s="14"/>
+      <c r="C43" s="15"/>
+      <c r="D43" s="15"/>
+      <c r="E43" s="15"/>
+      <c r="F43" s="15"/>
+      <c r="G43" s="15"/>
+      <c r="H43" s="15"/>
+      <c r="I43" s="15"/>
+      <c r="J43" s="15"/>
+      <c r="K43" s="15"/>
+      <c r="L43" s="15"/>
+      <c r="M43" s="15"/>
+      <c r="N43" s="16"/>
+      <c r="O43" s="17"/>
+    </row>
+    <row r="44" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B44" s="14"/>
+      <c r="C44" s="15"/>
+      <c r="D44" s="15"/>
+      <c r="E44" s="15"/>
+      <c r="F44" s="15"/>
+      <c r="G44" s="15"/>
+      <c r="H44" s="15"/>
+      <c r="I44" s="15"/>
+      <c r="J44" s="15"/>
+      <c r="K44" s="15"/>
+      <c r="L44" s="15"/>
+      <c r="M44" s="15"/>
+      <c r="N44" s="16"/>
+      <c r="O44" s="17"/>
+    </row>
+    <row r="45" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B45" s="14"/>
+      <c r="C45" s="15"/>
+      <c r="D45" s="15"/>
+      <c r="E45" s="15"/>
+      <c r="F45" s="15"/>
+      <c r="G45" s="15"/>
+      <c r="H45" s="15"/>
+      <c r="I45" s="15"/>
+      <c r="J45" s="15"/>
+      <c r="K45" s="15"/>
+      <c r="L45" s="15"/>
+      <c r="M45" s="15"/>
+      <c r="N45" s="16"/>
+      <c r="O45" s="17"/>
+    </row>
+    <row r="46" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B46" s="14"/>
+      <c r="C46" s="15"/>
+      <c r="D46" s="15"/>
+      <c r="E46" s="15"/>
+      <c r="F46" s="15"/>
+      <c r="G46" s="15"/>
+      <c r="H46" s="15"/>
+      <c r="I46" s="15"/>
+      <c r="J46" s="15"/>
+      <c r="K46" s="15"/>
+      <c r="L46" s="15"/>
+      <c r="M46" s="15"/>
+      <c r="N46" s="16"/>
+      <c r="O46" s="17"/>
+    </row>
+    <row r="47" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B47" s="14"/>
+      <c r="C47" s="15"/>
+      <c r="D47" s="15"/>
+      <c r="E47" s="15"/>
+      <c r="F47" s="15"/>
+      <c r="G47" s="15"/>
+      <c r="H47" s="15"/>
+      <c r="I47" s="15"/>
+      <c r="J47" s="15"/>
+      <c r="K47" s="15"/>
+      <c r="L47" s="15"/>
+      <c r="M47" s="15"/>
+      <c r="N47" s="16"/>
+      <c r="O47" s="17"/>
+    </row>
+    <row r="48" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B48" s="14"/>
+      <c r="C48" s="15"/>
+      <c r="D48" s="15"/>
+      <c r="E48" s="15"/>
+      <c r="F48" s="15"/>
+      <c r="G48" s="15"/>
+      <c r="H48" s="15"/>
+      <c r="I48" s="15"/>
+      <c r="J48" s="15"/>
+      <c r="K48" s="15"/>
+      <c r="L48" s="15"/>
+      <c r="M48" s="15"/>
+      <c r="N48" s="16"/>
+      <c r="O48" s="17"/>
+    </row>
+    <row r="49" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B49" s="18"/>
+      <c r="C49" s="19"/>
+      <c r="D49" s="19"/>
+      <c r="E49" s="19"/>
+      <c r="F49" s="19"/>
+      <c r="G49" s="19"/>
+      <c r="H49" s="19"/>
+      <c r="I49" s="19"/>
+      <c r="J49" s="19"/>
+      <c r="K49" s="19"/>
+      <c r="L49" s="19"/>
+      <c r="M49" s="19"/>
+      <c r="N49" s="20"/>
+      <c r="O49" s="21"/>
+    </row>
+    <row r="50" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B50" s="6"/>
+      <c r="C50" s="7"/>
+      <c r="D50" s="7"/>
+      <c r="E50" s="7"/>
+      <c r="F50" s="7"/>
+      <c r="G50" s="7"/>
+      <c r="H50" s="7"/>
+      <c r="I50" s="7"/>
+      <c r="J50" s="7"/>
+      <c r="K50" s="7"/>
+      <c r="L50" s="7"/>
+      <c r="M50" s="7"/>
+      <c r="N50" s="7"/>
+      <c r="O50" s="8"/>
+    </row>
+    <row r="51" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="C51" s="2"/>
+      <c r="D51" s="12" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="10" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B10" s="18"/>
-      <c r="C10" s="19"/>
-      <c r="D10" s="19"/>
-      <c r="E10" s="19"/>
-      <c r="F10" s="19"/>
-      <c r="G10" s="19"/>
-      <c r="H10" s="19"/>
-      <c r="I10" s="19"/>
-      <c r="J10" s="19"/>
-      <c r="K10" s="19"/>
-      <c r="L10" s="19"/>
-      <c r="M10" s="19"/>
-      <c r="N10" s="20"/>
-      <c r="O10" s="21"/>
-    </row>
-    <row r="11" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B11" s="18"/>
-      <c r="C11" s="19"/>
-      <c r="D11" s="19"/>
-      <c r="E11" s="19"/>
-      <c r="F11" s="19"/>
-      <c r="G11" s="19"/>
-      <c r="H11" s="19"/>
-      <c r="I11" s="19"/>
-      <c r="J11" s="19"/>
-      <c r="K11" s="19"/>
-      <c r="L11" s="19"/>
-      <c r="M11" s="19"/>
-      <c r="N11" s="20"/>
-      <c r="O11" s="21"/>
-    </row>
-    <row r="12" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B12" s="18"/>
-      <c r="C12" s="19"/>
-      <c r="D12" s="19"/>
-      <c r="E12" s="19"/>
-      <c r="F12" s="19"/>
-      <c r="G12" s="19"/>
-      <c r="H12" s="19"/>
-      <c r="I12" s="19"/>
-      <c r="J12" s="19"/>
-      <c r="K12" s="19"/>
-      <c r="L12" s="19"/>
-      <c r="M12" s="19"/>
-      <c r="N12" s="20"/>
-      <c r="O12" s="21"/>
-    </row>
-    <row r="13" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B13" s="18"/>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="19"/>
-      <c r="G13" s="19"/>
-      <c r="H13" s="19"/>
-      <c r="I13" s="19"/>
-      <c r="J13" s="19"/>
-      <c r="K13" s="19"/>
-      <c r="L13" s="19"/>
-      <c r="M13" s="19"/>
-      <c r="N13" s="20"/>
-      <c r="O13" s="21"/>
-    </row>
-    <row r="14" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B14" s="18"/>
-      <c r="C14" s="19"/>
-      <c r="D14" s="19"/>
-      <c r="E14" s="19"/>
-      <c r="F14" s="19"/>
-      <c r="G14" s="19"/>
-      <c r="H14" s="19"/>
-      <c r="I14" s="19"/>
-      <c r="J14" s="19"/>
-      <c r="K14" s="19"/>
-      <c r="L14" s="19"/>
-      <c r="M14" s="19"/>
-      <c r="N14" s="20"/>
-      <c r="O14" s="21"/>
-    </row>
-    <row r="15" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B15" s="18"/>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="19"/>
-      <c r="F15" s="19"/>
-      <c r="G15" s="19"/>
-      <c r="H15" s="19"/>
-      <c r="I15" s="19"/>
-      <c r="J15" s="19"/>
-      <c r="K15" s="19"/>
-      <c r="L15" s="19"/>
-      <c r="M15" s="19"/>
-      <c r="N15" s="20"/>
-      <c r="O15" s="21"/>
-    </row>
-    <row r="16" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B16" s="18"/>
-      <c r="C16" s="19"/>
-      <c r="D16" s="19"/>
-      <c r="E16" s="19"/>
-      <c r="F16" s="19"/>
-      <c r="G16" s="19"/>
-      <c r="H16" s="19"/>
-      <c r="I16" s="19"/>
-      <c r="J16" s="19"/>
-      <c r="K16" s="19"/>
-      <c r="L16" s="19"/>
-      <c r="M16" s="19"/>
-      <c r="N16" s="20"/>
-      <c r="O16" s="21"/>
-    </row>
-    <row r="17" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B17" s="18"/>
-      <c r="C17" s="19"/>
-      <c r="D17" s="19"/>
-      <c r="E17" s="19"/>
-      <c r="F17" s="19"/>
-      <c r="G17" s="19"/>
-      <c r="H17" s="19"/>
-      <c r="I17" s="19"/>
-      <c r="J17" s="19"/>
-      <c r="K17" s="19"/>
-      <c r="L17" s="19"/>
-      <c r="M17" s="19"/>
-      <c r="N17" s="20"/>
-      <c r="O17" s="21"/>
-    </row>
-    <row r="18" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B18" s="18"/>
-      <c r="C18" s="19"/>
-      <c r="D18" s="19"/>
-      <c r="E18" s="19"/>
-      <c r="F18" s="19"/>
-      <c r="G18" s="19"/>
-      <c r="H18" s="19"/>
-      <c r="I18" s="19"/>
-      <c r="J18" s="19"/>
-      <c r="K18" s="19"/>
-      <c r="L18" s="19"/>
-      <c r="M18" s="19"/>
-      <c r="N18" s="20"/>
-      <c r="O18" s="21"/>
-    </row>
-    <row r="19" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B19" s="18"/>
-      <c r="C19" s="19"/>
-      <c r="D19" s="19"/>
-      <c r="E19" s="19"/>
-      <c r="F19" s="19"/>
-      <c r="G19" s="19"/>
-      <c r="H19" s="19"/>
-      <c r="I19" s="19"/>
-      <c r="J19" s="19"/>
-      <c r="K19" s="19"/>
-      <c r="L19" s="19"/>
-      <c r="M19" s="19"/>
-      <c r="N19" s="20"/>
-      <c r="O19" s="21"/>
-    </row>
-    <row r="20" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B20" s="18"/>
-      <c r="C20" s="19"/>
-      <c r="D20" s="19"/>
-      <c r="E20" s="19"/>
-      <c r="F20" s="19"/>
-      <c r="G20" s="19"/>
-      <c r="H20" s="19"/>
-      <c r="I20" s="19"/>
-      <c r="J20" s="19"/>
-      <c r="K20" s="19"/>
-      <c r="L20" s="19"/>
-      <c r="M20" s="19"/>
-      <c r="N20" s="20"/>
-      <c r="O20" s="21"/>
-    </row>
-    <row r="21" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B21" s="18"/>
-      <c r="C21" s="19"/>
-      <c r="D21" s="19"/>
-      <c r="E21" s="19"/>
-      <c r="F21" s="19"/>
-      <c r="G21" s="19"/>
-      <c r="H21" s="19"/>
-      <c r="I21" s="19"/>
-      <c r="J21" s="19"/>
-      <c r="K21" s="19"/>
-      <c r="L21" s="19"/>
-      <c r="M21" s="19"/>
-      <c r="N21" s="20"/>
-      <c r="O21" s="21"/>
-    </row>
-    <row r="22" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B22" s="18"/>
-      <c r="C22" s="19"/>
-      <c r="D22" s="19"/>
-      <c r="E22" s="19"/>
-      <c r="F22" s="19"/>
-      <c r="G22" s="19"/>
-      <c r="H22" s="19"/>
-      <c r="I22" s="19"/>
-      <c r="J22" s="19"/>
-      <c r="K22" s="19"/>
-      <c r="L22" s="19"/>
-      <c r="M22" s="19"/>
-      <c r="N22" s="20"/>
-      <c r="O22" s="21"/>
-    </row>
-    <row r="23" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B23" s="18"/>
-      <c r="C23" s="19"/>
-      <c r="D23" s="19"/>
-      <c r="E23" s="19"/>
-      <c r="F23" s="19"/>
-      <c r="G23" s="19"/>
-      <c r="H23" s="19"/>
-      <c r="I23" s="19"/>
-      <c r="J23" s="19"/>
-      <c r="K23" s="19"/>
-      <c r="L23" s="19"/>
-      <c r="M23" s="19"/>
-      <c r="N23" s="20"/>
-      <c r="O23" s="21"/>
-    </row>
-    <row r="24" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B24" s="18"/>
-      <c r="C24" s="19"/>
-      <c r="D24" s="19"/>
-      <c r="E24" s="19"/>
-      <c r="F24" s="19"/>
-      <c r="G24" s="19"/>
-      <c r="H24" s="19"/>
-      <c r="I24" s="19"/>
-      <c r="J24" s="19"/>
-      <c r="K24" s="19"/>
-      <c r="L24" s="19"/>
-      <c r="M24" s="19"/>
-      <c r="N24" s="20"/>
-      <c r="O24" s="21"/>
-    </row>
-    <row r="25" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B25" s="18"/>
-      <c r="C25" s="19"/>
-      <c r="D25" s="19"/>
-      <c r="E25" s="19"/>
-      <c r="F25" s="19"/>
-      <c r="G25" s="19"/>
-      <c r="H25" s="19"/>
-      <c r="I25" s="19"/>
-      <c r="J25" s="19"/>
-      <c r="K25" s="19"/>
-      <c r="L25" s="19"/>
-      <c r="M25" s="19"/>
-      <c r="N25" s="20"/>
-      <c r="O25" s="21"/>
-    </row>
-    <row r="26" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B26" s="18"/>
-      <c r="C26" s="19"/>
-      <c r="D26" s="19"/>
-      <c r="E26" s="19"/>
-      <c r="F26" s="19"/>
-      <c r="G26" s="19"/>
-      <c r="H26" s="19"/>
-      <c r="I26" s="19"/>
-      <c r="J26" s="19"/>
-      <c r="K26" s="19"/>
-      <c r="L26" s="19"/>
-      <c r="M26" s="19"/>
-      <c r="N26" s="20"/>
-      <c r="O26" s="21"/>
-    </row>
-    <row r="27" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B27" s="18"/>
-      <c r="C27" s="19"/>
-      <c r="D27" s="19"/>
-      <c r="E27" s="19"/>
-      <c r="F27" s="19"/>
-      <c r="G27" s="19"/>
-      <c r="H27" s="19"/>
-      <c r="I27" s="19"/>
-      <c r="J27" s="19"/>
-      <c r="K27" s="19"/>
-      <c r="L27" s="19"/>
-      <c r="M27" s="19"/>
-      <c r="N27" s="20"/>
-      <c r="O27" s="21"/>
-    </row>
-    <row r="28" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B28" s="18"/>
-      <c r="C28" s="19"/>
-      <c r="D28" s="19"/>
-      <c r="E28" s="19"/>
-      <c r="F28" s="19"/>
-      <c r="G28" s="19"/>
-      <c r="H28" s="19"/>
-      <c r="I28" s="19"/>
-      <c r="J28" s="19"/>
-      <c r="K28" s="19"/>
-      <c r="L28" s="19"/>
-      <c r="M28" s="19"/>
-      <c r="N28" s="20"/>
-      <c r="O28" s="21"/>
-    </row>
-    <row r="29" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B29" s="18"/>
-      <c r="C29" s="19"/>
-      <c r="D29" s="19"/>
-      <c r="E29" s="19"/>
-      <c r="F29" s="19"/>
-      <c r="G29" s="19"/>
-      <c r="H29" s="19"/>
-      <c r="I29" s="19"/>
-      <c r="J29" s="19"/>
-      <c r="K29" s="19"/>
-      <c r="L29" s="19"/>
-      <c r="M29" s="19"/>
-      <c r="N29" s="20"/>
-      <c r="O29" s="21"/>
-    </row>
-    <row r="30" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B30" s="18"/>
-      <c r="C30" s="19"/>
-      <c r="D30" s="19"/>
-      <c r="E30" s="19"/>
-      <c r="F30" s="19"/>
-      <c r="G30" s="19"/>
-      <c r="H30" s="19"/>
-      <c r="I30" s="19"/>
-      <c r="J30" s="19"/>
-      <c r="K30" s="19"/>
-      <c r="L30" s="19"/>
-      <c r="M30" s="19"/>
-      <c r="N30" s="20"/>
-      <c r="O30" s="21"/>
-    </row>
-    <row r="31" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B31" s="18"/>
-      <c r="C31" s="19"/>
-      <c r="D31" s="19"/>
-      <c r="E31" s="19"/>
-      <c r="F31" s="19"/>
-      <c r="G31" s="19"/>
-      <c r="H31" s="19"/>
-      <c r="I31" s="19"/>
-      <c r="J31" s="19"/>
-      <c r="K31" s="19"/>
-      <c r="L31" s="19"/>
-      <c r="M31" s="19"/>
-      <c r="N31" s="20"/>
-      <c r="O31" s="21"/>
-    </row>
-    <row r="32" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B32" s="18"/>
-      <c r="C32" s="19"/>
-      <c r="D32" s="19"/>
-      <c r="E32" s="19"/>
-      <c r="F32" s="19"/>
-      <c r="G32" s="19"/>
-      <c r="H32" s="19"/>
-      <c r="I32" s="19"/>
-      <c r="J32" s="19"/>
-      <c r="K32" s="19"/>
-      <c r="L32" s="19"/>
-      <c r="M32" s="19"/>
-      <c r="N32" s="20"/>
-      <c r="O32" s="21"/>
-    </row>
-    <row r="33" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B33" s="18"/>
-      <c r="C33" s="19"/>
-      <c r="D33" s="19"/>
-      <c r="E33" s="19"/>
-      <c r="F33" s="19"/>
-      <c r="G33" s="19"/>
-      <c r="H33" s="19"/>
-      <c r="I33" s="19"/>
-      <c r="J33" s="19"/>
-      <c r="K33" s="19"/>
-      <c r="L33" s="19"/>
-      <c r="M33" s="19"/>
-      <c r="N33" s="20"/>
-      <c r="O33" s="21"/>
-    </row>
-    <row r="34" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B34" s="18"/>
-      <c r="C34" s="19"/>
-      <c r="D34" s="19"/>
-      <c r="E34" s="19"/>
-      <c r="F34" s="19"/>
-      <c r="G34" s="19"/>
-      <c r="H34" s="19"/>
-      <c r="I34" s="19"/>
-      <c r="J34" s="19"/>
-      <c r="K34" s="19"/>
-      <c r="L34" s="19"/>
-      <c r="M34" s="19"/>
-      <c r="N34" s="20"/>
-      <c r="O34" s="21"/>
-    </row>
-    <row r="35" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B35" s="18"/>
-      <c r="C35" s="19"/>
-      <c r="D35" s="19"/>
-      <c r="E35" s="19"/>
-      <c r="F35" s="19"/>
-      <c r="G35" s="19"/>
-      <c r="H35" s="19"/>
-      <c r="I35" s="19"/>
-      <c r="J35" s="19"/>
-      <c r="K35" s="19"/>
-      <c r="L35" s="19"/>
-      <c r="M35" s="19"/>
-      <c r="N35" s="20"/>
-      <c r="O35" s="21"/>
-    </row>
-    <row r="36" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B36" s="18"/>
-      <c r="C36" s="19"/>
-      <c r="D36" s="19"/>
-      <c r="E36" s="19"/>
-      <c r="F36" s="19"/>
-      <c r="G36" s="19"/>
-      <c r="H36" s="19"/>
-      <c r="I36" s="19"/>
-      <c r="J36" s="19"/>
-      <c r="K36" s="19"/>
-      <c r="L36" s="19"/>
-      <c r="M36" s="19"/>
-      <c r="N36" s="20"/>
-      <c r="O36" s="21"/>
-    </row>
-    <row r="37" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B37" s="18"/>
-      <c r="C37" s="19"/>
-      <c r="D37" s="19"/>
-      <c r="E37" s="19"/>
-      <c r="F37" s="19"/>
-      <c r="G37" s="19"/>
-      <c r="H37" s="19"/>
-      <c r="I37" s="19"/>
-      <c r="J37" s="19"/>
-      <c r="K37" s="19"/>
-      <c r="L37" s="19"/>
-      <c r="M37" s="19"/>
-      <c r="N37" s="20"/>
-      <c r="O37" s="21"/>
-    </row>
-    <row r="38" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B38" s="18"/>
-      <c r="C38" s="19"/>
-      <c r="D38" s="19"/>
-      <c r="E38" s="19"/>
-      <c r="F38" s="19"/>
-      <c r="G38" s="19"/>
-      <c r="H38" s="19"/>
-      <c r="I38" s="19"/>
-      <c r="J38" s="19"/>
-      <c r="K38" s="19"/>
-      <c r="L38" s="19"/>
-      <c r="M38" s="19"/>
-      <c r="N38" s="20"/>
-      <c r="O38" s="21"/>
-    </row>
-    <row r="39" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B39" s="18"/>
-      <c r="C39" s="19"/>
-      <c r="D39" s="19"/>
-      <c r="E39" s="19"/>
-      <c r="F39" s="19"/>
-      <c r="G39" s="19"/>
-      <c r="H39" s="19"/>
-      <c r="I39" s="19"/>
-      <c r="J39" s="19"/>
-      <c r="K39" s="19"/>
-      <c r="L39" s="19"/>
-      <c r="M39" s="19"/>
-      <c r="N39" s="20"/>
-      <c r="O39" s="21"/>
-    </row>
-    <row r="40" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B40" s="18"/>
-      <c r="C40" s="19"/>
-      <c r="D40" s="19"/>
-      <c r="E40" s="19"/>
-      <c r="F40" s="19"/>
-      <c r="G40" s="19"/>
-      <c r="H40" s="19"/>
-      <c r="I40" s="19"/>
-      <c r="J40" s="19"/>
-      <c r="K40" s="19"/>
-      <c r="L40" s="19"/>
-      <c r="M40" s="19"/>
-      <c r="N40" s="20"/>
-      <c r="O40" s="21"/>
-    </row>
-    <row r="41" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B41" s="18"/>
-      <c r="C41" s="19"/>
-      <c r="D41" s="19"/>
-      <c r="E41" s="19"/>
-      <c r="F41" s="19"/>
-      <c r="G41" s="19"/>
-      <c r="H41" s="19"/>
-      <c r="I41" s="19"/>
-      <c r="J41" s="19"/>
-      <c r="K41" s="19"/>
-      <c r="L41" s="19"/>
-      <c r="M41" s="19"/>
-      <c r="N41" s="20"/>
-      <c r="O41" s="21"/>
-    </row>
-    <row r="42" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B42" s="18"/>
-      <c r="C42" s="19"/>
-      <c r="D42" s="19"/>
-      <c r="E42" s="19"/>
-      <c r="F42" s="19"/>
-      <c r="G42" s="19"/>
-      <c r="H42" s="19"/>
-      <c r="I42" s="19"/>
-      <c r="J42" s="19"/>
-      <c r="K42" s="19"/>
-      <c r="L42" s="19"/>
-      <c r="M42" s="19"/>
-      <c r="N42" s="20"/>
-      <c r="O42" s="21"/>
-    </row>
-    <row r="43" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B43" s="18"/>
-      <c r="C43" s="19"/>
-      <c r="D43" s="19"/>
-      <c r="E43" s="19"/>
-      <c r="F43" s="19"/>
-      <c r="G43" s="19"/>
-      <c r="H43" s="19"/>
-      <c r="I43" s="19"/>
-      <c r="J43" s="19"/>
-      <c r="K43" s="19"/>
-      <c r="L43" s="19"/>
-      <c r="M43" s="19"/>
-      <c r="N43" s="20"/>
-      <c r="O43" s="21"/>
-    </row>
-    <row r="44" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B44" s="18"/>
-      <c r="C44" s="19"/>
-      <c r="D44" s="19"/>
-      <c r="E44" s="19"/>
-      <c r="F44" s="19"/>
-      <c r="G44" s="19"/>
-      <c r="H44" s="19"/>
-      <c r="I44" s="19"/>
-      <c r="J44" s="19"/>
-      <c r="K44" s="19"/>
-      <c r="L44" s="19"/>
-      <c r="M44" s="19"/>
-      <c r="N44" s="20"/>
-      <c r="O44" s="21"/>
-    </row>
-    <row r="45" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B45" s="18"/>
-      <c r="C45" s="19"/>
-      <c r="D45" s="19"/>
-      <c r="E45" s="19"/>
-      <c r="F45" s="19"/>
-      <c r="G45" s="19"/>
-      <c r="H45" s="19"/>
-      <c r="I45" s="19"/>
-      <c r="J45" s="19"/>
-      <c r="K45" s="19"/>
-      <c r="L45" s="19"/>
-      <c r="M45" s="19"/>
-      <c r="N45" s="20"/>
-      <c r="O45" s="21"/>
-    </row>
-    <row r="46" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B46" s="18"/>
-      <c r="C46" s="19"/>
-      <c r="D46" s="19"/>
-      <c r="E46" s="19"/>
-      <c r="F46" s="19"/>
-      <c r="G46" s="19"/>
-      <c r="H46" s="19"/>
-      <c r="I46" s="19"/>
-      <c r="J46" s="19"/>
-      <c r="K46" s="19"/>
-      <c r="L46" s="19"/>
-      <c r="M46" s="19"/>
-      <c r="N46" s="20"/>
-      <c r="O46" s="21"/>
-    </row>
-    <row r="47" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B47" s="18"/>
-      <c r="C47" s="19"/>
-      <c r="D47" s="19"/>
-      <c r="E47" s="19"/>
-      <c r="F47" s="19"/>
-      <c r="G47" s="19"/>
-      <c r="H47" s="19"/>
-      <c r="I47" s="19"/>
-      <c r="J47" s="19"/>
-      <c r="K47" s="19"/>
-      <c r="L47" s="19"/>
-      <c r="M47" s="19"/>
-      <c r="N47" s="20"/>
-      <c r="O47" s="21"/>
-    </row>
-    <row r="48" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B48" s="18"/>
-      <c r="C48" s="19"/>
-      <c r="D48" s="19"/>
-      <c r="E48" s="19"/>
-      <c r="F48" s="19"/>
-      <c r="G48" s="19"/>
-      <c r="H48" s="19"/>
-      <c r="I48" s="19"/>
-      <c r="J48" s="19"/>
-      <c r="K48" s="19"/>
-      <c r="L48" s="19"/>
-      <c r="M48" s="19"/>
-      <c r="N48" s="20"/>
-      <c r="O48" s="21"/>
-    </row>
-    <row r="49" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B49" s="22"/>
-      <c r="C49" s="23"/>
-      <c r="D49" s="23"/>
-      <c r="E49" s="23"/>
-      <c r="F49" s="23"/>
-      <c r="G49" s="23"/>
-      <c r="H49" s="23"/>
-      <c r="I49" s="23"/>
-      <c r="J49" s="23"/>
-      <c r="K49" s="23"/>
-      <c r="L49" s="23"/>
-      <c r="M49" s="23"/>
-      <c r="N49" s="24"/>
-      <c r="O49" s="25"/>
-    </row>
-    <row r="50" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B50" s="10"/>
-      <c r="C50" s="11"/>
-      <c r="D50" s="11"/>
-      <c r="E50" s="11"/>
-      <c r="F50" s="11"/>
-      <c r="G50" s="11"/>
-      <c r="H50" s="11"/>
-      <c r="I50" s="11"/>
-      <c r="J50" s="11"/>
-      <c r="K50" s="11"/>
-      <c r="L50" s="11"/>
-      <c r="M50" s="11"/>
-      <c r="N50" s="11"/>
-      <c r="O50" s="12"/>
-    </row>
-    <row r="51" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="C51" s="2"/>
-      <c r="D51" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="E51" s="16"/>
+      <c r="E51" s="12"/>
       <c r="F51" s="2"/>
       <c r="G51" s="2"/>
       <c r="H51" s="2"/>
       <c r="I51" s="2"/>
       <c r="J51" s="2"/>
-      <c r="K51" s="17" t="s">
-        <v>18</v>
+      <c r="K51" s="13" t="s">
+        <v>17</v>
       </c>
-      <c r="L51" s="17"/>
+      <c r="L51" s="13"/>
       <c r="M51" s="2"/>
       <c r="N51" s="2"/>
-      <c r="O51" s="9"/>
+      <c r="O51" s="5"/>
     </row>
     <row r="52" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C52" s="2"/>
@@ -1631,7 +1631,7 @@
       <c r="L52" s="2"/>
       <c r="M52" s="2"/>
       <c r="N52" s="2"/>
-      <c r="O52" s="9"/>
+      <c r="O52" s="5"/>
     </row>
     <row r="53" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C53" s="2"/>
@@ -1646,7 +1646,7 @@
       <c r="L53" s="2"/>
       <c r="M53" s="2"/>
       <c r="N53" s="2"/>
-      <c r="O53" s="9"/>
+      <c r="O53" s="5"/>
     </row>
     <row r="54" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C54" s="2"/>
@@ -1661,22 +1661,22 @@
       <c r="L54" s="2"/>
       <c r="M54" s="2"/>
       <c r="N54" s="2"/>
-      <c r="O54" s="9"/>
+      <c r="O54" s="5"/>
     </row>
     <row r="55" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C55" s="2"/>
-      <c r="D55" s="13"/>
-      <c r="E55" s="13"/>
+      <c r="D55" s="9"/>
+      <c r="E55" s="9"/>
       <c r="F55" s="2"/>
       <c r="G55" s="2"/>
       <c r="H55" s="2"/>
       <c r="I55" s="2"/>
       <c r="J55" s="2"/>
-      <c r="K55" s="13"/>
-      <c r="L55" s="13"/>
+      <c r="K55" s="9"/>
+      <c r="L55" s="9"/>
       <c r="M55" s="2"/>
       <c r="N55" s="2"/>
-      <c r="O55" s="9"/>
+      <c r="O55" s="5"/>
     </row>
     <row r="56" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C56" s="2"/>
@@ -1691,7 +1691,7 @@
       <c r="L56" s="2"/>
       <c r="M56" s="2"/>
       <c r="N56" s="2"/>
-      <c r="O56" s="9"/>
+      <c r="O56" s="5"/>
     </row>
     <row r="57" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C57" s="2"/>
@@ -1706,7 +1706,7 @@
       <c r="L57" s="2"/>
       <c r="M57" s="2"/>
       <c r="N57" s="2"/>
-      <c r="O57" s="9"/>
+      <c r="O57" s="5"/>
     </row>
     <row r="58" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C58" s="2"/>
@@ -1721,7 +1721,7 @@
       <c r="L58" s="2"/>
       <c r="M58" s="2"/>
       <c r="N58" s="2"/>
-      <c r="O58" s="9"/>
+      <c r="O58" s="5"/>
     </row>
     <row r="59" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C59" s="2"/>
@@ -1736,7 +1736,7 @@
       <c r="L59" s="2"/>
       <c r="M59" s="2"/>
       <c r="N59" s="2"/>
-      <c r="O59" s="9"/>
+      <c r="O59" s="5"/>
     </row>
     <row r="60" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C60" s="2"/>
@@ -1751,7 +1751,7 @@
       <c r="L60" s="2"/>
       <c r="M60" s="2"/>
       <c r="N60" s="2"/>
-      <c r="O60" s="9"/>
+      <c r="O60" s="5"/>
     </row>
     <row r="61" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C61" s="2"/>
@@ -1766,7 +1766,7 @@
       <c r="L61" s="2"/>
       <c r="M61" s="2"/>
       <c r="N61" s="2"/>
-      <c r="O61" s="9"/>
+      <c r="O61" s="5"/>
     </row>
     <row r="62" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C62" s="2"/>
@@ -1781,7 +1781,7 @@
       <c r="L62" s="2"/>
       <c r="M62" s="2"/>
       <c r="N62" s="2"/>
-      <c r="O62" s="9"/>
+      <c r="O62" s="5"/>
     </row>
     <row r="63" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C63" s="2"/>
@@ -1796,7 +1796,7 @@
       <c r="L63" s="2"/>
       <c r="M63" s="2"/>
       <c r="N63" s="2"/>
-      <c r="O63" s="9"/>
+      <c r="O63" s="5"/>
     </row>
     <row r="64" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C64" s="2"/>
@@ -1811,7 +1811,7 @@
       <c r="L64" s="2"/>
       <c r="M64" s="2"/>
       <c r="N64" s="2"/>
-      <c r="O64" s="9"/>
+      <c r="O64" s="5"/>
     </row>
     <row r="65" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C65" s="2"/>
@@ -1826,7 +1826,7 @@
       <c r="L65" s="2"/>
       <c r="M65" s="2"/>
       <c r="N65" s="2"/>
-      <c r="O65" s="9"/>
+      <c r="O65" s="5"/>
     </row>
     <row r="66" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C66" s="2"/>
@@ -1841,7 +1841,7 @@
       <c r="L66" s="2"/>
       <c r="M66" s="2"/>
       <c r="N66" s="2"/>
-      <c r="O66" s="9"/>
+      <c r="O66" s="5"/>
     </row>
     <row r="67" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C67" s="2"/>
@@ -1856,7 +1856,7 @@
       <c r="L67" s="2"/>
       <c r="M67" s="2"/>
       <c r="N67" s="2"/>
-      <c r="O67" s="9"/>
+      <c r="O67" s="5"/>
     </row>
     <row r="68" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C68" s="2"/>
@@ -1871,7 +1871,7 @@
       <c r="L68" s="2"/>
       <c r="M68" s="2"/>
       <c r="N68" s="2"/>
-      <c r="O68" s="9"/>
+      <c r="O68" s="5"/>
     </row>
     <row r="69" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C69" s="2"/>
@@ -1886,7 +1886,7 @@
       <c r="L69" s="2"/>
       <c r="M69" s="2"/>
       <c r="N69" s="2"/>
-      <c r="O69" s="9"/>
+      <c r="O69" s="5"/>
     </row>
     <row r="70" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C70" s="2"/>
@@ -1901,7 +1901,7 @@
       <c r="L70" s="2"/>
       <c r="M70" s="2"/>
       <c r="N70" s="2"/>
-      <c r="O70" s="9"/>
+      <c r="O70" s="5"/>
     </row>
     <row r="71" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C71" s="2"/>
@@ -1916,7 +1916,7 @@
       <c r="L71" s="2"/>
       <c r="M71" s="2"/>
       <c r="N71" s="2"/>
-      <c r="O71" s="9"/>
+      <c r="O71" s="5"/>
     </row>
     <row r="72" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C72" s="2"/>
@@ -1931,7 +1931,7 @@
       <c r="L72" s="2"/>
       <c r="M72" s="2"/>
       <c r="N72" s="2"/>
-      <c r="O72" s="9"/>
+      <c r="O72" s="5"/>
     </row>
     <row r="73" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C73" s="2"/>
@@ -1946,7 +1946,7 @@
       <c r="L73" s="2"/>
       <c r="M73" s="2"/>
       <c r="N73" s="2"/>
-      <c r="O73" s="9"/>
+      <c r="O73" s="5"/>
     </row>
     <row r="74" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C74" s="2"/>
@@ -1961,7 +1961,7 @@
       <c r="L74" s="2"/>
       <c r="M74" s="2"/>
       <c r="N74" s="2"/>
-      <c r="O74" s="9"/>
+      <c r="O74" s="5"/>
     </row>
     <row r="75" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C75" s="2"/>
@@ -1976,7 +1976,7 @@
       <c r="L75" s="2"/>
       <c r="M75" s="2"/>
       <c r="N75" s="2"/>
-      <c r="O75" s="9"/>
+      <c r="O75" s="5"/>
     </row>
     <row r="76" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C76" s="2"/>
@@ -1991,7 +1991,7 @@
       <c r="L76" s="2"/>
       <c r="M76" s="2"/>
       <c r="N76" s="2"/>
-      <c r="O76" s="9"/>
+      <c r="O76" s="5"/>
     </row>
     <row r="77" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C77" s="2"/>
@@ -2006,7 +2006,7 @@
       <c r="L77" s="2"/>
       <c r="M77" s="2"/>
       <c r="N77" s="2"/>
-      <c r="O77" s="9"/>
+      <c r="O77" s="5"/>
     </row>
     <row r="78" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C78" s="2"/>
@@ -2021,7 +2021,7 @@
       <c r="L78" s="2"/>
       <c r="M78" s="2"/>
       <c r="N78" s="2"/>
-      <c r="O78" s="9"/>
+      <c r="O78" s="5"/>
     </row>
     <row r="79" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C79" s="2"/>
@@ -2036,7 +2036,7 @@
       <c r="L79" s="2"/>
       <c r="M79" s="2"/>
       <c r="N79" s="2"/>
-      <c r="O79" s="9"/>
+      <c r="O79" s="5"/>
     </row>
     <row r="80" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C80" s="2"/>
@@ -2051,7 +2051,7 @@
       <c r="L80" s="2"/>
       <c r="M80" s="2"/>
       <c r="N80" s="2"/>
-      <c r="O80" s="9"/>
+      <c r="O80" s="5"/>
     </row>
     <row r="81" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C81" s="2"/>
@@ -2066,7 +2066,7 @@
       <c r="L81" s="2"/>
       <c r="M81" s="2"/>
       <c r="N81" s="2"/>
-      <c r="O81" s="9"/>
+      <c r="O81" s="5"/>
     </row>
     <row r="82" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C82" s="2"/>
@@ -2081,7 +2081,7 @@
       <c r="L82" s="2"/>
       <c r="M82" s="2"/>
       <c r="N82" s="2"/>
-      <c r="O82" s="9"/>
+      <c r="O82" s="5"/>
     </row>
     <row r="83" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C83" s="2"/>
@@ -2096,7 +2096,7 @@
       <c r="L83" s="2"/>
       <c r="M83" s="2"/>
       <c r="N83" s="2"/>
-      <c r="O83" s="9"/>
+      <c r="O83" s="5"/>
     </row>
     <row r="84" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C84" s="2"/>
@@ -2111,7 +2111,7 @@
       <c r="L84" s="2"/>
       <c r="M84" s="2"/>
       <c r="N84" s="2"/>
-      <c r="O84" s="9"/>
+      <c r="O84" s="5"/>
     </row>
     <row r="85" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C85" s="2"/>
@@ -2126,7 +2126,7 @@
       <c r="L85" s="2"/>
       <c r="M85" s="2"/>
       <c r="N85" s="2"/>
-      <c r="O85" s="9"/>
+      <c r="O85" s="5"/>
     </row>
     <row r="86" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C86" s="2"/>
@@ -2141,7 +2141,7 @@
       <c r="L86" s="2"/>
       <c r="M86" s="2"/>
       <c r="N86" s="2"/>
-      <c r="O86" s="9"/>
+      <c r="O86" s="5"/>
     </row>
     <row r="87" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C87" s="2"/>
@@ -2156,7 +2156,7 @@
       <c r="L87" s="2"/>
       <c r="M87" s="2"/>
       <c r="N87" s="2"/>
-      <c r="O87" s="9"/>
+      <c r="O87" s="5"/>
     </row>
     <row r="88" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C88" s="2"/>
@@ -2171,7 +2171,7 @@
       <c r="L88" s="2"/>
       <c r="M88" s="2"/>
       <c r="N88" s="2"/>
-      <c r="O88" s="9"/>
+      <c r="O88" s="5"/>
     </row>
     <row r="89" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C89" s="2"/>
@@ -2186,7 +2186,7 @@
       <c r="L89" s="2"/>
       <c r="M89" s="2"/>
       <c r="N89" s="2"/>
-      <c r="O89" s="9"/>
+      <c r="O89" s="5"/>
     </row>
     <row r="90" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C90" s="2"/>
@@ -2201,7 +2201,7 @@
       <c r="L90" s="2"/>
       <c r="M90" s="2"/>
       <c r="N90" s="2"/>
-      <c r="O90" s="9"/>
+      <c r="O90" s="5"/>
     </row>
     <row r="91" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C91" s="2"/>
@@ -2216,7 +2216,7 @@
       <c r="L91" s="2"/>
       <c r="M91" s="2"/>
       <c r="N91" s="2"/>
-      <c r="O91" s="9"/>
+      <c r="O91" s="5"/>
     </row>
     <row r="92" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C92" s="2"/>
@@ -2231,7 +2231,7 @@
       <c r="L92" s="2"/>
       <c r="M92" s="2"/>
       <c r="N92" s="2"/>
-      <c r="O92" s="9"/>
+      <c r="O92" s="5"/>
     </row>
     <row r="93" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C93" s="2"/>
@@ -2246,7 +2246,7 @@
       <c r="L93" s="2"/>
       <c r="M93" s="2"/>
       <c r="N93" s="2"/>
-      <c r="O93" s="9"/>
+      <c r="O93" s="5"/>
     </row>
     <row r="94" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C94" s="2"/>
@@ -2261,7 +2261,7 @@
       <c r="L94" s="2"/>
       <c r="M94" s="2"/>
       <c r="N94" s="2"/>
-      <c r="O94" s="9"/>
+      <c r="O94" s="5"/>
     </row>
     <row r="95" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C95" s="2"/>
@@ -2276,7 +2276,7 @@
       <c r="L95" s="2"/>
       <c r="M95" s="2"/>
       <c r="N95" s="2"/>
-      <c r="O95" s="9"/>
+      <c r="O95" s="5"/>
     </row>
     <row r="96" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C96" s="2"/>
@@ -2291,7 +2291,7 @@
       <c r="L96" s="2"/>
       <c r="M96" s="2"/>
       <c r="N96" s="2"/>
-      <c r="O96" s="9"/>
+      <c r="O96" s="5"/>
     </row>
     <row r="97" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C97" s="2"/>
@@ -2306,7 +2306,7 @@
       <c r="L97" s="2"/>
       <c r="M97" s="2"/>
       <c r="N97" s="2"/>
-      <c r="O97" s="9"/>
+      <c r="O97" s="5"/>
     </row>
     <row r="98" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C98" s="2"/>
@@ -2321,7 +2321,7 @@
       <c r="L98" s="2"/>
       <c r="M98" s="2"/>
       <c r="N98" s="2"/>
-      <c r="O98" s="9"/>
+      <c r="O98" s="5"/>
     </row>
     <row r="99" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C99" s="2"/>
@@ -2336,7 +2336,7 @@
       <c r="L99" s="2"/>
       <c r="M99" s="2"/>
       <c r="N99" s="2"/>
-      <c r="O99" s="9"/>
+      <c r="O99" s="5"/>
     </row>
     <row r="100" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C100" s="2"/>
@@ -2351,7 +2351,7 @@
       <c r="L100" s="2"/>
       <c r="M100" s="2"/>
       <c r="N100" s="2"/>
-      <c r="O100" s="9"/>
+      <c r="O100" s="5"/>
     </row>
     <row r="101" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C101" s="2"/>
@@ -2366,7 +2366,7 @@
       <c r="L101" s="2"/>
       <c r="M101" s="2"/>
       <c r="N101" s="2"/>
-      <c r="O101" s="9"/>
+      <c r="O101" s="5"/>
     </row>
     <row r="102" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C102" s="2"/>
@@ -2381,7 +2381,7 @@
       <c r="L102" s="2"/>
       <c r="M102" s="2"/>
       <c r="N102" s="2"/>
-      <c r="O102" s="9"/>
+      <c r="O102" s="5"/>
     </row>
     <row r="103" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C103" s="2"/>
@@ -2396,7 +2396,7 @@
       <c r="L103" s="2"/>
       <c r="M103" s="2"/>
       <c r="N103" s="2"/>
-      <c r="O103" s="9"/>
+      <c r="O103" s="5"/>
     </row>
     <row r="104" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C104" s="2"/>
@@ -2411,7 +2411,7 @@
       <c r="L104" s="2"/>
       <c r="M104" s="2"/>
       <c r="N104" s="2"/>
-      <c r="O104" s="9"/>
+      <c r="O104" s="5"/>
     </row>
     <row r="105" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C105" s="2"/>
@@ -2426,7 +2426,7 @@
       <c r="L105" s="2"/>
       <c r="M105" s="2"/>
       <c r="N105" s="2"/>
-      <c r="O105" s="9"/>
+      <c r="O105" s="5"/>
     </row>
     <row r="106" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C106" s="2"/>
@@ -2441,7 +2441,7 @@
       <c r="L106" s="2"/>
       <c r="M106" s="2"/>
       <c r="N106" s="2"/>
-      <c r="O106" s="9"/>
+      <c r="O106" s="5"/>
     </row>
     <row r="107" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C107" s="2"/>
@@ -2456,7 +2456,7 @@
       <c r="L107" s="2"/>
       <c r="M107" s="2"/>
       <c r="N107" s="2"/>
-      <c r="O107" s="9"/>
+      <c r="O107" s="5"/>
     </row>
     <row r="108" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C108" s="2"/>
@@ -2471,7 +2471,7 @@
       <c r="L108" s="2"/>
       <c r="M108" s="2"/>
       <c r="N108" s="2"/>
-      <c r="O108" s="9"/>
+      <c r="O108" s="5"/>
     </row>
     <row r="109" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C109" s="2"/>
@@ -2486,7 +2486,7 @@
       <c r="L109" s="2"/>
       <c r="M109" s="2"/>
       <c r="N109" s="2"/>
-      <c r="O109" s="9"/>
+      <c r="O109" s="5"/>
     </row>
     <row r="110" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C110" s="2"/>
@@ -2501,7 +2501,7 @@
       <c r="L110" s="2"/>
       <c r="M110" s="2"/>
       <c r="N110" s="2"/>
-      <c r="O110" s="9"/>
+      <c r="O110" s="5"/>
     </row>
     <row r="111" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C111" s="2"/>
@@ -2516,7 +2516,7 @@
       <c r="L111" s="2"/>
       <c r="M111" s="2"/>
       <c r="N111" s="2"/>
-      <c r="O111" s="9"/>
+      <c r="O111" s="5"/>
     </row>
     <row r="112" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C112" s="2"/>
@@ -2531,7 +2531,7 @@
       <c r="L112" s="2"/>
       <c r="M112" s="2"/>
       <c r="N112" s="2"/>
-      <c r="O112" s="9"/>
+      <c r="O112" s="5"/>
     </row>
     <row r="113" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C113" s="2"/>
@@ -2546,7 +2546,7 @@
       <c r="L113" s="2"/>
       <c r="M113" s="2"/>
       <c r="N113" s="2"/>
-      <c r="O113" s="9"/>
+      <c r="O113" s="5"/>
     </row>
     <row r="114" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C114" s="2"/>
@@ -2561,7 +2561,7 @@
       <c r="L114" s="2"/>
       <c r="M114" s="2"/>
       <c r="N114" s="2"/>
-      <c r="O114" s="9"/>
+      <c r="O114" s="5"/>
     </row>
     <row r="115" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C115" s="2"/>
@@ -2576,7 +2576,7 @@
       <c r="L115" s="2"/>
       <c r="M115" s="2"/>
       <c r="N115" s="2"/>
-      <c r="O115" s="9"/>
+      <c r="O115" s="5"/>
     </row>
     <row r="116" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C116" s="2"/>
@@ -2591,7 +2591,7 @@
       <c r="L116" s="2"/>
       <c r="M116" s="2"/>
       <c r="N116" s="2"/>
-      <c r="O116" s="9"/>
+      <c r="O116" s="5"/>
     </row>
     <row r="117" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C117" s="2"/>
@@ -2606,7 +2606,7 @@
       <c r="L117" s="2"/>
       <c r="M117" s="2"/>
       <c r="N117" s="2"/>
-      <c r="O117" s="9"/>
+      <c r="O117" s="5"/>
     </row>
     <row r="118" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C118" s="2"/>
@@ -2621,7 +2621,7 @@
       <c r="L118" s="2"/>
       <c r="M118" s="2"/>
       <c r="N118" s="2"/>
-      <c r="O118" s="9"/>
+      <c r="O118" s="5"/>
     </row>
     <row r="119" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C119" s="2"/>
@@ -2636,7 +2636,7 @@
       <c r="L119" s="2"/>
       <c r="M119" s="2"/>
       <c r="N119" s="2"/>
-      <c r="O119" s="9"/>
+      <c r="O119" s="5"/>
     </row>
     <row r="120" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C120" s="2"/>
@@ -2651,7 +2651,7 @@
       <c r="L120" s="2"/>
       <c r="M120" s="2"/>
       <c r="N120" s="2"/>
-      <c r="O120" s="9"/>
+      <c r="O120" s="5"/>
     </row>
     <row r="121" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C121" s="2"/>
@@ -2666,7 +2666,7 @@
       <c r="L121" s="2"/>
       <c r="M121" s="2"/>
       <c r="N121" s="2"/>
-      <c r="O121" s="9"/>
+      <c r="O121" s="5"/>
     </row>
     <row r="122" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C122" s="2"/>
@@ -2681,7 +2681,7 @@
       <c r="L122" s="2"/>
       <c r="M122" s="2"/>
       <c r="N122" s="2"/>
-      <c r="O122" s="9"/>
+      <c r="O122" s="5"/>
     </row>
     <row r="123" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C123" s="2"/>
@@ -2696,7 +2696,7 @@
       <c r="L123" s="2"/>
       <c r="M123" s="2"/>
       <c r="N123" s="2"/>
-      <c r="O123" s="9"/>
+      <c r="O123" s="5"/>
     </row>
     <row r="124" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C124" s="2"/>
@@ -2711,7 +2711,7 @@
       <c r="L124" s="2"/>
       <c r="M124" s="2"/>
       <c r="N124" s="2"/>
-      <c r="O124" s="9"/>
+      <c r="O124" s="5"/>
     </row>
     <row r="125" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C125" s="2"/>
@@ -2726,7 +2726,7 @@
       <c r="L125" s="2"/>
       <c r="M125" s="2"/>
       <c r="N125" s="2"/>
-      <c r="O125" s="9"/>
+      <c r="O125" s="5"/>
     </row>
     <row r="126" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C126" s="2"/>
@@ -2741,7 +2741,7 @@
       <c r="L126" s="2"/>
       <c r="M126" s="2"/>
       <c r="N126" s="2"/>
-      <c r="O126" s="9"/>
+      <c r="O126" s="5"/>
     </row>
     <row r="127" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C127" s="2"/>
@@ -2756,7 +2756,7 @@
       <c r="L127" s="2"/>
       <c r="M127" s="2"/>
       <c r="N127" s="2"/>
-      <c r="O127" s="9"/>
+      <c r="O127" s="5"/>
     </row>
     <row r="128" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C128" s="2"/>
@@ -2771,7 +2771,7 @@
       <c r="L128" s="2"/>
       <c r="M128" s="2"/>
       <c r="N128" s="2"/>
-      <c r="O128" s="9"/>
+      <c r="O128" s="5"/>
     </row>
     <row r="129" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C129" s="2"/>
@@ -2786,7 +2786,7 @@
       <c r="L129" s="2"/>
       <c r="M129" s="2"/>
       <c r="N129" s="2"/>
-      <c r="O129" s="9"/>
+      <c r="O129" s="5"/>
     </row>
     <row r="130" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C130" s="2"/>
@@ -2801,7 +2801,7 @@
       <c r="L130" s="2"/>
       <c r="M130" s="2"/>
       <c r="N130" s="2"/>
-      <c r="O130" s="9"/>
+      <c r="O130" s="5"/>
     </row>
     <row r="131" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C131" s="2"/>
@@ -2816,7 +2816,7 @@
       <c r="L131" s="2"/>
       <c r="M131" s="2"/>
       <c r="N131" s="2"/>
-      <c r="O131" s="9"/>
+      <c r="O131" s="5"/>
     </row>
     <row r="132" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C132" s="2"/>
@@ -2831,7 +2831,7 @@
       <c r="L132" s="2"/>
       <c r="M132" s="2"/>
       <c r="N132" s="2"/>
-      <c r="O132" s="9"/>
+      <c r="O132" s="5"/>
     </row>
     <row r="133" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C133" s="2"/>
@@ -2846,7 +2846,7 @@
       <c r="L133" s="2"/>
       <c r="M133" s="2"/>
       <c r="N133" s="2"/>
-      <c r="O133" s="9"/>
+      <c r="O133" s="5"/>
     </row>
     <row r="134" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C134" s="2"/>
@@ -2861,7 +2861,7 @@
       <c r="L134" s="2"/>
       <c r="M134" s="2"/>
       <c r="N134" s="2"/>
-      <c r="O134" s="9"/>
+      <c r="O134" s="5"/>
     </row>
     <row r="135" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C135" s="2"/>
@@ -2876,7 +2876,7 @@
       <c r="L135" s="2"/>
       <c r="M135" s="2"/>
       <c r="N135" s="2"/>
-      <c r="O135" s="9"/>
+      <c r="O135" s="5"/>
     </row>
     <row r="136" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C136" s="2"/>
@@ -2891,7 +2891,7 @@
       <c r="L136" s="2"/>
       <c r="M136" s="2"/>
       <c r="N136" s="2"/>
-      <c r="O136" s="9"/>
+      <c r="O136" s="5"/>
     </row>
     <row r="137" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C137" s="2"/>
@@ -2906,7 +2906,7 @@
       <c r="L137" s="2"/>
       <c r="M137" s="2"/>
       <c r="N137" s="2"/>
-      <c r="O137" s="9"/>
+      <c r="O137" s="5"/>
     </row>
     <row r="138" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C138" s="2"/>
@@ -2921,7 +2921,7 @@
       <c r="L138" s="2"/>
       <c r="M138" s="2"/>
       <c r="N138" s="2"/>
-      <c r="O138" s="9"/>
+      <c r="O138" s="5"/>
     </row>
     <row r="139" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C139" s="2"/>
@@ -2936,7 +2936,7 @@
       <c r="L139" s="2"/>
       <c r="M139" s="2"/>
       <c r="N139" s="2"/>
-      <c r="O139" s="9"/>
+      <c r="O139" s="5"/>
     </row>
     <row r="140" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C140" s="2"/>
@@ -2951,7 +2951,7 @@
       <c r="L140" s="2"/>
       <c r="M140" s="2"/>
       <c r="N140" s="2"/>
-      <c r="O140" s="9"/>
+      <c r="O140" s="5"/>
     </row>
     <row r="141" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C141" s="2"/>
@@ -2966,7 +2966,7 @@
       <c r="L141" s="2"/>
       <c r="M141" s="2"/>
       <c r="N141" s="2"/>
-      <c r="O141" s="9"/>
+      <c r="O141" s="5"/>
     </row>
     <row r="142" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C142" s="2"/>
@@ -2981,7 +2981,7 @@
       <c r="L142" s="2"/>
       <c r="M142" s="2"/>
       <c r="N142" s="2"/>
-      <c r="O142" s="9"/>
+      <c r="O142" s="5"/>
     </row>
     <row r="143" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C143" s="2"/>
@@ -2996,7 +2996,7 @@
       <c r="L143" s="2"/>
       <c r="M143" s="2"/>
       <c r="N143" s="2"/>
-      <c r="O143" s="9"/>
+      <c r="O143" s="5"/>
     </row>
     <row r="144" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C144" s="2"/>
@@ -3011,7 +3011,7 @@
       <c r="L144" s="2"/>
       <c r="M144" s="2"/>
       <c r="N144" s="2"/>
-      <c r="O144" s="9"/>
+      <c r="O144" s="5"/>
     </row>
     <row r="145" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C145" s="2"/>
@@ -3026,7 +3026,7 @@
       <c r="L145" s="2"/>
       <c r="M145" s="2"/>
       <c r="N145" s="2"/>
-      <c r="O145" s="9"/>
+      <c r="O145" s="5"/>
     </row>
     <row r="146" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C146" s="2"/>
@@ -3041,7 +3041,7 @@
       <c r="L146" s="2"/>
       <c r="M146" s="2"/>
       <c r="N146" s="2"/>
-      <c r="O146" s="9"/>
+      <c r="O146" s="5"/>
     </row>
     <row r="147" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C147" s="2"/>
@@ -3056,7 +3056,7 @@
       <c r="L147" s="2"/>
       <c r="M147" s="2"/>
       <c r="N147" s="2"/>
-      <c r="O147" s="9"/>
+      <c r="O147" s="5"/>
     </row>
     <row r="148" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C148" s="2"/>
@@ -3071,7 +3071,7 @@
       <c r="L148" s="2"/>
       <c r="M148" s="2"/>
       <c r="N148" s="2"/>
-      <c r="O148" s="9"/>
+      <c r="O148" s="5"/>
     </row>
     <row r="149" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C149" s="2"/>
@@ -3086,7 +3086,7 @@
       <c r="L149" s="2"/>
       <c r="M149" s="2"/>
       <c r="N149" s="2"/>
-      <c r="O149" s="9"/>
+      <c r="O149" s="5"/>
     </row>
     <row r="150" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C150" s="2"/>
@@ -3101,7 +3101,7 @@
       <c r="L150" s="2"/>
       <c r="M150" s="2"/>
       <c r="N150" s="2"/>
-      <c r="O150" s="9"/>
+      <c r="O150" s="5"/>
     </row>
     <row r="151" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C151" s="2"/>
@@ -3116,7 +3116,7 @@
       <c r="L151" s="2"/>
       <c r="M151" s="2"/>
       <c r="N151" s="2"/>
-      <c r="O151" s="9"/>
+      <c r="O151" s="5"/>
     </row>
     <row r="152" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C152" s="2"/>
@@ -3131,7 +3131,7 @@
       <c r="L152" s="2"/>
       <c r="M152" s="2"/>
       <c r="N152" s="2"/>
-      <c r="O152" s="9"/>
+      <c r="O152" s="5"/>
     </row>
     <row r="153" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C153" s="2"/>
@@ -3146,7 +3146,7 @@
       <c r="L153" s="2"/>
       <c r="M153" s="2"/>
       <c r="N153" s="2"/>
-      <c r="O153" s="9"/>
+      <c r="O153" s="5"/>
     </row>
     <row r="154" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C154" s="2"/>
@@ -3161,7 +3161,7 @@
       <c r="L154" s="2"/>
       <c r="M154" s="2"/>
       <c r="N154" s="2"/>
-      <c r="O154" s="9"/>
+      <c r="O154" s="5"/>
     </row>
     <row r="155" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C155" s="2"/>
@@ -3176,7 +3176,7 @@
       <c r="L155" s="2"/>
       <c r="M155" s="2"/>
       <c r="N155" s="2"/>
-      <c r="O155" s="9"/>
+      <c r="O155" s="5"/>
     </row>
     <row r="156" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C156" s="2"/>
@@ -3191,7 +3191,7 @@
       <c r="L156" s="2"/>
       <c r="M156" s="2"/>
       <c r="N156" s="2"/>
-      <c r="O156" s="9"/>
+      <c r="O156" s="5"/>
     </row>
     <row r="157" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C157" s="2"/>
@@ -3206,7 +3206,7 @@
       <c r="L157" s="2"/>
       <c r="M157" s="2"/>
       <c r="N157" s="2"/>
-      <c r="O157" s="9"/>
+      <c r="O157" s="5"/>
     </row>
     <row r="158" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C158" s="2"/>
@@ -3221,7 +3221,7 @@
       <c r="L158" s="2"/>
       <c r="M158" s="2"/>
       <c r="N158" s="2"/>
-      <c r="O158" s="9"/>
+      <c r="O158" s="5"/>
     </row>
     <row r="159" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C159" s="2"/>
@@ -3236,7 +3236,7 @@
       <c r="L159" s="2"/>
       <c r="M159" s="2"/>
       <c r="N159" s="2"/>
-      <c r="O159" s="9"/>
+      <c r="O159" s="5"/>
     </row>
     <row r="160" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C160" s="2"/>
@@ -3251,7 +3251,7 @@
       <c r="L160" s="2"/>
       <c r="M160" s="2"/>
       <c r="N160" s="2"/>
-      <c r="O160" s="9"/>
+      <c r="O160" s="5"/>
     </row>
     <row r="161" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C161" s="2"/>
@@ -3266,7 +3266,7 @@
       <c r="L161" s="2"/>
       <c r="M161" s="2"/>
       <c r="N161" s="2"/>
-      <c r="O161" s="9"/>
+      <c r="O161" s="5"/>
     </row>
     <row r="162" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C162" s="2"/>
@@ -3281,7 +3281,7 @@
       <c r="L162" s="2"/>
       <c r="M162" s="2"/>
       <c r="N162" s="2"/>
-      <c r="O162" s="9"/>
+      <c r="O162" s="5"/>
     </row>
     <row r="163" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C163" s="2"/>
@@ -3296,7 +3296,7 @@
       <c r="L163" s="2"/>
       <c r="M163" s="2"/>
       <c r="N163" s="2"/>
-      <c r="O163" s="9"/>
+      <c r="O163" s="5"/>
     </row>
     <row r="164" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C164" s="2"/>
@@ -3311,7 +3311,7 @@
       <c r="L164" s="2"/>
       <c r="M164" s="2"/>
       <c r="N164" s="2"/>
-      <c r="O164" s="9"/>
+      <c r="O164" s="5"/>
     </row>
     <row r="165" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C165" s="2"/>
@@ -3326,7 +3326,7 @@
       <c r="L165" s="2"/>
       <c r="M165" s="2"/>
       <c r="N165" s="2"/>
-      <c r="O165" s="9"/>
+      <c r="O165" s="5"/>
     </row>
     <row r="166" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C166" s="2"/>
@@ -3341,7 +3341,7 @@
       <c r="L166" s="2"/>
       <c r="M166" s="2"/>
       <c r="N166" s="2"/>
-      <c r="O166" s="9"/>
+      <c r="O166" s="5"/>
     </row>
     <row r="167" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C167" s="2"/>
@@ -3356,7 +3356,7 @@
       <c r="L167" s="2"/>
       <c r="M167" s="2"/>
       <c r="N167" s="2"/>
-      <c r="O167" s="9"/>
+      <c r="O167" s="5"/>
     </row>
     <row r="168" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C168" s="2"/>
@@ -3371,7 +3371,7 @@
       <c r="L168" s="2"/>
       <c r="M168" s="2"/>
       <c r="N168" s="2"/>
-      <c r="O168" s="9"/>
+      <c r="O168" s="5"/>
     </row>
     <row r="169" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C169" s="2"/>
@@ -3386,7 +3386,7 @@
       <c r="L169" s="2"/>
       <c r="M169" s="2"/>
       <c r="N169" s="2"/>
-      <c r="O169" s="9"/>
+      <c r="O169" s="5"/>
     </row>
     <row r="170" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C170" s="2"/>
@@ -3401,7 +3401,7 @@
       <c r="L170" s="2"/>
       <c r="M170" s="2"/>
       <c r="N170" s="2"/>
-      <c r="O170" s="9"/>
+      <c r="O170" s="5"/>
     </row>
     <row r="171" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C171" s="2"/>
@@ -3416,7 +3416,7 @@
       <c r="L171" s="2"/>
       <c r="M171" s="2"/>
       <c r="N171" s="2"/>
-      <c r="O171" s="9"/>
+      <c r="O171" s="5"/>
     </row>
     <row r="172" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C172" s="2"/>
@@ -3431,7 +3431,7 @@
       <c r="L172" s="2"/>
       <c r="M172" s="2"/>
       <c r="N172" s="2"/>
-      <c r="O172" s="9"/>
+      <c r="O172" s="5"/>
     </row>
     <row r="173" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C173" s="2"/>
@@ -3446,7 +3446,7 @@
       <c r="L173" s="2"/>
       <c r="M173" s="2"/>
       <c r="N173" s="2"/>
-      <c r="O173" s="9"/>
+      <c r="O173" s="5"/>
     </row>
     <row r="174" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C174" s="2"/>
@@ -3461,7 +3461,7 @@
       <c r="L174" s="2"/>
       <c r="M174" s="2"/>
       <c r="N174" s="2"/>
-      <c r="O174" s="9"/>
+      <c r="O174" s="5"/>
     </row>
     <row r="175" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C175" s="2"/>
@@ -3476,7 +3476,7 @@
       <c r="L175" s="2"/>
       <c r="M175" s="2"/>
       <c r="N175" s="2"/>
-      <c r="O175" s="9"/>
+      <c r="O175" s="5"/>
     </row>
     <row r="176" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C176" s="2"/>
@@ -3491,7 +3491,7 @@
       <c r="L176" s="2"/>
       <c r="M176" s="2"/>
       <c r="N176" s="2"/>
-      <c r="O176" s="9"/>
+      <c r="O176" s="5"/>
     </row>
     <row r="177" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C177" s="2"/>
@@ -3506,7 +3506,7 @@
       <c r="L177" s="2"/>
       <c r="M177" s="2"/>
       <c r="N177" s="2"/>
-      <c r="O177" s="9"/>
+      <c r="O177" s="5"/>
     </row>
     <row r="178" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C178" s="2"/>
@@ -3521,7 +3521,7 @@
       <c r="L178" s="2"/>
       <c r="M178" s="2"/>
       <c r="N178" s="2"/>
-      <c r="O178" s="9"/>
+      <c r="O178" s="5"/>
     </row>
     <row r="179" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C179" s="2"/>
@@ -3536,7 +3536,7 @@
       <c r="L179" s="2"/>
       <c r="M179" s="2"/>
       <c r="N179" s="2"/>
-      <c r="O179" s="9"/>
+      <c r="O179" s="5"/>
     </row>
     <row r="180" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C180" s="2"/>
@@ -3551,7 +3551,7 @@
       <c r="L180" s="2"/>
       <c r="M180" s="2"/>
       <c r="N180" s="2"/>
-      <c r="O180" s="9"/>
+      <c r="O180" s="5"/>
     </row>
     <row r="181" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C181" s="2"/>
@@ -3566,7 +3566,7 @@
       <c r="L181" s="2"/>
       <c r="M181" s="2"/>
       <c r="N181" s="2"/>
-      <c r="O181" s="9"/>
+      <c r="O181" s="5"/>
     </row>
     <row r="182" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C182" s="2"/>
@@ -3581,7 +3581,7 @@
       <c r="L182" s="2"/>
       <c r="M182" s="2"/>
       <c r="N182" s="2"/>
-      <c r="O182" s="9"/>
+      <c r="O182" s="5"/>
     </row>
     <row r="183" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C183" s="2"/>
@@ -3596,7 +3596,7 @@
       <c r="L183" s="2"/>
       <c r="M183" s="2"/>
       <c r="N183" s="2"/>
-      <c r="O183" s="9"/>
+      <c r="O183" s="5"/>
     </row>
     <row r="184" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C184" s="2"/>
@@ -3611,7 +3611,7 @@
       <c r="L184" s="2"/>
       <c r="M184" s="2"/>
       <c r="N184" s="2"/>
-      <c r="O184" s="9"/>
+      <c r="O184" s="5"/>
     </row>
     <row r="185" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C185" s="2"/>
@@ -3626,7 +3626,7 @@
       <c r="L185" s="2"/>
       <c r="M185" s="2"/>
       <c r="N185" s="2"/>
-      <c r="O185" s="9"/>
+      <c r="O185" s="5"/>
     </row>
     <row r="186" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C186" s="2"/>
@@ -3641,7 +3641,7 @@
       <c r="L186" s="2"/>
       <c r="M186" s="2"/>
       <c r="N186" s="2"/>
-      <c r="O186" s="9"/>
+      <c r="O186" s="5"/>
     </row>
     <row r="187" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C187" s="2"/>
@@ -3656,7 +3656,7 @@
       <c r="L187" s="2"/>
       <c r="M187" s="2"/>
       <c r="N187" s="2"/>
-      <c r="O187" s="9"/>
+      <c r="O187" s="5"/>
     </row>
     <row r="188" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C188" s="2"/>
@@ -3671,7 +3671,7 @@
       <c r="L188" s="2"/>
       <c r="M188" s="2"/>
       <c r="N188" s="2"/>
-      <c r="O188" s="9"/>
+      <c r="O188" s="5"/>
     </row>
     <row r="189" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C189" s="2"/>
@@ -3686,7 +3686,7 @@
       <c r="L189" s="2"/>
       <c r="M189" s="2"/>
       <c r="N189" s="2"/>
-      <c r="O189" s="9"/>
+      <c r="O189" s="5"/>
     </row>
     <row r="190" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C190" s="2"/>
@@ -3701,7 +3701,7 @@
       <c r="L190" s="2"/>
       <c r="M190" s="2"/>
       <c r="N190" s="2"/>
-      <c r="O190" s="9"/>
+      <c r="O190" s="5"/>
     </row>
     <row r="191" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C191" s="2"/>
@@ -3716,7 +3716,7 @@
       <c r="L191" s="2"/>
       <c r="M191" s="2"/>
       <c r="N191" s="2"/>
-      <c r="O191" s="9"/>
+      <c r="O191" s="5"/>
     </row>
     <row r="192" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C192" s="2"/>
@@ -3731,7 +3731,7 @@
       <c r="L192" s="2"/>
       <c r="M192" s="2"/>
       <c r="N192" s="2"/>
-      <c r="O192" s="9"/>
+      <c r="O192" s="5"/>
     </row>
     <row r="193" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C193" s="2"/>
@@ -3746,7 +3746,7 @@
       <c r="L193" s="2"/>
       <c r="M193" s="2"/>
       <c r="N193" s="2"/>
-      <c r="O193" s="9"/>
+      <c r="O193" s="5"/>
     </row>
     <row r="194" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C194" s="2"/>
@@ -3761,7 +3761,7 @@
       <c r="L194" s="2"/>
       <c r="M194" s="2"/>
       <c r="N194" s="2"/>
-      <c r="O194" s="9"/>
+      <c r="O194" s="5"/>
     </row>
     <row r="195" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C195" s="2"/>
@@ -3776,7 +3776,7 @@
       <c r="L195" s="2"/>
       <c r="M195" s="2"/>
       <c r="N195" s="2"/>
-      <c r="O195" s="9"/>
+      <c r="O195" s="5"/>
     </row>
     <row r="196" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C196" s="2"/>
@@ -3791,7 +3791,7 @@
       <c r="L196" s="2"/>
       <c r="M196" s="2"/>
       <c r="N196" s="2"/>
-      <c r="O196" s="9"/>
+      <c r="O196" s="5"/>
     </row>
     <row r="197" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C197" s="2"/>
@@ -3806,7 +3806,7 @@
       <c r="L197" s="2"/>
       <c r="M197" s="2"/>
       <c r="N197" s="2"/>
-      <c r="O197" s="9"/>
+      <c r="O197" s="5"/>
     </row>
     <row r="198" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C198" s="2"/>
@@ -3821,7 +3821,7 @@
       <c r="L198" s="2"/>
       <c r="M198" s="2"/>
       <c r="N198" s="2"/>
-      <c r="O198" s="9"/>
+      <c r="O198" s="5"/>
     </row>
     <row r="199" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C199" s="2"/>
@@ -3836,7 +3836,7 @@
       <c r="L199" s="2"/>
       <c r="M199" s="2"/>
       <c r="N199" s="2"/>
-      <c r="O199" s="9"/>
+      <c r="O199" s="5"/>
     </row>
     <row r="200" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C200" s="2"/>
@@ -3851,7 +3851,7 @@
       <c r="L200" s="2"/>
       <c r="M200" s="2"/>
       <c r="N200" s="2"/>
-      <c r="O200" s="9"/>
+      <c r="O200" s="5"/>
     </row>
     <row r="201" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C201" s="2"/>
@@ -3866,7 +3866,7 @@
       <c r="L201" s="2"/>
       <c r="M201" s="2"/>
       <c r="N201" s="2"/>
-      <c r="O201" s="9"/>
+      <c r="O201" s="5"/>
     </row>
     <row r="202" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C202" s="2"/>
@@ -3881,7 +3881,7 @@
       <c r="L202" s="2"/>
       <c r="M202" s="2"/>
       <c r="N202" s="2"/>
-      <c r="O202" s="9"/>
+      <c r="O202" s="5"/>
     </row>
     <row r="203" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C203" s="2"/>
@@ -3896,7 +3896,7 @@
       <c r="L203" s="2"/>
       <c r="M203" s="2"/>
       <c r="N203" s="2"/>
-      <c r="O203" s="9"/>
+      <c r="O203" s="5"/>
     </row>
     <row r="204" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C204" s="2"/>
@@ -3911,7 +3911,7 @@
       <c r="L204" s="2"/>
       <c r="M204" s="2"/>
       <c r="N204" s="2"/>
-      <c r="O204" s="9"/>
+      <c r="O204" s="5"/>
     </row>
     <row r="205" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C205" s="2"/>
@@ -3926,7 +3926,7 @@
       <c r="L205" s="2"/>
       <c r="M205" s="2"/>
       <c r="N205" s="2"/>
-      <c r="O205" s="9"/>
+      <c r="O205" s="5"/>
     </row>
     <row r="206" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C206" s="2"/>
@@ -3941,7 +3941,7 @@
       <c r="L206" s="2"/>
       <c r="M206" s="2"/>
       <c r="N206" s="2"/>
-      <c r="O206" s="9"/>
+      <c r="O206" s="5"/>
     </row>
     <row r="207" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C207" s="2"/>
@@ -3956,7 +3956,7 @@
       <c r="L207" s="2"/>
       <c r="M207" s="2"/>
       <c r="N207" s="2"/>
-      <c r="O207" s="9"/>
+      <c r="O207" s="5"/>
     </row>
     <row r="208" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C208" s="2"/>
@@ -3971,7 +3971,7 @@
       <c r="L208" s="2"/>
       <c r="M208" s="2"/>
       <c r="N208" s="2"/>
-      <c r="O208" s="9"/>
+      <c r="O208" s="5"/>
     </row>
     <row r="209" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C209" s="2"/>
@@ -3986,7 +3986,7 @@
       <c r="L209" s="2"/>
       <c r="M209" s="2"/>
       <c r="N209" s="2"/>
-      <c r="O209" s="9"/>
+      <c r="O209" s="5"/>
     </row>
     <row r="210" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C210" s="2"/>
@@ -4001,7 +4001,7 @@
       <c r="L210" s="2"/>
       <c r="M210" s="2"/>
       <c r="N210" s="2"/>
-      <c r="O210" s="9"/>
+      <c r="O210" s="5"/>
     </row>
     <row r="211" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C211" s="2"/>
@@ -4016,7 +4016,7 @@
       <c r="L211" s="2"/>
       <c r="M211" s="2"/>
       <c r="N211" s="2"/>
-      <c r="O211" s="9"/>
+      <c r="O211" s="5"/>
     </row>
     <row r="212" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C212" s="2"/>
@@ -4031,7 +4031,7 @@
       <c r="L212" s="2"/>
       <c r="M212" s="2"/>
       <c r="N212" s="2"/>
-      <c r="O212" s="9"/>
+      <c r="O212" s="5"/>
     </row>
     <row r="213" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C213" s="2"/>
@@ -4046,7 +4046,7 @@
       <c r="L213" s="2"/>
       <c r="M213" s="2"/>
       <c r="N213" s="2"/>
-      <c r="O213" s="9"/>
+      <c r="O213" s="5"/>
     </row>
     <row r="214" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C214" s="2"/>
@@ -4061,7 +4061,7 @@
       <c r="L214" s="2"/>
       <c r="M214" s="2"/>
       <c r="N214" s="2"/>
-      <c r="O214" s="9"/>
+      <c r="O214" s="5"/>
     </row>
     <row r="215" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C215" s="2"/>
@@ -4076,7 +4076,7 @@
       <c r="L215" s="2"/>
       <c r="M215" s="2"/>
       <c r="N215" s="2"/>
-      <c r="O215" s="9"/>
+      <c r="O215" s="5"/>
     </row>
     <row r="216" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C216" s="2"/>
@@ -4091,7 +4091,7 @@
       <c r="L216" s="2"/>
       <c r="M216" s="2"/>
       <c r="N216" s="2"/>
-      <c r="O216" s="9"/>
+      <c r="O216" s="5"/>
     </row>
     <row r="217" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C217" s="2"/>
@@ -4106,7 +4106,7 @@
       <c r="L217" s="2"/>
       <c r="M217" s="2"/>
       <c r="N217" s="2"/>
-      <c r="O217" s="9"/>
+      <c r="O217" s="5"/>
     </row>
     <row r="218" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C218" s="2"/>
@@ -4121,7 +4121,7 @@
       <c r="L218" s="2"/>
       <c r="M218" s="2"/>
       <c r="N218" s="2"/>
-      <c r="O218" s="9"/>
+      <c r="O218" s="5"/>
     </row>
     <row r="219" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C219" s="2"/>
@@ -4136,7 +4136,7 @@
       <c r="L219" s="2"/>
       <c r="M219" s="2"/>
       <c r="N219" s="2"/>
-      <c r="O219" s="9"/>
+      <c r="O219" s="5"/>
     </row>
     <row r="220" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C220" s="2"/>
@@ -4151,7 +4151,7 @@
       <c r="L220" s="2"/>
       <c r="M220" s="2"/>
       <c r="N220" s="2"/>
-      <c r="O220" s="9"/>
+      <c r="O220" s="5"/>
     </row>
     <row r="221" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C221" s="2"/>
@@ -4166,7 +4166,7 @@
       <c r="L221" s="2"/>
       <c r="M221" s="2"/>
       <c r="N221" s="2"/>
-      <c r="O221" s="9"/>
+      <c r="O221" s="5"/>
     </row>
     <row r="222" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C222" s="2"/>
@@ -4181,7 +4181,7 @@
       <c r="L222" s="2"/>
       <c r="M222" s="2"/>
       <c r="N222" s="2"/>
-      <c r="O222" s="9"/>
+      <c r="O222" s="5"/>
     </row>
     <row r="223" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C223" s="2"/>
@@ -4196,7 +4196,7 @@
       <c r="L223" s="2"/>
       <c r="M223" s="2"/>
       <c r="N223" s="2"/>
-      <c r="O223" s="9"/>
+      <c r="O223" s="5"/>
     </row>
     <row r="224" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C224" s="2"/>
@@ -4211,7 +4211,7 @@
       <c r="L224" s="2"/>
       <c r="M224" s="2"/>
       <c r="N224" s="2"/>
-      <c r="O224" s="9"/>
+      <c r="O224" s="5"/>
     </row>
     <row r="225" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C225" s="2"/>
@@ -4226,7 +4226,7 @@
       <c r="L225" s="2"/>
       <c r="M225" s="2"/>
       <c r="N225" s="2"/>
-      <c r="O225" s="9"/>
+      <c r="O225" s="5"/>
     </row>
     <row r="226" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C226" s="2"/>
@@ -4241,7 +4241,7 @@
       <c r="L226" s="2"/>
       <c r="M226" s="2"/>
       <c r="N226" s="2"/>
-      <c r="O226" s="9"/>
+      <c r="O226" s="5"/>
     </row>
     <row r="227" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C227" s="2"/>
@@ -4256,7 +4256,7 @@
       <c r="L227" s="2"/>
       <c r="M227" s="2"/>
       <c r="N227" s="2"/>
-      <c r="O227" s="9"/>
+      <c r="O227" s="5"/>
     </row>
     <row r="228" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C228" s="2"/>
@@ -4271,7 +4271,7 @@
       <c r="L228" s="2"/>
       <c r="M228" s="2"/>
       <c r="N228" s="2"/>
-      <c r="O228" s="9"/>
+      <c r="O228" s="5"/>
     </row>
     <row r="229" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C229" s="2"/>
@@ -4286,7 +4286,7 @@
       <c r="L229" s="2"/>
       <c r="M229" s="2"/>
       <c r="N229" s="2"/>
-      <c r="O229" s="9"/>
+      <c r="O229" s="5"/>
     </row>
     <row r="230" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C230" s="2"/>
@@ -4301,7 +4301,7 @@
       <c r="L230" s="2"/>
       <c r="M230" s="2"/>
       <c r="N230" s="2"/>
-      <c r="O230" s="9"/>
+      <c r="O230" s="5"/>
     </row>
     <row r="231" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C231" s="2"/>
@@ -4316,7 +4316,7 @@
       <c r="L231" s="2"/>
       <c r="M231" s="2"/>
       <c r="N231" s="2"/>
-      <c r="O231" s="9"/>
+      <c r="O231" s="5"/>
     </row>
     <row r="232" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C232" s="2"/>
@@ -4331,7 +4331,7 @@
       <c r="L232" s="2"/>
       <c r="M232" s="2"/>
       <c r="N232" s="2"/>
-      <c r="O232" s="9"/>
+      <c r="O232" s="5"/>
     </row>
     <row r="233" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C233" s="2"/>
@@ -4346,7 +4346,7 @@
       <c r="L233" s="2"/>
       <c r="M233" s="2"/>
       <c r="N233" s="2"/>
-      <c r="O233" s="9"/>
+      <c r="O233" s="5"/>
     </row>
     <row r="234" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C234" s="2"/>
@@ -4361,7 +4361,7 @@
       <c r="L234" s="2"/>
       <c r="M234" s="2"/>
       <c r="N234" s="2"/>
-      <c r="O234" s="9"/>
+      <c r="O234" s="5"/>
     </row>
     <row r="235" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C235" s="2"/>
@@ -4376,7 +4376,7 @@
       <c r="L235" s="2"/>
       <c r="M235" s="2"/>
       <c r="N235" s="2"/>
-      <c r="O235" s="9"/>
+      <c r="O235" s="5"/>
     </row>
     <row r="236" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C236" s="2"/>
@@ -4391,7 +4391,7 @@
       <c r="L236" s="2"/>
       <c r="M236" s="2"/>
       <c r="N236" s="2"/>
-      <c r="O236" s="9"/>
+      <c r="O236" s="5"/>
     </row>
     <row r="237" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C237" s="2"/>
@@ -4406,7 +4406,7 @@
       <c r="L237" s="2"/>
       <c r="M237" s="2"/>
       <c r="N237" s="2"/>
-      <c r="O237" s="9"/>
+      <c r="O237" s="5"/>
     </row>
     <row r="238" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C238" s="2"/>
@@ -4421,7 +4421,7 @@
       <c r="L238" s="2"/>
       <c r="M238" s="2"/>
       <c r="N238" s="2"/>
-      <c r="O238" s="9"/>
+      <c r="O238" s="5"/>
     </row>
     <row r="239" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C239" s="2"/>
@@ -4436,7 +4436,7 @@
       <c r="L239" s="2"/>
       <c r="M239" s="2"/>
       <c r="N239" s="2"/>
-      <c r="O239" s="9"/>
+      <c r="O239" s="5"/>
     </row>
     <row r="240" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C240" s="2"/>
@@ -4451,7 +4451,7 @@
       <c r="L240" s="2"/>
       <c r="M240" s="2"/>
       <c r="N240" s="2"/>
-      <c r="O240" s="9"/>
+      <c r="O240" s="5"/>
     </row>
     <row r="241" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C241" s="2"/>
@@ -4466,7 +4466,7 @@
       <c r="L241" s="2"/>
       <c r="M241" s="2"/>
       <c r="N241" s="2"/>
-      <c r="O241" s="9"/>
+      <c r="O241" s="5"/>
     </row>
     <row r="242" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C242" s="2"/>
@@ -4481,7 +4481,7 @@
       <c r="L242" s="2"/>
       <c r="M242" s="2"/>
       <c r="N242" s="2"/>
-      <c r="O242" s="9"/>
+      <c r="O242" s="5"/>
     </row>
     <row r="243" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C243" s="2"/>
@@ -4496,7 +4496,7 @@
       <c r="L243" s="2"/>
       <c r="M243" s="2"/>
       <c r="N243" s="2"/>
-      <c r="O243" s="9"/>
+      <c r="O243" s="5"/>
     </row>
     <row r="244" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C244" s="2"/>
@@ -4511,7 +4511,7 @@
       <c r="L244" s="2"/>
       <c r="M244" s="2"/>
       <c r="N244" s="2"/>
-      <c r="O244" s="9"/>
+      <c r="O244" s="5"/>
     </row>
     <row r="245" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C245" s="2"/>
@@ -4526,7 +4526,7 @@
       <c r="L245" s="2"/>
       <c r="M245" s="2"/>
       <c r="N245" s="2"/>
-      <c r="O245" s="9"/>
+      <c r="O245" s="5"/>
     </row>
     <row r="246" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C246" s="2"/>
@@ -4541,7 +4541,7 @@
       <c r="L246" s="2"/>
       <c r="M246" s="2"/>
       <c r="N246" s="2"/>
-      <c r="O246" s="9"/>
+      <c r="O246" s="5"/>
     </row>
     <row r="247" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C247" s="2"/>
@@ -4556,7 +4556,7 @@
       <c r="L247" s="2"/>
       <c r="M247" s="2"/>
       <c r="N247" s="2"/>
-      <c r="O247" s="9"/>
+      <c r="O247" s="5"/>
     </row>
     <row r="248" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C248" s="2"/>
@@ -4571,7 +4571,7 @@
       <c r="L248" s="2"/>
       <c r="M248" s="2"/>
       <c r="N248" s="2"/>
-      <c r="O248" s="9"/>
+      <c r="O248" s="5"/>
     </row>
     <row r="249" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C249" s="2"/>
@@ -4586,7 +4586,7 @@
       <c r="L249" s="2"/>
       <c r="M249" s="2"/>
       <c r="N249" s="2"/>
-      <c r="O249" s="9"/>
+      <c r="O249" s="5"/>
     </row>
     <row r="250" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C250" s="2"/>
@@ -4601,7 +4601,7 @@
       <c r="L250" s="2"/>
       <c r="M250" s="2"/>
       <c r="N250" s="2"/>
-      <c r="O250" s="9"/>
+      <c r="O250" s="5"/>
     </row>
     <row r="251" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C251" s="2"/>
@@ -4616,7 +4616,7 @@
       <c r="L251" s="2"/>
       <c r="M251" s="2"/>
       <c r="N251" s="2"/>
-      <c r="O251" s="9"/>
+      <c r="O251" s="5"/>
     </row>
     <row r="252" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C252" s="2"/>
@@ -4631,7 +4631,7 @@
       <c r="L252" s="2"/>
       <c r="M252" s="2"/>
       <c r="N252" s="2"/>
-      <c r="O252" s="9"/>
+      <c r="O252" s="5"/>
     </row>
     <row r="253" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C253" s="2"/>
@@ -4646,7 +4646,7 @@
       <c r="L253" s="2"/>
       <c r="M253" s="2"/>
       <c r="N253" s="2"/>
-      <c r="O253" s="9"/>
+      <c r="O253" s="5"/>
     </row>
     <row r="254" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C254" s="2"/>
@@ -4661,7 +4661,7 @@
       <c r="L254" s="2"/>
       <c r="M254" s="2"/>
       <c r="N254" s="2"/>
-      <c r="O254" s="9"/>
+      <c r="O254" s="5"/>
     </row>
     <row r="255" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C255" s="2"/>
@@ -4676,7 +4676,7 @@
       <c r="L255" s="2"/>
       <c r="M255" s="2"/>
       <c r="N255" s="2"/>
-      <c r="O255" s="9"/>
+      <c r="O255" s="5"/>
     </row>
     <row r="256" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C256" s="2"/>
@@ -4691,7 +4691,7 @@
       <c r="L256" s="2"/>
       <c r="M256" s="2"/>
       <c r="N256" s="2"/>
-      <c r="O256" s="9"/>
+      <c r="O256" s="5"/>
     </row>
     <row r="257" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C257" s="2"/>
@@ -4706,7 +4706,7 @@
       <c r="L257" s="2"/>
       <c r="M257" s="2"/>
       <c r="N257" s="2"/>
-      <c r="O257" s="9"/>
+      <c r="O257" s="5"/>
     </row>
     <row r="258" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C258" s="2"/>
@@ -4721,7 +4721,7 @@
       <c r="L258" s="2"/>
       <c r="M258" s="2"/>
       <c r="N258" s="2"/>
-      <c r="O258" s="9"/>
+      <c r="O258" s="5"/>
     </row>
     <row r="259" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C259" s="2"/>
@@ -4736,7 +4736,7 @@
       <c r="L259" s="2"/>
       <c r="M259" s="2"/>
       <c r="N259" s="2"/>
-      <c r="O259" s="9"/>
+      <c r="O259" s="5"/>
     </row>
     <row r="260" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C260" s="2"/>
@@ -4751,7 +4751,7 @@
       <c r="L260" s="2"/>
       <c r="M260" s="2"/>
       <c r="N260" s="2"/>
-      <c r="O260" s="9"/>
+      <c r="O260" s="5"/>
     </row>
     <row r="261" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C261" s="2"/>
@@ -4766,7 +4766,7 @@
       <c r="L261" s="2"/>
       <c r="M261" s="2"/>
       <c r="N261" s="2"/>
-      <c r="O261" s="9"/>
+      <c r="O261" s="5"/>
     </row>
     <row r="262" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C262" s="2"/>
@@ -4781,7 +4781,7 @@
       <c r="L262" s="2"/>
       <c r="M262" s="2"/>
       <c r="N262" s="2"/>
-      <c r="O262" s="9"/>
+      <c r="O262" s="5"/>
     </row>
     <row r="263" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C263" s="2"/>
@@ -4796,7 +4796,7 @@
       <c r="L263" s="2"/>
       <c r="M263" s="2"/>
       <c r="N263" s="2"/>
-      <c r="O263" s="9"/>
+      <c r="O263" s="5"/>
     </row>
     <row r="264" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C264" s="2"/>
@@ -4811,7 +4811,7 @@
       <c r="L264" s="2"/>
       <c r="M264" s="2"/>
       <c r="N264" s="2"/>
-      <c r="O264" s="9"/>
+      <c r="O264" s="5"/>
     </row>
     <row r="265" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C265" s="2"/>
@@ -4826,7 +4826,7 @@
       <c r="L265" s="2"/>
       <c r="M265" s="2"/>
       <c r="N265" s="2"/>
-      <c r="O265" s="9"/>
+      <c r="O265" s="5"/>
     </row>
     <row r="266" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C266" s="2"/>
@@ -4841,7 +4841,7 @@
       <c r="L266" s="2"/>
       <c r="M266" s="2"/>
       <c r="N266" s="2"/>
-      <c r="O266" s="9"/>
+      <c r="O266" s="5"/>
     </row>
     <row r="267" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C267" s="2"/>
@@ -4856,7 +4856,7 @@
       <c r="L267" s="2"/>
       <c r="M267" s="2"/>
       <c r="N267" s="2"/>
-      <c r="O267" s="9"/>
+      <c r="O267" s="5"/>
     </row>
     <row r="268" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C268" s="2"/>
@@ -4871,7 +4871,7 @@
       <c r="L268" s="2"/>
       <c r="M268" s="2"/>
       <c r="N268" s="2"/>
-      <c r="O268" s="9"/>
+      <c r="O268" s="5"/>
     </row>
     <row r="269" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C269" s="2"/>
@@ -4886,7 +4886,7 @@
       <c r="L269" s="2"/>
       <c r="M269" s="2"/>
       <c r="N269" s="2"/>
-      <c r="O269" s="9"/>
+      <c r="O269" s="5"/>
     </row>
     <row r="270" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C270" s="2"/>
@@ -4901,7 +4901,7 @@
       <c r="L270" s="2"/>
       <c r="M270" s="2"/>
       <c r="N270" s="2"/>
-      <c r="O270" s="9"/>
+      <c r="O270" s="5"/>
     </row>
     <row r="271" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C271" s="2"/>
@@ -4916,7 +4916,7 @@
       <c r="L271" s="2"/>
       <c r="M271" s="2"/>
       <c r="N271" s="2"/>
-      <c r="O271" s="9"/>
+      <c r="O271" s="5"/>
     </row>
     <row r="272" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C272" s="2"/>
@@ -4931,7 +4931,7 @@
       <c r="L272" s="2"/>
       <c r="M272" s="2"/>
       <c r="N272" s="2"/>
-      <c r="O272" s="9"/>
+      <c r="O272" s="5"/>
     </row>
     <row r="273" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C273" s="2"/>
@@ -4946,7 +4946,7 @@
       <c r="L273" s="2"/>
       <c r="M273" s="2"/>
       <c r="N273" s="2"/>
-      <c r="O273" s="9"/>
+      <c r="O273" s="5"/>
     </row>
     <row r="274" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C274" s="2"/>
@@ -4961,7 +4961,7 @@
       <c r="L274" s="2"/>
       <c r="M274" s="2"/>
       <c r="N274" s="2"/>
-      <c r="O274" s="9"/>
+      <c r="O274" s="5"/>
     </row>
     <row r="275" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C275" s="2"/>
@@ -4976,7 +4976,7 @@
       <c r="L275" s="2"/>
       <c r="M275" s="2"/>
       <c r="N275" s="2"/>
-      <c r="O275" s="9"/>
+      <c r="O275" s="5"/>
     </row>
     <row r="276" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C276" s="2"/>
@@ -4991,7 +4991,7 @@
       <c r="L276" s="2"/>
       <c r="M276" s="2"/>
       <c r="N276" s="2"/>
-      <c r="O276" s="9"/>
+      <c r="O276" s="5"/>
     </row>
     <row r="277" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C277" s="2"/>
@@ -5006,7 +5006,7 @@
       <c r="L277" s="2"/>
       <c r="M277" s="2"/>
       <c r="N277" s="2"/>
-      <c r="O277" s="9"/>
+      <c r="O277" s="5"/>
     </row>
     <row r="278" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C278" s="2"/>
@@ -5021,7 +5021,7 @@
       <c r="L278" s="2"/>
       <c r="M278" s="2"/>
       <c r="N278" s="2"/>
-      <c r="O278" s="9"/>
+      <c r="O278" s="5"/>
     </row>
     <row r="279" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C279" s="2"/>
@@ -5036,7 +5036,7 @@
       <c r="L279" s="2"/>
       <c r="M279" s="2"/>
       <c r="N279" s="2"/>
-      <c r="O279" s="9"/>
+      <c r="O279" s="5"/>
     </row>
     <row r="280" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C280" s="2"/>
@@ -5051,7 +5051,7 @@
       <c r="L280" s="2"/>
       <c r="M280" s="2"/>
       <c r="N280" s="2"/>
-      <c r="O280" s="9"/>
+      <c r="O280" s="5"/>
     </row>
     <row r="281" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C281" s="2"/>
@@ -5066,7 +5066,7 @@
       <c r="L281" s="2"/>
       <c r="M281" s="2"/>
       <c r="N281" s="2"/>
-      <c r="O281" s="9"/>
+      <c r="O281" s="5"/>
     </row>
     <row r="282" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C282" s="2"/>
@@ -5081,7 +5081,7 @@
       <c r="L282" s="2"/>
       <c r="M282" s="2"/>
       <c r="N282" s="2"/>
-      <c r="O282" s="9"/>
+      <c r="O282" s="5"/>
     </row>
     <row r="283" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C283" s="2"/>
@@ -5096,7 +5096,7 @@
       <c r="L283" s="2"/>
       <c r="M283" s="2"/>
       <c r="N283" s="2"/>
-      <c r="O283" s="9"/>
+      <c r="O283" s="5"/>
     </row>
     <row r="284" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C284" s="2"/>
@@ -5111,7 +5111,7 @@
       <c r="L284" s="2"/>
       <c r="M284" s="2"/>
       <c r="N284" s="2"/>
-      <c r="O284" s="9"/>
+      <c r="O284" s="5"/>
     </row>
     <row r="285" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C285" s="2"/>
@@ -5126,7 +5126,7 @@
       <c r="L285" s="2"/>
       <c r="M285" s="2"/>
       <c r="N285" s="2"/>
-      <c r="O285" s="9"/>
+      <c r="O285" s="5"/>
     </row>
     <row r="286" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C286" s="2"/>
@@ -5141,7 +5141,7 @@
       <c r="L286" s="2"/>
       <c r="M286" s="2"/>
       <c r="N286" s="2"/>
-      <c r="O286" s="9"/>
+      <c r="O286" s="5"/>
     </row>
     <row r="287" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C287" s="2"/>
@@ -5156,7 +5156,7 @@
       <c r="L287" s="2"/>
       <c r="M287" s="2"/>
       <c r="N287" s="2"/>
-      <c r="O287" s="9"/>
+      <c r="O287" s="5"/>
     </row>
     <row r="288" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C288" s="2"/>
@@ -5171,7 +5171,7 @@
       <c r="L288" s="2"/>
       <c r="M288" s="2"/>
       <c r="N288" s="2"/>
-      <c r="O288" s="9"/>
+      <c r="O288" s="5"/>
     </row>
     <row r="289" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C289" s="2"/>
@@ -5186,7 +5186,7 @@
       <c r="L289" s="2"/>
       <c r="M289" s="2"/>
       <c r="N289" s="2"/>
-      <c r="O289" s="9"/>
+      <c r="O289" s="5"/>
     </row>
     <row r="290" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C290" s="2"/>
@@ -5201,7 +5201,7 @@
       <c r="L290" s="2"/>
       <c r="M290" s="2"/>
       <c r="N290" s="2"/>
-      <c r="O290" s="9"/>
+      <c r="O290" s="5"/>
     </row>
     <row r="291" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C291" s="2"/>
@@ -5216,7 +5216,7 @@
       <c r="L291" s="2"/>
       <c r="M291" s="2"/>
       <c r="N291" s="2"/>
-      <c r="O291" s="9"/>
+      <c r="O291" s="5"/>
     </row>
     <row r="292" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C292" s="2"/>
@@ -5231,7 +5231,7 @@
       <c r="L292" s="2"/>
       <c r="M292" s="2"/>
       <c r="N292" s="2"/>
-      <c r="O292" s="9"/>
+      <c r="O292" s="5"/>
     </row>
     <row r="293" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C293" s="2"/>
@@ -5246,7 +5246,7 @@
       <c r="L293" s="2"/>
       <c r="M293" s="2"/>
       <c r="N293" s="2"/>
-      <c r="O293" s="9"/>
+      <c r="O293" s="5"/>
     </row>
     <row r="294" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C294" s="2"/>
@@ -5261,7 +5261,7 @@
       <c r="L294" s="2"/>
       <c r="M294" s="2"/>
       <c r="N294" s="2"/>
-      <c r="O294" s="9"/>
+      <c r="O294" s="5"/>
     </row>
     <row r="295" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C295" s="2"/>
@@ -5276,7 +5276,7 @@
       <c r="L295" s="2"/>
       <c r="M295" s="2"/>
       <c r="N295" s="2"/>
-      <c r="O295" s="9"/>
+      <c r="O295" s="5"/>
     </row>
     <row r="296" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C296" s="2"/>
@@ -5291,7 +5291,7 @@
       <c r="L296" s="2"/>
       <c r="M296" s="2"/>
       <c r="N296" s="2"/>
-      <c r="O296" s="9"/>
+      <c r="O296" s="5"/>
     </row>
     <row r="297" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C297" s="2"/>
@@ -5306,7 +5306,7 @@
       <c r="L297" s="2"/>
       <c r="M297" s="2"/>
       <c r="N297" s="2"/>
-      <c r="O297" s="9"/>
+      <c r="O297" s="5"/>
     </row>
     <row r="298" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C298" s="2"/>
@@ -5321,7 +5321,7 @@
       <c r="L298" s="2"/>
       <c r="M298" s="2"/>
       <c r="N298" s="2"/>
-      <c r="O298" s="9"/>
+      <c r="O298" s="5"/>
     </row>
     <row r="299" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C299" s="2"/>
@@ -5336,7 +5336,7 @@
       <c r="L299" s="2"/>
       <c r="M299" s="2"/>
       <c r="N299" s="2"/>
-      <c r="O299" s="9"/>
+      <c r="O299" s="5"/>
     </row>
     <row r="300" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C300" s="2"/>
@@ -5351,7 +5351,7 @@
       <c r="L300" s="2"/>
       <c r="M300" s="2"/>
       <c r="N300" s="2"/>
-      <c r="O300" s="9"/>
+      <c r="O300" s="5"/>
     </row>
     <row r="301" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C301" s="2"/>
@@ -5366,7 +5366,7 @@
       <c r="L301" s="2"/>
       <c r="M301" s="2"/>
       <c r="N301" s="2"/>
-      <c r="O301" s="9"/>
+      <c r="O301" s="5"/>
     </row>
     <row r="302" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C302" s="2"/>
@@ -5381,7 +5381,7 @@
       <c r="L302" s="2"/>
       <c r="M302" s="2"/>
       <c r="N302" s="2"/>
-      <c r="O302" s="9"/>
+      <c r="O302" s="5"/>
     </row>
     <row r="303" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C303" s="2"/>
@@ -5396,7 +5396,7 @@
       <c r="L303" s="2"/>
       <c r="M303" s="2"/>
       <c r="N303" s="2"/>
-      <c r="O303" s="9"/>
+      <c r="O303" s="5"/>
     </row>
     <row r="304" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C304" s="2"/>
@@ -5411,7 +5411,7 @@
       <c r="L304" s="2"/>
       <c r="M304" s="2"/>
       <c r="N304" s="2"/>
-      <c r="O304" s="9"/>
+      <c r="O304" s="5"/>
     </row>
     <row r="305" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C305" s="2"/>
@@ -5426,7 +5426,7 @@
       <c r="L305" s="2"/>
       <c r="M305" s="2"/>
       <c r="N305" s="2"/>
-      <c r="O305" s="9"/>
+      <c r="O305" s="5"/>
     </row>
     <row r="306" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C306" s="2"/>
@@ -5441,7 +5441,7 @@
       <c r="L306" s="2"/>
       <c r="M306" s="2"/>
       <c r="N306" s="2"/>
-      <c r="O306" s="9"/>
+      <c r="O306" s="5"/>
     </row>
     <row r="307" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C307" s="2"/>
@@ -5456,7 +5456,7 @@
       <c r="L307" s="2"/>
       <c r="M307" s="2"/>
       <c r="N307" s="2"/>
-      <c r="O307" s="9"/>
+      <c r="O307" s="5"/>
     </row>
     <row r="308" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C308" s="2"/>
@@ -5471,7 +5471,7 @@
       <c r="L308" s="2"/>
       <c r="M308" s="2"/>
       <c r="N308" s="2"/>
-      <c r="O308" s="9"/>
+      <c r="O308" s="5"/>
     </row>
     <row r="309" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C309" s="2"/>
@@ -5486,7 +5486,7 @@
       <c r="L309" s="2"/>
       <c r="M309" s="2"/>
       <c r="N309" s="2"/>
-      <c r="O309" s="9"/>
+      <c r="O309" s="5"/>
     </row>
     <row r="310" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C310" s="2"/>
@@ -5501,7 +5501,7 @@
       <c r="L310" s="2"/>
       <c r="M310" s="2"/>
       <c r="N310" s="2"/>
-      <c r="O310" s="9"/>
+      <c r="O310" s="5"/>
     </row>
     <row r="311" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C311" s="2"/>
@@ -5516,7 +5516,7 @@
       <c r="L311" s="2"/>
       <c r="M311" s="2"/>
       <c r="N311" s="2"/>
-      <c r="O311" s="9"/>
+      <c r="O311" s="5"/>
     </row>
     <row r="312" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C312" s="2"/>
@@ -5531,7 +5531,7 @@
       <c r="L312" s="2"/>
       <c r="M312" s="2"/>
       <c r="N312" s="2"/>
-      <c r="O312" s="9"/>
+      <c r="O312" s="5"/>
     </row>
     <row r="313" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C313" s="2"/>
@@ -5546,7 +5546,7 @@
       <c r="L313" s="2"/>
       <c r="M313" s="2"/>
       <c r="N313" s="2"/>
-      <c r="O313" s="9"/>
+      <c r="O313" s="5"/>
     </row>
     <row r="314" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C314" s="2"/>
@@ -5561,7 +5561,7 @@
       <c r="L314" s="2"/>
       <c r="M314" s="2"/>
       <c r="N314" s="2"/>
-      <c r="O314" s="9"/>
+      <c r="O314" s="5"/>
     </row>
     <row r="315" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C315" s="2"/>
@@ -5576,7 +5576,7 @@
       <c r="L315" s="2"/>
       <c r="M315" s="2"/>
       <c r="N315" s="2"/>
-      <c r="O315" s="9"/>
+      <c r="O315" s="5"/>
     </row>
     <row r="316" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C316" s="2"/>
@@ -5591,7 +5591,7 @@
       <c r="L316" s="2"/>
       <c r="M316" s="2"/>
       <c r="N316" s="2"/>
-      <c r="O316" s="9"/>
+      <c r="O316" s="5"/>
     </row>
     <row r="317" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C317" s="2"/>
@@ -5606,7 +5606,7 @@
       <c r="L317" s="2"/>
       <c r="M317" s="2"/>
       <c r="N317" s="2"/>
-      <c r="O317" s="9"/>
+      <c r="O317" s="5"/>
     </row>
     <row r="318" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C318" s="2"/>
@@ -5621,7 +5621,7 @@
       <c r="L318" s="2"/>
       <c r="M318" s="2"/>
       <c r="N318" s="2"/>
-      <c r="O318" s="9"/>
+      <c r="O318" s="5"/>
     </row>
     <row r="319" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C319" s="2"/>
@@ -5636,7 +5636,7 @@
       <c r="L319" s="2"/>
       <c r="M319" s="2"/>
       <c r="N319" s="2"/>
-      <c r="O319" s="9"/>
+      <c r="O319" s="5"/>
     </row>
     <row r="320" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C320" s="2"/>
@@ -5651,7 +5651,7 @@
       <c r="L320" s="2"/>
       <c r="M320" s="2"/>
       <c r="N320" s="2"/>
-      <c r="O320" s="9"/>
+      <c r="O320" s="5"/>
     </row>
     <row r="321" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C321" s="2"/>
@@ -5666,7 +5666,7 @@
       <c r="L321" s="2"/>
       <c r="M321" s="2"/>
       <c r="N321" s="2"/>
-      <c r="O321" s="9"/>
+      <c r="O321" s="5"/>
     </row>
     <row r="322" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C322" s="2"/>
@@ -5681,7 +5681,7 @@
       <c r="L322" s="2"/>
       <c r="M322" s="2"/>
       <c r="N322" s="2"/>
-      <c r="O322" s="9"/>
+      <c r="O322" s="5"/>
     </row>
     <row r="323" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C323" s="2"/>
@@ -5696,7 +5696,7 @@
       <c r="L323" s="2"/>
       <c r="M323" s="2"/>
       <c r="N323" s="2"/>
-      <c r="O323" s="9"/>
+      <c r="O323" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/templates/vacation_map_template.xlsx
+++ b/templates/vacation_map_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geral\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C58B953A-079F-4A0D-A29B-AA2FD4BEE4EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00E0B5D8-86E1-47D1-B0E5-7ACC5D6380C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B7894565-86C4-4C3D-8BBD-69A912659748}"/>
   </bookViews>
@@ -75,22 +75,6 @@
     <t>DEZEMBRO</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Associação Humanitária de Bombeiros de Faro </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>"Cruz Lusa"</t>
-    </r>
-  </si>
-  <si>
     <t>Rua Comandante Francisco Manuel, 7 a 13 | 8000-250 | Faro</t>
   </si>
   <si>
@@ -105,12 +89,28 @@
   <si>
     <t>Dias Úteis</t>
   </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Associação Humanitária de Bombeiros de Faro </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="13"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"Cruz Lusa"</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -149,7 +149,7 @@
     </font>
     <font>
       <b/>
-      <sz val="14"/>
+      <sz val="13"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -157,15 +157,22 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="13"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="13"/>
       <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="13"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -173,7 +180,7 @@
     <font>
       <b/>
       <u/>
-      <sz val="11"/>
+      <sz val="13"/>
       <color rgb="FF002060"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -181,7 +188,7 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="18"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -393,16 +400,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -420,53 +424,57 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -490,15 +498,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>650875</xdr:colOff>
+      <xdr:colOff>555625</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>57150</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>1485900</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>16872</xdr:rowOff>
+      <xdr:colOff>1390650</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>121647</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -527,7 +535,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="841375" y="57150"/>
+          <a:off x="746125" y="57150"/>
           <a:ext cx="835025" cy="912222"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -845,778 +853,778 @@
   <cols>
     <col min="1" max="1" width="2.85546875" customWidth="1"/>
     <col min="2" max="2" width="24.28515625" customWidth="1"/>
-    <col min="3" max="14" width="17.140625" style="1" customWidth="1"/>
-    <col min="15" max="15" width="10" style="4" customWidth="1"/>
+    <col min="3" max="14" width="17.85546875" style="1" customWidth="1"/>
+    <col min="15" max="15" width="10" style="3" customWidth="1"/>
     <col min="16" max="16" width="2.85546875" customWidth="1"/>
     <col min="17" max="16384" width="9.140625" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="C2" s="3" t="s">
+    <row r="2" spans="2:15" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="C2" s="23" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="2:15" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="C3" s="24" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="C3" t="s">
+    <row r="4" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="C4" s="25" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="C4" s="10" t="s">
+    <row r="6" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B6" s="26"/>
+      <c r="C6" s="26"/>
+      <c r="D6" s="26"/>
+      <c r="E6" s="26"/>
+      <c r="F6" s="26"/>
+      <c r="G6" s="26"/>
+      <c r="H6" s="26"/>
+      <c r="I6" s="26"/>
+      <c r="J6" s="26"/>
+      <c r="K6" s="26"/>
+      <c r="L6" s="26"/>
+      <c r="M6" s="26"/>
+      <c r="N6" s="26"/>
+      <c r="O6" s="26"/>
+    </row>
+    <row r="7" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B7" s="26"/>
+      <c r="C7" s="26"/>
+      <c r="D7" s="26"/>
+      <c r="E7" s="26"/>
+      <c r="F7" s="26"/>
+      <c r="G7" s="26"/>
+      <c r="H7" s="26"/>
+      <c r="I7" s="26"/>
+      <c r="J7" s="26"/>
+      <c r="K7" s="26"/>
+      <c r="L7" s="26"/>
+      <c r="M7" s="26"/>
+      <c r="N7" s="26"/>
+      <c r="O7" s="26"/>
+    </row>
+    <row r="8" spans="2:15" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="2:15" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="C9" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="D9" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="E9" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="F9" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="G9" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="H9" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="I9" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="J9" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="K9" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="L9" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="M9" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="N9" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="O9" s="22" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B10" s="11"/>
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="12"/>
+      <c r="H10" s="12"/>
+      <c r="I10" s="12"/>
+      <c r="J10" s="12"/>
+      <c r="K10" s="12"/>
+      <c r="L10" s="12"/>
+      <c r="M10" s="12"/>
+      <c r="N10" s="13"/>
+      <c r="O10" s="14"/>
+    </row>
+    <row r="11" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B11" s="11"/>
+      <c r="C11" s="12"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="12"/>
+      <c r="H11" s="12"/>
+      <c r="I11" s="12"/>
+      <c r="J11" s="12"/>
+      <c r="K11" s="12"/>
+      <c r="L11" s="12"/>
+      <c r="M11" s="12"/>
+      <c r="N11" s="13"/>
+      <c r="O11" s="14"/>
+    </row>
+    <row r="12" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B12" s="11"/>
+      <c r="C12" s="12"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="12"/>
+      <c r="H12" s="12"/>
+      <c r="I12" s="12"/>
+      <c r="J12" s="12"/>
+      <c r="K12" s="12"/>
+      <c r="L12" s="12"/>
+      <c r="M12" s="12"/>
+      <c r="N12" s="13"/>
+      <c r="O12" s="14"/>
+    </row>
+    <row r="13" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B13" s="11"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12"/>
+      <c r="G13" s="12"/>
+      <c r="H13" s="12"/>
+      <c r="I13" s="12"/>
+      <c r="J13" s="12"/>
+      <c r="K13" s="12"/>
+      <c r="L13" s="12"/>
+      <c r="M13" s="12"/>
+      <c r="N13" s="13"/>
+      <c r="O13" s="14"/>
+    </row>
+    <row r="14" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B14" s="11"/>
+      <c r="C14" s="12"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="12"/>
+      <c r="G14" s="12"/>
+      <c r="H14" s="12"/>
+      <c r="I14" s="12"/>
+      <c r="J14" s="12"/>
+      <c r="K14" s="12"/>
+      <c r="L14" s="12"/>
+      <c r="M14" s="12"/>
+      <c r="N14" s="13"/>
+      <c r="O14" s="14"/>
+    </row>
+    <row r="15" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B15" s="11"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="12"/>
+      <c r="G15" s="12"/>
+      <c r="H15" s="12"/>
+      <c r="I15" s="12"/>
+      <c r="J15" s="12"/>
+      <c r="K15" s="12"/>
+      <c r="L15" s="12"/>
+      <c r="M15" s="12"/>
+      <c r="N15" s="13"/>
+      <c r="O15" s="14"/>
+    </row>
+    <row r="16" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B16" s="11"/>
+      <c r="C16" s="12"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="12"/>
+      <c r="F16" s="12"/>
+      <c r="G16" s="12"/>
+      <c r="H16" s="12"/>
+      <c r="I16" s="12"/>
+      <c r="J16" s="12"/>
+      <c r="K16" s="12"/>
+      <c r="L16" s="12"/>
+      <c r="M16" s="12"/>
+      <c r="N16" s="13"/>
+      <c r="O16" s="14"/>
+    </row>
+    <row r="17" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B17" s="11"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="12"/>
+      <c r="G17" s="12"/>
+      <c r="H17" s="12"/>
+      <c r="I17" s="12"/>
+      <c r="J17" s="12"/>
+      <c r="K17" s="12"/>
+      <c r="L17" s="12"/>
+      <c r="M17" s="12"/>
+      <c r="N17" s="13"/>
+      <c r="O17" s="14"/>
+    </row>
+    <row r="18" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B18" s="11"/>
+      <c r="C18" s="12"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="12"/>
+      <c r="G18" s="12"/>
+      <c r="H18" s="12"/>
+      <c r="I18" s="12"/>
+      <c r="J18" s="12"/>
+      <c r="K18" s="12"/>
+      <c r="L18" s="12"/>
+      <c r="M18" s="12"/>
+      <c r="N18" s="13"/>
+      <c r="O18" s="14"/>
+    </row>
+    <row r="19" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B19" s="11"/>
+      <c r="C19" s="12"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="12"/>
+      <c r="F19" s="12"/>
+      <c r="G19" s="12"/>
+      <c r="H19" s="12"/>
+      <c r="I19" s="12"/>
+      <c r="J19" s="12"/>
+      <c r="K19" s="12"/>
+      <c r="L19" s="12"/>
+      <c r="M19" s="12"/>
+      <c r="N19" s="13"/>
+      <c r="O19" s="14"/>
+    </row>
+    <row r="20" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B20" s="11"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="12"/>
+      <c r="G20" s="12"/>
+      <c r="H20" s="12"/>
+      <c r="I20" s="12"/>
+      <c r="J20" s="12"/>
+      <c r="K20" s="12"/>
+      <c r="L20" s="12"/>
+      <c r="M20" s="12"/>
+      <c r="N20" s="13"/>
+      <c r="O20" s="14"/>
+    </row>
+    <row r="21" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B21" s="11"/>
+      <c r="C21" s="12"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="12"/>
+      <c r="G21" s="12"/>
+      <c r="H21" s="12"/>
+      <c r="I21" s="12"/>
+      <c r="J21" s="12"/>
+      <c r="K21" s="12"/>
+      <c r="L21" s="12"/>
+      <c r="M21" s="12"/>
+      <c r="N21" s="13"/>
+      <c r="O21" s="14"/>
+    </row>
+    <row r="22" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B22" s="11"/>
+      <c r="C22" s="12"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="12"/>
+      <c r="G22" s="12"/>
+      <c r="H22" s="12"/>
+      <c r="I22" s="12"/>
+      <c r="J22" s="12"/>
+      <c r="K22" s="12"/>
+      <c r="L22" s="12"/>
+      <c r="M22" s="12"/>
+      <c r="N22" s="13"/>
+      <c r="O22" s="14"/>
+    </row>
+    <row r="23" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B23" s="11"/>
+      <c r="C23" s="12"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="12"/>
+      <c r="G23" s="12"/>
+      <c r="H23" s="12"/>
+      <c r="I23" s="12"/>
+      <c r="J23" s="12"/>
+      <c r="K23" s="12"/>
+      <c r="L23" s="12"/>
+      <c r="M23" s="12"/>
+      <c r="N23" s="13"/>
+      <c r="O23" s="14"/>
+    </row>
+    <row r="24" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B24" s="11"/>
+      <c r="C24" s="12"/>
+      <c r="D24" s="12"/>
+      <c r="E24" s="12"/>
+      <c r="F24" s="12"/>
+      <c r="G24" s="12"/>
+      <c r="H24" s="12"/>
+      <c r="I24" s="12"/>
+      <c r="J24" s="12"/>
+      <c r="K24" s="12"/>
+      <c r="L24" s="12"/>
+      <c r="M24" s="12"/>
+      <c r="N24" s="13"/>
+      <c r="O24" s="14"/>
+    </row>
+    <row r="25" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B25" s="11"/>
+      <c r="C25" s="12"/>
+      <c r="D25" s="12"/>
+      <c r="E25" s="12"/>
+      <c r="F25" s="12"/>
+      <c r="G25" s="12"/>
+      <c r="H25" s="12"/>
+      <c r="I25" s="12"/>
+      <c r="J25" s="12"/>
+      <c r="K25" s="12"/>
+      <c r="L25" s="12"/>
+      <c r="M25" s="12"/>
+      <c r="N25" s="13"/>
+      <c r="O25" s="14"/>
+    </row>
+    <row r="26" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B26" s="11"/>
+      <c r="C26" s="12"/>
+      <c r="D26" s="12"/>
+      <c r="E26" s="12"/>
+      <c r="F26" s="12"/>
+      <c r="G26" s="12"/>
+      <c r="H26" s="12"/>
+      <c r="I26" s="12"/>
+      <c r="J26" s="12"/>
+      <c r="K26" s="12"/>
+      <c r="L26" s="12"/>
+      <c r="M26" s="12"/>
+      <c r="N26" s="13"/>
+      <c r="O26" s="14"/>
+    </row>
+    <row r="27" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B27" s="11"/>
+      <c r="C27" s="12"/>
+      <c r="D27" s="12"/>
+      <c r="E27" s="12"/>
+      <c r="F27" s="12"/>
+      <c r="G27" s="12"/>
+      <c r="H27" s="12"/>
+      <c r="I27" s="12"/>
+      <c r="J27" s="12"/>
+      <c r="K27" s="12"/>
+      <c r="L27" s="12"/>
+      <c r="M27" s="12"/>
+      <c r="N27" s="13"/>
+      <c r="O27" s="14"/>
+    </row>
+    <row r="28" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B28" s="11"/>
+      <c r="C28" s="12"/>
+      <c r="D28" s="12"/>
+      <c r="E28" s="12"/>
+      <c r="F28" s="12"/>
+      <c r="G28" s="12"/>
+      <c r="H28" s="12"/>
+      <c r="I28" s="12"/>
+      <c r="J28" s="12"/>
+      <c r="K28" s="12"/>
+      <c r="L28" s="12"/>
+      <c r="M28" s="12"/>
+      <c r="N28" s="13"/>
+      <c r="O28" s="14"/>
+    </row>
+    <row r="29" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B29" s="11"/>
+      <c r="C29" s="12"/>
+      <c r="D29" s="12"/>
+      <c r="E29" s="12"/>
+      <c r="F29" s="12"/>
+      <c r="G29" s="12"/>
+      <c r="H29" s="12"/>
+      <c r="I29" s="12"/>
+      <c r="J29" s="12"/>
+      <c r="K29" s="12"/>
+      <c r="L29" s="12"/>
+      <c r="M29" s="12"/>
+      <c r="N29" s="13"/>
+      <c r="O29" s="14"/>
+    </row>
+    <row r="30" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B30" s="11"/>
+      <c r="C30" s="12"/>
+      <c r="D30" s="12"/>
+      <c r="E30" s="12"/>
+      <c r="F30" s="12"/>
+      <c r="G30" s="12"/>
+      <c r="H30" s="12"/>
+      <c r="I30" s="12"/>
+      <c r="J30" s="12"/>
+      <c r="K30" s="12"/>
+      <c r="L30" s="12"/>
+      <c r="M30" s="12"/>
+      <c r="N30" s="13"/>
+      <c r="O30" s="14"/>
+    </row>
+    <row r="31" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B31" s="11"/>
+      <c r="C31" s="12"/>
+      <c r="D31" s="12"/>
+      <c r="E31" s="12"/>
+      <c r="F31" s="12"/>
+      <c r="G31" s="12"/>
+      <c r="H31" s="12"/>
+      <c r="I31" s="12"/>
+      <c r="J31" s="12"/>
+      <c r="K31" s="12"/>
+      <c r="L31" s="12"/>
+      <c r="M31" s="12"/>
+      <c r="N31" s="13"/>
+      <c r="O31" s="14"/>
+    </row>
+    <row r="32" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B32" s="11"/>
+      <c r="C32" s="12"/>
+      <c r="D32" s="12"/>
+      <c r="E32" s="12"/>
+      <c r="F32" s="12"/>
+      <c r="G32" s="12"/>
+      <c r="H32" s="12"/>
+      <c r="I32" s="12"/>
+      <c r="J32" s="12"/>
+      <c r="K32" s="12"/>
+      <c r="L32" s="12"/>
+      <c r="M32" s="12"/>
+      <c r="N32" s="13"/>
+      <c r="O32" s="14"/>
+    </row>
+    <row r="33" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B33" s="11"/>
+      <c r="C33" s="12"/>
+      <c r="D33" s="12"/>
+      <c r="E33" s="12"/>
+      <c r="F33" s="12"/>
+      <c r="G33" s="12"/>
+      <c r="H33" s="12"/>
+      <c r="I33" s="12"/>
+      <c r="J33" s="12"/>
+      <c r="K33" s="12"/>
+      <c r="L33" s="12"/>
+      <c r="M33" s="12"/>
+      <c r="N33" s="13"/>
+      <c r="O33" s="14"/>
+    </row>
+    <row r="34" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B34" s="11"/>
+      <c r="C34" s="12"/>
+      <c r="D34" s="12"/>
+      <c r="E34" s="12"/>
+      <c r="F34" s="12"/>
+      <c r="G34" s="12"/>
+      <c r="H34" s="12"/>
+      <c r="I34" s="12"/>
+      <c r="J34" s="12"/>
+      <c r="K34" s="12"/>
+      <c r="L34" s="12"/>
+      <c r="M34" s="12"/>
+      <c r="N34" s="13"/>
+      <c r="O34" s="14"/>
+    </row>
+    <row r="35" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B35" s="11"/>
+      <c r="C35" s="12"/>
+      <c r="D35" s="12"/>
+      <c r="E35" s="12"/>
+      <c r="F35" s="12"/>
+      <c r="G35" s="12"/>
+      <c r="H35" s="12"/>
+      <c r="I35" s="12"/>
+      <c r="J35" s="12"/>
+      <c r="K35" s="12"/>
+      <c r="L35" s="12"/>
+      <c r="M35" s="12"/>
+      <c r="N35" s="13"/>
+      <c r="O35" s="14"/>
+    </row>
+    <row r="36" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B36" s="11"/>
+      <c r="C36" s="12"/>
+      <c r="D36" s="12"/>
+      <c r="E36" s="12"/>
+      <c r="F36" s="12"/>
+      <c r="G36" s="12"/>
+      <c r="H36" s="12"/>
+      <c r="I36" s="12"/>
+      <c r="J36" s="12"/>
+      <c r="K36" s="12"/>
+      <c r="L36" s="12"/>
+      <c r="M36" s="12"/>
+      <c r="N36" s="13"/>
+      <c r="O36" s="14"/>
+    </row>
+    <row r="37" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B37" s="11"/>
+      <c r="C37" s="12"/>
+      <c r="D37" s="12"/>
+      <c r="E37" s="12"/>
+      <c r="F37" s="12"/>
+      <c r="G37" s="12"/>
+      <c r="H37" s="12"/>
+      <c r="I37" s="12"/>
+      <c r="J37" s="12"/>
+      <c r="K37" s="12"/>
+      <c r="L37" s="12"/>
+      <c r="M37" s="12"/>
+      <c r="N37" s="13"/>
+      <c r="O37" s="14"/>
+    </row>
+    <row r="38" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B38" s="11"/>
+      <c r="C38" s="12"/>
+      <c r="D38" s="12"/>
+      <c r="E38" s="12"/>
+      <c r="F38" s="12"/>
+      <c r="G38" s="12"/>
+      <c r="H38" s="12"/>
+      <c r="I38" s="12"/>
+      <c r="J38" s="12"/>
+      <c r="K38" s="12"/>
+      <c r="L38" s="12"/>
+      <c r="M38" s="12"/>
+      <c r="N38" s="13"/>
+      <c r="O38" s="14"/>
+    </row>
+    <row r="39" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B39" s="11"/>
+      <c r="C39" s="12"/>
+      <c r="D39" s="12"/>
+      <c r="E39" s="12"/>
+      <c r="F39" s="12"/>
+      <c r="G39" s="12"/>
+      <c r="H39" s="12"/>
+      <c r="I39" s="12"/>
+      <c r="J39" s="12"/>
+      <c r="K39" s="12"/>
+      <c r="L39" s="12"/>
+      <c r="M39" s="12"/>
+      <c r="N39" s="13"/>
+      <c r="O39" s="14"/>
+    </row>
+    <row r="40" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B40" s="11"/>
+      <c r="C40" s="12"/>
+      <c r="D40" s="12"/>
+      <c r="E40" s="12"/>
+      <c r="F40" s="12"/>
+      <c r="G40" s="12"/>
+      <c r="H40" s="12"/>
+      <c r="I40" s="12"/>
+      <c r="J40" s="12"/>
+      <c r="K40" s="12"/>
+      <c r="L40" s="12"/>
+      <c r="M40" s="12"/>
+      <c r="N40" s="13"/>
+      <c r="O40" s="14"/>
+    </row>
+    <row r="41" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B41" s="11"/>
+      <c r="C41" s="12"/>
+      <c r="D41" s="12"/>
+      <c r="E41" s="12"/>
+      <c r="F41" s="12"/>
+      <c r="G41" s="12"/>
+      <c r="H41" s="12"/>
+      <c r="I41" s="12"/>
+      <c r="J41" s="12"/>
+      <c r="K41" s="12"/>
+      <c r="L41" s="12"/>
+      <c r="M41" s="12"/>
+      <c r="N41" s="13"/>
+      <c r="O41" s="14"/>
+    </row>
+    <row r="42" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B42" s="11"/>
+      <c r="C42" s="12"/>
+      <c r="D42" s="12"/>
+      <c r="E42" s="12"/>
+      <c r="F42" s="12"/>
+      <c r="G42" s="12"/>
+      <c r="H42" s="12"/>
+      <c r="I42" s="12"/>
+      <c r="J42" s="12"/>
+      <c r="K42" s="12"/>
+      <c r="L42" s="12"/>
+      <c r="M42" s="12"/>
+      <c r="N42" s="13"/>
+      <c r="O42" s="14"/>
+    </row>
+    <row r="43" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B43" s="11"/>
+      <c r="C43" s="12"/>
+      <c r="D43" s="12"/>
+      <c r="E43" s="12"/>
+      <c r="F43" s="12"/>
+      <c r="G43" s="12"/>
+      <c r="H43" s="12"/>
+      <c r="I43" s="12"/>
+      <c r="J43" s="12"/>
+      <c r="K43" s="12"/>
+      <c r="L43" s="12"/>
+      <c r="M43" s="12"/>
+      <c r="N43" s="13"/>
+      <c r="O43" s="14"/>
+    </row>
+    <row r="44" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B44" s="11"/>
+      <c r="C44" s="12"/>
+      <c r="D44" s="12"/>
+      <c r="E44" s="12"/>
+      <c r="F44" s="12"/>
+      <c r="G44" s="12"/>
+      <c r="H44" s="12"/>
+      <c r="I44" s="12"/>
+      <c r="J44" s="12"/>
+      <c r="K44" s="12"/>
+      <c r="L44" s="12"/>
+      <c r="M44" s="12"/>
+      <c r="N44" s="13"/>
+      <c r="O44" s="14"/>
+    </row>
+    <row r="45" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B45" s="11"/>
+      <c r="C45" s="12"/>
+      <c r="D45" s="12"/>
+      <c r="E45" s="12"/>
+      <c r="F45" s="12"/>
+      <c r="G45" s="12"/>
+      <c r="H45" s="12"/>
+      <c r="I45" s="12"/>
+      <c r="J45" s="12"/>
+      <c r="K45" s="12"/>
+      <c r="L45" s="12"/>
+      <c r="M45" s="12"/>
+      <c r="N45" s="13"/>
+      <c r="O45" s="14"/>
+    </row>
+    <row r="46" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B46" s="11"/>
+      <c r="C46" s="12"/>
+      <c r="D46" s="12"/>
+      <c r="E46" s="12"/>
+      <c r="F46" s="12"/>
+      <c r="G46" s="12"/>
+      <c r="H46" s="12"/>
+      <c r="I46" s="12"/>
+      <c r="J46" s="12"/>
+      <c r="K46" s="12"/>
+      <c r="L46" s="12"/>
+      <c r="M46" s="12"/>
+      <c r="N46" s="13"/>
+      <c r="O46" s="14"/>
+    </row>
+    <row r="47" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B47" s="11"/>
+      <c r="C47" s="12"/>
+      <c r="D47" s="12"/>
+      <c r="E47" s="12"/>
+      <c r="F47" s="12"/>
+      <c r="G47" s="12"/>
+      <c r="H47" s="12"/>
+      <c r="I47" s="12"/>
+      <c r="J47" s="12"/>
+      <c r="K47" s="12"/>
+      <c r="L47" s="12"/>
+      <c r="M47" s="12"/>
+      <c r="N47" s="13"/>
+      <c r="O47" s="14"/>
+    </row>
+    <row r="48" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B48" s="11"/>
+      <c r="C48" s="12"/>
+      <c r="D48" s="12"/>
+      <c r="E48" s="12"/>
+      <c r="F48" s="12"/>
+      <c r="G48" s="12"/>
+      <c r="H48" s="12"/>
+      <c r="I48" s="12"/>
+      <c r="J48" s="12"/>
+      <c r="K48" s="12"/>
+      <c r="L48" s="12"/>
+      <c r="M48" s="12"/>
+      <c r="N48" s="13"/>
+      <c r="O48" s="14"/>
+    </row>
+    <row r="49" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B49" s="15"/>
+      <c r="C49" s="16"/>
+      <c r="D49" s="16"/>
+      <c r="E49" s="16"/>
+      <c r="F49" s="16"/>
+      <c r="G49" s="16"/>
+      <c r="H49" s="16"/>
+      <c r="I49" s="16"/>
+      <c r="J49" s="16"/>
+      <c r="K49" s="16"/>
+      <c r="L49" s="16"/>
+      <c r="M49" s="16"/>
+      <c r="N49" s="17"/>
+      <c r="O49" s="18"/>
+    </row>
+    <row r="50" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B50" s="5"/>
+      <c r="C50" s="6"/>
+      <c r="D50" s="6"/>
+      <c r="E50" s="6"/>
+      <c r="F50" s="6"/>
+      <c r="G50" s="6"/>
+      <c r="H50" s="6"/>
+      <c r="I50" s="6"/>
+      <c r="J50" s="6"/>
+      <c r="K50" s="6"/>
+      <c r="L50" s="6"/>
+      <c r="M50" s="6"/>
+      <c r="N50" s="6"/>
+      <c r="O50" s="7"/>
+    </row>
+    <row r="51" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="C51" s="2"/>
+      <c r="D51" s="9" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B6" s="11"/>
-      <c r="C6" s="11"/>
-      <c r="D6" s="11"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="11"/>
-      <c r="H6" s="11"/>
-      <c r="I6" s="11"/>
-      <c r="J6" s="11"/>
-      <c r="K6" s="11"/>
-      <c r="L6" s="11"/>
-      <c r="M6" s="11"/>
-      <c r="N6" s="11"/>
-      <c r="O6" s="11"/>
-    </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B7" s="11"/>
-      <c r="C7" s="11"/>
-      <c r="D7" s="11"/>
-      <c r="E7" s="11"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="11"/>
-      <c r="H7" s="11"/>
-      <c r="I7" s="11"/>
-      <c r="J7" s="11"/>
-      <c r="K7" s="11"/>
-      <c r="L7" s="11"/>
-      <c r="M7" s="11"/>
-      <c r="N7" s="11"/>
-      <c r="O7" s="11"/>
-    </row>
-    <row r="8" spans="2:15" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9" spans="2:15" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="C9" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="D9" s="23" t="s">
-        <v>2</v>
-      </c>
-      <c r="E9" s="23" t="s">
-        <v>3</v>
-      </c>
-      <c r="F9" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="G9" s="23" t="s">
-        <v>5</v>
-      </c>
-      <c r="H9" s="23" t="s">
-        <v>6</v>
-      </c>
-      <c r="I9" s="23" t="s">
-        <v>7</v>
-      </c>
-      <c r="J9" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="K9" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="L9" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="M9" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="N9" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="O9" s="25" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B10" s="14"/>
-      <c r="C10" s="15"/>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="15"/>
-      <c r="G10" s="15"/>
-      <c r="H10" s="15"/>
-      <c r="I10" s="15"/>
-      <c r="J10" s="15"/>
-      <c r="K10" s="15"/>
-      <c r="L10" s="15"/>
-      <c r="M10" s="15"/>
-      <c r="N10" s="16"/>
-      <c r="O10" s="17"/>
-    </row>
-    <row r="11" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B11" s="14"/>
-      <c r="C11" s="15"/>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="15"/>
-      <c r="G11" s="15"/>
-      <c r="H11" s="15"/>
-      <c r="I11" s="15"/>
-      <c r="J11" s="15"/>
-      <c r="K11" s="15"/>
-      <c r="L11" s="15"/>
-      <c r="M11" s="15"/>
-      <c r="N11" s="16"/>
-      <c r="O11" s="17"/>
-    </row>
-    <row r="12" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B12" s="14"/>
-      <c r="C12" s="15"/>
-      <c r="D12" s="15"/>
-      <c r="E12" s="15"/>
-      <c r="F12" s="15"/>
-      <c r="G12" s="15"/>
-      <c r="H12" s="15"/>
-      <c r="I12" s="15"/>
-      <c r="J12" s="15"/>
-      <c r="K12" s="15"/>
-      <c r="L12" s="15"/>
-      <c r="M12" s="15"/>
-      <c r="N12" s="16"/>
-      <c r="O12" s="17"/>
-    </row>
-    <row r="13" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B13" s="14"/>
-      <c r="C13" s="15"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="15"/>
-      <c r="H13" s="15"/>
-      <c r="I13" s="15"/>
-      <c r="J13" s="15"/>
-      <c r="K13" s="15"/>
-      <c r="L13" s="15"/>
-      <c r="M13" s="15"/>
-      <c r="N13" s="16"/>
-      <c r="O13" s="17"/>
-    </row>
-    <row r="14" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B14" s="14"/>
-      <c r="C14" s="15"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="15"/>
-      <c r="G14" s="15"/>
-      <c r="H14" s="15"/>
-      <c r="I14" s="15"/>
-      <c r="J14" s="15"/>
-      <c r="K14" s="15"/>
-      <c r="L14" s="15"/>
-      <c r="M14" s="15"/>
-      <c r="N14" s="16"/>
-      <c r="O14" s="17"/>
-    </row>
-    <row r="15" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B15" s="14"/>
-      <c r="C15" s="15"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="15"/>
-      <c r="G15" s="15"/>
-      <c r="H15" s="15"/>
-      <c r="I15" s="15"/>
-      <c r="J15" s="15"/>
-      <c r="K15" s="15"/>
-      <c r="L15" s="15"/>
-      <c r="M15" s="15"/>
-      <c r="N15" s="16"/>
-      <c r="O15" s="17"/>
-    </row>
-    <row r="16" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B16" s="14"/>
-      <c r="C16" s="15"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="15"/>
-      <c r="F16" s="15"/>
-      <c r="G16" s="15"/>
-      <c r="H16" s="15"/>
-      <c r="I16" s="15"/>
-      <c r="J16" s="15"/>
-      <c r="K16" s="15"/>
-      <c r="L16" s="15"/>
-      <c r="M16" s="15"/>
-      <c r="N16" s="16"/>
-      <c r="O16" s="17"/>
-    </row>
-    <row r="17" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B17" s="14"/>
-      <c r="C17" s="15"/>
-      <c r="D17" s="15"/>
-      <c r="E17" s="15"/>
-      <c r="F17" s="15"/>
-      <c r="G17" s="15"/>
-      <c r="H17" s="15"/>
-      <c r="I17" s="15"/>
-      <c r="J17" s="15"/>
-      <c r="K17" s="15"/>
-      <c r="L17" s="15"/>
-      <c r="M17" s="15"/>
-      <c r="N17" s="16"/>
-      <c r="O17" s="17"/>
-    </row>
-    <row r="18" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B18" s="14"/>
-      <c r="C18" s="15"/>
-      <c r="D18" s="15"/>
-      <c r="E18" s="15"/>
-      <c r="F18" s="15"/>
-      <c r="G18" s="15"/>
-      <c r="H18" s="15"/>
-      <c r="I18" s="15"/>
-      <c r="J18" s="15"/>
-      <c r="K18" s="15"/>
-      <c r="L18" s="15"/>
-      <c r="M18" s="15"/>
-      <c r="N18" s="16"/>
-      <c r="O18" s="17"/>
-    </row>
-    <row r="19" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B19" s="14"/>
-      <c r="C19" s="15"/>
-      <c r="D19" s="15"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="15"/>
-      <c r="G19" s="15"/>
-      <c r="H19" s="15"/>
-      <c r="I19" s="15"/>
-      <c r="J19" s="15"/>
-      <c r="K19" s="15"/>
-      <c r="L19" s="15"/>
-      <c r="M19" s="15"/>
-      <c r="N19" s="16"/>
-      <c r="O19" s="17"/>
-    </row>
-    <row r="20" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B20" s="14"/>
-      <c r="C20" s="15"/>
-      <c r="D20" s="15"/>
-      <c r="E20" s="15"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="15"/>
-      <c r="H20" s="15"/>
-      <c r="I20" s="15"/>
-      <c r="J20" s="15"/>
-      <c r="K20" s="15"/>
-      <c r="L20" s="15"/>
-      <c r="M20" s="15"/>
-      <c r="N20" s="16"/>
-      <c r="O20" s="17"/>
-    </row>
-    <row r="21" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B21" s="14"/>
-      <c r="C21" s="15"/>
-      <c r="D21" s="15"/>
-      <c r="E21" s="15"/>
-      <c r="F21" s="15"/>
-      <c r="G21" s="15"/>
-      <c r="H21" s="15"/>
-      <c r="I21" s="15"/>
-      <c r="J21" s="15"/>
-      <c r="K21" s="15"/>
-      <c r="L21" s="15"/>
-      <c r="M21" s="15"/>
-      <c r="N21" s="16"/>
-      <c r="O21" s="17"/>
-    </row>
-    <row r="22" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B22" s="14"/>
-      <c r="C22" s="15"/>
-      <c r="D22" s="15"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="15"/>
-      <c r="G22" s="15"/>
-      <c r="H22" s="15"/>
-      <c r="I22" s="15"/>
-      <c r="J22" s="15"/>
-      <c r="K22" s="15"/>
-      <c r="L22" s="15"/>
-      <c r="M22" s="15"/>
-      <c r="N22" s="16"/>
-      <c r="O22" s="17"/>
-    </row>
-    <row r="23" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B23" s="14"/>
-      <c r="C23" s="15"/>
-      <c r="D23" s="15"/>
-      <c r="E23" s="15"/>
-      <c r="F23" s="15"/>
-      <c r="G23" s="15"/>
-      <c r="H23" s="15"/>
-      <c r="I23" s="15"/>
-      <c r="J23" s="15"/>
-      <c r="K23" s="15"/>
-      <c r="L23" s="15"/>
-      <c r="M23" s="15"/>
-      <c r="N23" s="16"/>
-      <c r="O23" s="17"/>
-    </row>
-    <row r="24" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B24" s="14"/>
-      <c r="C24" s="15"/>
-      <c r="D24" s="15"/>
-      <c r="E24" s="15"/>
-      <c r="F24" s="15"/>
-      <c r="G24" s="15"/>
-      <c r="H24" s="15"/>
-      <c r="I24" s="15"/>
-      <c r="J24" s="15"/>
-      <c r="K24" s="15"/>
-      <c r="L24" s="15"/>
-      <c r="M24" s="15"/>
-      <c r="N24" s="16"/>
-      <c r="O24" s="17"/>
-    </row>
-    <row r="25" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B25" s="14"/>
-      <c r="C25" s="15"/>
-      <c r="D25" s="15"/>
-      <c r="E25" s="15"/>
-      <c r="F25" s="15"/>
-      <c r="G25" s="15"/>
-      <c r="H25" s="15"/>
-      <c r="I25" s="15"/>
-      <c r="J25" s="15"/>
-      <c r="K25" s="15"/>
-      <c r="L25" s="15"/>
-      <c r="M25" s="15"/>
-      <c r="N25" s="16"/>
-      <c r="O25" s="17"/>
-    </row>
-    <row r="26" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B26" s="14"/>
-      <c r="C26" s="15"/>
-      <c r="D26" s="15"/>
-      <c r="E26" s="15"/>
-      <c r="F26" s="15"/>
-      <c r="G26" s="15"/>
-      <c r="H26" s="15"/>
-      <c r="I26" s="15"/>
-      <c r="J26" s="15"/>
-      <c r="K26" s="15"/>
-      <c r="L26" s="15"/>
-      <c r="M26" s="15"/>
-      <c r="N26" s="16"/>
-      <c r="O26" s="17"/>
-    </row>
-    <row r="27" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B27" s="14"/>
-      <c r="C27" s="15"/>
-      <c r="D27" s="15"/>
-      <c r="E27" s="15"/>
-      <c r="F27" s="15"/>
-      <c r="G27" s="15"/>
-      <c r="H27" s="15"/>
-      <c r="I27" s="15"/>
-      <c r="J27" s="15"/>
-      <c r="K27" s="15"/>
-      <c r="L27" s="15"/>
-      <c r="M27" s="15"/>
-      <c r="N27" s="16"/>
-      <c r="O27" s="17"/>
-    </row>
-    <row r="28" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B28" s="14"/>
-      <c r="C28" s="15"/>
-      <c r="D28" s="15"/>
-      <c r="E28" s="15"/>
-      <c r="F28" s="15"/>
-      <c r="G28" s="15"/>
-      <c r="H28" s="15"/>
-      <c r="I28" s="15"/>
-      <c r="J28" s="15"/>
-      <c r="K28" s="15"/>
-      <c r="L28" s="15"/>
-      <c r="M28" s="15"/>
-      <c r="N28" s="16"/>
-      <c r="O28" s="17"/>
-    </row>
-    <row r="29" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B29" s="14"/>
-      <c r="C29" s="15"/>
-      <c r="D29" s="15"/>
-      <c r="E29" s="15"/>
-      <c r="F29" s="15"/>
-      <c r="G29" s="15"/>
-      <c r="H29" s="15"/>
-      <c r="I29" s="15"/>
-      <c r="J29" s="15"/>
-      <c r="K29" s="15"/>
-      <c r="L29" s="15"/>
-      <c r="M29" s="15"/>
-      <c r="N29" s="16"/>
-      <c r="O29" s="17"/>
-    </row>
-    <row r="30" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B30" s="14"/>
-      <c r="C30" s="15"/>
-      <c r="D30" s="15"/>
-      <c r="E30" s="15"/>
-      <c r="F30" s="15"/>
-      <c r="G30" s="15"/>
-      <c r="H30" s="15"/>
-      <c r="I30" s="15"/>
-      <c r="J30" s="15"/>
-      <c r="K30" s="15"/>
-      <c r="L30" s="15"/>
-      <c r="M30" s="15"/>
-      <c r="N30" s="16"/>
-      <c r="O30" s="17"/>
-    </row>
-    <row r="31" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B31" s="14"/>
-      <c r="C31" s="15"/>
-      <c r="D31" s="15"/>
-      <c r="E31" s="15"/>
-      <c r="F31" s="15"/>
-      <c r="G31" s="15"/>
-      <c r="H31" s="15"/>
-      <c r="I31" s="15"/>
-      <c r="J31" s="15"/>
-      <c r="K31" s="15"/>
-      <c r="L31" s="15"/>
-      <c r="M31" s="15"/>
-      <c r="N31" s="16"/>
-      <c r="O31" s="17"/>
-    </row>
-    <row r="32" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B32" s="14"/>
-      <c r="C32" s="15"/>
-      <c r="D32" s="15"/>
-      <c r="E32" s="15"/>
-      <c r="F32" s="15"/>
-      <c r="G32" s="15"/>
-      <c r="H32" s="15"/>
-      <c r="I32" s="15"/>
-      <c r="J32" s="15"/>
-      <c r="K32" s="15"/>
-      <c r="L32" s="15"/>
-      <c r="M32" s="15"/>
-      <c r="N32" s="16"/>
-      <c r="O32" s="17"/>
-    </row>
-    <row r="33" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B33" s="14"/>
-      <c r="C33" s="15"/>
-      <c r="D33" s="15"/>
-      <c r="E33" s="15"/>
-      <c r="F33" s="15"/>
-      <c r="G33" s="15"/>
-      <c r="H33" s="15"/>
-      <c r="I33" s="15"/>
-      <c r="J33" s="15"/>
-      <c r="K33" s="15"/>
-      <c r="L33" s="15"/>
-      <c r="M33" s="15"/>
-      <c r="N33" s="16"/>
-      <c r="O33" s="17"/>
-    </row>
-    <row r="34" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B34" s="14"/>
-      <c r="C34" s="15"/>
-      <c r="D34" s="15"/>
-      <c r="E34" s="15"/>
-      <c r="F34" s="15"/>
-      <c r="G34" s="15"/>
-      <c r="H34" s="15"/>
-      <c r="I34" s="15"/>
-      <c r="J34" s="15"/>
-      <c r="K34" s="15"/>
-      <c r="L34" s="15"/>
-      <c r="M34" s="15"/>
-      <c r="N34" s="16"/>
-      <c r="O34" s="17"/>
-    </row>
-    <row r="35" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B35" s="14"/>
-      <c r="C35" s="15"/>
-      <c r="D35" s="15"/>
-      <c r="E35" s="15"/>
-      <c r="F35" s="15"/>
-      <c r="G35" s="15"/>
-      <c r="H35" s="15"/>
-      <c r="I35" s="15"/>
-      <c r="J35" s="15"/>
-      <c r="K35" s="15"/>
-      <c r="L35" s="15"/>
-      <c r="M35" s="15"/>
-      <c r="N35" s="16"/>
-      <c r="O35" s="17"/>
-    </row>
-    <row r="36" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B36" s="14"/>
-      <c r="C36" s="15"/>
-      <c r="D36" s="15"/>
-      <c r="E36" s="15"/>
-      <c r="F36" s="15"/>
-      <c r="G36" s="15"/>
-      <c r="H36" s="15"/>
-      <c r="I36" s="15"/>
-      <c r="J36" s="15"/>
-      <c r="K36" s="15"/>
-      <c r="L36" s="15"/>
-      <c r="M36" s="15"/>
-      <c r="N36" s="16"/>
-      <c r="O36" s="17"/>
-    </row>
-    <row r="37" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B37" s="14"/>
-      <c r="C37" s="15"/>
-      <c r="D37" s="15"/>
-      <c r="E37" s="15"/>
-      <c r="F37" s="15"/>
-      <c r="G37" s="15"/>
-      <c r="H37" s="15"/>
-      <c r="I37" s="15"/>
-      <c r="J37" s="15"/>
-      <c r="K37" s="15"/>
-      <c r="L37" s="15"/>
-      <c r="M37" s="15"/>
-      <c r="N37" s="16"/>
-      <c r="O37" s="17"/>
-    </row>
-    <row r="38" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B38" s="14"/>
-      <c r="C38" s="15"/>
-      <c r="D38" s="15"/>
-      <c r="E38" s="15"/>
-      <c r="F38" s="15"/>
-      <c r="G38" s="15"/>
-      <c r="H38" s="15"/>
-      <c r="I38" s="15"/>
-      <c r="J38" s="15"/>
-      <c r="K38" s="15"/>
-      <c r="L38" s="15"/>
-      <c r="M38" s="15"/>
-      <c r="N38" s="16"/>
-      <c r="O38" s="17"/>
-    </row>
-    <row r="39" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B39" s="14"/>
-      <c r="C39" s="15"/>
-      <c r="D39" s="15"/>
-      <c r="E39" s="15"/>
-      <c r="F39" s="15"/>
-      <c r="G39" s="15"/>
-      <c r="H39" s="15"/>
-      <c r="I39" s="15"/>
-      <c r="J39" s="15"/>
-      <c r="K39" s="15"/>
-      <c r="L39" s="15"/>
-      <c r="M39" s="15"/>
-      <c r="N39" s="16"/>
-      <c r="O39" s="17"/>
-    </row>
-    <row r="40" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B40" s="14"/>
-      <c r="C40" s="15"/>
-      <c r="D40" s="15"/>
-      <c r="E40" s="15"/>
-      <c r="F40" s="15"/>
-      <c r="G40" s="15"/>
-      <c r="H40" s="15"/>
-      <c r="I40" s="15"/>
-      <c r="J40" s="15"/>
-      <c r="K40" s="15"/>
-      <c r="L40" s="15"/>
-      <c r="M40" s="15"/>
-      <c r="N40" s="16"/>
-      <c r="O40" s="17"/>
-    </row>
-    <row r="41" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B41" s="14"/>
-      <c r="C41" s="15"/>
-      <c r="D41" s="15"/>
-      <c r="E41" s="15"/>
-      <c r="F41" s="15"/>
-      <c r="G41" s="15"/>
-      <c r="H41" s="15"/>
-      <c r="I41" s="15"/>
-      <c r="J41" s="15"/>
-      <c r="K41" s="15"/>
-      <c r="L41" s="15"/>
-      <c r="M41" s="15"/>
-      <c r="N41" s="16"/>
-      <c r="O41" s="17"/>
-    </row>
-    <row r="42" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B42" s="14"/>
-      <c r="C42" s="15"/>
-      <c r="D42" s="15"/>
-      <c r="E42" s="15"/>
-      <c r="F42" s="15"/>
-      <c r="G42" s="15"/>
-      <c r="H42" s="15"/>
-      <c r="I42" s="15"/>
-      <c r="J42" s="15"/>
-      <c r="K42" s="15"/>
-      <c r="L42" s="15"/>
-      <c r="M42" s="15"/>
-      <c r="N42" s="16"/>
-      <c r="O42" s="17"/>
-    </row>
-    <row r="43" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B43" s="14"/>
-      <c r="C43" s="15"/>
-      <c r="D43" s="15"/>
-      <c r="E43" s="15"/>
-      <c r="F43" s="15"/>
-      <c r="G43" s="15"/>
-      <c r="H43" s="15"/>
-      <c r="I43" s="15"/>
-      <c r="J43" s="15"/>
-      <c r="K43" s="15"/>
-      <c r="L43" s="15"/>
-      <c r="M43" s="15"/>
-      <c r="N43" s="16"/>
-      <c r="O43" s="17"/>
-    </row>
-    <row r="44" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B44" s="14"/>
-      <c r="C44" s="15"/>
-      <c r="D44" s="15"/>
-      <c r="E44" s="15"/>
-      <c r="F44" s="15"/>
-      <c r="G44" s="15"/>
-      <c r="H44" s="15"/>
-      <c r="I44" s="15"/>
-      <c r="J44" s="15"/>
-      <c r="K44" s="15"/>
-      <c r="L44" s="15"/>
-      <c r="M44" s="15"/>
-      <c r="N44" s="16"/>
-      <c r="O44" s="17"/>
-    </row>
-    <row r="45" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B45" s="14"/>
-      <c r="C45" s="15"/>
-      <c r="D45" s="15"/>
-      <c r="E45" s="15"/>
-      <c r="F45" s="15"/>
-      <c r="G45" s="15"/>
-      <c r="H45" s="15"/>
-      <c r="I45" s="15"/>
-      <c r="J45" s="15"/>
-      <c r="K45" s="15"/>
-      <c r="L45" s="15"/>
-      <c r="M45" s="15"/>
-      <c r="N45" s="16"/>
-      <c r="O45" s="17"/>
-    </row>
-    <row r="46" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B46" s="14"/>
-      <c r="C46" s="15"/>
-      <c r="D46" s="15"/>
-      <c r="E46" s="15"/>
-      <c r="F46" s="15"/>
-      <c r="G46" s="15"/>
-      <c r="H46" s="15"/>
-      <c r="I46" s="15"/>
-      <c r="J46" s="15"/>
-      <c r="K46" s="15"/>
-      <c r="L46" s="15"/>
-      <c r="M46" s="15"/>
-      <c r="N46" s="16"/>
-      <c r="O46" s="17"/>
-    </row>
-    <row r="47" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B47" s="14"/>
-      <c r="C47" s="15"/>
-      <c r="D47" s="15"/>
-      <c r="E47" s="15"/>
-      <c r="F47" s="15"/>
-      <c r="G47" s="15"/>
-      <c r="H47" s="15"/>
-      <c r="I47" s="15"/>
-      <c r="J47" s="15"/>
-      <c r="K47" s="15"/>
-      <c r="L47" s="15"/>
-      <c r="M47" s="15"/>
-      <c r="N47" s="16"/>
-      <c r="O47" s="17"/>
-    </row>
-    <row r="48" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B48" s="14"/>
-      <c r="C48" s="15"/>
-      <c r="D48" s="15"/>
-      <c r="E48" s="15"/>
-      <c r="F48" s="15"/>
-      <c r="G48" s="15"/>
-      <c r="H48" s="15"/>
-      <c r="I48" s="15"/>
-      <c r="J48" s="15"/>
-      <c r="K48" s="15"/>
-      <c r="L48" s="15"/>
-      <c r="M48" s="15"/>
-      <c r="N48" s="16"/>
-      <c r="O48" s="17"/>
-    </row>
-    <row r="49" spans="2:15" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B49" s="18"/>
-      <c r="C49" s="19"/>
-      <c r="D49" s="19"/>
-      <c r="E49" s="19"/>
-      <c r="F49" s="19"/>
-      <c r="G49" s="19"/>
-      <c r="H49" s="19"/>
-      <c r="I49" s="19"/>
-      <c r="J49" s="19"/>
-      <c r="K49" s="19"/>
-      <c r="L49" s="19"/>
-      <c r="M49" s="19"/>
-      <c r="N49" s="20"/>
-      <c r="O49" s="21"/>
-    </row>
-    <row r="50" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B50" s="6"/>
-      <c r="C50" s="7"/>
-      <c r="D50" s="7"/>
-      <c r="E50" s="7"/>
-      <c r="F50" s="7"/>
-      <c r="G50" s="7"/>
-      <c r="H50" s="7"/>
-      <c r="I50" s="7"/>
-      <c r="J50" s="7"/>
-      <c r="K50" s="7"/>
-      <c r="L50" s="7"/>
-      <c r="M50" s="7"/>
-      <c r="N50" s="7"/>
-      <c r="O50" s="8"/>
-    </row>
-    <row r="51" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="C51" s="2"/>
-      <c r="D51" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="E51" s="12"/>
+      <c r="E51" s="9"/>
       <c r="F51" s="2"/>
       <c r="G51" s="2"/>
       <c r="H51" s="2"/>
       <c r="I51" s="2"/>
       <c r="J51" s="2"/>
-      <c r="K51" s="13" t="s">
-        <v>17</v>
+      <c r="K51" s="10" t="s">
+        <v>16</v>
       </c>
-      <c r="L51" s="13"/>
+      <c r="L51" s="10"/>
       <c r="M51" s="2"/>
       <c r="N51" s="2"/>
-      <c r="O51" s="5"/>
+      <c r="O51" s="4"/>
     </row>
     <row r="52" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C52" s="2"/>
@@ -1631,7 +1639,7 @@
       <c r="L52" s="2"/>
       <c r="M52" s="2"/>
       <c r="N52" s="2"/>
-      <c r="O52" s="5"/>
+      <c r="O52" s="4"/>
     </row>
     <row r="53" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C53" s="2"/>
@@ -1646,7 +1654,7 @@
       <c r="L53" s="2"/>
       <c r="M53" s="2"/>
       <c r="N53" s="2"/>
-      <c r="O53" s="5"/>
+      <c r="O53" s="4"/>
     </row>
     <row r="54" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C54" s="2"/>
@@ -1661,22 +1669,22 @@
       <c r="L54" s="2"/>
       <c r="M54" s="2"/>
       <c r="N54" s="2"/>
-      <c r="O54" s="5"/>
+      <c r="O54" s="4"/>
     </row>
     <row r="55" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C55" s="2"/>
-      <c r="D55" s="9"/>
-      <c r="E55" s="9"/>
+      <c r="D55" s="8"/>
+      <c r="E55" s="8"/>
       <c r="F55" s="2"/>
       <c r="G55" s="2"/>
       <c r="H55" s="2"/>
       <c r="I55" s="2"/>
       <c r="J55" s="2"/>
-      <c r="K55" s="9"/>
-      <c r="L55" s="9"/>
+      <c r="K55" s="8"/>
+      <c r="L55" s="8"/>
       <c r="M55" s="2"/>
       <c r="N55" s="2"/>
-      <c r="O55" s="5"/>
+      <c r="O55" s="4"/>
     </row>
     <row r="56" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C56" s="2"/>
@@ -1691,7 +1699,7 @@
       <c r="L56" s="2"/>
       <c r="M56" s="2"/>
       <c r="N56" s="2"/>
-      <c r="O56" s="5"/>
+      <c r="O56" s="4"/>
     </row>
     <row r="57" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C57" s="2"/>
@@ -1706,7 +1714,7 @@
       <c r="L57" s="2"/>
       <c r="M57" s="2"/>
       <c r="N57" s="2"/>
-      <c r="O57" s="5"/>
+      <c r="O57" s="4"/>
     </row>
     <row r="58" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C58" s="2"/>
@@ -1721,7 +1729,7 @@
       <c r="L58" s="2"/>
       <c r="M58" s="2"/>
       <c r="N58" s="2"/>
-      <c r="O58" s="5"/>
+      <c r="O58" s="4"/>
     </row>
     <row r="59" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C59" s="2"/>
@@ -1736,7 +1744,7 @@
       <c r="L59" s="2"/>
       <c r="M59" s="2"/>
       <c r="N59" s="2"/>
-      <c r="O59" s="5"/>
+      <c r="O59" s="4"/>
     </row>
     <row r="60" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C60" s="2"/>
@@ -1751,7 +1759,7 @@
       <c r="L60" s="2"/>
       <c r="M60" s="2"/>
       <c r="N60" s="2"/>
-      <c r="O60" s="5"/>
+      <c r="O60" s="4"/>
     </row>
     <row r="61" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C61" s="2"/>
@@ -1766,7 +1774,7 @@
       <c r="L61" s="2"/>
       <c r="M61" s="2"/>
       <c r="N61" s="2"/>
-      <c r="O61" s="5"/>
+      <c r="O61" s="4"/>
     </row>
     <row r="62" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C62" s="2"/>
@@ -1781,7 +1789,7 @@
       <c r="L62" s="2"/>
       <c r="M62" s="2"/>
       <c r="N62" s="2"/>
-      <c r="O62" s="5"/>
+      <c r="O62" s="4"/>
     </row>
     <row r="63" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C63" s="2"/>
@@ -1796,7 +1804,7 @@
       <c r="L63" s="2"/>
       <c r="M63" s="2"/>
       <c r="N63" s="2"/>
-      <c r="O63" s="5"/>
+      <c r="O63" s="4"/>
     </row>
     <row r="64" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C64" s="2"/>
@@ -1811,7 +1819,7 @@
       <c r="L64" s="2"/>
       <c r="M64" s="2"/>
       <c r="N64" s="2"/>
-      <c r="O64" s="5"/>
+      <c r="O64" s="4"/>
     </row>
     <row r="65" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C65" s="2"/>
@@ -1826,7 +1834,7 @@
       <c r="L65" s="2"/>
       <c r="M65" s="2"/>
       <c r="N65" s="2"/>
-      <c r="O65" s="5"/>
+      <c r="O65" s="4"/>
     </row>
     <row r="66" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C66" s="2"/>
@@ -1841,7 +1849,7 @@
       <c r="L66" s="2"/>
       <c r="M66" s="2"/>
       <c r="N66" s="2"/>
-      <c r="O66" s="5"/>
+      <c r="O66" s="4"/>
     </row>
     <row r="67" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C67" s="2"/>
@@ -1856,7 +1864,7 @@
       <c r="L67" s="2"/>
       <c r="M67" s="2"/>
       <c r="N67" s="2"/>
-      <c r="O67" s="5"/>
+      <c r="O67" s="4"/>
     </row>
     <row r="68" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C68" s="2"/>
@@ -1871,7 +1879,7 @@
       <c r="L68" s="2"/>
       <c r="M68" s="2"/>
       <c r="N68" s="2"/>
-      <c r="O68" s="5"/>
+      <c r="O68" s="4"/>
     </row>
     <row r="69" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C69" s="2"/>
@@ -1886,7 +1894,7 @@
       <c r="L69" s="2"/>
       <c r="M69" s="2"/>
       <c r="N69" s="2"/>
-      <c r="O69" s="5"/>
+      <c r="O69" s="4"/>
     </row>
     <row r="70" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C70" s="2"/>
@@ -1901,7 +1909,7 @@
       <c r="L70" s="2"/>
       <c r="M70" s="2"/>
       <c r="N70" s="2"/>
-      <c r="O70" s="5"/>
+      <c r="O70" s="4"/>
     </row>
     <row r="71" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C71" s="2"/>
@@ -1916,7 +1924,7 @@
       <c r="L71" s="2"/>
       <c r="M71" s="2"/>
       <c r="N71" s="2"/>
-      <c r="O71" s="5"/>
+      <c r="O71" s="4"/>
     </row>
     <row r="72" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C72" s="2"/>
@@ -1931,7 +1939,7 @@
       <c r="L72" s="2"/>
       <c r="M72" s="2"/>
       <c r="N72" s="2"/>
-      <c r="O72" s="5"/>
+      <c r="O72" s="4"/>
     </row>
     <row r="73" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C73" s="2"/>
@@ -1946,7 +1954,7 @@
       <c r="L73" s="2"/>
       <c r="M73" s="2"/>
       <c r="N73" s="2"/>
-      <c r="O73" s="5"/>
+      <c r="O73" s="4"/>
     </row>
     <row r="74" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C74" s="2"/>
@@ -1961,7 +1969,7 @@
       <c r="L74" s="2"/>
       <c r="M74" s="2"/>
       <c r="N74" s="2"/>
-      <c r="O74" s="5"/>
+      <c r="O74" s="4"/>
     </row>
     <row r="75" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C75" s="2"/>
@@ -1976,7 +1984,7 @@
       <c r="L75" s="2"/>
       <c r="M75" s="2"/>
       <c r="N75" s="2"/>
-      <c r="O75" s="5"/>
+      <c r="O75" s="4"/>
     </row>
     <row r="76" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C76" s="2"/>
@@ -1991,7 +1999,7 @@
       <c r="L76" s="2"/>
       <c r="M76" s="2"/>
       <c r="N76" s="2"/>
-      <c r="O76" s="5"/>
+      <c r="O76" s="4"/>
     </row>
     <row r="77" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C77" s="2"/>
@@ -2006,7 +2014,7 @@
       <c r="L77" s="2"/>
       <c r="M77" s="2"/>
       <c r="N77" s="2"/>
-      <c r="O77" s="5"/>
+      <c r="O77" s="4"/>
     </row>
     <row r="78" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C78" s="2"/>
@@ -2021,7 +2029,7 @@
       <c r="L78" s="2"/>
       <c r="M78" s="2"/>
       <c r="N78" s="2"/>
-      <c r="O78" s="5"/>
+      <c r="O78" s="4"/>
     </row>
     <row r="79" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C79" s="2"/>
@@ -2036,7 +2044,7 @@
       <c r="L79" s="2"/>
       <c r="M79" s="2"/>
       <c r="N79" s="2"/>
-      <c r="O79" s="5"/>
+      <c r="O79" s="4"/>
     </row>
     <row r="80" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C80" s="2"/>
@@ -2051,7 +2059,7 @@
       <c r="L80" s="2"/>
       <c r="M80" s="2"/>
       <c r="N80" s="2"/>
-      <c r="O80" s="5"/>
+      <c r="O80" s="4"/>
     </row>
     <row r="81" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C81" s="2"/>
@@ -2066,7 +2074,7 @@
       <c r="L81" s="2"/>
       <c r="M81" s="2"/>
       <c r="N81" s="2"/>
-      <c r="O81" s="5"/>
+      <c r="O81" s="4"/>
     </row>
     <row r="82" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C82" s="2"/>
@@ -2081,7 +2089,7 @@
       <c r="L82" s="2"/>
       <c r="M82" s="2"/>
       <c r="N82" s="2"/>
-      <c r="O82" s="5"/>
+      <c r="O82" s="4"/>
     </row>
     <row r="83" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C83" s="2"/>
@@ -2096,7 +2104,7 @@
       <c r="L83" s="2"/>
       <c r="M83" s="2"/>
       <c r="N83" s="2"/>
-      <c r="O83" s="5"/>
+      <c r="O83" s="4"/>
     </row>
     <row r="84" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C84" s="2"/>
@@ -2111,7 +2119,7 @@
       <c r="L84" s="2"/>
       <c r="M84" s="2"/>
       <c r="N84" s="2"/>
-      <c r="O84" s="5"/>
+      <c r="O84" s="4"/>
     </row>
     <row r="85" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C85" s="2"/>
@@ -2126,7 +2134,7 @@
       <c r="L85" s="2"/>
       <c r="M85" s="2"/>
       <c r="N85" s="2"/>
-      <c r="O85" s="5"/>
+      <c r="O85" s="4"/>
     </row>
     <row r="86" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C86" s="2"/>
@@ -2141,7 +2149,7 @@
       <c r="L86" s="2"/>
       <c r="M86" s="2"/>
       <c r="N86" s="2"/>
-      <c r="O86" s="5"/>
+      <c r="O86" s="4"/>
     </row>
     <row r="87" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C87" s="2"/>
@@ -2156,7 +2164,7 @@
       <c r="L87" s="2"/>
       <c r="M87" s="2"/>
       <c r="N87" s="2"/>
-      <c r="O87" s="5"/>
+      <c r="O87" s="4"/>
     </row>
     <row r="88" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C88" s="2"/>
@@ -2171,7 +2179,7 @@
       <c r="L88" s="2"/>
       <c r="M88" s="2"/>
       <c r="N88" s="2"/>
-      <c r="O88" s="5"/>
+      <c r="O88" s="4"/>
     </row>
     <row r="89" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C89" s="2"/>
@@ -2186,7 +2194,7 @@
       <c r="L89" s="2"/>
       <c r="M89" s="2"/>
       <c r="N89" s="2"/>
-      <c r="O89" s="5"/>
+      <c r="O89" s="4"/>
     </row>
     <row r="90" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C90" s="2"/>
@@ -2201,7 +2209,7 @@
       <c r="L90" s="2"/>
       <c r="M90" s="2"/>
       <c r="N90" s="2"/>
-      <c r="O90" s="5"/>
+      <c r="O90" s="4"/>
     </row>
     <row r="91" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C91" s="2"/>
@@ -2216,7 +2224,7 @@
       <c r="L91" s="2"/>
       <c r="M91" s="2"/>
       <c r="N91" s="2"/>
-      <c r="O91" s="5"/>
+      <c r="O91" s="4"/>
     </row>
     <row r="92" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C92" s="2"/>
@@ -2231,7 +2239,7 @@
       <c r="L92" s="2"/>
       <c r="M92" s="2"/>
       <c r="N92" s="2"/>
-      <c r="O92" s="5"/>
+      <c r="O92" s="4"/>
     </row>
     <row r="93" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C93" s="2"/>
@@ -2246,7 +2254,7 @@
       <c r="L93" s="2"/>
       <c r="M93" s="2"/>
       <c r="N93" s="2"/>
-      <c r="O93" s="5"/>
+      <c r="O93" s="4"/>
     </row>
     <row r="94" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C94" s="2"/>
@@ -2261,7 +2269,7 @@
       <c r="L94" s="2"/>
       <c r="M94" s="2"/>
       <c r="N94" s="2"/>
-      <c r="O94" s="5"/>
+      <c r="O94" s="4"/>
     </row>
     <row r="95" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C95" s="2"/>
@@ -2276,7 +2284,7 @@
       <c r="L95" s="2"/>
       <c r="M95" s="2"/>
       <c r="N95" s="2"/>
-      <c r="O95" s="5"/>
+      <c r="O95" s="4"/>
     </row>
     <row r="96" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C96" s="2"/>
@@ -2291,7 +2299,7 @@
       <c r="L96" s="2"/>
       <c r="M96" s="2"/>
       <c r="N96" s="2"/>
-      <c r="O96" s="5"/>
+      <c r="O96" s="4"/>
     </row>
     <row r="97" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C97" s="2"/>
@@ -2306,7 +2314,7 @@
       <c r="L97" s="2"/>
       <c r="M97" s="2"/>
       <c r="N97" s="2"/>
-      <c r="O97" s="5"/>
+      <c r="O97" s="4"/>
     </row>
     <row r="98" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C98" s="2"/>
@@ -2321,7 +2329,7 @@
       <c r="L98" s="2"/>
       <c r="M98" s="2"/>
       <c r="N98" s="2"/>
-      <c r="O98" s="5"/>
+      <c r="O98" s="4"/>
     </row>
     <row r="99" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C99" s="2"/>
@@ -2336,7 +2344,7 @@
       <c r="L99" s="2"/>
       <c r="M99" s="2"/>
       <c r="N99" s="2"/>
-      <c r="O99" s="5"/>
+      <c r="O99" s="4"/>
     </row>
     <row r="100" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C100" s="2"/>
@@ -2351,7 +2359,7 @@
       <c r="L100" s="2"/>
       <c r="M100" s="2"/>
       <c r="N100" s="2"/>
-      <c r="O100" s="5"/>
+      <c r="O100" s="4"/>
     </row>
     <row r="101" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C101" s="2"/>
@@ -2366,7 +2374,7 @@
       <c r="L101" s="2"/>
       <c r="M101" s="2"/>
       <c r="N101" s="2"/>
-      <c r="O101" s="5"/>
+      <c r="O101" s="4"/>
     </row>
     <row r="102" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C102" s="2"/>
@@ -2381,7 +2389,7 @@
       <c r="L102" s="2"/>
       <c r="M102" s="2"/>
       <c r="N102" s="2"/>
-      <c r="O102" s="5"/>
+      <c r="O102" s="4"/>
     </row>
     <row r="103" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C103" s="2"/>
@@ -2396,7 +2404,7 @@
       <c r="L103" s="2"/>
       <c r="M103" s="2"/>
       <c r="N103" s="2"/>
-      <c r="O103" s="5"/>
+      <c r="O103" s="4"/>
     </row>
     <row r="104" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C104" s="2"/>
@@ -2411,7 +2419,7 @@
       <c r="L104" s="2"/>
       <c r="M104" s="2"/>
       <c r="N104" s="2"/>
-      <c r="O104" s="5"/>
+      <c r="O104" s="4"/>
     </row>
     <row r="105" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C105" s="2"/>
@@ -2426,7 +2434,7 @@
       <c r="L105" s="2"/>
       <c r="M105" s="2"/>
       <c r="N105" s="2"/>
-      <c r="O105" s="5"/>
+      <c r="O105" s="4"/>
     </row>
     <row r="106" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C106" s="2"/>
@@ -2441,7 +2449,7 @@
       <c r="L106" s="2"/>
       <c r="M106" s="2"/>
       <c r="N106" s="2"/>
-      <c r="O106" s="5"/>
+      <c r="O106" s="4"/>
     </row>
     <row r="107" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C107" s="2"/>
@@ -2456,7 +2464,7 @@
       <c r="L107" s="2"/>
       <c r="M107" s="2"/>
       <c r="N107" s="2"/>
-      <c r="O107" s="5"/>
+      <c r="O107" s="4"/>
     </row>
     <row r="108" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C108" s="2"/>
@@ -2471,7 +2479,7 @@
       <c r="L108" s="2"/>
       <c r="M108" s="2"/>
       <c r="N108" s="2"/>
-      <c r="O108" s="5"/>
+      <c r="O108" s="4"/>
     </row>
     <row r="109" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C109" s="2"/>
@@ -2486,7 +2494,7 @@
       <c r="L109" s="2"/>
       <c r="M109" s="2"/>
       <c r="N109" s="2"/>
-      <c r="O109" s="5"/>
+      <c r="O109" s="4"/>
     </row>
     <row r="110" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C110" s="2"/>
@@ -2501,7 +2509,7 @@
       <c r="L110" s="2"/>
       <c r="M110" s="2"/>
       <c r="N110" s="2"/>
-      <c r="O110" s="5"/>
+      <c r="O110" s="4"/>
     </row>
     <row r="111" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C111" s="2"/>
@@ -2516,7 +2524,7 @@
       <c r="L111" s="2"/>
       <c r="M111" s="2"/>
       <c r="N111" s="2"/>
-      <c r="O111" s="5"/>
+      <c r="O111" s="4"/>
     </row>
     <row r="112" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C112" s="2"/>
@@ -2531,7 +2539,7 @@
       <c r="L112" s="2"/>
       <c r="M112" s="2"/>
       <c r="N112" s="2"/>
-      <c r="O112" s="5"/>
+      <c r="O112" s="4"/>
     </row>
     <row r="113" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C113" s="2"/>
@@ -2546,7 +2554,7 @@
       <c r="L113" s="2"/>
       <c r="M113" s="2"/>
       <c r="N113" s="2"/>
-      <c r="O113" s="5"/>
+      <c r="O113" s="4"/>
     </row>
     <row r="114" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C114" s="2"/>
@@ -2561,7 +2569,7 @@
       <c r="L114" s="2"/>
       <c r="M114" s="2"/>
       <c r="N114" s="2"/>
-      <c r="O114" s="5"/>
+      <c r="O114" s="4"/>
     </row>
     <row r="115" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C115" s="2"/>
@@ -2576,7 +2584,7 @@
       <c r="L115" s="2"/>
       <c r="M115" s="2"/>
       <c r="N115" s="2"/>
-      <c r="O115" s="5"/>
+      <c r="O115" s="4"/>
     </row>
     <row r="116" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C116" s="2"/>
@@ -2591,7 +2599,7 @@
       <c r="L116" s="2"/>
       <c r="M116" s="2"/>
       <c r="N116" s="2"/>
-      <c r="O116" s="5"/>
+      <c r="O116" s="4"/>
     </row>
     <row r="117" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C117" s="2"/>
@@ -2606,7 +2614,7 @@
       <c r="L117" s="2"/>
       <c r="M117" s="2"/>
       <c r="N117" s="2"/>
-      <c r="O117" s="5"/>
+      <c r="O117" s="4"/>
     </row>
     <row r="118" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C118" s="2"/>
@@ -2621,7 +2629,7 @@
       <c r="L118" s="2"/>
       <c r="M118" s="2"/>
       <c r="N118" s="2"/>
-      <c r="O118" s="5"/>
+      <c r="O118" s="4"/>
     </row>
     <row r="119" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C119" s="2"/>
@@ -2636,7 +2644,7 @@
       <c r="L119" s="2"/>
       <c r="M119" s="2"/>
       <c r="N119" s="2"/>
-      <c r="O119" s="5"/>
+      <c r="O119" s="4"/>
     </row>
     <row r="120" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C120" s="2"/>
@@ -2651,7 +2659,7 @@
       <c r="L120" s="2"/>
       <c r="M120" s="2"/>
       <c r="N120" s="2"/>
-      <c r="O120" s="5"/>
+      <c r="O120" s="4"/>
     </row>
     <row r="121" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C121" s="2"/>
@@ -2666,7 +2674,7 @@
       <c r="L121" s="2"/>
       <c r="M121" s="2"/>
       <c r="N121" s="2"/>
-      <c r="O121" s="5"/>
+      <c r="O121" s="4"/>
     </row>
     <row r="122" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C122" s="2"/>
@@ -2681,7 +2689,7 @@
       <c r="L122" s="2"/>
       <c r="M122" s="2"/>
       <c r="N122" s="2"/>
-      <c r="O122" s="5"/>
+      <c r="O122" s="4"/>
     </row>
     <row r="123" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C123" s="2"/>
@@ -2696,7 +2704,7 @@
       <c r="L123" s="2"/>
       <c r="M123" s="2"/>
       <c r="N123" s="2"/>
-      <c r="O123" s="5"/>
+      <c r="O123" s="4"/>
     </row>
     <row r="124" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C124" s="2"/>
@@ -2711,7 +2719,7 @@
       <c r="L124" s="2"/>
       <c r="M124" s="2"/>
       <c r="N124" s="2"/>
-      <c r="O124" s="5"/>
+      <c r="O124" s="4"/>
     </row>
     <row r="125" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C125" s="2"/>
@@ -2726,7 +2734,7 @@
       <c r="L125" s="2"/>
       <c r="M125" s="2"/>
       <c r="N125" s="2"/>
-      <c r="O125" s="5"/>
+      <c r="O125" s="4"/>
     </row>
     <row r="126" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C126" s="2"/>
@@ -2741,7 +2749,7 @@
       <c r="L126" s="2"/>
       <c r="M126" s="2"/>
       <c r="N126" s="2"/>
-      <c r="O126" s="5"/>
+      <c r="O126" s="4"/>
     </row>
     <row r="127" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C127" s="2"/>
@@ -2756,7 +2764,7 @@
       <c r="L127" s="2"/>
       <c r="M127" s="2"/>
       <c r="N127" s="2"/>
-      <c r="O127" s="5"/>
+      <c r="O127" s="4"/>
     </row>
     <row r="128" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C128" s="2"/>
@@ -2771,7 +2779,7 @@
       <c r="L128" s="2"/>
       <c r="M128" s="2"/>
       <c r="N128" s="2"/>
-      <c r="O128" s="5"/>
+      <c r="O128" s="4"/>
     </row>
     <row r="129" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C129" s="2"/>
@@ -2786,7 +2794,7 @@
       <c r="L129" s="2"/>
       <c r="M129" s="2"/>
       <c r="N129" s="2"/>
-      <c r="O129" s="5"/>
+      <c r="O129" s="4"/>
     </row>
     <row r="130" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C130" s="2"/>
@@ -2801,7 +2809,7 @@
       <c r="L130" s="2"/>
       <c r="M130" s="2"/>
       <c r="N130" s="2"/>
-      <c r="O130" s="5"/>
+      <c r="O130" s="4"/>
     </row>
     <row r="131" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C131" s="2"/>
@@ -2816,7 +2824,7 @@
       <c r="L131" s="2"/>
       <c r="M131" s="2"/>
       <c r="N131" s="2"/>
-      <c r="O131" s="5"/>
+      <c r="O131" s="4"/>
     </row>
     <row r="132" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C132" s="2"/>
@@ -2831,7 +2839,7 @@
       <c r="L132" s="2"/>
       <c r="M132" s="2"/>
       <c r="N132" s="2"/>
-      <c r="O132" s="5"/>
+      <c r="O132" s="4"/>
     </row>
     <row r="133" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C133" s="2"/>
@@ -2846,7 +2854,7 @@
       <c r="L133" s="2"/>
       <c r="M133" s="2"/>
       <c r="N133" s="2"/>
-      <c r="O133" s="5"/>
+      <c r="O133" s="4"/>
     </row>
     <row r="134" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C134" s="2"/>
@@ -2861,7 +2869,7 @@
       <c r="L134" s="2"/>
       <c r="M134" s="2"/>
       <c r="N134" s="2"/>
-      <c r="O134" s="5"/>
+      <c r="O134" s="4"/>
     </row>
     <row r="135" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C135" s="2"/>
@@ -2876,7 +2884,7 @@
       <c r="L135" s="2"/>
       <c r="M135" s="2"/>
       <c r="N135" s="2"/>
-      <c r="O135" s="5"/>
+      <c r="O135" s="4"/>
     </row>
     <row r="136" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C136" s="2"/>
@@ -2891,7 +2899,7 @@
       <c r="L136" s="2"/>
       <c r="M136" s="2"/>
       <c r="N136" s="2"/>
-      <c r="O136" s="5"/>
+      <c r="O136" s="4"/>
     </row>
     <row r="137" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C137" s="2"/>
@@ -2906,7 +2914,7 @@
       <c r="L137" s="2"/>
       <c r="M137" s="2"/>
       <c r="N137" s="2"/>
-      <c r="O137" s="5"/>
+      <c r="O137" s="4"/>
     </row>
     <row r="138" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C138" s="2"/>
@@ -2921,7 +2929,7 @@
       <c r="L138" s="2"/>
       <c r="M138" s="2"/>
       <c r="N138" s="2"/>
-      <c r="O138" s="5"/>
+      <c r="O138" s="4"/>
     </row>
     <row r="139" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C139" s="2"/>
@@ -2936,7 +2944,7 @@
       <c r="L139" s="2"/>
       <c r="M139" s="2"/>
       <c r="N139" s="2"/>
-      <c r="O139" s="5"/>
+      <c r="O139" s="4"/>
     </row>
     <row r="140" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C140" s="2"/>
@@ -2951,7 +2959,7 @@
       <c r="L140" s="2"/>
       <c r="M140" s="2"/>
       <c r="N140" s="2"/>
-      <c r="O140" s="5"/>
+      <c r="O140" s="4"/>
     </row>
     <row r="141" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C141" s="2"/>
@@ -2966,7 +2974,7 @@
       <c r="L141" s="2"/>
       <c r="M141" s="2"/>
       <c r="N141" s="2"/>
-      <c r="O141" s="5"/>
+      <c r="O141" s="4"/>
     </row>
     <row r="142" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C142" s="2"/>
@@ -2981,7 +2989,7 @@
       <c r="L142" s="2"/>
       <c r="M142" s="2"/>
       <c r="N142" s="2"/>
-      <c r="O142" s="5"/>
+      <c r="O142" s="4"/>
     </row>
     <row r="143" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C143" s="2"/>
@@ -2996,7 +3004,7 @@
       <c r="L143" s="2"/>
       <c r="M143" s="2"/>
       <c r="N143" s="2"/>
-      <c r="O143" s="5"/>
+      <c r="O143" s="4"/>
     </row>
     <row r="144" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C144" s="2"/>
@@ -3011,7 +3019,7 @@
       <c r="L144" s="2"/>
       <c r="M144" s="2"/>
       <c r="N144" s="2"/>
-      <c r="O144" s="5"/>
+      <c r="O144" s="4"/>
     </row>
     <row r="145" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C145" s="2"/>
@@ -3026,7 +3034,7 @@
       <c r="L145" s="2"/>
       <c r="M145" s="2"/>
       <c r="N145" s="2"/>
-      <c r="O145" s="5"/>
+      <c r="O145" s="4"/>
     </row>
     <row r="146" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C146" s="2"/>
@@ -3041,7 +3049,7 @@
       <c r="L146" s="2"/>
       <c r="M146" s="2"/>
       <c r="N146" s="2"/>
-      <c r="O146" s="5"/>
+      <c r="O146" s="4"/>
     </row>
     <row r="147" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C147" s="2"/>
@@ -3056,7 +3064,7 @@
       <c r="L147" s="2"/>
       <c r="M147" s="2"/>
       <c r="N147" s="2"/>
-      <c r="O147" s="5"/>
+      <c r="O147" s="4"/>
     </row>
     <row r="148" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C148" s="2"/>
@@ -3071,7 +3079,7 @@
       <c r="L148" s="2"/>
       <c r="M148" s="2"/>
       <c r="N148" s="2"/>
-      <c r="O148" s="5"/>
+      <c r="O148" s="4"/>
     </row>
     <row r="149" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C149" s="2"/>
@@ -3086,7 +3094,7 @@
       <c r="L149" s="2"/>
       <c r="M149" s="2"/>
       <c r="N149" s="2"/>
-      <c r="O149" s="5"/>
+      <c r="O149" s="4"/>
     </row>
     <row r="150" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C150" s="2"/>
@@ -3101,7 +3109,7 @@
       <c r="L150" s="2"/>
       <c r="M150" s="2"/>
       <c r="N150" s="2"/>
-      <c r="O150" s="5"/>
+      <c r="O150" s="4"/>
     </row>
     <row r="151" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C151" s="2"/>
@@ -3116,7 +3124,7 @@
       <c r="L151" s="2"/>
       <c r="M151" s="2"/>
       <c r="N151" s="2"/>
-      <c r="O151" s="5"/>
+      <c r="O151" s="4"/>
     </row>
     <row r="152" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C152" s="2"/>
@@ -3131,7 +3139,7 @@
       <c r="L152" s="2"/>
       <c r="M152" s="2"/>
       <c r="N152" s="2"/>
-      <c r="O152" s="5"/>
+      <c r="O152" s="4"/>
     </row>
     <row r="153" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C153" s="2"/>
@@ -3146,7 +3154,7 @@
       <c r="L153" s="2"/>
       <c r="M153" s="2"/>
       <c r="N153" s="2"/>
-      <c r="O153" s="5"/>
+      <c r="O153" s="4"/>
     </row>
     <row r="154" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C154" s="2"/>
@@ -3161,7 +3169,7 @@
       <c r="L154" s="2"/>
       <c r="M154" s="2"/>
       <c r="N154" s="2"/>
-      <c r="O154" s="5"/>
+      <c r="O154" s="4"/>
     </row>
     <row r="155" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C155" s="2"/>
@@ -3176,7 +3184,7 @@
       <c r="L155" s="2"/>
       <c r="M155" s="2"/>
       <c r="N155" s="2"/>
-      <c r="O155" s="5"/>
+      <c r="O155" s="4"/>
     </row>
     <row r="156" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C156" s="2"/>
@@ -3191,7 +3199,7 @@
       <c r="L156" s="2"/>
       <c r="M156" s="2"/>
       <c r="N156" s="2"/>
-      <c r="O156" s="5"/>
+      <c r="O156" s="4"/>
     </row>
     <row r="157" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C157" s="2"/>
@@ -3206,7 +3214,7 @@
       <c r="L157" s="2"/>
       <c r="M157" s="2"/>
       <c r="N157" s="2"/>
-      <c r="O157" s="5"/>
+      <c r="O157" s="4"/>
     </row>
     <row r="158" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C158" s="2"/>
@@ -3221,7 +3229,7 @@
       <c r="L158" s="2"/>
       <c r="M158" s="2"/>
       <c r="N158" s="2"/>
-      <c r="O158" s="5"/>
+      <c r="O158" s="4"/>
     </row>
     <row r="159" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C159" s="2"/>
@@ -3236,7 +3244,7 @@
       <c r="L159" s="2"/>
       <c r="M159" s="2"/>
       <c r="N159" s="2"/>
-      <c r="O159" s="5"/>
+      <c r="O159" s="4"/>
     </row>
     <row r="160" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C160" s="2"/>
@@ -3251,7 +3259,7 @@
       <c r="L160" s="2"/>
       <c r="M160" s="2"/>
       <c r="N160" s="2"/>
-      <c r="O160" s="5"/>
+      <c r="O160" s="4"/>
     </row>
     <row r="161" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C161" s="2"/>
@@ -3266,7 +3274,7 @@
       <c r="L161" s="2"/>
       <c r="M161" s="2"/>
       <c r="N161" s="2"/>
-      <c r="O161" s="5"/>
+      <c r="O161" s="4"/>
     </row>
     <row r="162" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C162" s="2"/>
@@ -3281,7 +3289,7 @@
       <c r="L162" s="2"/>
       <c r="M162" s="2"/>
       <c r="N162" s="2"/>
-      <c r="O162" s="5"/>
+      <c r="O162" s="4"/>
     </row>
     <row r="163" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C163" s="2"/>
@@ -3296,7 +3304,7 @@
       <c r="L163" s="2"/>
       <c r="M163" s="2"/>
       <c r="N163" s="2"/>
-      <c r="O163" s="5"/>
+      <c r="O163" s="4"/>
     </row>
     <row r="164" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C164" s="2"/>
@@ -3311,7 +3319,7 @@
       <c r="L164" s="2"/>
       <c r="M164" s="2"/>
       <c r="N164" s="2"/>
-      <c r="O164" s="5"/>
+      <c r="O164" s="4"/>
     </row>
     <row r="165" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C165" s="2"/>
@@ -3326,7 +3334,7 @@
       <c r="L165" s="2"/>
       <c r="M165" s="2"/>
       <c r="N165" s="2"/>
-      <c r="O165" s="5"/>
+      <c r="O165" s="4"/>
     </row>
     <row r="166" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C166" s="2"/>
@@ -3341,7 +3349,7 @@
       <c r="L166" s="2"/>
       <c r="M166" s="2"/>
       <c r="N166" s="2"/>
-      <c r="O166" s="5"/>
+      <c r="O166" s="4"/>
     </row>
     <row r="167" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C167" s="2"/>
@@ -3356,7 +3364,7 @@
       <c r="L167" s="2"/>
       <c r="M167" s="2"/>
       <c r="N167" s="2"/>
-      <c r="O167" s="5"/>
+      <c r="O167" s="4"/>
     </row>
     <row r="168" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C168" s="2"/>
@@ -3371,7 +3379,7 @@
       <c r="L168" s="2"/>
       <c r="M168" s="2"/>
       <c r="N168" s="2"/>
-      <c r="O168" s="5"/>
+      <c r="O168" s="4"/>
     </row>
     <row r="169" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C169" s="2"/>
@@ -3386,7 +3394,7 @@
       <c r="L169" s="2"/>
       <c r="M169" s="2"/>
       <c r="N169" s="2"/>
-      <c r="O169" s="5"/>
+      <c r="O169" s="4"/>
     </row>
     <row r="170" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C170" s="2"/>
@@ -3401,7 +3409,7 @@
       <c r="L170" s="2"/>
       <c r="M170" s="2"/>
       <c r="N170" s="2"/>
-      <c r="O170" s="5"/>
+      <c r="O170" s="4"/>
     </row>
     <row r="171" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C171" s="2"/>
@@ -3416,7 +3424,7 @@
       <c r="L171" s="2"/>
       <c r="M171" s="2"/>
       <c r="N171" s="2"/>
-      <c r="O171" s="5"/>
+      <c r="O171" s="4"/>
     </row>
     <row r="172" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C172" s="2"/>
@@ -3431,7 +3439,7 @@
       <c r="L172" s="2"/>
       <c r="M172" s="2"/>
       <c r="N172" s="2"/>
-      <c r="O172" s="5"/>
+      <c r="O172" s="4"/>
     </row>
     <row r="173" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C173" s="2"/>
@@ -3446,7 +3454,7 @@
       <c r="L173" s="2"/>
       <c r="M173" s="2"/>
       <c r="N173" s="2"/>
-      <c r="O173" s="5"/>
+      <c r="O173" s="4"/>
     </row>
     <row r="174" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C174" s="2"/>
@@ -3461,7 +3469,7 @@
       <c r="L174" s="2"/>
       <c r="M174" s="2"/>
       <c r="N174" s="2"/>
-      <c r="O174" s="5"/>
+      <c r="O174" s="4"/>
     </row>
     <row r="175" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C175" s="2"/>
@@ -3476,7 +3484,7 @@
       <c r="L175" s="2"/>
       <c r="M175" s="2"/>
       <c r="N175" s="2"/>
-      <c r="O175" s="5"/>
+      <c r="O175" s="4"/>
     </row>
     <row r="176" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C176" s="2"/>
@@ -3491,7 +3499,7 @@
       <c r="L176" s="2"/>
       <c r="M176" s="2"/>
       <c r="N176" s="2"/>
-      <c r="O176" s="5"/>
+      <c r="O176" s="4"/>
     </row>
     <row r="177" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C177" s="2"/>
@@ -3506,7 +3514,7 @@
       <c r="L177" s="2"/>
       <c r="M177" s="2"/>
       <c r="N177" s="2"/>
-      <c r="O177" s="5"/>
+      <c r="O177" s="4"/>
     </row>
     <row r="178" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C178" s="2"/>
@@ -3521,7 +3529,7 @@
       <c r="L178" s="2"/>
       <c r="M178" s="2"/>
       <c r="N178" s="2"/>
-      <c r="O178" s="5"/>
+      <c r="O178" s="4"/>
     </row>
     <row r="179" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C179" s="2"/>
@@ -3536,7 +3544,7 @@
       <c r="L179" s="2"/>
       <c r="M179" s="2"/>
       <c r="N179" s="2"/>
-      <c r="O179" s="5"/>
+      <c r="O179" s="4"/>
     </row>
     <row r="180" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C180" s="2"/>
@@ -3551,7 +3559,7 @@
       <c r="L180" s="2"/>
       <c r="M180" s="2"/>
       <c r="N180" s="2"/>
-      <c r="O180" s="5"/>
+      <c r="O180" s="4"/>
     </row>
     <row r="181" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C181" s="2"/>
@@ -3566,7 +3574,7 @@
       <c r="L181" s="2"/>
       <c r="M181" s="2"/>
       <c r="N181" s="2"/>
-      <c r="O181" s="5"/>
+      <c r="O181" s="4"/>
     </row>
     <row r="182" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C182" s="2"/>
@@ -3581,7 +3589,7 @@
       <c r="L182" s="2"/>
       <c r="M182" s="2"/>
       <c r="N182" s="2"/>
-      <c r="O182" s="5"/>
+      <c r="O182" s="4"/>
     </row>
     <row r="183" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C183" s="2"/>
@@ -3596,7 +3604,7 @@
       <c r="L183" s="2"/>
       <c r="M183" s="2"/>
       <c r="N183" s="2"/>
-      <c r="O183" s="5"/>
+      <c r="O183" s="4"/>
     </row>
     <row r="184" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C184" s="2"/>
@@ -3611,7 +3619,7 @@
       <c r="L184" s="2"/>
       <c r="M184" s="2"/>
       <c r="N184" s="2"/>
-      <c r="O184" s="5"/>
+      <c r="O184" s="4"/>
     </row>
     <row r="185" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C185" s="2"/>
@@ -3626,7 +3634,7 @@
       <c r="L185" s="2"/>
       <c r="M185" s="2"/>
       <c r="N185" s="2"/>
-      <c r="O185" s="5"/>
+      <c r="O185" s="4"/>
     </row>
     <row r="186" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C186" s="2"/>
@@ -3641,7 +3649,7 @@
       <c r="L186" s="2"/>
       <c r="M186" s="2"/>
       <c r="N186" s="2"/>
-      <c r="O186" s="5"/>
+      <c r="O186" s="4"/>
     </row>
     <row r="187" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C187" s="2"/>
@@ -3656,7 +3664,7 @@
       <c r="L187" s="2"/>
       <c r="M187" s="2"/>
       <c r="N187" s="2"/>
-      <c r="O187" s="5"/>
+      <c r="O187" s="4"/>
     </row>
     <row r="188" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C188" s="2"/>
@@ -3671,7 +3679,7 @@
       <c r="L188" s="2"/>
       <c r="M188" s="2"/>
       <c r="N188" s="2"/>
-      <c r="O188" s="5"/>
+      <c r="O188" s="4"/>
     </row>
     <row r="189" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C189" s="2"/>
@@ -3686,7 +3694,7 @@
       <c r="L189" s="2"/>
       <c r="M189" s="2"/>
       <c r="N189" s="2"/>
-      <c r="O189" s="5"/>
+      <c r="O189" s="4"/>
     </row>
     <row r="190" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C190" s="2"/>
@@ -3701,7 +3709,7 @@
       <c r="L190" s="2"/>
       <c r="M190" s="2"/>
       <c r="N190" s="2"/>
-      <c r="O190" s="5"/>
+      <c r="O190" s="4"/>
     </row>
     <row r="191" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C191" s="2"/>
@@ -3716,7 +3724,7 @@
       <c r="L191" s="2"/>
       <c r="M191" s="2"/>
       <c r="N191" s="2"/>
-      <c r="O191" s="5"/>
+      <c r="O191" s="4"/>
     </row>
     <row r="192" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C192" s="2"/>
@@ -3731,7 +3739,7 @@
       <c r="L192" s="2"/>
       <c r="M192" s="2"/>
       <c r="N192" s="2"/>
-      <c r="O192" s="5"/>
+      <c r="O192" s="4"/>
     </row>
     <row r="193" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C193" s="2"/>
@@ -3746,7 +3754,7 @@
       <c r="L193" s="2"/>
       <c r="M193" s="2"/>
       <c r="N193" s="2"/>
-      <c r="O193" s="5"/>
+      <c r="O193" s="4"/>
     </row>
     <row r="194" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C194" s="2"/>
@@ -3761,7 +3769,7 @@
       <c r="L194" s="2"/>
       <c r="M194" s="2"/>
       <c r="N194" s="2"/>
-      <c r="O194" s="5"/>
+      <c r="O194" s="4"/>
     </row>
     <row r="195" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C195" s="2"/>
@@ -3776,7 +3784,7 @@
       <c r="L195" s="2"/>
       <c r="M195" s="2"/>
       <c r="N195" s="2"/>
-      <c r="O195" s="5"/>
+      <c r="O195" s="4"/>
     </row>
     <row r="196" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C196" s="2"/>
@@ -3791,7 +3799,7 @@
       <c r="L196" s="2"/>
       <c r="M196" s="2"/>
       <c r="N196" s="2"/>
-      <c r="O196" s="5"/>
+      <c r="O196" s="4"/>
     </row>
     <row r="197" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C197" s="2"/>
@@ -3806,7 +3814,7 @@
       <c r="L197" s="2"/>
       <c r="M197" s="2"/>
       <c r="N197" s="2"/>
-      <c r="O197" s="5"/>
+      <c r="O197" s="4"/>
     </row>
     <row r="198" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C198" s="2"/>
@@ -3821,7 +3829,7 @@
       <c r="L198" s="2"/>
       <c r="M198" s="2"/>
       <c r="N198" s="2"/>
-      <c r="O198" s="5"/>
+      <c r="O198" s="4"/>
     </row>
     <row r="199" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C199" s="2"/>
@@ -3836,7 +3844,7 @@
       <c r="L199" s="2"/>
       <c r="M199" s="2"/>
       <c r="N199" s="2"/>
-      <c r="O199" s="5"/>
+      <c r="O199" s="4"/>
     </row>
     <row r="200" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C200" s="2"/>
@@ -3851,7 +3859,7 @@
       <c r="L200" s="2"/>
       <c r="M200" s="2"/>
       <c r="N200" s="2"/>
-      <c r="O200" s="5"/>
+      <c r="O200" s="4"/>
     </row>
     <row r="201" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C201" s="2"/>
@@ -3866,7 +3874,7 @@
       <c r="L201" s="2"/>
       <c r="M201" s="2"/>
       <c r="N201" s="2"/>
-      <c r="O201" s="5"/>
+      <c r="O201" s="4"/>
     </row>
     <row r="202" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C202" s="2"/>
@@ -3881,7 +3889,7 @@
       <c r="L202" s="2"/>
       <c r="M202" s="2"/>
       <c r="N202" s="2"/>
-      <c r="O202" s="5"/>
+      <c r="O202" s="4"/>
     </row>
     <row r="203" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C203" s="2"/>
@@ -3896,7 +3904,7 @@
       <c r="L203" s="2"/>
       <c r="M203" s="2"/>
       <c r="N203" s="2"/>
-      <c r="O203" s="5"/>
+      <c r="O203" s="4"/>
     </row>
     <row r="204" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C204" s="2"/>
@@ -3911,7 +3919,7 @@
       <c r="L204" s="2"/>
       <c r="M204" s="2"/>
       <c r="N204" s="2"/>
-      <c r="O204" s="5"/>
+      <c r="O204" s="4"/>
     </row>
     <row r="205" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C205" s="2"/>
@@ -3926,7 +3934,7 @@
       <c r="L205" s="2"/>
       <c r="M205" s="2"/>
       <c r="N205" s="2"/>
-      <c r="O205" s="5"/>
+      <c r="O205" s="4"/>
     </row>
     <row r="206" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C206" s="2"/>
@@ -3941,7 +3949,7 @@
       <c r="L206" s="2"/>
       <c r="M206" s="2"/>
       <c r="N206" s="2"/>
-      <c r="O206" s="5"/>
+      <c r="O206" s="4"/>
     </row>
     <row r="207" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C207" s="2"/>
@@ -3956,7 +3964,7 @@
       <c r="L207" s="2"/>
       <c r="M207" s="2"/>
       <c r="N207" s="2"/>
-      <c r="O207" s="5"/>
+      <c r="O207" s="4"/>
     </row>
     <row r="208" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C208" s="2"/>
@@ -3971,7 +3979,7 @@
       <c r="L208" s="2"/>
       <c r="M208" s="2"/>
       <c r="N208" s="2"/>
-      <c r="O208" s="5"/>
+      <c r="O208" s="4"/>
     </row>
     <row r="209" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C209" s="2"/>
@@ -3986,7 +3994,7 @@
       <c r="L209" s="2"/>
       <c r="M209" s="2"/>
       <c r="N209" s="2"/>
-      <c r="O209" s="5"/>
+      <c r="O209" s="4"/>
     </row>
     <row r="210" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C210" s="2"/>
@@ -4001,7 +4009,7 @@
       <c r="L210" s="2"/>
       <c r="M210" s="2"/>
       <c r="N210" s="2"/>
-      <c r="O210" s="5"/>
+      <c r="O210" s="4"/>
     </row>
     <row r="211" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C211" s="2"/>
@@ -4016,7 +4024,7 @@
       <c r="L211" s="2"/>
       <c r="M211" s="2"/>
       <c r="N211" s="2"/>
-      <c r="O211" s="5"/>
+      <c r="O211" s="4"/>
     </row>
     <row r="212" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C212" s="2"/>
@@ -4031,7 +4039,7 @@
       <c r="L212" s="2"/>
       <c r="M212" s="2"/>
       <c r="N212" s="2"/>
-      <c r="O212" s="5"/>
+      <c r="O212" s="4"/>
     </row>
     <row r="213" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C213" s="2"/>
@@ -4046,7 +4054,7 @@
       <c r="L213" s="2"/>
       <c r="M213" s="2"/>
       <c r="N213" s="2"/>
-      <c r="O213" s="5"/>
+      <c r="O213" s="4"/>
     </row>
     <row r="214" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C214" s="2"/>
@@ -4061,7 +4069,7 @@
       <c r="L214" s="2"/>
       <c r="M214" s="2"/>
       <c r="N214" s="2"/>
-      <c r="O214" s="5"/>
+      <c r="O214" s="4"/>
     </row>
     <row r="215" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C215" s="2"/>
@@ -4076,7 +4084,7 @@
       <c r="L215" s="2"/>
       <c r="M215" s="2"/>
       <c r="N215" s="2"/>
-      <c r="O215" s="5"/>
+      <c r="O215" s="4"/>
     </row>
     <row r="216" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C216" s="2"/>
@@ -4091,7 +4099,7 @@
       <c r="L216" s="2"/>
       <c r="M216" s="2"/>
       <c r="N216" s="2"/>
-      <c r="O216" s="5"/>
+      <c r="O216" s="4"/>
     </row>
     <row r="217" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C217" s="2"/>
@@ -4106,7 +4114,7 @@
       <c r="L217" s="2"/>
       <c r="M217" s="2"/>
       <c r="N217" s="2"/>
-      <c r="O217" s="5"/>
+      <c r="O217" s="4"/>
     </row>
     <row r="218" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C218" s="2"/>
@@ -4121,7 +4129,7 @@
       <c r="L218" s="2"/>
       <c r="M218" s="2"/>
       <c r="N218" s="2"/>
-      <c r="O218" s="5"/>
+      <c r="O218" s="4"/>
     </row>
     <row r="219" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C219" s="2"/>
@@ -4136,7 +4144,7 @@
       <c r="L219" s="2"/>
       <c r="M219" s="2"/>
       <c r="N219" s="2"/>
-      <c r="O219" s="5"/>
+      <c r="O219" s="4"/>
     </row>
     <row r="220" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C220" s="2"/>
@@ -4151,7 +4159,7 @@
       <c r="L220" s="2"/>
       <c r="M220" s="2"/>
       <c r="N220" s="2"/>
-      <c r="O220" s="5"/>
+      <c r="O220" s="4"/>
     </row>
     <row r="221" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C221" s="2"/>
@@ -4166,7 +4174,7 @@
       <c r="L221" s="2"/>
       <c r="M221" s="2"/>
       <c r="N221" s="2"/>
-      <c r="O221" s="5"/>
+      <c r="O221" s="4"/>
     </row>
     <row r="222" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C222" s="2"/>
@@ -4181,7 +4189,7 @@
       <c r="L222" s="2"/>
       <c r="M222" s="2"/>
       <c r="N222" s="2"/>
-      <c r="O222" s="5"/>
+      <c r="O222" s="4"/>
     </row>
     <row r="223" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C223" s="2"/>
@@ -4196,7 +4204,7 @@
       <c r="L223" s="2"/>
       <c r="M223" s="2"/>
       <c r="N223" s="2"/>
-      <c r="O223" s="5"/>
+      <c r="O223" s="4"/>
     </row>
     <row r="224" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C224" s="2"/>
@@ -4211,7 +4219,7 @@
       <c r="L224" s="2"/>
       <c r="M224" s="2"/>
       <c r="N224" s="2"/>
-      <c r="O224" s="5"/>
+      <c r="O224" s="4"/>
     </row>
     <row r="225" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C225" s="2"/>
@@ -4226,7 +4234,7 @@
       <c r="L225" s="2"/>
       <c r="M225" s="2"/>
       <c r="N225" s="2"/>
-      <c r="O225" s="5"/>
+      <c r="O225" s="4"/>
     </row>
     <row r="226" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C226" s="2"/>
@@ -4241,7 +4249,7 @@
       <c r="L226" s="2"/>
       <c r="M226" s="2"/>
       <c r="N226" s="2"/>
-      <c r="O226" s="5"/>
+      <c r="O226" s="4"/>
     </row>
     <row r="227" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C227" s="2"/>
@@ -4256,7 +4264,7 @@
       <c r="L227" s="2"/>
       <c r="M227" s="2"/>
       <c r="N227" s="2"/>
-      <c r="O227" s="5"/>
+      <c r="O227" s="4"/>
     </row>
     <row r="228" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C228" s="2"/>
@@ -4271,7 +4279,7 @@
       <c r="L228" s="2"/>
       <c r="M228" s="2"/>
       <c r="N228" s="2"/>
-      <c r="O228" s="5"/>
+      <c r="O228" s="4"/>
     </row>
     <row r="229" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C229" s="2"/>
@@ -4286,7 +4294,7 @@
       <c r="L229" s="2"/>
       <c r="M229" s="2"/>
       <c r="N229" s="2"/>
-      <c r="O229" s="5"/>
+      <c r="O229" s="4"/>
     </row>
     <row r="230" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C230" s="2"/>
@@ -4301,7 +4309,7 @@
       <c r="L230" s="2"/>
       <c r="M230" s="2"/>
       <c r="N230" s="2"/>
-      <c r="O230" s="5"/>
+      <c r="O230" s="4"/>
     </row>
     <row r="231" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C231" s="2"/>
@@ -4316,7 +4324,7 @@
       <c r="L231" s="2"/>
       <c r="M231" s="2"/>
       <c r="N231" s="2"/>
-      <c r="O231" s="5"/>
+      <c r="O231" s="4"/>
     </row>
     <row r="232" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C232" s="2"/>
@@ -4331,7 +4339,7 @@
       <c r="L232" s="2"/>
       <c r="M232" s="2"/>
       <c r="N232" s="2"/>
-      <c r="O232" s="5"/>
+      <c r="O232" s="4"/>
     </row>
     <row r="233" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C233" s="2"/>
@@ -4346,7 +4354,7 @@
       <c r="L233" s="2"/>
       <c r="M233" s="2"/>
       <c r="N233" s="2"/>
-      <c r="O233" s="5"/>
+      <c r="O233" s="4"/>
     </row>
     <row r="234" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C234" s="2"/>
@@ -4361,7 +4369,7 @@
       <c r="L234" s="2"/>
       <c r="M234" s="2"/>
       <c r="N234" s="2"/>
-      <c r="O234" s="5"/>
+      <c r="O234" s="4"/>
     </row>
     <row r="235" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C235" s="2"/>
@@ -4376,7 +4384,7 @@
       <c r="L235" s="2"/>
       <c r="M235" s="2"/>
       <c r="N235" s="2"/>
-      <c r="O235" s="5"/>
+      <c r="O235" s="4"/>
     </row>
     <row r="236" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C236" s="2"/>
@@ -4391,7 +4399,7 @@
       <c r="L236" s="2"/>
       <c r="M236" s="2"/>
       <c r="N236" s="2"/>
-      <c r="O236" s="5"/>
+      <c r="O236" s="4"/>
     </row>
     <row r="237" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C237" s="2"/>
@@ -4406,7 +4414,7 @@
       <c r="L237" s="2"/>
       <c r="M237" s="2"/>
       <c r="N237" s="2"/>
-      <c r="O237" s="5"/>
+      <c r="O237" s="4"/>
     </row>
     <row r="238" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C238" s="2"/>
@@ -4421,7 +4429,7 @@
       <c r="L238" s="2"/>
       <c r="M238" s="2"/>
       <c r="N238" s="2"/>
-      <c r="O238" s="5"/>
+      <c r="O238" s="4"/>
     </row>
     <row r="239" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C239" s="2"/>
@@ -4436,7 +4444,7 @@
       <c r="L239" s="2"/>
       <c r="M239" s="2"/>
       <c r="N239" s="2"/>
-      <c r="O239" s="5"/>
+      <c r="O239" s="4"/>
     </row>
     <row r="240" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C240" s="2"/>
@@ -4451,7 +4459,7 @@
       <c r="L240" s="2"/>
       <c r="M240" s="2"/>
       <c r="N240" s="2"/>
-      <c r="O240" s="5"/>
+      <c r="O240" s="4"/>
     </row>
     <row r="241" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C241" s="2"/>
@@ -4466,7 +4474,7 @@
       <c r="L241" s="2"/>
       <c r="M241" s="2"/>
       <c r="N241" s="2"/>
-      <c r="O241" s="5"/>
+      <c r="O241" s="4"/>
     </row>
     <row r="242" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C242" s="2"/>
@@ -4481,7 +4489,7 @@
       <c r="L242" s="2"/>
       <c r="M242" s="2"/>
       <c r="N242" s="2"/>
-      <c r="O242" s="5"/>
+      <c r="O242" s="4"/>
     </row>
     <row r="243" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C243" s="2"/>
@@ -4496,7 +4504,7 @@
       <c r="L243" s="2"/>
       <c r="M243" s="2"/>
       <c r="N243" s="2"/>
-      <c r="O243" s="5"/>
+      <c r="O243" s="4"/>
     </row>
     <row r="244" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C244" s="2"/>
@@ -4511,7 +4519,7 @@
       <c r="L244" s="2"/>
       <c r="M244" s="2"/>
       <c r="N244" s="2"/>
-      <c r="O244" s="5"/>
+      <c r="O244" s="4"/>
     </row>
     <row r="245" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C245" s="2"/>
@@ -4526,7 +4534,7 @@
       <c r="L245" s="2"/>
       <c r="M245" s="2"/>
       <c r="N245" s="2"/>
-      <c r="O245" s="5"/>
+      <c r="O245" s="4"/>
     </row>
     <row r="246" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C246" s="2"/>
@@ -4541,7 +4549,7 @@
       <c r="L246" s="2"/>
       <c r="M246" s="2"/>
       <c r="N246" s="2"/>
-      <c r="O246" s="5"/>
+      <c r="O246" s="4"/>
     </row>
     <row r="247" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C247" s="2"/>
@@ -4556,7 +4564,7 @@
       <c r="L247" s="2"/>
       <c r="M247" s="2"/>
       <c r="N247" s="2"/>
-      <c r="O247" s="5"/>
+      <c r="O247" s="4"/>
     </row>
     <row r="248" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C248" s="2"/>
@@ -4571,7 +4579,7 @@
       <c r="L248" s="2"/>
       <c r="M248" s="2"/>
       <c r="N248" s="2"/>
-      <c r="O248" s="5"/>
+      <c r="O248" s="4"/>
     </row>
     <row r="249" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C249" s="2"/>
@@ -4586,7 +4594,7 @@
       <c r="L249" s="2"/>
       <c r="M249" s="2"/>
       <c r="N249" s="2"/>
-      <c r="O249" s="5"/>
+      <c r="O249" s="4"/>
     </row>
     <row r="250" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C250" s="2"/>
@@ -4601,7 +4609,7 @@
       <c r="L250" s="2"/>
       <c r="M250" s="2"/>
       <c r="N250" s="2"/>
-      <c r="O250" s="5"/>
+      <c r="O250" s="4"/>
     </row>
     <row r="251" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C251" s="2"/>
@@ -4616,7 +4624,7 @@
       <c r="L251" s="2"/>
       <c r="M251" s="2"/>
       <c r="N251" s="2"/>
-      <c r="O251" s="5"/>
+      <c r="O251" s="4"/>
     </row>
     <row r="252" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C252" s="2"/>
@@ -4631,7 +4639,7 @@
       <c r="L252" s="2"/>
       <c r="M252" s="2"/>
       <c r="N252" s="2"/>
-      <c r="O252" s="5"/>
+      <c r="O252" s="4"/>
     </row>
     <row r="253" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C253" s="2"/>
@@ -4646,7 +4654,7 @@
       <c r="L253" s="2"/>
       <c r="M253" s="2"/>
       <c r="N253" s="2"/>
-      <c r="O253" s="5"/>
+      <c r="O253" s="4"/>
     </row>
     <row r="254" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C254" s="2"/>
@@ -4661,7 +4669,7 @@
       <c r="L254" s="2"/>
       <c r="M254" s="2"/>
       <c r="N254" s="2"/>
-      <c r="O254" s="5"/>
+      <c r="O254" s="4"/>
     </row>
     <row r="255" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C255" s="2"/>
@@ -4676,7 +4684,7 @@
       <c r="L255" s="2"/>
       <c r="M255" s="2"/>
       <c r="N255" s="2"/>
-      <c r="O255" s="5"/>
+      <c r="O255" s="4"/>
     </row>
     <row r="256" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C256" s="2"/>
@@ -4691,7 +4699,7 @@
       <c r="L256" s="2"/>
       <c r="M256" s="2"/>
       <c r="N256" s="2"/>
-      <c r="O256" s="5"/>
+      <c r="O256" s="4"/>
     </row>
     <row r="257" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C257" s="2"/>
@@ -4706,7 +4714,7 @@
       <c r="L257" s="2"/>
       <c r="M257" s="2"/>
       <c r="N257" s="2"/>
-      <c r="O257" s="5"/>
+      <c r="O257" s="4"/>
     </row>
     <row r="258" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C258" s="2"/>
@@ -4721,7 +4729,7 @@
       <c r="L258" s="2"/>
       <c r="M258" s="2"/>
       <c r="N258" s="2"/>
-      <c r="O258" s="5"/>
+      <c r="O258" s="4"/>
     </row>
     <row r="259" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C259" s="2"/>
@@ -4736,7 +4744,7 @@
       <c r="L259" s="2"/>
       <c r="M259" s="2"/>
       <c r="N259" s="2"/>
-      <c r="O259" s="5"/>
+      <c r="O259" s="4"/>
     </row>
     <row r="260" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C260" s="2"/>
@@ -4751,7 +4759,7 @@
       <c r="L260" s="2"/>
       <c r="M260" s="2"/>
       <c r="N260" s="2"/>
-      <c r="O260" s="5"/>
+      <c r="O260" s="4"/>
     </row>
     <row r="261" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C261" s="2"/>
@@ -4766,7 +4774,7 @@
       <c r="L261" s="2"/>
       <c r="M261" s="2"/>
       <c r="N261" s="2"/>
-      <c r="O261" s="5"/>
+      <c r="O261" s="4"/>
     </row>
     <row r="262" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C262" s="2"/>
@@ -4781,7 +4789,7 @@
       <c r="L262" s="2"/>
       <c r="M262" s="2"/>
       <c r="N262" s="2"/>
-      <c r="O262" s="5"/>
+      <c r="O262" s="4"/>
     </row>
     <row r="263" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C263" s="2"/>
@@ -4796,7 +4804,7 @@
       <c r="L263" s="2"/>
       <c r="M263" s="2"/>
       <c r="N263" s="2"/>
-      <c r="O263" s="5"/>
+      <c r="O263" s="4"/>
     </row>
     <row r="264" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C264" s="2"/>
@@ -4811,7 +4819,7 @@
       <c r="L264" s="2"/>
       <c r="M264" s="2"/>
       <c r="N264" s="2"/>
-      <c r="O264" s="5"/>
+      <c r="O264" s="4"/>
     </row>
     <row r="265" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C265" s="2"/>
@@ -4826,7 +4834,7 @@
       <c r="L265" s="2"/>
       <c r="M265" s="2"/>
       <c r="N265" s="2"/>
-      <c r="O265" s="5"/>
+      <c r="O265" s="4"/>
     </row>
     <row r="266" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C266" s="2"/>
@@ -4841,7 +4849,7 @@
       <c r="L266" s="2"/>
       <c r="M266" s="2"/>
       <c r="N266" s="2"/>
-      <c r="O266" s="5"/>
+      <c r="O266" s="4"/>
     </row>
     <row r="267" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C267" s="2"/>
@@ -4856,7 +4864,7 @@
       <c r="L267" s="2"/>
       <c r="M267" s="2"/>
       <c r="N267" s="2"/>
-      <c r="O267" s="5"/>
+      <c r="O267" s="4"/>
     </row>
     <row r="268" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C268" s="2"/>
@@ -4871,7 +4879,7 @@
       <c r="L268" s="2"/>
       <c r="M268" s="2"/>
       <c r="N268" s="2"/>
-      <c r="O268" s="5"/>
+      <c r="O268" s="4"/>
     </row>
     <row r="269" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C269" s="2"/>
@@ -4886,7 +4894,7 @@
       <c r="L269" s="2"/>
       <c r="M269" s="2"/>
       <c r="N269" s="2"/>
-      <c r="O269" s="5"/>
+      <c r="O269" s="4"/>
     </row>
     <row r="270" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C270" s="2"/>
@@ -4901,7 +4909,7 @@
       <c r="L270" s="2"/>
       <c r="M270" s="2"/>
       <c r="N270" s="2"/>
-      <c r="O270" s="5"/>
+      <c r="O270" s="4"/>
     </row>
     <row r="271" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C271" s="2"/>
@@ -4916,7 +4924,7 @@
       <c r="L271" s="2"/>
       <c r="M271" s="2"/>
       <c r="N271" s="2"/>
-      <c r="O271" s="5"/>
+      <c r="O271" s="4"/>
     </row>
     <row r="272" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C272" s="2"/>
@@ -4931,7 +4939,7 @@
       <c r="L272" s="2"/>
       <c r="M272" s="2"/>
       <c r="N272" s="2"/>
-      <c r="O272" s="5"/>
+      <c r="O272" s="4"/>
     </row>
     <row r="273" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C273" s="2"/>
@@ -4946,7 +4954,7 @@
       <c r="L273" s="2"/>
       <c r="M273" s="2"/>
       <c r="N273" s="2"/>
-      <c r="O273" s="5"/>
+      <c r="O273" s="4"/>
     </row>
     <row r="274" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C274" s="2"/>
@@ -4961,7 +4969,7 @@
       <c r="L274" s="2"/>
       <c r="M274" s="2"/>
       <c r="N274" s="2"/>
-      <c r="O274" s="5"/>
+      <c r="O274" s="4"/>
     </row>
     <row r="275" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C275" s="2"/>
@@ -4976,7 +4984,7 @@
       <c r="L275" s="2"/>
       <c r="M275" s="2"/>
       <c r="N275" s="2"/>
-      <c r="O275" s="5"/>
+      <c r="O275" s="4"/>
     </row>
     <row r="276" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C276" s="2"/>
@@ -4991,7 +4999,7 @@
       <c r="L276" s="2"/>
       <c r="M276" s="2"/>
       <c r="N276" s="2"/>
-      <c r="O276" s="5"/>
+      <c r="O276" s="4"/>
     </row>
     <row r="277" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C277" s="2"/>
@@ -5006,7 +5014,7 @@
       <c r="L277" s="2"/>
       <c r="M277" s="2"/>
       <c r="N277" s="2"/>
-      <c r="O277" s="5"/>
+      <c r="O277" s="4"/>
     </row>
     <row r="278" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C278" s="2"/>
@@ -5021,7 +5029,7 @@
       <c r="L278" s="2"/>
       <c r="M278" s="2"/>
       <c r="N278" s="2"/>
-      <c r="O278" s="5"/>
+      <c r="O278" s="4"/>
     </row>
     <row r="279" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C279" s="2"/>
@@ -5036,7 +5044,7 @@
       <c r="L279" s="2"/>
       <c r="M279" s="2"/>
       <c r="N279" s="2"/>
-      <c r="O279" s="5"/>
+      <c r="O279" s="4"/>
     </row>
     <row r="280" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C280" s="2"/>
@@ -5051,7 +5059,7 @@
       <c r="L280" s="2"/>
       <c r="M280" s="2"/>
       <c r="N280" s="2"/>
-      <c r="O280" s="5"/>
+      <c r="O280" s="4"/>
     </row>
     <row r="281" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C281" s="2"/>
@@ -5066,7 +5074,7 @@
       <c r="L281" s="2"/>
       <c r="M281" s="2"/>
       <c r="N281" s="2"/>
-      <c r="O281" s="5"/>
+      <c r="O281" s="4"/>
     </row>
     <row r="282" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C282" s="2"/>
@@ -5081,7 +5089,7 @@
       <c r="L282" s="2"/>
       <c r="M282" s="2"/>
       <c r="N282" s="2"/>
-      <c r="O282" s="5"/>
+      <c r="O282" s="4"/>
     </row>
     <row r="283" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C283" s="2"/>
@@ -5096,7 +5104,7 @@
       <c r="L283" s="2"/>
       <c r="M283" s="2"/>
       <c r="N283" s="2"/>
-      <c r="O283" s="5"/>
+      <c r="O283" s="4"/>
     </row>
     <row r="284" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C284" s="2"/>
@@ -5111,7 +5119,7 @@
       <c r="L284" s="2"/>
       <c r="M284" s="2"/>
       <c r="N284" s="2"/>
-      <c r="O284" s="5"/>
+      <c r="O284" s="4"/>
     </row>
     <row r="285" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C285" s="2"/>
@@ -5126,7 +5134,7 @@
       <c r="L285" s="2"/>
       <c r="M285" s="2"/>
       <c r="N285" s="2"/>
-      <c r="O285" s="5"/>
+      <c r="O285" s="4"/>
     </row>
     <row r="286" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C286" s="2"/>
@@ -5141,7 +5149,7 @@
       <c r="L286" s="2"/>
       <c r="M286" s="2"/>
       <c r="N286" s="2"/>
-      <c r="O286" s="5"/>
+      <c r="O286" s="4"/>
     </row>
     <row r="287" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C287" s="2"/>
@@ -5156,7 +5164,7 @@
       <c r="L287" s="2"/>
       <c r="M287" s="2"/>
       <c r="N287" s="2"/>
-      <c r="O287" s="5"/>
+      <c r="O287" s="4"/>
     </row>
     <row r="288" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C288" s="2"/>
@@ -5171,7 +5179,7 @@
       <c r="L288" s="2"/>
       <c r="M288" s="2"/>
       <c r="N288" s="2"/>
-      <c r="O288" s="5"/>
+      <c r="O288" s="4"/>
     </row>
     <row r="289" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C289" s="2"/>
@@ -5186,7 +5194,7 @@
       <c r="L289" s="2"/>
       <c r="M289" s="2"/>
       <c r="N289" s="2"/>
-      <c r="O289" s="5"/>
+      <c r="O289" s="4"/>
     </row>
     <row r="290" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C290" s="2"/>
@@ -5201,7 +5209,7 @@
       <c r="L290" s="2"/>
       <c r="M290" s="2"/>
       <c r="N290" s="2"/>
-      <c r="O290" s="5"/>
+      <c r="O290" s="4"/>
     </row>
     <row r="291" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C291" s="2"/>
@@ -5216,7 +5224,7 @@
       <c r="L291" s="2"/>
       <c r="M291" s="2"/>
       <c r="N291" s="2"/>
-      <c r="O291" s="5"/>
+      <c r="O291" s="4"/>
     </row>
     <row r="292" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C292" s="2"/>
@@ -5231,7 +5239,7 @@
       <c r="L292" s="2"/>
       <c r="M292" s="2"/>
       <c r="N292" s="2"/>
-      <c r="O292" s="5"/>
+      <c r="O292" s="4"/>
     </row>
     <row r="293" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C293" s="2"/>
@@ -5246,7 +5254,7 @@
       <c r="L293" s="2"/>
       <c r="M293" s="2"/>
       <c r="N293" s="2"/>
-      <c r="O293" s="5"/>
+      <c r="O293" s="4"/>
     </row>
     <row r="294" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C294" s="2"/>
@@ -5261,7 +5269,7 @@
       <c r="L294" s="2"/>
       <c r="M294" s="2"/>
       <c r="N294" s="2"/>
-      <c r="O294" s="5"/>
+      <c r="O294" s="4"/>
     </row>
     <row r="295" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C295" s="2"/>
@@ -5276,7 +5284,7 @@
       <c r="L295" s="2"/>
       <c r="M295" s="2"/>
       <c r="N295" s="2"/>
-      <c r="O295" s="5"/>
+      <c r="O295" s="4"/>
     </row>
     <row r="296" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C296" s="2"/>
@@ -5291,7 +5299,7 @@
       <c r="L296" s="2"/>
       <c r="M296" s="2"/>
       <c r="N296" s="2"/>
-      <c r="O296" s="5"/>
+      <c r="O296" s="4"/>
     </row>
     <row r="297" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C297" s="2"/>
@@ -5306,7 +5314,7 @@
       <c r="L297" s="2"/>
       <c r="M297" s="2"/>
       <c r="N297" s="2"/>
-      <c r="O297" s="5"/>
+      <c r="O297" s="4"/>
     </row>
     <row r="298" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C298" s="2"/>
@@ -5321,7 +5329,7 @@
       <c r="L298" s="2"/>
       <c r="M298" s="2"/>
       <c r="N298" s="2"/>
-      <c r="O298" s="5"/>
+      <c r="O298" s="4"/>
     </row>
     <row r="299" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C299" s="2"/>
@@ -5336,7 +5344,7 @@
       <c r="L299" s="2"/>
       <c r="M299" s="2"/>
       <c r="N299" s="2"/>
-      <c r="O299" s="5"/>
+      <c r="O299" s="4"/>
     </row>
     <row r="300" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C300" s="2"/>
@@ -5351,7 +5359,7 @@
       <c r="L300" s="2"/>
       <c r="M300" s="2"/>
       <c r="N300" s="2"/>
-      <c r="O300" s="5"/>
+      <c r="O300" s="4"/>
     </row>
     <row r="301" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C301" s="2"/>
@@ -5366,7 +5374,7 @@
       <c r="L301" s="2"/>
       <c r="M301" s="2"/>
       <c r="N301" s="2"/>
-      <c r="O301" s="5"/>
+      <c r="O301" s="4"/>
     </row>
     <row r="302" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C302" s="2"/>
@@ -5381,7 +5389,7 @@
       <c r="L302" s="2"/>
       <c r="M302" s="2"/>
       <c r="N302" s="2"/>
-      <c r="O302" s="5"/>
+      <c r="O302" s="4"/>
     </row>
     <row r="303" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C303" s="2"/>
@@ -5396,7 +5404,7 @@
       <c r="L303" s="2"/>
       <c r="M303" s="2"/>
       <c r="N303" s="2"/>
-      <c r="O303" s="5"/>
+      <c r="O303" s="4"/>
     </row>
     <row r="304" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C304" s="2"/>
@@ -5411,7 +5419,7 @@
       <c r="L304" s="2"/>
       <c r="M304" s="2"/>
       <c r="N304" s="2"/>
-      <c r="O304" s="5"/>
+      <c r="O304" s="4"/>
     </row>
     <row r="305" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C305" s="2"/>
@@ -5426,7 +5434,7 @@
       <c r="L305" s="2"/>
       <c r="M305" s="2"/>
       <c r="N305" s="2"/>
-      <c r="O305" s="5"/>
+      <c r="O305" s="4"/>
     </row>
     <row r="306" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C306" s="2"/>
@@ -5441,7 +5449,7 @@
       <c r="L306" s="2"/>
       <c r="M306" s="2"/>
       <c r="N306" s="2"/>
-      <c r="O306" s="5"/>
+      <c r="O306" s="4"/>
     </row>
     <row r="307" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C307" s="2"/>
@@ -5456,7 +5464,7 @@
       <c r="L307" s="2"/>
       <c r="M307" s="2"/>
       <c r="N307" s="2"/>
-      <c r="O307" s="5"/>
+      <c r="O307" s="4"/>
     </row>
     <row r="308" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C308" s="2"/>
@@ -5471,7 +5479,7 @@
       <c r="L308" s="2"/>
       <c r="M308" s="2"/>
       <c r="N308" s="2"/>
-      <c r="O308" s="5"/>
+      <c r="O308" s="4"/>
     </row>
     <row r="309" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C309" s="2"/>
@@ -5486,7 +5494,7 @@
       <c r="L309" s="2"/>
       <c r="M309" s="2"/>
       <c r="N309" s="2"/>
-      <c r="O309" s="5"/>
+      <c r="O309" s="4"/>
     </row>
     <row r="310" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C310" s="2"/>
@@ -5501,7 +5509,7 @@
       <c r="L310" s="2"/>
       <c r="M310" s="2"/>
       <c r="N310" s="2"/>
-      <c r="O310" s="5"/>
+      <c r="O310" s="4"/>
     </row>
     <row r="311" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C311" s="2"/>
@@ -5516,7 +5524,7 @@
       <c r="L311" s="2"/>
       <c r="M311" s="2"/>
       <c r="N311" s="2"/>
-      <c r="O311" s="5"/>
+      <c r="O311" s="4"/>
     </row>
     <row r="312" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C312" s="2"/>
@@ -5531,7 +5539,7 @@
       <c r="L312" s="2"/>
       <c r="M312" s="2"/>
       <c r="N312" s="2"/>
-      <c r="O312" s="5"/>
+      <c r="O312" s="4"/>
     </row>
     <row r="313" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C313" s="2"/>
@@ -5546,7 +5554,7 @@
       <c r="L313" s="2"/>
       <c r="M313" s="2"/>
       <c r="N313" s="2"/>
-      <c r="O313" s="5"/>
+      <c r="O313" s="4"/>
     </row>
     <row r="314" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C314" s="2"/>
@@ -5561,7 +5569,7 @@
       <c r="L314" s="2"/>
       <c r="M314" s="2"/>
       <c r="N314" s="2"/>
-      <c r="O314" s="5"/>
+      <c r="O314" s="4"/>
     </row>
     <row r="315" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C315" s="2"/>
@@ -5576,7 +5584,7 @@
       <c r="L315" s="2"/>
       <c r="M315" s="2"/>
       <c r="N315" s="2"/>
-      <c r="O315" s="5"/>
+      <c r="O315" s="4"/>
     </row>
     <row r="316" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C316" s="2"/>
@@ -5591,7 +5599,7 @@
       <c r="L316" s="2"/>
       <c r="M316" s="2"/>
       <c r="N316" s="2"/>
-      <c r="O316" s="5"/>
+      <c r="O316" s="4"/>
     </row>
     <row r="317" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C317" s="2"/>
@@ -5606,7 +5614,7 @@
       <c r="L317" s="2"/>
       <c r="M317" s="2"/>
       <c r="N317" s="2"/>
-      <c r="O317" s="5"/>
+      <c r="O317" s="4"/>
     </row>
     <row r="318" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C318" s="2"/>
@@ -5621,7 +5629,7 @@
       <c r="L318" s="2"/>
       <c r="M318" s="2"/>
       <c r="N318" s="2"/>
-      <c r="O318" s="5"/>
+      <c r="O318" s="4"/>
     </row>
     <row r="319" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C319" s="2"/>
@@ -5636,7 +5644,7 @@
       <c r="L319" s="2"/>
       <c r="M319" s="2"/>
       <c r="N319" s="2"/>
-      <c r="O319" s="5"/>
+      <c r="O319" s="4"/>
     </row>
     <row r="320" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C320" s="2"/>
@@ -5651,7 +5659,7 @@
       <c r="L320" s="2"/>
       <c r="M320" s="2"/>
       <c r="N320" s="2"/>
-      <c r="O320" s="5"/>
+      <c r="O320" s="4"/>
     </row>
     <row r="321" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C321" s="2"/>
@@ -5666,7 +5674,7 @@
       <c r="L321" s="2"/>
       <c r="M321" s="2"/>
       <c r="N321" s="2"/>
-      <c r="O321" s="5"/>
+      <c r="O321" s="4"/>
     </row>
     <row r="322" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C322" s="2"/>
@@ -5681,7 +5689,7 @@
       <c r="L322" s="2"/>
       <c r="M322" s="2"/>
       <c r="N322" s="2"/>
-      <c r="O322" s="5"/>
+      <c r="O322" s="4"/>
     </row>
     <row r="323" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C323" s="2"/>
@@ -5696,7 +5704,7 @@
       <c r="L323" s="2"/>
       <c r="M323" s="2"/>
       <c r="N323" s="2"/>
-      <c r="O323" s="5"/>
+      <c r="O323" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/templates/vacation_map_template.xlsx
+++ b/templates/vacation_map_template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geral\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\F. Martins\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B60A419-4BE9-49A2-A4F8-AD0B92E37D86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E1A18D7-FB4F-4269-B143-18EF24DFD52C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B7894565-86C4-4C3D-8BBD-69A912659748}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B7894565-86C4-4C3D-8BBD-69A912659748}"/>
   </bookViews>
   <sheets>
     <sheet name="Folha1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>Nome</t>
   </si>
@@ -104,9 +104,6 @@
       </rPr>
       <t>"Cruz Lusa"</t>
     </r>
-  </si>
-  <si>
-    <t>00 a 00 e 00 a 00</t>
   </si>
 </sst>
 </file>
@@ -395,9 +392,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -426,6 +420,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -501,9 +498,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema Office 2013 - 2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -541,7 +538,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -647,7 +644,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -789,7 +786,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -827,723 +824,721 @@
       </c>
     </row>
     <row r="6" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B6" s="20"/>
-      <c r="C6" s="20"/>
-      <c r="D6" s="20"/>
-      <c r="E6" s="20"/>
-      <c r="F6" s="20"/>
-      <c r="G6" s="20"/>
-      <c r="H6" s="20"/>
-      <c r="I6" s="20"/>
-      <c r="J6" s="20"/>
-      <c r="K6" s="20"/>
-      <c r="L6" s="20"/>
-      <c r="M6" s="20"/>
-      <c r="N6" s="20"/>
-      <c r="O6" s="20"/>
+      <c r="B6" s="19"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="19"/>
+      <c r="H6" s="19"/>
+      <c r="I6" s="19"/>
+      <c r="J6" s="19"/>
+      <c r="K6" s="19"/>
+      <c r="L6" s="19"/>
+      <c r="M6" s="19"/>
+      <c r="N6" s="19"/>
+      <c r="O6" s="19"/>
     </row>
     <row r="7" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B7" s="20"/>
-      <c r="C7" s="20"/>
-      <c r="D7" s="20"/>
-      <c r="E7" s="20"/>
-      <c r="F7" s="20"/>
-      <c r="G7" s="20"/>
-      <c r="H7" s="20"/>
-      <c r="I7" s="20"/>
-      <c r="J7" s="20"/>
-      <c r="K7" s="20"/>
-      <c r="L7" s="20"/>
-      <c r="M7" s="20"/>
-      <c r="N7" s="20"/>
-      <c r="O7" s="20"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="19"/>
+      <c r="H7" s="19"/>
+      <c r="I7" s="19"/>
+      <c r="J7" s="19"/>
+      <c r="K7" s="19"/>
+      <c r="L7" s="19"/>
+      <c r="M7" s="19"/>
+      <c r="N7" s="19"/>
+      <c r="O7" s="19"/>
     </row>
     <row r="8" spans="2:15" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="9" spans="2:15" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="17" t="s">
+      <c r="B9" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="C9" s="18" t="s">
+      <c r="C9" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="D9" s="18" t="s">
+      <c r="D9" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="E9" s="18" t="s">
+      <c r="E9" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="F9" s="18" t="s">
+      <c r="F9" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="G9" s="18" t="s">
+      <c r="G9" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="H9" s="18" t="s">
+      <c r="H9" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="I9" s="18" t="s">
+      <c r="I9" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="J9" s="18" t="s">
+      <c r="J9" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="K9" s="18" t="s">
+      <c r="K9" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="L9" s="18" t="s">
+      <c r="L9" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="M9" s="18" t="s">
+      <c r="M9" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="N9" s="18" t="s">
+      <c r="N9" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="O9" s="19" t="s">
+      <c r="O9" s="18" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="10" spans="2:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="11"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="12"/>
-      <c r="I10" s="12"/>
-      <c r="J10" s="12"/>
-      <c r="K10" s="12"/>
-      <c r="L10" s="12"/>
-      <c r="M10" s="12"/>
-      <c r="N10" s="12"/>
-      <c r="O10" s="13"/>
+      <c r="B10" s="10"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="11"/>
+      <c r="J10" s="11"/>
+      <c r="K10" s="11"/>
+      <c r="L10" s="11"/>
+      <c r="M10" s="11"/>
+      <c r="N10" s="11"/>
+      <c r="O10" s="12"/>
     </row>
     <row r="11" spans="2:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="11"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="12"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="12"/>
-      <c r="J11" s="12"/>
-      <c r="K11" s="12"/>
-      <c r="L11" s="12"/>
-      <c r="M11" s="12"/>
-      <c r="N11" s="12"/>
-      <c r="O11" s="13"/>
+      <c r="B11" s="10"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="11"/>
+      <c r="J11" s="11"/>
+      <c r="K11" s="11"/>
+      <c r="L11" s="11"/>
+      <c r="M11" s="11"/>
+      <c r="N11" s="11"/>
+      <c r="O11" s="12"/>
     </row>
     <row r="12" spans="2:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="11"/>
-      <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="12"/>
-      <c r="I12" s="12"/>
-      <c r="J12" s="12"/>
-      <c r="K12" s="12"/>
-      <c r="L12" s="12"/>
-      <c r="M12" s="12"/>
-      <c r="N12" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="O12" s="13"/>
+      <c r="B12" s="10"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="11"/>
+      <c r="I12" s="11"/>
+      <c r="J12" s="11"/>
+      <c r="K12" s="11"/>
+      <c r="L12" s="11"/>
+      <c r="M12" s="11"/>
+      <c r="N12" s="11"/>
+      <c r="O12" s="12"/>
     </row>
     <row r="13" spans="2:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="11"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="12"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="12"/>
-      <c r="H13" s="12"/>
-      <c r="I13" s="12"/>
-      <c r="J13" s="12"/>
-      <c r="K13" s="12"/>
-      <c r="L13" s="12"/>
-      <c r="M13" s="12"/>
-      <c r="N13" s="12"/>
-      <c r="O13" s="13"/>
+      <c r="B13" s="10"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="11"/>
+      <c r="J13" s="11"/>
+      <c r="K13" s="11"/>
+      <c r="L13" s="11"/>
+      <c r="M13" s="11"/>
+      <c r="N13" s="11"/>
+      <c r="O13" s="12"/>
     </row>
     <row r="14" spans="2:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="11"/>
-      <c r="C14" s="12"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="12"/>
-      <c r="H14" s="12"/>
-      <c r="I14" s="12"/>
-      <c r="J14" s="12"/>
-      <c r="K14" s="12"/>
-      <c r="L14" s="12"/>
-      <c r="M14" s="12"/>
-      <c r="N14" s="12"/>
-      <c r="O14" s="13"/>
+      <c r="B14" s="10"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="11"/>
+      <c r="J14" s="11"/>
+      <c r="K14" s="11"/>
+      <c r="L14" s="11"/>
+      <c r="M14" s="11"/>
+      <c r="N14" s="11"/>
+      <c r="O14" s="12"/>
     </row>
     <row r="15" spans="2:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="11"/>
-      <c r="C15" s="12"/>
-      <c r="D15" s="12"/>
-      <c r="E15" s="12"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="12"/>
-      <c r="H15" s="12"/>
-      <c r="I15" s="12"/>
-      <c r="J15" s="12"/>
-      <c r="K15" s="12"/>
-      <c r="L15" s="12"/>
-      <c r="M15" s="12"/>
-      <c r="N15" s="12"/>
-      <c r="O15" s="13"/>
+      <c r="B15" s="10"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="11"/>
+      <c r="J15" s="11"/>
+      <c r="K15" s="11"/>
+      <c r="L15" s="11"/>
+      <c r="M15" s="11"/>
+      <c r="N15" s="11"/>
+      <c r="O15" s="12"/>
     </row>
     <row r="16" spans="2:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="11"/>
-      <c r="C16" s="12"/>
-      <c r="D16" s="12"/>
-      <c r="E16" s="12"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="12"/>
-      <c r="H16" s="12"/>
-      <c r="I16" s="12"/>
-      <c r="J16" s="12"/>
-      <c r="K16" s="12"/>
-      <c r="L16" s="12"/>
-      <c r="M16" s="12"/>
-      <c r="N16" s="12"/>
-      <c r="O16" s="13"/>
+      <c r="B16" s="10"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="11"/>
+      <c r="I16" s="11"/>
+      <c r="J16" s="11"/>
+      <c r="K16" s="11"/>
+      <c r="L16" s="11"/>
+      <c r="M16" s="11"/>
+      <c r="N16" s="11"/>
+      <c r="O16" s="12"/>
     </row>
     <row r="17" spans="2:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="11"/>
-      <c r="C17" s="12"/>
-      <c r="D17" s="12"/>
-      <c r="E17" s="12"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="12"/>
-      <c r="H17" s="12"/>
-      <c r="I17" s="12"/>
-      <c r="J17" s="12"/>
-      <c r="K17" s="12"/>
-      <c r="L17" s="12"/>
-      <c r="M17" s="12"/>
-      <c r="N17" s="12"/>
-      <c r="O17" s="13"/>
+      <c r="B17" s="10"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="11"/>
+      <c r="J17" s="11"/>
+      <c r="K17" s="11"/>
+      <c r="L17" s="11"/>
+      <c r="M17" s="11"/>
+      <c r="N17" s="11"/>
+      <c r="O17" s="12"/>
     </row>
     <row r="18" spans="2:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="11"/>
-      <c r="C18" s="12"/>
-      <c r="D18" s="12"/>
-      <c r="E18" s="12"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="12"/>
-      <c r="H18" s="12"/>
-      <c r="I18" s="12"/>
-      <c r="J18" s="12"/>
-      <c r="K18" s="12"/>
-      <c r="L18" s="12"/>
-      <c r="M18" s="12"/>
-      <c r="N18" s="12"/>
-      <c r="O18" s="13"/>
+      <c r="B18" s="10"/>
+      <c r="C18" s="11"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="11"/>
+      <c r="I18" s="11"/>
+      <c r="J18" s="11"/>
+      <c r="K18" s="11"/>
+      <c r="L18" s="11"/>
+      <c r="M18" s="11"/>
+      <c r="N18" s="11"/>
+      <c r="O18" s="12"/>
     </row>
     <row r="19" spans="2:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="11"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="12"/>
-      <c r="H19" s="12"/>
-      <c r="I19" s="12"/>
-      <c r="J19" s="12"/>
-      <c r="K19" s="12"/>
-      <c r="L19" s="12"/>
-      <c r="M19" s="12"/>
-      <c r="N19" s="12"/>
-      <c r="O19" s="13"/>
+      <c r="B19" s="10"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="11"/>
+      <c r="I19" s="11"/>
+      <c r="J19" s="11"/>
+      <c r="K19" s="11"/>
+      <c r="L19" s="11"/>
+      <c r="M19" s="11"/>
+      <c r="N19" s="11"/>
+      <c r="O19" s="12"/>
     </row>
     <row r="20" spans="2:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="11"/>
-      <c r="C20" s="12"/>
-      <c r="D20" s="12"/>
-      <c r="E20" s="12"/>
-      <c r="F20" s="12"/>
-      <c r="G20" s="12"/>
-      <c r="H20" s="12"/>
-      <c r="I20" s="12"/>
-      <c r="J20" s="12"/>
-      <c r="K20" s="12"/>
-      <c r="L20" s="12"/>
-      <c r="M20" s="12"/>
-      <c r="N20" s="12"/>
-      <c r="O20" s="13"/>
+      <c r="B20" s="10"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="11"/>
+      <c r="G20" s="11"/>
+      <c r="H20" s="11"/>
+      <c r="I20" s="11"/>
+      <c r="J20" s="11"/>
+      <c r="K20" s="11"/>
+      <c r="L20" s="11"/>
+      <c r="M20" s="11"/>
+      <c r="N20" s="11"/>
+      <c r="O20" s="12"/>
     </row>
     <row r="21" spans="2:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="11"/>
-      <c r="C21" s="12"/>
-      <c r="D21" s="12"/>
-      <c r="E21" s="12"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="12"/>
-      <c r="H21" s="12"/>
-      <c r="I21" s="12"/>
-      <c r="J21" s="12"/>
-      <c r="K21" s="12"/>
-      <c r="L21" s="12"/>
-      <c r="M21" s="12"/>
-      <c r="N21" s="12"/>
-      <c r="O21" s="13"/>
+      <c r="B21" s="10"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="11"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="11"/>
+      <c r="J21" s="11"/>
+      <c r="K21" s="11"/>
+      <c r="L21" s="11"/>
+      <c r="M21" s="11"/>
+      <c r="N21" s="11"/>
+      <c r="O21" s="12"/>
     </row>
     <row r="22" spans="2:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="11"/>
-      <c r="C22" s="12"/>
-      <c r="D22" s="12"/>
-      <c r="E22" s="12"/>
-      <c r="F22" s="12"/>
-      <c r="G22" s="12"/>
-      <c r="H22" s="12"/>
-      <c r="I22" s="12"/>
-      <c r="J22" s="12"/>
-      <c r="K22" s="12"/>
-      <c r="L22" s="12"/>
-      <c r="M22" s="12"/>
-      <c r="N22" s="12"/>
-      <c r="O22" s="13"/>
+      <c r="B22" s="10"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="11"/>
+      <c r="H22" s="11"/>
+      <c r="I22" s="11"/>
+      <c r="J22" s="11"/>
+      <c r="K22" s="11"/>
+      <c r="L22" s="11"/>
+      <c r="M22" s="11"/>
+      <c r="N22" s="11"/>
+      <c r="O22" s="12"/>
     </row>
     <row r="23" spans="2:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="11"/>
-      <c r="C23" s="12"/>
-      <c r="D23" s="12"/>
-      <c r="E23" s="12"/>
-      <c r="F23" s="12"/>
-      <c r="G23" s="12"/>
-      <c r="H23" s="12"/>
-      <c r="I23" s="12"/>
-      <c r="J23" s="12"/>
-      <c r="K23" s="12"/>
-      <c r="L23" s="12"/>
-      <c r="M23" s="12"/>
-      <c r="N23" s="12"/>
-      <c r="O23" s="13"/>
+      <c r="B23" s="10"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="11"/>
+      <c r="H23" s="11"/>
+      <c r="I23" s="11"/>
+      <c r="J23" s="11"/>
+      <c r="K23" s="11"/>
+      <c r="L23" s="11"/>
+      <c r="M23" s="11"/>
+      <c r="N23" s="11"/>
+      <c r="O23" s="12"/>
     </row>
     <row r="24" spans="2:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="11"/>
-      <c r="C24" s="12"/>
-      <c r="D24" s="12"/>
-      <c r="E24" s="12"/>
-      <c r="F24" s="12"/>
-      <c r="G24" s="12"/>
-      <c r="H24" s="12"/>
-      <c r="I24" s="12"/>
-      <c r="J24" s="12"/>
-      <c r="K24" s="12"/>
-      <c r="L24" s="12"/>
-      <c r="M24" s="12"/>
-      <c r="N24" s="12"/>
-      <c r="O24" s="13"/>
+      <c r="B24" s="10"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="11"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="11"/>
+      <c r="H24" s="11"/>
+      <c r="I24" s="11"/>
+      <c r="J24" s="11"/>
+      <c r="K24" s="11"/>
+      <c r="L24" s="11"/>
+      <c r="M24" s="11"/>
+      <c r="N24" s="11"/>
+      <c r="O24" s="12"/>
     </row>
     <row r="25" spans="2:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="11"/>
-      <c r="C25" s="12"/>
-      <c r="D25" s="12"/>
-      <c r="E25" s="12"/>
-      <c r="F25" s="12"/>
-      <c r="G25" s="12"/>
-      <c r="H25" s="12"/>
-      <c r="I25" s="12"/>
-      <c r="J25" s="12"/>
-      <c r="K25" s="12"/>
-      <c r="L25" s="12"/>
-      <c r="M25" s="12"/>
-      <c r="N25" s="12"/>
-      <c r="O25" s="13"/>
+      <c r="B25" s="10"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="11"/>
+      <c r="I25" s="11"/>
+      <c r="J25" s="11"/>
+      <c r="K25" s="11"/>
+      <c r="L25" s="11"/>
+      <c r="M25" s="11"/>
+      <c r="N25" s="11"/>
+      <c r="O25" s="12"/>
     </row>
     <row r="26" spans="2:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="11"/>
-      <c r="C26" s="12"/>
-      <c r="D26" s="12"/>
-      <c r="E26" s="12"/>
-      <c r="F26" s="12"/>
-      <c r="G26" s="12"/>
-      <c r="H26" s="12"/>
-      <c r="I26" s="12"/>
-      <c r="J26" s="12"/>
-      <c r="K26" s="12"/>
-      <c r="L26" s="12"/>
-      <c r="M26" s="12"/>
-      <c r="N26" s="12"/>
-      <c r="O26" s="13"/>
+      <c r="B26" s="10"/>
+      <c r="C26" s="11"/>
+      <c r="D26" s="11"/>
+      <c r="E26" s="11"/>
+      <c r="F26" s="11"/>
+      <c r="G26" s="11"/>
+      <c r="H26" s="11"/>
+      <c r="I26" s="11"/>
+      <c r="J26" s="11"/>
+      <c r="K26" s="11"/>
+      <c r="L26" s="11"/>
+      <c r="M26" s="11"/>
+      <c r="N26" s="11"/>
+      <c r="O26" s="12"/>
     </row>
     <row r="27" spans="2:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="11"/>
-      <c r="C27" s="12"/>
-      <c r="D27" s="12"/>
-      <c r="E27" s="12"/>
-      <c r="F27" s="12"/>
-      <c r="G27" s="12"/>
-      <c r="H27" s="12"/>
-      <c r="I27" s="12"/>
-      <c r="J27" s="12"/>
-      <c r="K27" s="12"/>
-      <c r="L27" s="12"/>
-      <c r="M27" s="12"/>
-      <c r="N27" s="12"/>
-      <c r="O27" s="13"/>
+      <c r="B27" s="10"/>
+      <c r="C27" s="11"/>
+      <c r="D27" s="11"/>
+      <c r="E27" s="11"/>
+      <c r="F27" s="11"/>
+      <c r="G27" s="11"/>
+      <c r="H27" s="11"/>
+      <c r="I27" s="11"/>
+      <c r="J27" s="11"/>
+      <c r="K27" s="11"/>
+      <c r="L27" s="11"/>
+      <c r="M27" s="11"/>
+      <c r="N27" s="11"/>
+      <c r="O27" s="12"/>
     </row>
     <row r="28" spans="2:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="11"/>
-      <c r="C28" s="12"/>
-      <c r="D28" s="12"/>
-      <c r="E28" s="12"/>
-      <c r="F28" s="12"/>
-      <c r="G28" s="12"/>
-      <c r="H28" s="12"/>
-      <c r="I28" s="12"/>
-      <c r="J28" s="12"/>
-      <c r="K28" s="12"/>
-      <c r="L28" s="12"/>
-      <c r="M28" s="12"/>
-      <c r="N28" s="12"/>
-      <c r="O28" s="13"/>
+      <c r="B28" s="10"/>
+      <c r="C28" s="11"/>
+      <c r="D28" s="11"/>
+      <c r="E28" s="11"/>
+      <c r="F28" s="11"/>
+      <c r="G28" s="11"/>
+      <c r="H28" s="11"/>
+      <c r="I28" s="11"/>
+      <c r="J28" s="11"/>
+      <c r="K28" s="11"/>
+      <c r="L28" s="11"/>
+      <c r="M28" s="11"/>
+      <c r="N28" s="11"/>
+      <c r="O28" s="12"/>
     </row>
     <row r="29" spans="2:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="11"/>
-      <c r="C29" s="12"/>
-      <c r="D29" s="12"/>
-      <c r="E29" s="12"/>
-      <c r="F29" s="12"/>
-      <c r="G29" s="12"/>
-      <c r="H29" s="12"/>
-      <c r="I29" s="12"/>
-      <c r="J29" s="12"/>
-      <c r="K29" s="12"/>
-      <c r="L29" s="12"/>
-      <c r="M29" s="12"/>
-      <c r="N29" s="12"/>
-      <c r="O29" s="13"/>
+      <c r="B29" s="10"/>
+      <c r="C29" s="11"/>
+      <c r="D29" s="11"/>
+      <c r="E29" s="11"/>
+      <c r="F29" s="11"/>
+      <c r="G29" s="11"/>
+      <c r="H29" s="11"/>
+      <c r="I29" s="11"/>
+      <c r="J29" s="11"/>
+      <c r="K29" s="11"/>
+      <c r="L29" s="11"/>
+      <c r="M29" s="11"/>
+      <c r="N29" s="11"/>
+      <c r="O29" s="12"/>
     </row>
     <row r="30" spans="2:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="11"/>
-      <c r="C30" s="12"/>
-      <c r="D30" s="12"/>
-      <c r="E30" s="12"/>
-      <c r="F30" s="12"/>
-      <c r="G30" s="12"/>
-      <c r="H30" s="12"/>
-      <c r="I30" s="12"/>
-      <c r="J30" s="12"/>
-      <c r="K30" s="12"/>
-      <c r="L30" s="12"/>
-      <c r="M30" s="12"/>
-      <c r="N30" s="12"/>
-      <c r="O30" s="13"/>
+      <c r="B30" s="10"/>
+      <c r="C30" s="11"/>
+      <c r="D30" s="11"/>
+      <c r="E30" s="11"/>
+      <c r="F30" s="11"/>
+      <c r="G30" s="11"/>
+      <c r="H30" s="11"/>
+      <c r="I30" s="11"/>
+      <c r="J30" s="11"/>
+      <c r="K30" s="11"/>
+      <c r="L30" s="11"/>
+      <c r="M30" s="11"/>
+      <c r="N30" s="11"/>
+      <c r="O30" s="12"/>
     </row>
     <row r="31" spans="2:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="11"/>
-      <c r="C31" s="12"/>
-      <c r="D31" s="12"/>
-      <c r="E31" s="12"/>
-      <c r="F31" s="12"/>
-      <c r="G31" s="12"/>
-      <c r="H31" s="12"/>
-      <c r="I31" s="12"/>
-      <c r="J31" s="12"/>
-      <c r="K31" s="12"/>
-      <c r="L31" s="12"/>
-      <c r="M31" s="12"/>
-      <c r="N31" s="12"/>
-      <c r="O31" s="13"/>
+      <c r="B31" s="10"/>
+      <c r="C31" s="11"/>
+      <c r="D31" s="11"/>
+      <c r="E31" s="11"/>
+      <c r="F31" s="11"/>
+      <c r="G31" s="11"/>
+      <c r="H31" s="11"/>
+      <c r="I31" s="11"/>
+      <c r="J31" s="11"/>
+      <c r="K31" s="11"/>
+      <c r="L31" s="11"/>
+      <c r="M31" s="11"/>
+      <c r="N31" s="11"/>
+      <c r="O31" s="12"/>
     </row>
     <row r="32" spans="2:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="11"/>
-      <c r="C32" s="12"/>
-      <c r="D32" s="12"/>
-      <c r="E32" s="12"/>
-      <c r="F32" s="12"/>
-      <c r="G32" s="12"/>
-      <c r="H32" s="12"/>
-      <c r="I32" s="12"/>
-      <c r="J32" s="12"/>
-      <c r="K32" s="12"/>
-      <c r="L32" s="12"/>
-      <c r="M32" s="12"/>
-      <c r="N32" s="12"/>
-      <c r="O32" s="13"/>
+      <c r="B32" s="10"/>
+      <c r="C32" s="11"/>
+      <c r="D32" s="11"/>
+      <c r="E32" s="11"/>
+      <c r="F32" s="11"/>
+      <c r="G32" s="11"/>
+      <c r="H32" s="11"/>
+      <c r="I32" s="11"/>
+      <c r="J32" s="11"/>
+      <c r="K32" s="11"/>
+      <c r="L32" s="11"/>
+      <c r="M32" s="11"/>
+      <c r="N32" s="11"/>
+      <c r="O32" s="12"/>
     </row>
     <row r="33" spans="2:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="11"/>
-      <c r="C33" s="12"/>
-      <c r="D33" s="12"/>
-      <c r="E33" s="12"/>
-      <c r="F33" s="12"/>
-      <c r="G33" s="12"/>
-      <c r="H33" s="12"/>
-      <c r="I33" s="12"/>
-      <c r="J33" s="12"/>
-      <c r="K33" s="12"/>
-      <c r="L33" s="12"/>
-      <c r="M33" s="12"/>
-      <c r="N33" s="12"/>
-      <c r="O33" s="13"/>
+      <c r="B33" s="10"/>
+      <c r="C33" s="11"/>
+      <c r="D33" s="11"/>
+      <c r="E33" s="11"/>
+      <c r="F33" s="11"/>
+      <c r="G33" s="11"/>
+      <c r="H33" s="11"/>
+      <c r="I33" s="11"/>
+      <c r="J33" s="11"/>
+      <c r="K33" s="11"/>
+      <c r="L33" s="11"/>
+      <c r="M33" s="11"/>
+      <c r="N33" s="11"/>
+      <c r="O33" s="12"/>
     </row>
     <row r="34" spans="2:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="11"/>
-      <c r="C34" s="12"/>
-      <c r="D34" s="12"/>
-      <c r="E34" s="12"/>
-      <c r="F34" s="12"/>
-      <c r="G34" s="12"/>
-      <c r="H34" s="12"/>
-      <c r="I34" s="12"/>
-      <c r="J34" s="12"/>
-      <c r="K34" s="12"/>
-      <c r="L34" s="12"/>
-      <c r="M34" s="12"/>
-      <c r="N34" s="12"/>
-      <c r="O34" s="13"/>
+      <c r="B34" s="10"/>
+      <c r="C34" s="11"/>
+      <c r="D34" s="11"/>
+      <c r="E34" s="11"/>
+      <c r="F34" s="11"/>
+      <c r="G34" s="11"/>
+      <c r="H34" s="11"/>
+      <c r="I34" s="11"/>
+      <c r="J34" s="11"/>
+      <c r="K34" s="11"/>
+      <c r="L34" s="11"/>
+      <c r="M34" s="11"/>
+      <c r="N34" s="11"/>
+      <c r="O34" s="12"/>
     </row>
     <row r="35" spans="2:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="11"/>
-      <c r="C35" s="12"/>
-      <c r="D35" s="12"/>
-      <c r="E35" s="12"/>
-      <c r="F35" s="12"/>
-      <c r="G35" s="12"/>
-      <c r="H35" s="12"/>
-      <c r="I35" s="12"/>
-      <c r="J35" s="12"/>
-      <c r="K35" s="12"/>
-      <c r="L35" s="12"/>
-      <c r="M35" s="12"/>
-      <c r="N35" s="12"/>
-      <c r="O35" s="13"/>
+      <c r="B35" s="10"/>
+      <c r="C35" s="11"/>
+      <c r="D35" s="11"/>
+      <c r="E35" s="11"/>
+      <c r="F35" s="11"/>
+      <c r="G35" s="11"/>
+      <c r="H35" s="11"/>
+      <c r="I35" s="11"/>
+      <c r="J35" s="11"/>
+      <c r="K35" s="11"/>
+      <c r="L35" s="11"/>
+      <c r="M35" s="11"/>
+      <c r="N35" s="11"/>
+      <c r="O35" s="12"/>
     </row>
     <row r="36" spans="2:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="11"/>
-      <c r="C36" s="12"/>
-      <c r="D36" s="12"/>
-      <c r="E36" s="12"/>
-      <c r="F36" s="12"/>
-      <c r="G36" s="12"/>
-      <c r="H36" s="12"/>
-      <c r="I36" s="12"/>
-      <c r="J36" s="12"/>
-      <c r="K36" s="12"/>
-      <c r="L36" s="12"/>
-      <c r="M36" s="12"/>
-      <c r="N36" s="12"/>
-      <c r="O36" s="13"/>
+      <c r="B36" s="10"/>
+      <c r="C36" s="11"/>
+      <c r="D36" s="11"/>
+      <c r="E36" s="11"/>
+      <c r="F36" s="11"/>
+      <c r="G36" s="11"/>
+      <c r="H36" s="11"/>
+      <c r="I36" s="11"/>
+      <c r="J36" s="11"/>
+      <c r="K36" s="11"/>
+      <c r="L36" s="11"/>
+      <c r="M36" s="11"/>
+      <c r="N36" s="11"/>
+      <c r="O36" s="12"/>
     </row>
     <row r="37" spans="2:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="11"/>
-      <c r="C37" s="12"/>
-      <c r="D37" s="12"/>
-      <c r="E37" s="12"/>
-      <c r="F37" s="12"/>
-      <c r="G37" s="12"/>
-      <c r="H37" s="12"/>
-      <c r="I37" s="12"/>
-      <c r="J37" s="12"/>
-      <c r="K37" s="12"/>
-      <c r="L37" s="12"/>
-      <c r="M37" s="12"/>
-      <c r="N37" s="12"/>
-      <c r="O37" s="13"/>
+      <c r="B37" s="10"/>
+      <c r="C37" s="11"/>
+      <c r="D37" s="11"/>
+      <c r="E37" s="11"/>
+      <c r="F37" s="11"/>
+      <c r="G37" s="11"/>
+      <c r="H37" s="11"/>
+      <c r="I37" s="11"/>
+      <c r="J37" s="11"/>
+      <c r="K37" s="11"/>
+      <c r="L37" s="11"/>
+      <c r="M37" s="11"/>
+      <c r="N37" s="11"/>
+      <c r="O37" s="12"/>
     </row>
     <row r="38" spans="2:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="11"/>
-      <c r="C38" s="12"/>
-      <c r="D38" s="12"/>
-      <c r="E38" s="12"/>
-      <c r="F38" s="12"/>
-      <c r="G38" s="12"/>
-      <c r="H38" s="12"/>
-      <c r="I38" s="12"/>
-      <c r="J38" s="12"/>
-      <c r="K38" s="12"/>
-      <c r="L38" s="12"/>
-      <c r="M38" s="12"/>
-      <c r="N38" s="12"/>
-      <c r="O38" s="13"/>
+      <c r="B38" s="10"/>
+      <c r="C38" s="11"/>
+      <c r="D38" s="11"/>
+      <c r="E38" s="11"/>
+      <c r="F38" s="11"/>
+      <c r="G38" s="11"/>
+      <c r="H38" s="11"/>
+      <c r="I38" s="11"/>
+      <c r="J38" s="11"/>
+      <c r="K38" s="11"/>
+      <c r="L38" s="11"/>
+      <c r="M38" s="11"/>
+      <c r="N38" s="11"/>
+      <c r="O38" s="12"/>
     </row>
     <row r="39" spans="2:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="11"/>
-      <c r="C39" s="12"/>
-      <c r="D39" s="12"/>
-      <c r="E39" s="12"/>
-      <c r="F39" s="12"/>
-      <c r="G39" s="12"/>
-      <c r="H39" s="12"/>
-      <c r="I39" s="12"/>
-      <c r="J39" s="12"/>
-      <c r="K39" s="12"/>
-      <c r="L39" s="12"/>
-      <c r="M39" s="12"/>
-      <c r="N39" s="12"/>
-      <c r="O39" s="13"/>
+      <c r="B39" s="10"/>
+      <c r="C39" s="11"/>
+      <c r="D39" s="11"/>
+      <c r="E39" s="11"/>
+      <c r="F39" s="11"/>
+      <c r="G39" s="11"/>
+      <c r="H39" s="11"/>
+      <c r="I39" s="11"/>
+      <c r="J39" s="11"/>
+      <c r="K39" s="11"/>
+      <c r="L39" s="11"/>
+      <c r="M39" s="11"/>
+      <c r="N39" s="11"/>
+      <c r="O39" s="12"/>
     </row>
     <row r="40" spans="2:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="11"/>
-      <c r="C40" s="12"/>
-      <c r="D40" s="12"/>
-      <c r="E40" s="12"/>
-      <c r="F40" s="12"/>
-      <c r="G40" s="12"/>
-      <c r="H40" s="12"/>
-      <c r="I40" s="12"/>
-      <c r="J40" s="12"/>
-      <c r="K40" s="12"/>
-      <c r="L40" s="12"/>
-      <c r="M40" s="12"/>
-      <c r="N40" s="12"/>
-      <c r="O40" s="13"/>
+      <c r="B40" s="10"/>
+      <c r="C40" s="11"/>
+      <c r="D40" s="11"/>
+      <c r="E40" s="11"/>
+      <c r="F40" s="11"/>
+      <c r="G40" s="11"/>
+      <c r="H40" s="11"/>
+      <c r="I40" s="11"/>
+      <c r="J40" s="11"/>
+      <c r="K40" s="11"/>
+      <c r="L40" s="11"/>
+      <c r="M40" s="11"/>
+      <c r="N40" s="11"/>
+      <c r="O40" s="12"/>
     </row>
     <row r="41" spans="2:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="11"/>
-      <c r="C41" s="12"/>
-      <c r="D41" s="12"/>
-      <c r="E41" s="12"/>
-      <c r="F41" s="12"/>
-      <c r="G41" s="12"/>
-      <c r="H41" s="12"/>
-      <c r="I41" s="12"/>
-      <c r="J41" s="12"/>
-      <c r="K41" s="12"/>
-      <c r="L41" s="12"/>
-      <c r="M41" s="12"/>
-      <c r="N41" s="12"/>
-      <c r="O41" s="13"/>
+      <c r="B41" s="10"/>
+      <c r="C41" s="11"/>
+      <c r="D41" s="11"/>
+      <c r="E41" s="11"/>
+      <c r="F41" s="11"/>
+      <c r="G41" s="11"/>
+      <c r="H41" s="11"/>
+      <c r="I41" s="11"/>
+      <c r="J41" s="11"/>
+      <c r="K41" s="11"/>
+      <c r="L41" s="11"/>
+      <c r="M41" s="11"/>
+      <c r="N41" s="11"/>
+      <c r="O41" s="12"/>
     </row>
     <row r="42" spans="2:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="11"/>
-      <c r="C42" s="12"/>
-      <c r="D42" s="12"/>
-      <c r="E42" s="12"/>
-      <c r="F42" s="12"/>
-      <c r="G42" s="12"/>
-      <c r="H42" s="12"/>
-      <c r="I42" s="12"/>
-      <c r="J42" s="12"/>
-      <c r="K42" s="12"/>
-      <c r="L42" s="12"/>
-      <c r="M42" s="12"/>
-      <c r="N42" s="12"/>
-      <c r="O42" s="13"/>
+      <c r="B42" s="10"/>
+      <c r="C42" s="11"/>
+      <c r="D42" s="11"/>
+      <c r="E42" s="11"/>
+      <c r="F42" s="11"/>
+      <c r="G42" s="11"/>
+      <c r="H42" s="11"/>
+      <c r="I42" s="11"/>
+      <c r="J42" s="11"/>
+      <c r="K42" s="11"/>
+      <c r="L42" s="11"/>
+      <c r="M42" s="11"/>
+      <c r="N42" s="11"/>
+      <c r="O42" s="12"/>
     </row>
     <row r="43" spans="2:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="11"/>
-      <c r="C43" s="12"/>
-      <c r="D43" s="12"/>
-      <c r="E43" s="12"/>
-      <c r="F43" s="12"/>
-      <c r="G43" s="12"/>
-      <c r="H43" s="12"/>
-      <c r="I43" s="12"/>
-      <c r="J43" s="12"/>
-      <c r="K43" s="12"/>
-      <c r="L43" s="12"/>
-      <c r="M43" s="12"/>
-      <c r="N43" s="12"/>
-      <c r="O43" s="13"/>
+      <c r="B43" s="10"/>
+      <c r="C43" s="11"/>
+      <c r="D43" s="11"/>
+      <c r="E43" s="11"/>
+      <c r="F43" s="11"/>
+      <c r="G43" s="11"/>
+      <c r="H43" s="11"/>
+      <c r="I43" s="11"/>
+      <c r="J43" s="11"/>
+      <c r="K43" s="11"/>
+      <c r="L43" s="11"/>
+      <c r="M43" s="11"/>
+      <c r="N43" s="11"/>
+      <c r="O43" s="12"/>
     </row>
     <row r="44" spans="2:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="11"/>
-      <c r="C44" s="12"/>
-      <c r="D44" s="12"/>
-      <c r="E44" s="12"/>
-      <c r="F44" s="12"/>
-      <c r="G44" s="12"/>
-      <c r="H44" s="12"/>
-      <c r="I44" s="12"/>
-      <c r="J44" s="12"/>
-      <c r="K44" s="12"/>
-      <c r="L44" s="12"/>
-      <c r="M44" s="12"/>
-      <c r="N44" s="12"/>
-      <c r="O44" s="13"/>
+      <c r="B44" s="10"/>
+      <c r="C44" s="11"/>
+      <c r="D44" s="11"/>
+      <c r="E44" s="11"/>
+      <c r="F44" s="11"/>
+      <c r="G44" s="11"/>
+      <c r="H44" s="11"/>
+      <c r="I44" s="11"/>
+      <c r="J44" s="11"/>
+      <c r="K44" s="11"/>
+      <c r="L44" s="11"/>
+      <c r="M44" s="11"/>
+      <c r="N44" s="11"/>
+      <c r="O44" s="12"/>
     </row>
     <row r="45" spans="2:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="11"/>
-      <c r="C45" s="12"/>
-      <c r="D45" s="12"/>
-      <c r="E45" s="12"/>
-      <c r="F45" s="12"/>
-      <c r="G45" s="12"/>
-      <c r="H45" s="12"/>
-      <c r="I45" s="12"/>
-      <c r="J45" s="12"/>
-      <c r="K45" s="12"/>
-      <c r="L45" s="12"/>
-      <c r="M45" s="12"/>
-      <c r="N45" s="12"/>
-      <c r="O45" s="13"/>
+      <c r="B45" s="10"/>
+      <c r="C45" s="11"/>
+      <c r="D45" s="11"/>
+      <c r="E45" s="11"/>
+      <c r="F45" s="11"/>
+      <c r="G45" s="11"/>
+      <c r="H45" s="11"/>
+      <c r="I45" s="11"/>
+      <c r="J45" s="11"/>
+      <c r="K45" s="11"/>
+      <c r="L45" s="11"/>
+      <c r="M45" s="11"/>
+      <c r="N45" s="11"/>
+      <c r="O45" s="12"/>
     </row>
     <row r="46" spans="2:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="11"/>
-      <c r="C46" s="12"/>
-      <c r="D46" s="12"/>
-      <c r="E46" s="12"/>
-      <c r="F46" s="12"/>
-      <c r="G46" s="12"/>
-      <c r="H46" s="12"/>
-      <c r="I46" s="12"/>
-      <c r="J46" s="12"/>
-      <c r="K46" s="12"/>
-      <c r="L46" s="12"/>
-      <c r="M46" s="12"/>
-      <c r="N46" s="12"/>
-      <c r="O46" s="13"/>
+      <c r="B46" s="10"/>
+      <c r="C46" s="11"/>
+      <c r="D46" s="11"/>
+      <c r="E46" s="11"/>
+      <c r="F46" s="11"/>
+      <c r="G46" s="11"/>
+      <c r="H46" s="11"/>
+      <c r="I46" s="11"/>
+      <c r="J46" s="11"/>
+      <c r="K46" s="11"/>
+      <c r="L46" s="11"/>
+      <c r="M46" s="11"/>
+      <c r="N46" s="11"/>
+      <c r="O46" s="12"/>
     </row>
     <row r="47" spans="2:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="11"/>
-      <c r="C47" s="12"/>
-      <c r="D47" s="12"/>
-      <c r="E47" s="12"/>
-      <c r="F47" s="12"/>
-      <c r="G47" s="12"/>
-      <c r="H47" s="12"/>
-      <c r="I47" s="12"/>
-      <c r="J47" s="12"/>
-      <c r="K47" s="12"/>
-      <c r="L47" s="12"/>
-      <c r="M47" s="12"/>
-      <c r="N47" s="12"/>
-      <c r="O47" s="13"/>
+      <c r="B47" s="10"/>
+      <c r="C47" s="11"/>
+      <c r="D47" s="11"/>
+      <c r="E47" s="11"/>
+      <c r="F47" s="11"/>
+      <c r="G47" s="11"/>
+      <c r="H47" s="11"/>
+      <c r="I47" s="11"/>
+      <c r="J47" s="11"/>
+      <c r="K47" s="11"/>
+      <c r="L47" s="11"/>
+      <c r="M47" s="11"/>
+      <c r="N47" s="11"/>
+      <c r="O47" s="12"/>
     </row>
     <row r="48" spans="2:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="11"/>
-      <c r="C48" s="12"/>
-      <c r="D48" s="12"/>
-      <c r="E48" s="12"/>
-      <c r="F48" s="12"/>
-      <c r="G48" s="12"/>
-      <c r="H48" s="12"/>
-      <c r="I48" s="12"/>
-      <c r="J48" s="12"/>
-      <c r="K48" s="12"/>
-      <c r="L48" s="12"/>
-      <c r="M48" s="12"/>
-      <c r="N48" s="12"/>
-      <c r="O48" s="13"/>
+      <c r="B48" s="10"/>
+      <c r="C48" s="11"/>
+      <c r="D48" s="11"/>
+      <c r="E48" s="11"/>
+      <c r="F48" s="11"/>
+      <c r="G48" s="11"/>
+      <c r="H48" s="11"/>
+      <c r="I48" s="11"/>
+      <c r="J48" s="11"/>
+      <c r="K48" s="11"/>
+      <c r="L48" s="11"/>
+      <c r="M48" s="11"/>
+      <c r="N48" s="11"/>
+      <c r="O48" s="12"/>
     </row>
     <row r="49" spans="2:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="14"/>
-      <c r="C49" s="15"/>
-      <c r="D49" s="15"/>
-      <c r="E49" s="15"/>
-      <c r="F49" s="15"/>
-      <c r="G49" s="15"/>
-      <c r="H49" s="15"/>
-      <c r="I49" s="15"/>
-      <c r="J49" s="15"/>
-      <c r="K49" s="15"/>
-      <c r="L49" s="15"/>
-      <c r="M49" s="15"/>
-      <c r="N49" s="15"/>
-      <c r="O49" s="16"/>
+      <c r="B49" s="13"/>
+      <c r="C49" s="14"/>
+      <c r="D49" s="14"/>
+      <c r="E49" s="14"/>
+      <c r="F49" s="14"/>
+      <c r="G49" s="14"/>
+      <c r="H49" s="14"/>
+      <c r="I49" s="14"/>
+      <c r="J49" s="14"/>
+      <c r="K49" s="14"/>
+      <c r="L49" s="14"/>
+      <c r="M49" s="14"/>
+      <c r="N49" s="14"/>
+      <c r="O49" s="15"/>
     </row>
     <row r="50" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C50" s="2"/>
@@ -1562,19 +1557,19 @@
     </row>
     <row r="51" spans="2:15" ht="19.5" x14ac:dyDescent="0.25">
       <c r="C51" s="2"/>
-      <c r="D51" s="10" t="s">
+      <c r="D51" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="E51" s="10"/>
+      <c r="E51" s="20"/>
       <c r="F51" s="9"/>
       <c r="G51" s="9"/>
       <c r="H51" s="9"/>
       <c r="I51" s="9"/>
       <c r="J51" s="9"/>
-      <c r="K51" s="10" t="s">
+      <c r="K51" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="L51" s="10"/>
+      <c r="L51" s="20"/>
       <c r="M51" s="2"/>
       <c r="N51" s="2"/>
       <c r="O51" s="4"/>
